--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812C7BB0-8EBF-4FF9-A0B8-9D7C0A2901BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BDCC6A-89B5-46FC-BC90-7971D1570296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1653,7 +1653,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="270">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5357,11 +5357,18 @@
         <v>224</v>
       </c>
       <c r="I2" s="87">
-        <v>256</v>
-      </c>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87"/>
+        <v>128</v>
+      </c>
+      <c r="J2" s="87" t="str">
+        <f>SUBSTITUTE($F2,"hazr-","")&amp;"-disk02"</f>
+        <v>t-cs-chtweb01-disk02</v>
+      </c>
+      <c r="K2" s="87" t="s">
+        <v>224</v>
+      </c>
+      <c r="L2" s="87">
+        <v>128</v>
+      </c>
       <c r="M2" s="87">
         <v>3</v>
       </c>
@@ -5404,11 +5411,18 @@
         <v>224</v>
       </c>
       <c r="I3" s="88">
-        <v>256</v>
-      </c>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
+        <v>128</v>
+      </c>
+      <c r="J3" s="88" t="str">
+        <f>SUBSTITUTE($F3,"hazr-","")&amp;"-disk02"</f>
+        <v>t-cs-chtintweb01-disk02</v>
+      </c>
+      <c r="K3" s="88" t="s">
+        <v>224</v>
+      </c>
+      <c r="L3" s="88">
+        <v>128</v>
+      </c>
       <c r="M3" s="88">
         <v>3</v>
       </c>

--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BDCC6A-89B5-46FC-BC90-7971D1570296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5840B433-3807-466E-8247-5533D979651F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1653,7 +1653,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="279">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2661,6 +2661,42 @@
   </si>
   <si>
     <t>10.157.168.11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temp-test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.168.22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Linux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temp-test01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.168.20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.168.21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temp-test02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temp-test03</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3110,7 +3146,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3403,6 +3439,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3962,8 +4007,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF3" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
-  <autoFilter ref="B1:AF3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF6" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
+  <autoFilter ref="B1:AF6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="30"/>
     <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="29">
@@ -4559,7 +4604,7 @@
       </c>
     </row>
     <row r="2" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
+      <c r="A2" s="98"/>
       <c r="B2" s="56" t="s">
         <v>234</v>
       </c>
@@ -4634,7 +4679,7 @@
       <c r="BK2" s="52"/>
     </row>
     <row r="3" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A3" s="83"/>
+      <c r="A3" s="99"/>
       <c r="B3" s="56" t="s">
         <v>234</v>
       </c>
@@ -4940,7 +4985,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AF6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
@@ -5072,7 +5117,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" s="52"/>
+      <c r="A2" s="82"/>
       <c r="B2" s="1" t="s">
         <v>234</v>
       </c>
@@ -5161,7 +5206,7 @@
       <c r="AF2" s="1"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" s="52"/>
+      <c r="A3" s="82"/>
       <c r="B3" s="1" t="s">
         <v>234</v>
       </c>
@@ -5248,6 +5293,269 @@
       </c>
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D4" s="94" t="s">
+        <v>261</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H4" s="81" t="s">
+        <v>222</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2</v>
+      </c>
+      <c r="J4" s="1">
+        <v>8</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="L4" s="80" t="s">
+        <v>221</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="O4" s="94" t="str">
+        <f>SUBSTITUTE(F4,"hazr-","")&amp;"-osdisk"</f>
+        <v>temp-test01-osdisk</v>
+      </c>
+      <c r="P4" s="1">
+        <v>64</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="R4" s="94"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="94"/>
+      <c r="U4" s="94" t="str">
+        <f>SUBSTITUTE(F4,"hazr-","")&amp;"-nic"</f>
+        <v>temp-test01-nic</v>
+      </c>
+      <c r="V4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="AA4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D5" s="94" t="s">
+        <v>261</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="H5" s="81" t="s">
+        <v>222</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2</v>
+      </c>
+      <c r="J5" s="1">
+        <v>8</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="L5" s="80" t="s">
+        <v>221</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="O5" s="94" t="str">
+        <f>SUBSTITUTE(F5,"hazr-","")&amp;"-osdisk"</f>
+        <v>temp-test02-osdisk</v>
+      </c>
+      <c r="P5" s="1">
+        <v>64</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="R5" s="94" t="s">
+        <v>275</v>
+      </c>
+      <c r="S5" s="1"/>
+      <c r="T5" s="94"/>
+      <c r="U5" s="94" t="str">
+        <f>SUBSTITUTE(F5,"hazr-","")&amp;"-nic"</f>
+        <v>temp-test02-nic</v>
+      </c>
+      <c r="V5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="AA5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D6" s="94" t="s">
+        <v>261</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="H6" s="81" t="s">
+        <v>222</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2</v>
+      </c>
+      <c r="J6" s="1">
+        <v>8</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="L6" s="80" t="s">
+        <v>221</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="O6" s="94" t="str">
+        <f>SUBSTITUTE(F6,"hazr-","")&amp;"-osdisk"</f>
+        <v>temp-test03-osdisk</v>
+      </c>
+      <c r="P6" s="1">
+        <v>64</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="R6" s="94"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="94"/>
+      <c r="U6" s="94" t="str">
+        <f>SUBSTITUTE(F6,"hazr-","")&amp;"-nic"</f>
+        <v>temp-test03-nic</v>
+      </c>
+      <c r="V6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="AA6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5261,7 +5569,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F281E7-0665-4BB7-80DB-4208A01A998B}">
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.25" style="89" customWidth="1"/>
@@ -5333,7 +5641,7 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="97"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="87" t="s">
         <v>234</v>
       </c>
@@ -5387,7 +5695,7 @@
       <c r="R2" s="85"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="97"/>
+      <c r="A3" s="100"/>
       <c r="B3" s="88" t="s">
         <v>234</v>
       </c>
@@ -5404,7 +5712,7 @@
         <v>263</v>
       </c>
       <c r="G3" s="88" t="str">
-        <f t="shared" ref="G3" si="0">SUBSTITUTE($F3,"hazr-","")&amp;"-disk01"</f>
+        <f t="shared" ref="G3:G6" si="0">SUBSTITUTE($F3,"hazr-","")&amp;"-disk01"</f>
         <v>t-cs-chtintweb01-disk01</v>
       </c>
       <c r="H3" s="88" t="s">
@@ -5442,43 +5750,164 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="97"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88"/>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
+      <c r="B4" s="88" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="88" t="s">
+        <v>234</v>
+      </c>
+      <c r="D4" s="88" t="s">
+        <v>261</v>
+      </c>
+      <c r="E4" s="93" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="96" t="s">
+        <v>270</v>
+      </c>
+      <c r="G4" s="88" t="str">
+        <f t="shared" si="0"/>
+        <v>temp-test-disk01</v>
+      </c>
+      <c r="H4" s="88" t="s">
+        <v>224</v>
+      </c>
+      <c r="I4" s="88">
+        <v>128</v>
+      </c>
+      <c r="J4" s="88" t="str">
+        <f>SUBSTITUTE($F4,"hazr-","")&amp;"-disk02"</f>
+        <v>temp-test-disk02</v>
+      </c>
+      <c r="K4" s="88" t="s">
+        <v>224</v>
+      </c>
+      <c r="L4" s="88">
+        <v>128</v>
+      </c>
+      <c r="M4" s="88">
+        <v>3</v>
+      </c>
+      <c r="N4" s="88" t="s">
+        <v>246</v>
+      </c>
+      <c r="O4" s="88" t="s">
+        <v>250</v>
+      </c>
+      <c r="P4" s="88" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q4" s="88" t="b">
+        <v>1</v>
+      </c>
       <c r="R4" s="56"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="97"/>
-      <c r="B5" s="88"/>
-      <c r="C5" s="88"/>
-      <c r="D5" s="88"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="88"/>
-      <c r="G5" s="88"/>
-      <c r="H5" s="88"/>
-      <c r="I5" s="88"/>
-      <c r="J5" s="88"/>
-      <c r="K5" s="88"/>
-      <c r="L5" s="88"/>
-      <c r="M5" s="88"/>
-      <c r="N5" s="88"/>
-      <c r="O5" s="88"/>
-      <c r="P5" s="88"/>
-      <c r="Q5" s="88"/>
+      <c r="B5" s="88" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="88" t="s">
+        <v>234</v>
+      </c>
+      <c r="D5" s="88" t="s">
+        <v>261</v>
+      </c>
+      <c r="E5" s="93" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="96" t="s">
+        <v>270</v>
+      </c>
+      <c r="G5" s="88" t="str">
+        <f t="shared" si="0"/>
+        <v>temp-test-disk01</v>
+      </c>
+      <c r="H5" s="88" t="s">
+        <v>224</v>
+      </c>
+      <c r="I5" s="88">
+        <v>128</v>
+      </c>
+      <c r="J5" s="88" t="str">
+        <f>SUBSTITUTE($F5,"hazr-","")&amp;"-disk02"</f>
+        <v>temp-test-disk02</v>
+      </c>
+      <c r="K5" s="88" t="s">
+        <v>224</v>
+      </c>
+      <c r="L5" s="88">
+        <v>128</v>
+      </c>
+      <c r="M5" s="88">
+        <v>3</v>
+      </c>
+      <c r="N5" s="88" t="s">
+        <v>246</v>
+      </c>
+      <c r="O5" s="88" t="s">
+        <v>250</v>
+      </c>
+      <c r="P5" s="88" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q5" s="88" t="b">
+        <v>1</v>
+      </c>
       <c r="R5" s="56"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B6" s="88" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" s="88" t="s">
+        <v>234</v>
+      </c>
+      <c r="D6" s="88" t="s">
+        <v>261</v>
+      </c>
+      <c r="E6" s="93" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="96" t="s">
+        <v>270</v>
+      </c>
+      <c r="G6" s="88" t="str">
+        <f t="shared" si="0"/>
+        <v>temp-test-disk01</v>
+      </c>
+      <c r="H6" s="88" t="s">
+        <v>224</v>
+      </c>
+      <c r="I6" s="88">
+        <v>128</v>
+      </c>
+      <c r="J6" s="88" t="str">
+        <f>SUBSTITUTE($F6,"hazr-","")&amp;"-disk02"</f>
+        <v>temp-test-disk02</v>
+      </c>
+      <c r="K6" s="88" t="s">
+        <v>224</v>
+      </c>
+      <c r="L6" s="88">
+        <v>128</v>
+      </c>
+      <c r="M6" s="88">
+        <v>3</v>
+      </c>
+      <c r="N6" s="88" t="s">
+        <v>246</v>
+      </c>
+      <c r="O6" s="88" t="s">
+        <v>250</v>
+      </c>
+      <c r="P6" s="88" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q6" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" s="56"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5840B433-3807-466E-8247-5533D979651F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D2D9CB-3EE3-4058-9205-B87AB9440CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1653,7 +1653,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="270">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2640,10 +2640,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_Base_Image/versions/0.0.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>t-cs-ap-sbn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2664,39 +2660,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>temp-test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.168.22</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Linux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>temp-test01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.168.20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>`</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.168.21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>temp-test02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>temp-test03</t>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_Base_Image/versions/0.0.4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5135,7 +5099,7 @@
         <v>262</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H2" s="81" t="s">
         <v>222</v>
@@ -5156,7 +5120,7 @@
         <v>223</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="O2" s="94" t="str">
         <f t="shared" ref="O2:O3" si="0">SUBSTITUTE(F2,"hazr-","")&amp;"-osdisk"</f>
@@ -5188,7 +5152,7 @@
         <v>251</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AA2" s="1" t="b">
         <v>1</v>
@@ -5197,7 +5161,7 @@
         <v>250</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AD2" s="1">
         <v>3</v>
@@ -5224,7 +5188,7 @@
         <v>263</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H3" s="81" t="s">
         <v>222</v>
@@ -5245,7 +5209,7 @@
         <v>223</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="O3" s="94" t="str">
         <f t="shared" si="0"/>
@@ -5277,7 +5241,7 @@
         <v>252</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AA3" s="1" t="b">
         <v>1</v>
@@ -5286,7 +5250,7 @@
         <v>250</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AD3" s="1">
         <v>3</v>
@@ -5295,265 +5259,98 @@
       <c r="AF3" s="1"/>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="D4" s="94" t="s">
-        <v>261</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="H4" s="81" t="s">
-        <v>222</v>
-      </c>
-      <c r="I4" s="1">
-        <v>2</v>
-      </c>
-      <c r="J4" s="1">
-        <v>8</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="L4" s="80" t="s">
-        <v>221</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="O4" s="94" t="str">
-        <f>SUBSTITUTE(F4,"hazr-","")&amp;"-osdisk"</f>
-        <v>temp-test01-osdisk</v>
-      </c>
-      <c r="P4" s="1">
-        <v>64</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>224</v>
-      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="80"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="94"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
       <c r="R4" s="94"/>
       <c r="S4" s="1"/>
       <c r="T4" s="94"/>
-      <c r="U4" s="94" t="str">
-        <f>SUBSTITUTE(F4,"hazr-","")&amp;"-nic"</f>
-        <v>temp-test01-nic</v>
-      </c>
-      <c r="V4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="AA4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="AD4" s="1">
-        <v>3</v>
-      </c>
+      <c r="U4" s="94"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
       <c r="AF4" s="1"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="D5" s="94" t="s">
-        <v>261</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="H5" s="81" t="s">
-        <v>222</v>
-      </c>
-      <c r="I5" s="1">
-        <v>2</v>
-      </c>
-      <c r="J5" s="1">
-        <v>8</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="L5" s="80" t="s">
-        <v>221</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="O5" s="94" t="str">
-        <f>SUBSTITUTE(F5,"hazr-","")&amp;"-osdisk"</f>
-        <v>temp-test02-osdisk</v>
-      </c>
-      <c r="P5" s="1">
-        <v>64</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="R5" s="94" t="s">
-        <v>275</v>
-      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="94"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="94"/>
       <c r="S5" s="1"/>
       <c r="T5" s="94"/>
-      <c r="U5" s="94" t="str">
-        <f>SUBSTITUTE(F5,"hazr-","")&amp;"-nic"</f>
-        <v>temp-test02-nic</v>
-      </c>
-      <c r="V5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="X5" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="Z5" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="AA5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="AC5" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="AD5" s="1">
-        <v>3</v>
-      </c>
+      <c r="U5" s="94"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="D6" s="94" t="s">
-        <v>261</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="H6" s="81" t="s">
-        <v>222</v>
-      </c>
-      <c r="I6" s="1">
-        <v>2</v>
-      </c>
-      <c r="J6" s="1">
-        <v>8</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="L6" s="80" t="s">
-        <v>221</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="O6" s="94" t="str">
-        <f>SUBSTITUTE(F6,"hazr-","")&amp;"-osdisk"</f>
-        <v>temp-test03-osdisk</v>
-      </c>
-      <c r="P6" s="1">
-        <v>64</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>224</v>
-      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="94"/>
+      <c r="E6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="94"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
       <c r="R6" s="94"/>
       <c r="S6" s="1"/>
       <c r="T6" s="94"/>
-      <c r="U6" s="94" t="str">
-        <f>SUBSTITUTE(F6,"hazr-","")&amp;"-nic"</f>
-        <v>temp-test03-nic</v>
-      </c>
-      <c r="V6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="Y6" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="Z6" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="AA6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="AC6" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>3</v>
-      </c>
+      <c r="U6" s="94"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
     </row>
@@ -5687,7 +5484,7 @@
         <v>250</v>
       </c>
       <c r="P2" s="87" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q2" s="87" t="b">
         <v>1</v>
@@ -5741,7 +5538,7 @@
         <v>250</v>
       </c>
       <c r="P3" s="88" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q3" s="88" t="b">
         <v>1</v>
@@ -5750,163 +5547,61 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="97"/>
-      <c r="B4" s="88" t="s">
-        <v>234</v>
-      </c>
-      <c r="C4" s="88" t="s">
-        <v>234</v>
-      </c>
-      <c r="D4" s="88" t="s">
-        <v>261</v>
-      </c>
-      <c r="E4" s="93" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="96" t="s">
-        <v>270</v>
-      </c>
-      <c r="G4" s="88" t="str">
-        <f t="shared" si="0"/>
-        <v>temp-test-disk01</v>
-      </c>
-      <c r="H4" s="88" t="s">
-        <v>224</v>
-      </c>
-      <c r="I4" s="88">
-        <v>128</v>
-      </c>
-      <c r="J4" s="88" t="str">
-        <f>SUBSTITUTE($F4,"hazr-","")&amp;"-disk02"</f>
-        <v>temp-test-disk02</v>
-      </c>
-      <c r="K4" s="88" t="s">
-        <v>224</v>
-      </c>
-      <c r="L4" s="88">
-        <v>128</v>
-      </c>
-      <c r="M4" s="88">
-        <v>3</v>
-      </c>
-      <c r="N4" s="88" t="s">
-        <v>246</v>
-      </c>
-      <c r="O4" s="88" t="s">
-        <v>250</v>
-      </c>
-      <c r="P4" s="88" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q4" s="88" t="b">
-        <v>1</v>
-      </c>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
       <c r="R4" s="56"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="97"/>
-      <c r="B5" s="88" t="s">
-        <v>234</v>
-      </c>
-      <c r="C5" s="88" t="s">
-        <v>234</v>
-      </c>
-      <c r="D5" s="88" t="s">
-        <v>261</v>
-      </c>
-      <c r="E5" s="93" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="96" t="s">
-        <v>270</v>
-      </c>
-      <c r="G5" s="88" t="str">
-        <f t="shared" si="0"/>
-        <v>temp-test-disk01</v>
-      </c>
-      <c r="H5" s="88" t="s">
-        <v>224</v>
-      </c>
-      <c r="I5" s="88">
-        <v>128</v>
-      </c>
-      <c r="J5" s="88" t="str">
-        <f>SUBSTITUTE($F5,"hazr-","")&amp;"-disk02"</f>
-        <v>temp-test-disk02</v>
-      </c>
-      <c r="K5" s="88" t="s">
-        <v>224</v>
-      </c>
-      <c r="L5" s="88">
-        <v>128</v>
-      </c>
-      <c r="M5" s="88">
-        <v>3</v>
-      </c>
-      <c r="N5" s="88" t="s">
-        <v>246</v>
-      </c>
-      <c r="O5" s="88" t="s">
-        <v>250</v>
-      </c>
-      <c r="P5" s="88" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q5" s="88" t="b">
-        <v>1</v>
-      </c>
+      <c r="B5" s="88"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="88"/>
+      <c r="I5" s="88"/>
+      <c r="J5" s="88"/>
+      <c r="K5" s="88"/>
+      <c r="L5" s="88"/>
+      <c r="M5" s="88"/>
+      <c r="N5" s="88"/>
+      <c r="O5" s="88"/>
+      <c r="P5" s="88"/>
+      <c r="Q5" s="88"/>
       <c r="R5" s="56"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B6" s="88" t="s">
-        <v>234</v>
-      </c>
-      <c r="C6" s="88" t="s">
-        <v>234</v>
-      </c>
-      <c r="D6" s="88" t="s">
-        <v>261</v>
-      </c>
-      <c r="E6" s="93" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="96" t="s">
-        <v>270</v>
-      </c>
-      <c r="G6" s="88" t="str">
-        <f t="shared" si="0"/>
-        <v>temp-test-disk01</v>
-      </c>
-      <c r="H6" s="88" t="s">
-        <v>224</v>
-      </c>
-      <c r="I6" s="88">
-        <v>128</v>
-      </c>
-      <c r="J6" s="88" t="str">
-        <f>SUBSTITUTE($F6,"hazr-","")&amp;"-disk02"</f>
-        <v>temp-test-disk02</v>
-      </c>
-      <c r="K6" s="88" t="s">
-        <v>224</v>
-      </c>
-      <c r="L6" s="88">
-        <v>128</v>
-      </c>
-      <c r="M6" s="88">
-        <v>3</v>
-      </c>
-      <c r="N6" s="88" t="s">
-        <v>246</v>
-      </c>
-      <c r="O6" s="88" t="s">
-        <v>250</v>
-      </c>
-      <c r="P6" s="88" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q6" s="88" t="b">
-        <v>1</v>
-      </c>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="96"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="88"/>
+      <c r="K6" s="88"/>
+      <c r="L6" s="88"/>
+      <c r="M6" s="88"/>
+      <c r="N6" s="88"/>
+      <c r="O6" s="88"/>
+      <c r="P6" s="88"/>
+      <c r="Q6" s="88"/>
       <c r="R6" s="56"/>
     </row>
   </sheetData>

--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D2D9CB-3EE3-4058-9205-B87AB9440CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E17F478-1CB1-41C1-8EA1-2408B201C478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -49,7 +49,7 @@
     <author>zenithn</author>
   </authors>
   <commentList>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{4E95A42A-EE05-46FF-9ADE-8C06C9CCADD3}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{4E95A42A-EE05-46FF-9ADE-8C06C9CCADD3}">
       <text>
         <r>
           <rPr>
@@ -1653,7 +1653,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="266">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1781,10 +1781,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>O</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NSGName</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1969,14 +1965,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DEV</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NW</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1985,34 +1973,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>STG-NW-RG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STG-WEB-RG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEV-NW-RG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEV-WEB-RG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>testprdnwvnet</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>teststgnwvnet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>testdevnwvnet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Subnet1 Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2071,14 +2035,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PRDWEB01-nic</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PRDWEB02-nic</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>VNetRG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2661,6 +2617,34 @@
   </si>
   <si>
     <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_Base_Image/versions/0.0.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Role2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t-cs-db-sbn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t-cs-pe-sbn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t-cs-web-nsg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t-cs-ap-nsg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t-cs-db-nsg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t-cs-pe-nsg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3110,7 +3094,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3393,22 +3377,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4393,196 +4371,196 @@
         <v>3</v>
       </c>
       <c r="F1" s="51" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G1" s="51" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="H1" s="55" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="I1" s="55" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="J1" s="51" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K1" s="51" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="L1" s="55" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="M1" s="55" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="N1" s="55" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="O1" s="55" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="P1" s="55" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q1" s="55" t="s">
+        <v>163</v>
+      </c>
+      <c r="R1" s="55" t="s">
+        <v>164</v>
+      </c>
+      <c r="S1" s="55" t="s">
+        <v>165</v>
+      </c>
+      <c r="T1" s="55" t="s">
+        <v>166</v>
+      </c>
+      <c r="U1" s="55" t="s">
+        <v>167</v>
+      </c>
+      <c r="V1" s="55" t="s">
+        <v>168</v>
+      </c>
+      <c r="W1" s="55" t="s">
+        <v>169</v>
+      </c>
+      <c r="X1" s="55" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y1" s="55" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z1" s="55" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA1" s="55" t="s">
         <v>173</v>
       </c>
-      <c r="Q1" s="55" t="s">
+      <c r="AB1" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="R1" s="55" t="s">
+      <c r="AC1" s="55" t="s">
         <v>175</v>
       </c>
-      <c r="S1" s="55" t="s">
+      <c r="AD1" s="55" t="s">
         <v>176</v>
       </c>
-      <c r="T1" s="55" t="s">
+      <c r="AE1" s="55" t="s">
         <v>177</v>
       </c>
-      <c r="U1" s="55" t="s">
+      <c r="AF1" s="55" t="s">
         <v>178</v>
       </c>
-      <c r="V1" s="55" t="s">
+      <c r="AG1" s="55" t="s">
         <v>179</v>
       </c>
-      <c r="W1" s="55" t="s">
+      <c r="AH1" s="55" t="s">
         <v>180</v>
       </c>
-      <c r="X1" s="55" t="s">
+      <c r="AI1" s="55" t="s">
         <v>181</v>
       </c>
-      <c r="Y1" s="55" t="s">
+      <c r="AJ1" s="55" t="s">
         <v>182</v>
       </c>
-      <c r="Z1" s="55" t="s">
+      <c r="AK1" s="55" t="s">
         <v>183</v>
       </c>
-      <c r="AA1" s="55" t="s">
+      <c r="AL1" s="55" t="s">
         <v>184</v>
       </c>
-      <c r="AB1" s="55" t="s">
+      <c r="AM1" s="55" t="s">
         <v>185</v>
       </c>
-      <c r="AC1" s="55" t="s">
+      <c r="AN1" s="55" t="s">
         <v>186</v>
       </c>
-      <c r="AD1" s="55" t="s">
+      <c r="AO1" s="55" t="s">
         <v>187</v>
       </c>
-      <c r="AE1" s="55" t="s">
+      <c r="AP1" s="55" t="s">
         <v>188</v>
       </c>
-      <c r="AF1" s="55" t="s">
+      <c r="AQ1" s="55" t="s">
         <v>189</v>
       </c>
-      <c r="AG1" s="55" t="s">
+      <c r="AR1" s="55" t="s">
         <v>190</v>
       </c>
-      <c r="AH1" s="55" t="s">
+      <c r="AS1" s="55" t="s">
         <v>191</v>
       </c>
-      <c r="AI1" s="55" t="s">
+      <c r="AT1" s="55" t="s">
         <v>192</v>
       </c>
-      <c r="AJ1" s="55" t="s">
+      <c r="AU1" s="55" t="s">
         <v>193</v>
       </c>
-      <c r="AK1" s="55" t="s">
+      <c r="AV1" s="55" t="s">
         <v>194</v>
       </c>
-      <c r="AL1" s="55" t="s">
+      <c r="AW1" s="55" t="s">
         <v>195</v>
       </c>
-      <c r="AM1" s="55" t="s">
+      <c r="AX1" s="55" t="s">
         <v>196</v>
       </c>
-      <c r="AN1" s="55" t="s">
+      <c r="AY1" s="55" t="s">
         <v>197</v>
       </c>
-      <c r="AO1" s="55" t="s">
+      <c r="AZ1" s="55" t="s">
         <v>198</v>
       </c>
-      <c r="AP1" s="55" t="s">
+      <c r="BA1" s="55" t="s">
         <v>199</v>
       </c>
-      <c r="AQ1" s="55" t="s">
+      <c r="BB1" s="55" t="s">
         <v>200</v>
       </c>
-      <c r="AR1" s="55" t="s">
+      <c r="BC1" s="55" t="s">
         <v>201</v>
       </c>
-      <c r="AS1" s="55" t="s">
+      <c r="BD1" s="55" t="s">
         <v>202</v>
       </c>
-      <c r="AT1" s="55" t="s">
+      <c r="BE1" s="55" t="s">
         <v>203</v>
       </c>
-      <c r="AU1" s="55" t="s">
+      <c r="BF1" s="55" t="s">
         <v>204</v>
       </c>
-      <c r="AV1" s="55" t="s">
+      <c r="BG1" s="55" t="s">
         <v>205</v>
       </c>
-      <c r="AW1" s="55" t="s">
+      <c r="BH1" s="55" t="s">
         <v>206</v>
       </c>
-      <c r="AX1" s="55" t="s">
+      <c r="BI1" s="55" t="s">
         <v>207</v>
       </c>
-      <c r="AY1" s="55" t="s">
+      <c r="BJ1" s="55" t="s">
         <v>208</v>
       </c>
-      <c r="AZ1" s="55" t="s">
+      <c r="BK1" s="55" t="s">
         <v>209</v>
       </c>
-      <c r="BA1" s="55" t="s">
-        <v>210</v>
-      </c>
-      <c r="BB1" s="55" t="s">
-        <v>211</v>
-      </c>
-      <c r="BC1" s="55" t="s">
-        <v>212</v>
-      </c>
-      <c r="BD1" s="55" t="s">
-        <v>213</v>
-      </c>
-      <c r="BE1" s="55" t="s">
-        <v>214</v>
-      </c>
-      <c r="BF1" s="55" t="s">
-        <v>215</v>
-      </c>
-      <c r="BG1" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="BH1" s="55" t="s">
-        <v>217</v>
-      </c>
-      <c r="BI1" s="55" t="s">
-        <v>218</v>
-      </c>
-      <c r="BJ1" s="55" t="s">
-        <v>219</v>
-      </c>
-      <c r="BK1" s="55" t="s">
-        <v>220</v>
-      </c>
     </row>
     <row r="2" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A2" s="98"/>
+      <c r="A2" s="52"/>
       <c r="B2" s="56" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="E2" s="56" t="s">
         <v>24</v>
       </c>
       <c r="F2" s="56" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="G2" s="56"/>
       <c r="H2" s="56"/>
@@ -4643,21 +4621,21 @@
       <c r="BK2" s="52"/>
     </row>
     <row r="3" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A3" s="99"/>
+      <c r="A3" s="97"/>
       <c r="B3" s="56" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="E3" s="56" t="s">
         <v>24</v>
       </c>
       <c r="F3" s="56" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="G3" s="56"/>
       <c r="H3" s="56"/>
@@ -4791,19 +4769,19 @@
         <v>3</v>
       </c>
       <c r="F1" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="82"/>
       <c r="B2" s="56" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="E2" s="56" t="s">
         <v>24</v>
@@ -4813,13 +4791,13 @@
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="83"/>
       <c r="B3" s="56" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="E3" s="56" t="s">
         <v>24</v>
@@ -4829,13 +4807,13 @@
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="82"/>
       <c r="B4" s="56" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="E4" s="56" t="s">
         <v>24</v>
@@ -4845,13 +4823,13 @@
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="83"/>
       <c r="B5" s="56" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="E5" s="56" t="s">
         <v>24</v>
@@ -4861,13 +4839,13 @@
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="82"/>
       <c r="B6" s="56" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="E6" s="56" t="s">
         <v>24</v>
@@ -4877,13 +4855,13 @@
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="83"/>
       <c r="B7" s="56" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="E7" s="56" t="s">
         <v>24</v>
@@ -4893,13 +4871,13 @@
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="82"/>
       <c r="B8" s="56" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="E8" s="56" t="s">
         <v>24</v>
@@ -4909,13 +4887,13 @@
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="82"/>
       <c r="B9" s="56" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E9" s="56" t="s">
         <v>24</v>
@@ -4925,13 +4903,13 @@
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="83"/>
       <c r="B10" s="56" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="E10" s="56" t="s">
         <v>24</v>
@@ -5020,7 +4998,7 @@
         <v>10</v>
       </c>
       <c r="M1" s="43" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="N1" s="43" t="s">
         <v>28</v>
@@ -5047,13 +5025,13 @@
         <v>17</v>
       </c>
       <c r="V1" s="43" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="W1" s="43" t="s">
         <v>18</v>
       </c>
       <c r="X1" s="43" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="Y1" s="43" t="s">
         <v>19</v>
@@ -5062,13 +5040,13 @@
         <v>20</v>
       </c>
       <c r="AA1" s="43" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="AB1" s="43" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="AC1" s="43" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="AD1" s="43" t="s">
         <v>25</v>
@@ -5083,26 +5061,26 @@
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" s="82"/>
       <c r="B2" s="1" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C2" s="1" t="str" cm="1">
         <f t="array" ref="C2">UPPER(INDEX(_xlfn.TEXTSPLIT($D2, "-"), 3))</f>
         <v>CS</v>
       </c>
-      <c r="D2" s="94" t="s">
-        <v>261</v>
+      <c r="D2" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="H2" s="81" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="I2" s="1">
         <v>2</v>
@@ -5111,18 +5089,18 @@
         <v>8</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="O2" s="94" t="str">
+        <v>258</v>
+      </c>
+      <c r="O2" s="1" t="str">
         <f t="shared" ref="O2:O3" si="0">SUBSTITUTE(F2,"hazr-","")&amp;"-osdisk"</f>
         <v>t-cs-chtweb01-osdisk</v>
       </c>
@@ -5130,12 +5108,12 @@
         <v>64</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="R2" s="94"/>
+        <v>213</v>
+      </c>
+      <c r="R2" s="1"/>
       <c r="S2" s="1"/>
-      <c r="T2" s="94"/>
-      <c r="U2" s="94" t="str">
+      <c r="T2" s="1"/>
+      <c r="U2" s="1" t="str">
         <f t="shared" ref="U2:U3" si="1">SUBSTITUTE(F2,"hazr-","")&amp;"-nic"</f>
         <v>t-cs-chtweb01-nic</v>
       </c>
@@ -5146,22 +5124,22 @@
         <v>1</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="AA2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="AD2" s="1">
         <v>3</v>
@@ -5172,26 +5150,26 @@
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" s="82"/>
       <c r="B3" s="1" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C3" s="1" t="str" cm="1">
         <f t="array" ref="C3">UPPER(INDEX(_xlfn.TEXTSPLIT($D3, "-"), 3))</f>
         <v>CS</v>
       </c>
-      <c r="D3" s="94" t="s">
-        <v>261</v>
+      <c r="D3" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="H3" s="81" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="I3" s="1">
         <v>2</v>
@@ -5200,18 +5178,18 @@
         <v>8</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="L3" s="80" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="O3" s="94" t="str">
+        <v>258</v>
+      </c>
+      <c r="O3" s="1" t="str">
         <f t="shared" si="0"/>
         <v>t-cs-chtintweb01-osdisk</v>
       </c>
@@ -5219,12 +5197,12 @@
         <v>64</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="R3" s="94"/>
+        <v>213</v>
+      </c>
+      <c r="R3" s="1"/>
       <c r="S3" s="1"/>
-      <c r="T3" s="94"/>
-      <c r="U3" s="94" t="str">
+      <c r="T3" s="1"/>
+      <c r="U3" s="1" t="str">
         <f t="shared" si="1"/>
         <v>t-cs-chtintweb01-nic</v>
       </c>
@@ -5235,22 +5213,22 @@
         <v>1</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="AA3" s="1" t="b">
         <v>1</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="AD3" s="1">
         <v>3</v>
@@ -5261,7 +5239,7 @@
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="94"/>
+      <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="81"/>
@@ -5271,13 +5249,13 @@
       <c r="L4" s="80"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="94"/>
+      <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
-      <c r="R4" s="94"/>
+      <c r="R4" s="1"/>
       <c r="S4" s="1"/>
-      <c r="T4" s="94"/>
-      <c r="U4" s="94"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -5293,7 +5271,7 @@
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="94"/>
+      <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="81"/>
@@ -5303,13 +5281,13 @@
       <c r="L5" s="80"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="94"/>
+      <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
-      <c r="R5" s="94"/>
+      <c r="R5" s="1"/>
       <c r="S5" s="1"/>
-      <c r="T5" s="94"/>
-      <c r="U5" s="94"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
@@ -5325,7 +5303,7 @@
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="94"/>
+      <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="81"/>
@@ -5335,13 +5313,13 @@
       <c r="L6" s="80"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
-      <c r="O6" s="94"/>
+      <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
-      <c r="R6" s="94"/>
+      <c r="R6" s="1"/>
       <c r="S6" s="1"/>
-      <c r="T6" s="94"/>
-      <c r="U6" s="94"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
@@ -5398,68 +5376,68 @@
         <v>3</v>
       </c>
       <c r="F1" s="86" t="s">
+        <v>225</v>
+      </c>
+      <c r="G1" s="86" t="s">
+        <v>227</v>
+      </c>
+      <c r="H1" s="86" t="s">
+        <v>229</v>
+      </c>
+      <c r="I1" s="86" t="s">
+        <v>230</v>
+      </c>
+      <c r="J1" s="86" t="s">
+        <v>228</v>
+      </c>
+      <c r="K1" s="86" t="s">
+        <v>231</v>
+      </c>
+      <c r="L1" s="86" t="s">
+        <v>232</v>
+      </c>
+      <c r="M1" s="86" t="s">
+        <v>226</v>
+      </c>
+      <c r="N1" s="86" t="s">
+        <v>234</v>
+      </c>
+      <c r="O1" s="86" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="86" t="s">
-        <v>238</v>
-      </c>
-      <c r="H1" s="86" t="s">
-        <v>240</v>
-      </c>
-      <c r="I1" s="86" t="s">
-        <v>241</v>
-      </c>
-      <c r="J1" s="86" t="s">
-        <v>239</v>
-      </c>
-      <c r="K1" s="86" t="s">
-        <v>242</v>
-      </c>
-      <c r="L1" s="86" t="s">
-        <v>243</v>
-      </c>
-      <c r="M1" s="86" t="s">
-        <v>237</v>
-      </c>
-      <c r="N1" s="86" t="s">
-        <v>245</v>
-      </c>
-      <c r="O1" s="86" t="s">
-        <v>247</v>
-      </c>
       <c r="P1" s="86" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="Q1" s="86" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="R1" s="91" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="98"/>
       <c r="B2" s="87" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C2" s="87" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="D2" s="87" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="E2" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="95" t="s">
-        <v>262</v>
+      <c r="F2" s="94" t="s">
+        <v>251</v>
       </c>
       <c r="G2" s="87" t="str">
         <f>SUBSTITUTE($F2,"hazr-","")&amp;"-disk01"</f>
         <v>t-cs-chtweb01-disk01</v>
       </c>
       <c r="H2" s="87" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="I2" s="87">
         <v>128</v>
@@ -5469,7 +5447,7 @@
         <v>t-cs-chtweb01-disk02</v>
       </c>
       <c r="K2" s="87" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="L2" s="87">
         <v>128</v>
@@ -5478,13 +5456,13 @@
         <v>3</v>
       </c>
       <c r="N2" s="87" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="O2" s="87" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="P2" s="87" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="Q2" s="87" t="b">
         <v>1</v>
@@ -5492,28 +5470,28 @@
       <c r="R2" s="85"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="100"/>
+      <c r="A3" s="98"/>
       <c r="B3" s="88" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C3" s="88" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="D3" s="88" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="E3" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="96" t="s">
-        <v>263</v>
+      <c r="F3" s="95" t="s">
+        <v>252</v>
       </c>
       <c r="G3" s="88" t="str">
-        <f t="shared" ref="G3:G6" si="0">SUBSTITUTE($F3,"hazr-","")&amp;"-disk01"</f>
+        <f t="shared" ref="G3" si="0">SUBSTITUTE($F3,"hazr-","")&amp;"-disk01"</f>
         <v>t-cs-chtintweb01-disk01</v>
       </c>
       <c r="H3" s="88" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="I3" s="88">
         <v>128</v>
@@ -5523,7 +5501,7 @@
         <v>t-cs-chtintweb01-disk02</v>
       </c>
       <c r="K3" s="88" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="L3" s="88">
         <v>128</v>
@@ -5532,13 +5510,13 @@
         <v>3</v>
       </c>
       <c r="N3" s="88" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="O3" s="88" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="P3" s="88" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="Q3" s="88" t="b">
         <v>1</v>
@@ -5546,12 +5524,12 @@
       <c r="R3" s="56"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="97"/>
+      <c r="A4" s="96"/>
       <c r="B4" s="88"/>
       <c r="C4" s="88"/>
       <c r="D4" s="88"/>
       <c r="E4" s="93"/>
-      <c r="F4" s="96"/>
+      <c r="F4" s="95"/>
       <c r="G4" s="88"/>
       <c r="H4" s="88"/>
       <c r="I4" s="88"/>
@@ -5566,12 +5544,12 @@
       <c r="R4" s="56"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="97"/>
+      <c r="A5" s="96"/>
       <c r="B5" s="88"/>
       <c r="C5" s="88"/>
       <c r="D5" s="88"/>
       <c r="E5" s="93"/>
-      <c r="F5" s="96"/>
+      <c r="F5" s="95"/>
       <c r="G5" s="88"/>
       <c r="H5" s="88"/>
       <c r="I5" s="88"/>
@@ -5590,7 +5568,7 @@
       <c r="C6" s="88"/>
       <c r="D6" s="88"/>
       <c r="E6" s="93"/>
-      <c r="F6" s="96"/>
+      <c r="F6" s="95"/>
       <c r="G6" s="88"/>
       <c r="H6" s="88"/>
       <c r="I6" s="88"/>
@@ -5612,184 +5590,190 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAB1F184-7BFC-47CB-AC71-63C76B7E3D12}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="B1:K6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.5" customWidth="1"/>
-    <col min="5" max="5" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="1" max="1" width="1.5" customWidth="1"/>
+    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5" customWidth="1"/>
+    <col min="7" max="7" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="C1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="D1" s="45" t="s">
+        <v>259</v>
+      </c>
+      <c r="E1" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="47" t="s">
-        <v>109</v>
-      </c>
       <c r="F1" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="G1" s="46" t="s">
-        <v>111</v>
-      </c>
-      <c r="H1" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="H1" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="I1" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="K1" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2" s="4" t="str" cm="1">
+        <f t="array" ref="C2">UPPER(INDEX(_xlfn.TEXTSPLIT($F2, "-"), 2))</f>
+        <v>CS</v>
+      </c>
+      <c r="D2" s="4" t="str" cm="1">
+        <f t="array" ref="D2">UPPER(INDEX(_xlfn.TEXTSPLIT($F2, "-"), 3))</f>
+        <v>WEB</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="J2" s="4"/>
+      <c r="K2" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D2" s="4" t="str">
-        <f>IF(I2="O",H2&amp;"-NSG",G2&amp;"-NSG")</f>
-        <v>PRDWEB01-nic-NSG</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>81</v>
-      </c>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="6" t="str">
-        <f>IF(I3="O",H3&amp;"-NSG",G3&amp;"-NSG")</f>
-        <v>PRDWEB02-nic-NSG</v>
+        <v>223</v>
+      </c>
+      <c r="C3" s="6" t="str" cm="1">
+        <f t="array" ref="C3">UPPER(INDEX(_xlfn.TEXTSPLIT($F2, "-"), 2))</f>
+        <v>CS</v>
+      </c>
+      <c r="D3" s="6" t="str" cm="1">
+        <f t="array" ref="D3">UPPER(INDEX(_xlfn.TEXTSPLIT($F3, "-"), 3))</f>
+        <v>AP</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>84</v>
+        <v>239</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="G3" s="6"/>
+        <v>263</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>239</v>
+      </c>
       <c r="H3" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>23</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="K3" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="4" t="str">
-        <f>IF(I4="O",A4&amp;H4&amp;"-NSG",A4&amp;G4&amp;"-NSG")</f>
-        <v>PRDWEBSubnet-NSG</v>
+        <v>223</v>
+      </c>
+      <c r="C4" s="4" t="str" cm="1">
+        <f t="array" ref="C4">UPPER(INDEX(_xlfn.TEXTSPLIT($F4, "-"), 2))</f>
+        <v>CS</v>
+      </c>
+      <c r="D4" s="4" t="str" cm="1">
+        <f t="array" ref="D4">UPPER(INDEX(_xlfn.TEXTSPLIT($F4, "-"), 3))</f>
+        <v>DB</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>84</v>
+        <v>239</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>89</v>
+        <v>264</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>82</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="6" t="str">
-        <f>IF(I5="O",A5&amp;H5&amp;"-NSG",A5&amp;G5&amp;"-NSG")</f>
-        <v>STGWEBSubnet-NSG</v>
+        <v>223</v>
+      </c>
+      <c r="C5" s="6" t="str" cm="1">
+        <f t="array" ref="C5">UPPER(INDEX(_xlfn.TEXTSPLIT($F5, "-"), 2))</f>
+        <v>CS</v>
+      </c>
+      <c r="D5" s="6" t="str" cm="1">
+        <f t="array" ref="D5">UPPER(INDEX(_xlfn.TEXTSPLIT($F5, "-"), 3))</f>
+        <v>PE</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>85</v>
+        <v>239</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>90</v>
+        <v>265</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" s="53" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="4" t="str">
-        <f>IF(I6="O",A6&amp;H6&amp;"-NSG",A6&amp;G6&amp;"-NSG")</f>
-        <v>DEVAPPSubnet-NSG</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="G6" s="53" t="s">
-        <v>99</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="J5" s="6"/>
+      <c r="K5" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
       <c r="H6" s="53"/>
-      <c r="I6" s="54" t="s">
-        <v>38</v>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="54" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -5826,34 +5810,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D1" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="F1" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="G1" s="46" t="s">
-        <v>41</v>
-      </c>
       <c r="H1" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="49" t="s">
+      <c r="J1" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="J1" s="49" t="s">
+      <c r="K1" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="K1" s="49" t="s">
+      <c r="L1" s="49" t="s">
         <v>57</v>
-      </c>
-      <c r="L1" s="49" t="s">
-        <v>58</v>
       </c>
       <c r="M1" s="50" t="s">
         <v>22</v>
@@ -5867,28 +5851,28 @@
         <v>29</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D2" s="15">
         <v>100</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H2" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" s="30" t="s">
         <v>59</v>
-      </c>
-      <c r="I2" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="J2" s="30" t="s">
-        <v>60</v>
       </c>
       <c r="K2" s="30" t="s">
         <v>26</v>
@@ -5897,7 +5881,7 @@
         <v>22</v>
       </c>
       <c r="M2" s="24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -5908,37 +5892,37 @@
         <v>29</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D3" s="4">
         <v>110</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="31" t="s">
-        <v>60</v>
-      </c>
       <c r="J3" s="31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K3" s="31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L3" s="31">
         <v>80</v>
       </c>
       <c r="M3" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
@@ -5949,37 +5933,37 @@
         <v>29</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D4" s="9">
         <v>4095</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H4" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="32" t="s">
-        <v>62</v>
-      </c>
       <c r="J4" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K4" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L4" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M4" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
@@ -5990,37 +5974,37 @@
         <v>29</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D5" s="9">
         <v>4096</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I5" s="32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K5" s="32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L5" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M5" s="26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
@@ -6031,37 +6015,37 @@
         <v>29</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D6" s="12">
         <v>100</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I6" s="33" t="s">
         <v>26</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M6" s="27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -6072,7 +6056,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -6093,12 +6077,12 @@
         <v>29</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
@@ -6116,37 +6100,37 @@
         <v>29</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D9" s="22">
         <v>4096</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F9" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="22" t="s">
-        <v>45</v>
-      </c>
       <c r="H9" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I9" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J9" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K9" s="35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L9" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M9" s="29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6172,28 +6156,28 @@
         <v>29</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D11" s="13">
         <v>100</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H11" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" s="36" t="s">
         <v>59</v>
-      </c>
-      <c r="I11" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="J11" s="36" t="s">
-        <v>60</v>
       </c>
       <c r="K11" s="36" t="s">
         <v>27</v>
@@ -6212,7 +6196,7 @@
         <v>29</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -6233,37 +6217,37 @@
         <v>29</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D13" s="9">
         <v>4095</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H13" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="32" t="s">
-        <v>62</v>
-      </c>
       <c r="J13" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K13" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L13" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M13" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
@@ -6274,37 +6258,37 @@
         <v>29</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D14" s="9">
         <v>4096</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I14" s="32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J14" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K14" s="32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L14" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
@@ -6315,12 +6299,12 @@
         <v>29</v>
       </c>
       <c r="C15" s="63" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D15" s="63"/>
       <c r="E15" s="63"/>
       <c r="F15" s="63" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G15" s="63"/>
       <c r="H15" s="64"/>
@@ -6338,12 +6322,12 @@
         <v>29</v>
       </c>
       <c r="C16" s="63" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D16" s="63"/>
       <c r="E16" s="63"/>
       <c r="F16" s="63" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G16" s="63"/>
       <c r="H16" s="63"/>
@@ -6361,12 +6345,12 @@
         <v>29</v>
       </c>
       <c r="C17" s="63" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D17" s="63"/>
       <c r="E17" s="63"/>
       <c r="F17" s="63" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G17" s="63"/>
       <c r="H17" s="63"/>
@@ -6384,37 +6368,37 @@
         <v>29</v>
       </c>
       <c r="C18" s="63" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D18" s="68">
         <v>4096</v>
       </c>
       <c r="E18" s="68" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18" s="67" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="68" t="s">
-        <v>45</v>
-      </c>
       <c r="H18" s="69" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I18" s="70" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J18" s="70" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K18" s="70" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L18" s="70" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M18" s="68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6440,28 +6424,28 @@
         <v>30</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D20" s="15">
         <v>150</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H20" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="I20" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="J20" s="30" t="s">
         <v>59</v>
-      </c>
-      <c r="I20" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="J20" s="30" t="s">
-        <v>60</v>
       </c>
       <c r="K20" s="30" t="s">
         <v>26</v>
@@ -6470,7 +6454,7 @@
         <v>22</v>
       </c>
       <c r="M20" s="24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
@@ -6481,34 +6465,34 @@
         <v>30</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D21" s="4">
         <v>160</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H21" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I21" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="I21" s="31" t="s">
-        <v>60</v>
-      </c>
       <c r="J21" s="31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K21" s="31" t="s">
         <v>27</v>
       </c>
       <c r="L21" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M21" s="25"/>
     </row>
@@ -6520,37 +6504,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D22" s="9">
         <v>4095</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H22" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I22" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="32" t="s">
-        <v>62</v>
-      </c>
       <c r="J22" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K22" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L22" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M22" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
@@ -6561,37 +6545,37 @@
         <v>29</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D23" s="9">
         <v>4096</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I23" s="32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J23" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K23" s="32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L23" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M23" s="26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -6602,12 +6586,12 @@
         <v>30</v>
       </c>
       <c r="C24" s="63" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D24" s="63"/>
       <c r="E24" s="63"/>
       <c r="F24" s="63" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G24" s="63"/>
       <c r="H24" s="64"/>
@@ -6625,12 +6609,12 @@
         <v>30</v>
       </c>
       <c r="C25" s="63" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D25" s="63"/>
       <c r="E25" s="63"/>
       <c r="F25" s="63" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G25" s="63"/>
       <c r="H25" s="63"/>
@@ -6648,12 +6632,12 @@
         <v>30</v>
       </c>
       <c r="C26" s="63" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D26" s="63"/>
       <c r="E26" s="63"/>
       <c r="F26" s="63" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G26" s="63"/>
       <c r="H26" s="63"/>
@@ -6671,37 +6655,37 @@
         <v>30</v>
       </c>
       <c r="C27" s="75" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D27" s="76">
         <v>4096</v>
       </c>
       <c r="E27" s="76" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F27" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="G27" s="76" t="s">
-        <v>45</v>
-      </c>
       <c r="H27" s="77" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I27" s="78" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J27" s="78" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K27" s="78" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L27" s="78" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M27" s="79" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6727,15 +6711,15 @@
         <v>32</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
       <c r="F29" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H29" s="13"/>
       <c r="I29" s="36"/>
@@ -6752,15 +6736,15 @@
         <v>32</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H30" s="4"/>
       <c r="I30" s="31"/>
@@ -6777,37 +6761,37 @@
         <v>29</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D31" s="9">
         <v>4095</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H31" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I31" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="I31" s="32" t="s">
-        <v>62</v>
-      </c>
       <c r="J31" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K31" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L31" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M31" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
@@ -6818,37 +6802,37 @@
         <v>29</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D32" s="9">
         <v>4096</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I32" s="32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J32" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K32" s="32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L32" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M32" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -6859,37 +6843,37 @@
         <v>32</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D33" s="12">
         <v>200</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H33" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="I33" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="J33" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="I33" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="J33" s="33" t="s">
-        <v>60</v>
-      </c>
       <c r="K33" s="33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L33" s="33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M33" s="27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
@@ -6900,12 +6884,12 @@
         <v>32</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
@@ -6923,12 +6907,12 @@
         <v>32</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
@@ -6946,37 +6930,37 @@
         <v>32</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D36" s="11">
         <v>4096</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F36" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G36" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G36" s="11" t="s">
-        <v>45</v>
-      </c>
       <c r="H36" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K36" s="37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L36" s="37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M36" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -7013,46 +6997,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C1" s="58" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="E1" s="58" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="F1" s="58" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="G1" s="58" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="H1" s="58" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="I1" s="58" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="J1" s="58" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="K1" s="59" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="L1" s="59" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M1" s="59" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="N1" s="59" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="O1" s="58" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -7060,44 +7044,44 @@
         <v>23</v>
       </c>
       <c r="B2" s="56" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C2" s="56" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="F2" s="56" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G2" s="56"/>
       <c r="H2" s="56" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="I2" s="56" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="J2" s="56" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K2" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="L2" s="56" t="s">
-        <v>98</v>
-      </c>
       <c r="M2" s="56" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="N2" s="56" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="O2" s="56" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -7105,46 +7089,46 @@
         <v>23</v>
       </c>
       <c r="B3" s="56" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C3" s="56" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="E3" s="56" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="F3" s="56" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="G3" s="56">
         <v>1</v>
       </c>
       <c r="H3" s="56" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="I3" s="56" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="J3" s="56" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K3" s="56" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L3" s="56" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="M3" s="56" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="N3" s="56" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="O3" s="56" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -7424,25 +7408,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1" s="58" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="F1" s="59" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G1" s="59" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="H1" s="59" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -7450,13 +7434,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="56" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E2" s="56">
         <v>80</v>
@@ -7474,13 +7458,13 @@
         <v>23</v>
       </c>
       <c r="B3" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="56" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="56" t="s">
-        <v>143</v>
-      </c>
       <c r="D3" s="56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E3" s="56">
         <v>8080</v>
@@ -7498,19 +7482,19 @@
         <v>23</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="E4" s="56">
         <v>443</v>
       </c>
       <c r="F4" s="60" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G4" s="56">
         <v>5</v>
@@ -7524,19 +7508,19 @@
         <v>23</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="E5" s="56">
         <v>80</v>
       </c>
       <c r="F5" s="60" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G5" s="56">
         <v>5</v>
@@ -7550,13 +7534,13 @@
         <v>23</v>
       </c>
       <c r="B6" s="61" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D6" s="61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6" s="61">
         <v>80</v>
@@ -7574,13 +7558,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="61" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C7" s="61" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D7" s="61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" s="61">
         <v>22</v>
@@ -7598,19 +7582,19 @@
         <v>23</v>
       </c>
       <c r="B8" s="61" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C8" s="61" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D8" s="61" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="E8" s="61">
         <v>443</v>
       </c>
       <c r="F8" s="62" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G8" s="61">
         <v>5</v>
@@ -7624,19 +7608,19 @@
         <v>23</v>
       </c>
       <c r="B9" s="61" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C9" s="61" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="D9" s="61" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="E9" s="61">
         <v>80</v>
       </c>
       <c r="F9" s="62" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G9" s="61">
         <v>5</v>
@@ -7671,43 +7655,43 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E1" s="59" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="F1" s="59" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="G1" s="59" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="H1" s="58" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="I1" s="59" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="J1" s="59" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="K1" s="59" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="L1" s="59" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="M1" s="59" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="N1" s="59" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -7715,16 +7699,16 @@
         <v>23</v>
       </c>
       <c r="B2" s="56" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F2" s="56">
         <v>80</v>
@@ -7733,19 +7717,19 @@
         <v>0</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="I2" s="56">
         <v>80</v>
       </c>
       <c r="J2" s="56" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="K2" s="56">
         <v>4</v>
       </c>
       <c r="L2" s="56" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="M2" s="56" t="b">
         <v>1</v>
@@ -7759,16 +7743,16 @@
         <v>23</v>
       </c>
       <c r="B3" s="56" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E3" s="56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F3" s="56">
         <v>8080</v>
@@ -7777,19 +7761,19 @@
         <v>0</v>
       </c>
       <c r="H3" s="56" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I3" s="56">
         <v>8080</v>
       </c>
       <c r="J3" s="56" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="K3" s="56">
         <v>4</v>
       </c>
       <c r="L3" s="56" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="M3" s="56" t="b">
         <v>1</v>
@@ -7803,16 +7787,16 @@
         <v>23</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F4" s="56">
         <v>443</v>
@@ -7821,19 +7805,19 @@
         <v>0</v>
       </c>
       <c r="H4" s="56" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I4" s="56">
         <v>443</v>
       </c>
       <c r="J4" s="56" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="K4" s="56">
         <v>4</v>
       </c>
       <c r="L4" s="56" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="M4" s="56" t="b">
         <v>1</v>
@@ -7847,16 +7831,16 @@
         <v>23</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E5" s="56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F5" s="56">
         <v>22</v>
@@ -7865,19 +7849,19 @@
         <v>0</v>
       </c>
       <c r="H5" s="56" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I5" s="56">
         <v>22</v>
       </c>
       <c r="J5" s="56" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="K5" s="56">
         <v>4</v>
       </c>
       <c r="L5" s="56" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="M5" s="56" t="b">
         <v>1</v>
@@ -7984,12 +7968,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8137,15 +8118,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8169,17 +8161,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -7968,9 +7968,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8118,26 +8121,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8161,9 +8153,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E17F478-1CB1-41C1-8EA1-2408B201C478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C17A5ED-23AE-4882-ABB8-F85E501AFA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,10 +18,11 @@
     <sheet name="VM" sheetId="1" r:id="rId3"/>
     <sheet name="VM_Datadisk" sheetId="14" r:id="rId4"/>
     <sheet name="NSG" sheetId="2" r:id="rId5"/>
-    <sheet name="NSG_Rule" sheetId="3" r:id="rId6"/>
-    <sheet name="LB" sheetId="6" r:id="rId7"/>
-    <sheet name="LB_Probe" sheetId="10" r:id="rId8"/>
-    <sheet name="LB_Rule" sheetId="11" r:id="rId9"/>
+    <sheet name="UDR" sheetId="15" r:id="rId6"/>
+    <sheet name="NSG_Rule" sheetId="3" r:id="rId7"/>
+    <sheet name="LB" sheetId="6" r:id="rId8"/>
+    <sheet name="LB_Probe" sheetId="10" r:id="rId9"/>
+    <sheet name="LB_Rule" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1653,7 +1654,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="438">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2646,6 +2647,543 @@
   <si>
     <t>t-cs-pe-nsg</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t-dch-ext-vnet-udr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t-dch-int-vnet-udr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RouteName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UDRName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Internet</t>
+  </si>
+  <si>
+    <t>hazr-o-devops-int-vnet_1</t>
+  </si>
+  <si>
+    <t>hazr-o-devops-int-vnet_2</t>
+  </si>
+  <si>
+    <t>hazr-o-devops-int-vnet_3</t>
+  </si>
+  <si>
+    <t>hazr-o-devops-int-vnet_4</t>
+  </si>
+  <si>
+    <t>hazr-l-comm-vnet</t>
+  </si>
+  <si>
+    <t>Onprem01</t>
+  </si>
+  <si>
+    <t>Onprem02</t>
+  </si>
+  <si>
+    <t>Onprem03</t>
+  </si>
+  <si>
+    <t>Onprem04</t>
+  </si>
+  <si>
+    <t>Onprem05</t>
+  </si>
+  <si>
+    <t>Onprem06</t>
+  </si>
+  <si>
+    <t>Onprem07</t>
+  </si>
+  <si>
+    <t>Onprem08</t>
+  </si>
+  <si>
+    <t>Onprem09</t>
+  </si>
+  <si>
+    <t>Onprem10</t>
+  </si>
+  <si>
+    <t>hazr-d-dch-ext-vnet_2</t>
+  </si>
+  <si>
+    <t>hazr-d-dch-ext-vnet_3</t>
+  </si>
+  <si>
+    <t>hazr-d-dch-ext-vnet_4</t>
+  </si>
+  <si>
+    <t>hazr-d-dch-ext-vnet_5</t>
+  </si>
+  <si>
+    <t>hazr-d-dch-ext-vnet_6</t>
+  </si>
+  <si>
+    <t>hazr-d-dch-ext-vnet_7</t>
+  </si>
+  <si>
+    <t>hazr-d-dch-ext-vnet_8</t>
+  </si>
+  <si>
+    <t>hazr-d-dch-ext-vnet_9</t>
+  </si>
+  <si>
+    <t>AddressPrefix</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0.0.0/0</t>
+  </si>
+  <si>
+    <t>10.155.128.0/24</t>
+  </si>
+  <si>
+    <t>10.155.129.0/24</t>
+  </si>
+  <si>
+    <t>10.155.130.0/24</t>
+  </si>
+  <si>
+    <t>10.155.131.0/24</t>
+  </si>
+  <si>
+    <t>10.155.160.0/22</t>
+  </si>
+  <si>
+    <t>10.0.0.0/8</t>
+  </si>
+  <si>
+    <t>172.16.0.0/16</t>
+  </si>
+  <si>
+    <t>172.18.0.0/16</t>
+  </si>
+  <si>
+    <t>172.20.0.0/16</t>
+  </si>
+  <si>
+    <t>172.26.0.0/16</t>
+  </si>
+  <si>
+    <t>172.28.0.0/16</t>
+  </si>
+  <si>
+    <t>172.29.0.0/16</t>
+  </si>
+  <si>
+    <t>172.30.0.0/16</t>
+  </si>
+  <si>
+    <t>172.31.0.0/16</t>
+  </si>
+  <si>
+    <t>172.32.0.0/16</t>
+  </si>
+  <si>
+    <t>NextHopType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VirtualAppliance</t>
+  </si>
+  <si>
+    <t>NextHopIpAddress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.155.200.4</t>
+  </si>
+  <si>
+    <t>hazr-lt-sec-int-vnet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.155.193.128/26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_1</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_2</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_3</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_4</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_5</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_6</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_7</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_8</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_9</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_10</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_11</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_12</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_13</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_14</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_15</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_16</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_17</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_18</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_19</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_20</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_21</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_22</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_23</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_24</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_25</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_26</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_27</t>
+  </si>
+  <si>
+    <t>10.157.144.0/24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.145.0/24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.146.0/24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.147.0/24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.148.0/24</t>
+  </si>
+  <si>
+    <t>10.157.149.0/24</t>
+  </si>
+  <si>
+    <t>10.157.150.0/24</t>
+  </si>
+  <si>
+    <t>10.157.151.0/24</t>
+  </si>
+  <si>
+    <t>10.157.152.0/24</t>
+  </si>
+  <si>
+    <t>10.157.153.0/24</t>
+  </si>
+  <si>
+    <t>10.157.154.0/24</t>
+  </si>
+  <si>
+    <t>10.157.155.0/24</t>
+  </si>
+  <si>
+    <t>10.157.157.0/24</t>
+  </si>
+  <si>
+    <t>10.157.158.0/24</t>
+  </si>
+  <si>
+    <t>10.157.159.0/24</t>
+  </si>
+  <si>
+    <t>10.157.160.0/24</t>
+  </si>
+  <si>
+    <t>10.157.161.0/24</t>
+  </si>
+  <si>
+    <t>10.157.162.0/24</t>
+  </si>
+  <si>
+    <t>10.157.163.0/24</t>
+  </si>
+  <si>
+    <t>10.157.164.0/24</t>
+  </si>
+  <si>
+    <t>10.157.165.0/24</t>
+  </si>
+  <si>
+    <t>10.157.166.0/24</t>
+  </si>
+  <si>
+    <t>10.157.167.0/24</t>
+  </si>
+  <si>
+    <t>10.157.168.0/24</t>
+  </si>
+  <si>
+    <t>10.157.169.0/24</t>
+  </si>
+  <si>
+    <t>10.157.156.0/24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_28</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_29</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_30</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_31</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_32</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_33</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_34</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_35</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_36</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_37</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_38</t>
+  </si>
+  <si>
+    <t>10.157.170.0/24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.171.0/24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.172.0/24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.173.0/24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.174.0/24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.175.0/24</t>
+  </si>
+  <si>
+    <t>10.157.176.0/24</t>
+  </si>
+  <si>
+    <t>10.157.177.0/24</t>
+  </si>
+  <si>
+    <t>10.157.178.0/24</t>
+  </si>
+  <si>
+    <t>10.157.179.0/24</t>
+  </si>
+  <si>
+    <t>10.157.180.0/24</t>
+  </si>
+  <si>
+    <t>10.157.181.0/24</t>
+  </si>
+  <si>
+    <t>10.157.182.0/24</t>
+  </si>
+  <si>
+    <t>10.157.183.0/24</t>
+  </si>
+  <si>
+    <t>10.157.184.0/24</t>
+  </si>
+  <si>
+    <t>10.157.185.0/24</t>
+  </si>
+  <si>
+    <t>10.157.186.0/24</t>
+  </si>
+  <si>
+    <t>10.157.187.0/24</t>
+  </si>
+  <si>
+    <t>10.157.188.0/24</t>
+  </si>
+  <si>
+    <t>10.157.189.0/24</t>
+  </si>
+  <si>
+    <t>10.157.190.0/24</t>
+  </si>
+  <si>
+    <t>10.157.191.0/24</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_39</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_40</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_41</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_42</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_43</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_44</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_45</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_46</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_47</t>
+  </si>
+  <si>
+    <t>hazr-t-dch-int-vnet_48</t>
+  </si>
+  <si>
+    <t>hazr-l-comm-vnet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dch-ext-vnet_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.128.0/24</t>
+  </si>
+  <si>
+    <t>10.157.129.0/24</t>
+  </si>
+  <si>
+    <t>10.157.130.0/24</t>
+  </si>
+  <si>
+    <t>10.157.131.0/24</t>
+  </si>
+  <si>
+    <t>10.157.132.0/24</t>
+  </si>
+  <si>
+    <t>10.157.133.0/24</t>
+  </si>
+  <si>
+    <t>10.157.134.0/24</t>
+  </si>
+  <si>
+    <t>10.157.135.0/24</t>
+  </si>
+  <si>
+    <t>10.157.136.0/24</t>
+  </si>
+  <si>
+    <t>10.157.137.0/24</t>
+  </si>
+  <si>
+    <t>10.157.138.0/24</t>
+  </si>
+  <si>
+    <t>10.157.139.0/24</t>
+  </si>
+  <si>
+    <t>10.157.140.0/24</t>
+  </si>
+  <si>
+    <t>10.157.141.0/24</t>
+  </si>
+  <si>
+    <t>10.157.142.0/24</t>
+  </si>
+  <si>
+    <t>10.157.143.0/24</t>
+  </si>
+  <si>
+    <t>hazr-d-dch-ext-vnet_10</t>
+  </si>
+  <si>
+    <t>hazr-d-dch-ext-vnet_11</t>
+  </si>
+  <si>
+    <t>hazr-d-dch-ext-vnet_12</t>
+  </si>
+  <si>
+    <t>hazr-d-dch-ext-vnet_13</t>
+  </si>
+  <si>
+    <t>hazr-d-dch-ext-vnet_14</t>
+  </si>
+  <si>
+    <t>hazr-d-dch-ext-vnet_15</t>
+  </si>
+  <si>
+    <t>hazr-d-dch-ext-vnet_16</t>
   </si>
 </sst>
 </file>
@@ -3094,7 +3632,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3391,6 +3929,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4742,6 +5295,338 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BC862D-08E7-4593-9A34-4D2B508CF25B}">
+  <dimension ref="A1:N11"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="58" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1" s="58" t="s">
+        <v>120</v>
+      </c>
+      <c r="I1" s="59" t="s">
+        <v>139</v>
+      </c>
+      <c r="J1" s="59" t="s">
+        <v>123</v>
+      </c>
+      <c r="K1" s="59" t="s">
+        <v>141</v>
+      </c>
+      <c r="L1" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="M1" s="59" t="s">
+        <v>157</v>
+      </c>
+      <c r="N1" s="59" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>148</v>
+      </c>
+      <c r="D2" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="E2" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="56">
+        <v>80</v>
+      </c>
+      <c r="G2" s="56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="56">
+        <v>80</v>
+      </c>
+      <c r="J2" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2" s="56">
+        <v>4</v>
+      </c>
+      <c r="L2" s="56" t="s">
+        <v>143</v>
+      </c>
+      <c r="M2" s="56" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" s="56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="56" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="E3" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="56">
+        <v>8080</v>
+      </c>
+      <c r="G3" s="56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" s="56" t="s">
+        <v>118</v>
+      </c>
+      <c r="I3" s="56">
+        <v>8080</v>
+      </c>
+      <c r="J3" s="56" t="s">
+        <v>132</v>
+      </c>
+      <c r="K3" s="56">
+        <v>4</v>
+      </c>
+      <c r="L3" s="56" t="s">
+        <v>143</v>
+      </c>
+      <c r="M3" s="56" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" s="56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="56" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="56" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="56">
+        <v>443</v>
+      </c>
+      <c r="G4" s="56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="56" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="56">
+        <v>443</v>
+      </c>
+      <c r="J4" s="56" t="s">
+        <v>127</v>
+      </c>
+      <c r="K4" s="56">
+        <v>4</v>
+      </c>
+      <c r="L4" s="56" t="s">
+        <v>152</v>
+      </c>
+      <c r="M4" s="56" t="b">
+        <v>1</v>
+      </c>
+      <c r="N4" s="56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="56" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="56" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="56" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="56">
+        <v>22</v>
+      </c>
+      <c r="G5" s="56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="56" t="s">
+        <v>118</v>
+      </c>
+      <c r="I5" s="56">
+        <v>22</v>
+      </c>
+      <c r="J5" s="56" t="s">
+        <v>156</v>
+      </c>
+      <c r="K5" s="56">
+        <v>4</v>
+      </c>
+      <c r="L5" s="56" t="s">
+        <v>153</v>
+      </c>
+      <c r="M5" s="56" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" s="56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="N11" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4551C21F-24D7-4C3A-A8CD-5A629D1AA37B}">
   <dimension ref="A1:F71"/>
@@ -5785,6 +6670,2998 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5444DC07-76A1-42D8-823C-45359A57A751}">
+  <dimension ref="B1:K99"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.25" customWidth="1"/>
+    <col min="2" max="3" width="9" style="89"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.125" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B1" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="101" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="47" t="s">
+        <v>269</v>
+      </c>
+      <c r="G1" s="47" t="s">
+        <v>268</v>
+      </c>
+      <c r="H1" s="47" t="s">
+        <v>294</v>
+      </c>
+      <c r="I1" s="46" t="s">
+        <v>311</v>
+      </c>
+      <c r="J1" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="K1" s="46"/>
+    </row>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B2" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2" s="89" t="str" cm="1">
+        <f t="array" ref="C2">UPPER(INDEX(_xlfn.TEXTSPLIT($F2, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G2" s="99" t="s">
+        <v>270</v>
+      </c>
+      <c r="H2" s="99" t="s">
+        <v>295</v>
+      </c>
+      <c r="I2" t="s">
+        <v>312</v>
+      </c>
+      <c r="J2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B3" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3" s="89" t="str" cm="1">
+        <f t="array" ref="C3">UPPER(INDEX(_xlfn.TEXTSPLIT($F3, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G3" s="99" t="s">
+        <v>271</v>
+      </c>
+      <c r="H3" s="99" t="s">
+        <v>296</v>
+      </c>
+      <c r="I3" t="s">
+        <v>312</v>
+      </c>
+      <c r="J3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C4" s="89" t="str" cm="1">
+        <f t="array" ref="C4">UPPER(INDEX(_xlfn.TEXTSPLIT($F4, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G4" s="99" t="s">
+        <v>272</v>
+      </c>
+      <c r="H4" s="99" t="s">
+        <v>297</v>
+      </c>
+      <c r="I4" t="s">
+        <v>312</v>
+      </c>
+      <c r="J4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B5" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C5" s="89" t="str" cm="1">
+        <f t="array" ref="C5">UPPER(INDEX(_xlfn.TEXTSPLIT($F5, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D5" t="s">
+        <v>239</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>266</v>
+      </c>
+      <c r="G5" s="99" t="s">
+        <v>273</v>
+      </c>
+      <c r="H5" s="99" t="s">
+        <v>298</v>
+      </c>
+      <c r="I5" t="s">
+        <v>312</v>
+      </c>
+      <c r="J5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C6" s="89" t="str" cm="1">
+        <f t="array" ref="C6">UPPER(INDEX(_xlfn.TEXTSPLIT($F6, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>266</v>
+      </c>
+      <c r="G6" s="99" t="s">
+        <v>274</v>
+      </c>
+      <c r="H6" s="99" t="s">
+        <v>299</v>
+      </c>
+      <c r="I6" t="s">
+        <v>312</v>
+      </c>
+      <c r="J6" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B7" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C7" s="89" t="str" cm="1">
+        <f t="array" ref="C7">UPPER(INDEX(_xlfn.TEXTSPLIT($F7, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D7" t="s">
+        <v>239</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
+        <v>266</v>
+      </c>
+      <c r="G7" s="99" t="s">
+        <v>275</v>
+      </c>
+      <c r="H7" s="99" t="s">
+        <v>300</v>
+      </c>
+      <c r="I7" t="s">
+        <v>312</v>
+      </c>
+      <c r="J7" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B8" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C8" s="89" t="str" cm="1">
+        <f t="array" ref="C8">UPPER(INDEX(_xlfn.TEXTSPLIT($F8, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D8" t="s">
+        <v>239</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G8" s="99" t="s">
+        <v>315</v>
+      </c>
+      <c r="H8" s="99" t="s">
+        <v>316</v>
+      </c>
+      <c r="I8" t="s">
+        <v>312</v>
+      </c>
+      <c r="J8" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B9" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="89" t="str" cm="1">
+        <f t="array" ref="C9">UPPER(INDEX(_xlfn.TEXTSPLIT($F9, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" t="s">
+        <v>266</v>
+      </c>
+      <c r="G9" s="99" t="s">
+        <v>317</v>
+      </c>
+      <c r="H9" s="99" t="s">
+        <v>344</v>
+      </c>
+      <c r="I9" t="s">
+        <v>312</v>
+      </c>
+      <c r="J9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B10" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C10" s="89" t="str" cm="1">
+        <f t="array" ref="C10">UPPER(INDEX(_xlfn.TEXTSPLIT($F10, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D10" t="s">
+        <v>239</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
+        <v>266</v>
+      </c>
+      <c r="G10" s="99" t="s">
+        <v>318</v>
+      </c>
+      <c r="H10" s="99" t="s">
+        <v>345</v>
+      </c>
+      <c r="I10" t="s">
+        <v>312</v>
+      </c>
+      <c r="J10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B11" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C11" s="89" t="str" cm="1">
+        <f t="array" ref="C11">UPPER(INDEX(_xlfn.TEXTSPLIT($F11, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D11" t="s">
+        <v>239</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" t="s">
+        <v>266</v>
+      </c>
+      <c r="G11" s="99" t="s">
+        <v>319</v>
+      </c>
+      <c r="H11" s="99" t="s">
+        <v>346</v>
+      </c>
+      <c r="I11" t="s">
+        <v>312</v>
+      </c>
+      <c r="J11" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B12" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="89" t="str" cm="1">
+        <f t="array" ref="C12">UPPER(INDEX(_xlfn.TEXTSPLIT($F12, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D12" t="s">
+        <v>239</v>
+      </c>
+      <c r="E12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" t="s">
+        <v>266</v>
+      </c>
+      <c r="G12" s="99" t="s">
+        <v>320</v>
+      </c>
+      <c r="H12" s="99" t="s">
+        <v>347</v>
+      </c>
+      <c r="I12" t="s">
+        <v>312</v>
+      </c>
+      <c r="J12" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B13" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="89" t="str" cm="1">
+        <f t="array" ref="C13">UPPER(INDEX(_xlfn.TEXTSPLIT($F13, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D13" t="s">
+        <v>239</v>
+      </c>
+      <c r="E13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" t="s">
+        <v>266</v>
+      </c>
+      <c r="G13" s="99" t="s">
+        <v>321</v>
+      </c>
+      <c r="H13" s="99" t="s">
+        <v>348</v>
+      </c>
+      <c r="I13" t="s">
+        <v>312</v>
+      </c>
+      <c r="J13" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C14" s="89" t="str" cm="1">
+        <f t="array" ref="C14">UPPER(INDEX(_xlfn.TEXTSPLIT($F14, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" t="s">
+        <v>266</v>
+      </c>
+      <c r="G14" s="99" t="s">
+        <v>322</v>
+      </c>
+      <c r="H14" s="99" t="s">
+        <v>349</v>
+      </c>
+      <c r="I14" t="s">
+        <v>312</v>
+      </c>
+      <c r="J14" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B15" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C15" s="89" t="str" cm="1">
+        <f t="array" ref="C15">UPPER(INDEX(_xlfn.TEXTSPLIT($F15, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D15" t="s">
+        <v>239</v>
+      </c>
+      <c r="E15" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" t="s">
+        <v>266</v>
+      </c>
+      <c r="G15" s="99" t="s">
+        <v>323</v>
+      </c>
+      <c r="H15" s="99" t="s">
+        <v>350</v>
+      </c>
+      <c r="I15" t="s">
+        <v>312</v>
+      </c>
+      <c r="J15" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C16" s="89" t="str" cm="1">
+        <f t="array" ref="C16">UPPER(INDEX(_xlfn.TEXTSPLIT($F16, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D16" t="s">
+        <v>239</v>
+      </c>
+      <c r="E16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" t="s">
+        <v>266</v>
+      </c>
+      <c r="G16" s="99" t="s">
+        <v>324</v>
+      </c>
+      <c r="H16" s="99" t="s">
+        <v>351</v>
+      </c>
+      <c r="I16" t="s">
+        <v>312</v>
+      </c>
+      <c r="J16" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B17" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C17" s="89" t="str" cm="1">
+        <f t="array" ref="C17">UPPER(INDEX(_xlfn.TEXTSPLIT($F17, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D17" t="s">
+        <v>239</v>
+      </c>
+      <c r="E17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" t="s">
+        <v>266</v>
+      </c>
+      <c r="G17" s="99" t="s">
+        <v>325</v>
+      </c>
+      <c r="H17" s="99" t="s">
+        <v>352</v>
+      </c>
+      <c r="I17" t="s">
+        <v>312</v>
+      </c>
+      <c r="J17" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C18" s="89" t="str" cm="1">
+        <f t="array" ref="C18">UPPER(INDEX(_xlfn.TEXTSPLIT($F18, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D18" t="s">
+        <v>239</v>
+      </c>
+      <c r="E18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" t="s">
+        <v>266</v>
+      </c>
+      <c r="G18" s="99" t="s">
+        <v>326</v>
+      </c>
+      <c r="H18" s="99" t="s">
+        <v>353</v>
+      </c>
+      <c r="I18" t="s">
+        <v>312</v>
+      </c>
+      <c r="J18" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B19" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C19" s="89" t="str" cm="1">
+        <f t="array" ref="C19">UPPER(INDEX(_xlfn.TEXTSPLIT($F19, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D19" t="s">
+        <v>239</v>
+      </c>
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" t="s">
+        <v>266</v>
+      </c>
+      <c r="G19" s="99" t="s">
+        <v>327</v>
+      </c>
+      <c r="H19" s="99" t="s">
+        <v>354</v>
+      </c>
+      <c r="I19" t="s">
+        <v>312</v>
+      </c>
+      <c r="J19" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B20" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C20" s="89" t="str" cm="1">
+        <f t="array" ref="C20">UPPER(INDEX(_xlfn.TEXTSPLIT($F20, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D20" t="s">
+        <v>239</v>
+      </c>
+      <c r="E20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" t="s">
+        <v>266</v>
+      </c>
+      <c r="G20" s="99" t="s">
+        <v>328</v>
+      </c>
+      <c r="H20" s="99" t="s">
+        <v>355</v>
+      </c>
+      <c r="I20" t="s">
+        <v>312</v>
+      </c>
+      <c r="J20" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B21" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C21" s="89" t="str" cm="1">
+        <f t="array" ref="C21">UPPER(INDEX(_xlfn.TEXTSPLIT($F21, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D21" t="s">
+        <v>239</v>
+      </c>
+      <c r="E21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" t="s">
+        <v>266</v>
+      </c>
+      <c r="G21" s="99" t="s">
+        <v>329</v>
+      </c>
+      <c r="H21" s="99" t="s">
+        <v>369</v>
+      </c>
+      <c r="I21" t="s">
+        <v>312</v>
+      </c>
+      <c r="J21" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B22" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C22" s="89" t="str" cm="1">
+        <f t="array" ref="C22">UPPER(INDEX(_xlfn.TEXTSPLIT($F22, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D22" t="s">
+        <v>239</v>
+      </c>
+      <c r="E22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" t="s">
+        <v>266</v>
+      </c>
+      <c r="G22" s="99" t="s">
+        <v>330</v>
+      </c>
+      <c r="H22" s="99" t="s">
+        <v>356</v>
+      </c>
+      <c r="I22" t="s">
+        <v>312</v>
+      </c>
+      <c r="J22" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B23" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C23" s="89" t="str" cm="1">
+        <f t="array" ref="C23">UPPER(INDEX(_xlfn.TEXTSPLIT($F23, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D23" t="s">
+        <v>239</v>
+      </c>
+      <c r="E23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" t="s">
+        <v>266</v>
+      </c>
+      <c r="G23" s="99" t="s">
+        <v>331</v>
+      </c>
+      <c r="H23" s="99" t="s">
+        <v>357</v>
+      </c>
+      <c r="I23" t="s">
+        <v>312</v>
+      </c>
+      <c r="J23" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B24" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C24" s="89" t="str" cm="1">
+        <f t="array" ref="C24">UPPER(INDEX(_xlfn.TEXTSPLIT($F24, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D24" t="s">
+        <v>239</v>
+      </c>
+      <c r="E24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" t="s">
+        <v>266</v>
+      </c>
+      <c r="G24" s="99" t="s">
+        <v>332</v>
+      </c>
+      <c r="H24" s="99" t="s">
+        <v>358</v>
+      </c>
+      <c r="I24" t="s">
+        <v>312</v>
+      </c>
+      <c r="J24" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B25" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C25" s="89" t="str" cm="1">
+        <f t="array" ref="C25">UPPER(INDEX(_xlfn.TEXTSPLIT($F25, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D25" t="s">
+        <v>239</v>
+      </c>
+      <c r="E25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" t="s">
+        <v>266</v>
+      </c>
+      <c r="G25" s="99" t="s">
+        <v>333</v>
+      </c>
+      <c r="H25" s="99" t="s">
+        <v>359</v>
+      </c>
+      <c r="I25" t="s">
+        <v>312</v>
+      </c>
+      <c r="J25" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B26" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C26" s="89" t="str" cm="1">
+        <f t="array" ref="C26">UPPER(INDEX(_xlfn.TEXTSPLIT($F26, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D26" t="s">
+        <v>239</v>
+      </c>
+      <c r="E26" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" t="s">
+        <v>266</v>
+      </c>
+      <c r="G26" s="99" t="s">
+        <v>334</v>
+      </c>
+      <c r="H26" s="99" t="s">
+        <v>360</v>
+      </c>
+      <c r="I26" t="s">
+        <v>312</v>
+      </c>
+      <c r="J26" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B27" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C27" s="89" t="str" cm="1">
+        <f t="array" ref="C27">UPPER(INDEX(_xlfn.TEXTSPLIT($F27, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D27" t="s">
+        <v>239</v>
+      </c>
+      <c r="E27" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" t="s">
+        <v>266</v>
+      </c>
+      <c r="G27" s="99" t="s">
+        <v>335</v>
+      </c>
+      <c r="H27" s="99" t="s">
+        <v>361</v>
+      </c>
+      <c r="I27" t="s">
+        <v>312</v>
+      </c>
+      <c r="J27" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B28" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C28" s="89" t="str" cm="1">
+        <f t="array" ref="C28">UPPER(INDEX(_xlfn.TEXTSPLIT($F28, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D28" t="s">
+        <v>239</v>
+      </c>
+      <c r="E28" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" t="s">
+        <v>266</v>
+      </c>
+      <c r="G28" s="99" t="s">
+        <v>336</v>
+      </c>
+      <c r="H28" s="99" t="s">
+        <v>362</v>
+      </c>
+      <c r="I28" t="s">
+        <v>312</v>
+      </c>
+      <c r="J28" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B29" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C29" s="89" t="str" cm="1">
+        <f t="array" ref="C29">UPPER(INDEX(_xlfn.TEXTSPLIT($F29, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D29" t="s">
+        <v>239</v>
+      </c>
+      <c r="E29" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" t="s">
+        <v>266</v>
+      </c>
+      <c r="G29" s="99" t="s">
+        <v>337</v>
+      </c>
+      <c r="H29" s="99" t="s">
+        <v>363</v>
+      </c>
+      <c r="I29" t="s">
+        <v>312</v>
+      </c>
+      <c r="J29" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B30" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C30" s="89" t="str" cm="1">
+        <f t="array" ref="C30">UPPER(INDEX(_xlfn.TEXTSPLIT($F30, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D30" t="s">
+        <v>239</v>
+      </c>
+      <c r="E30" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" t="s">
+        <v>266</v>
+      </c>
+      <c r="G30" s="99" t="s">
+        <v>338</v>
+      </c>
+      <c r="H30" s="99" t="s">
+        <v>364</v>
+      </c>
+      <c r="I30" t="s">
+        <v>312</v>
+      </c>
+      <c r="J30" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B31" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C31" s="89" t="str" cm="1">
+        <f t="array" ref="C31">UPPER(INDEX(_xlfn.TEXTSPLIT($F31, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D31" t="s">
+        <v>239</v>
+      </c>
+      <c r="E31" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" t="s">
+        <v>266</v>
+      </c>
+      <c r="G31" s="99" t="s">
+        <v>339</v>
+      </c>
+      <c r="H31" s="99" t="s">
+        <v>365</v>
+      </c>
+      <c r="I31" t="s">
+        <v>312</v>
+      </c>
+      <c r="J31" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B32" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C32" s="89" t="str" cm="1">
+        <f t="array" ref="C32">UPPER(INDEX(_xlfn.TEXTSPLIT($F32, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D32" t="s">
+        <v>239</v>
+      </c>
+      <c r="E32" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" t="s">
+        <v>266</v>
+      </c>
+      <c r="G32" s="99" t="s">
+        <v>340</v>
+      </c>
+      <c r="H32" s="99" t="s">
+        <v>366</v>
+      </c>
+      <c r="I32" t="s">
+        <v>312</v>
+      </c>
+      <c r="J32" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B33" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C33" s="89" t="str" cm="1">
+        <f t="array" ref="C33">UPPER(INDEX(_xlfn.TEXTSPLIT($F33, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E33" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" t="s">
+        <v>266</v>
+      </c>
+      <c r="G33" s="99" t="s">
+        <v>341</v>
+      </c>
+      <c r="H33" s="99" t="s">
+        <v>367</v>
+      </c>
+      <c r="I33" t="s">
+        <v>312</v>
+      </c>
+      <c r="J33" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B34" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C34" s="89" t="str" cm="1">
+        <f t="array" ref="C34">UPPER(INDEX(_xlfn.TEXTSPLIT($F34, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D34" t="s">
+        <v>239</v>
+      </c>
+      <c r="E34" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" t="s">
+        <v>266</v>
+      </c>
+      <c r="G34" s="99" t="s">
+        <v>342</v>
+      </c>
+      <c r="H34" s="99" t="s">
+        <v>368</v>
+      </c>
+      <c r="I34" t="s">
+        <v>312</v>
+      </c>
+      <c r="J34" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B35" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C35" s="89" t="str" cm="1">
+        <f t="array" ref="C35">UPPER(INDEX(_xlfn.TEXTSPLIT($F35, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D35" t="s">
+        <v>239</v>
+      </c>
+      <c r="E35" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" t="s">
+        <v>266</v>
+      </c>
+      <c r="G35" s="99" t="s">
+        <v>343</v>
+      </c>
+      <c r="H35" s="99" t="s">
+        <v>381</v>
+      </c>
+      <c r="I35" t="s">
+        <v>312</v>
+      </c>
+      <c r="J35" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B36" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C36" s="89" t="str" cm="1">
+        <f t="array" ref="C36">UPPER(INDEX(_xlfn.TEXTSPLIT($F36, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D36" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" t="s">
+        <v>266</v>
+      </c>
+      <c r="G36" s="99" t="s">
+        <v>370</v>
+      </c>
+      <c r="H36" s="99" t="s">
+        <v>382</v>
+      </c>
+      <c r="I36" t="s">
+        <v>312</v>
+      </c>
+      <c r="J36" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B37" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C37" s="89" t="str" cm="1">
+        <f t="array" ref="C37">UPPER(INDEX(_xlfn.TEXTSPLIT($F37, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D37" t="s">
+        <v>239</v>
+      </c>
+      <c r="E37" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" t="s">
+        <v>266</v>
+      </c>
+      <c r="G37" s="99" t="s">
+        <v>371</v>
+      </c>
+      <c r="H37" s="99" t="s">
+        <v>383</v>
+      </c>
+      <c r="I37" t="s">
+        <v>312</v>
+      </c>
+      <c r="J37" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B38" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C38" s="89" t="str" cm="1">
+        <f t="array" ref="C38">UPPER(INDEX(_xlfn.TEXTSPLIT($F38, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D38" t="s">
+        <v>239</v>
+      </c>
+      <c r="E38" t="s">
+        <v>24</v>
+      </c>
+      <c r="F38" t="s">
+        <v>266</v>
+      </c>
+      <c r="G38" s="99" t="s">
+        <v>372</v>
+      </c>
+      <c r="H38" s="99" t="s">
+        <v>384</v>
+      </c>
+      <c r="I38" t="s">
+        <v>312</v>
+      </c>
+      <c r="J38" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B39" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C39" s="89" t="str" cm="1">
+        <f t="array" ref="C39">UPPER(INDEX(_xlfn.TEXTSPLIT($F39, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D39" t="s">
+        <v>239</v>
+      </c>
+      <c r="E39" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" t="s">
+        <v>266</v>
+      </c>
+      <c r="G39" s="99" t="s">
+        <v>373</v>
+      </c>
+      <c r="H39" s="99" t="s">
+        <v>385</v>
+      </c>
+      <c r="I39" t="s">
+        <v>312</v>
+      </c>
+      <c r="J39" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B40" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C40" s="89" t="str" cm="1">
+        <f t="array" ref="C40">UPPER(INDEX(_xlfn.TEXTSPLIT($F40, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D40" t="s">
+        <v>239</v>
+      </c>
+      <c r="E40" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" t="s">
+        <v>266</v>
+      </c>
+      <c r="G40" s="99" t="s">
+        <v>374</v>
+      </c>
+      <c r="H40" s="99" t="s">
+        <v>386</v>
+      </c>
+      <c r="I40" t="s">
+        <v>312</v>
+      </c>
+      <c r="J40" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B41" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C41" s="89" t="str" cm="1">
+        <f t="array" ref="C41">UPPER(INDEX(_xlfn.TEXTSPLIT($F41, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D41" t="s">
+        <v>239</v>
+      </c>
+      <c r="E41" t="s">
+        <v>24</v>
+      </c>
+      <c r="F41" t="s">
+        <v>266</v>
+      </c>
+      <c r="G41" s="99" t="s">
+        <v>375</v>
+      </c>
+      <c r="H41" s="99" t="s">
+        <v>387</v>
+      </c>
+      <c r="I41" t="s">
+        <v>312</v>
+      </c>
+      <c r="J41" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B42" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C42" s="89" t="str" cm="1">
+        <f t="array" ref="C42">UPPER(INDEX(_xlfn.TEXTSPLIT($F42, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D42" t="s">
+        <v>239</v>
+      </c>
+      <c r="E42" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" t="s">
+        <v>266</v>
+      </c>
+      <c r="G42" s="99" t="s">
+        <v>376</v>
+      </c>
+      <c r="H42" s="99" t="s">
+        <v>388</v>
+      </c>
+      <c r="I42" t="s">
+        <v>312</v>
+      </c>
+      <c r="J42" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B43" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C43" s="89" t="str" cm="1">
+        <f t="array" ref="C43">UPPER(INDEX(_xlfn.TEXTSPLIT($F43, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D43" t="s">
+        <v>239</v>
+      </c>
+      <c r="E43" t="s">
+        <v>24</v>
+      </c>
+      <c r="F43" t="s">
+        <v>266</v>
+      </c>
+      <c r="G43" s="99" t="s">
+        <v>377</v>
+      </c>
+      <c r="H43" s="99" t="s">
+        <v>389</v>
+      </c>
+      <c r="I43" t="s">
+        <v>312</v>
+      </c>
+      <c r="J43" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B44" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C44" s="89" t="str" cm="1">
+        <f t="array" ref="C44">UPPER(INDEX(_xlfn.TEXTSPLIT($F44, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D44" t="s">
+        <v>239</v>
+      </c>
+      <c r="E44" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" t="s">
+        <v>266</v>
+      </c>
+      <c r="G44" s="99" t="s">
+        <v>378</v>
+      </c>
+      <c r="H44" s="99" t="s">
+        <v>390</v>
+      </c>
+      <c r="I44" t="s">
+        <v>312</v>
+      </c>
+      <c r="J44" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B45" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C45" s="89" t="str" cm="1">
+        <f t="array" ref="C45">UPPER(INDEX(_xlfn.TEXTSPLIT($F45, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D45" t="s">
+        <v>239</v>
+      </c>
+      <c r="E45" t="s">
+        <v>24</v>
+      </c>
+      <c r="F45" t="s">
+        <v>266</v>
+      </c>
+      <c r="G45" s="99" t="s">
+        <v>379</v>
+      </c>
+      <c r="H45" s="99" t="s">
+        <v>391</v>
+      </c>
+      <c r="I45" t="s">
+        <v>312</v>
+      </c>
+      <c r="J45" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B46" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C46" s="89" t="str" cm="1">
+        <f t="array" ref="C46">UPPER(INDEX(_xlfn.TEXTSPLIT($F46, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D46" t="s">
+        <v>239</v>
+      </c>
+      <c r="E46" t="s">
+        <v>24</v>
+      </c>
+      <c r="F46" t="s">
+        <v>266</v>
+      </c>
+      <c r="G46" s="99" t="s">
+        <v>380</v>
+      </c>
+      <c r="H46" s="99" t="s">
+        <v>392</v>
+      </c>
+      <c r="I46" t="s">
+        <v>312</v>
+      </c>
+      <c r="J46" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B47" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C47" s="89" t="str" cm="1">
+        <f t="array" ref="C47">UPPER(INDEX(_xlfn.TEXTSPLIT($F47, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D47" t="s">
+        <v>239</v>
+      </c>
+      <c r="E47" t="s">
+        <v>24</v>
+      </c>
+      <c r="F47" t="s">
+        <v>266</v>
+      </c>
+      <c r="G47" s="99" t="s">
+        <v>403</v>
+      </c>
+      <c r="H47" s="99" t="s">
+        <v>393</v>
+      </c>
+      <c r="I47" t="s">
+        <v>312</v>
+      </c>
+      <c r="J47" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B48" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C48" s="89" t="str" cm="1">
+        <f t="array" ref="C48">UPPER(INDEX(_xlfn.TEXTSPLIT($F48, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D48" t="s">
+        <v>239</v>
+      </c>
+      <c r="E48" t="s">
+        <v>24</v>
+      </c>
+      <c r="F48" t="s">
+        <v>266</v>
+      </c>
+      <c r="G48" s="99" t="s">
+        <v>404</v>
+      </c>
+      <c r="H48" s="99" t="s">
+        <v>394</v>
+      </c>
+      <c r="I48" t="s">
+        <v>312</v>
+      </c>
+      <c r="J48" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B49" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C49" s="89" t="str" cm="1">
+        <f t="array" ref="C49">UPPER(INDEX(_xlfn.TEXTSPLIT($F49, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D49" t="s">
+        <v>239</v>
+      </c>
+      <c r="E49" t="s">
+        <v>24</v>
+      </c>
+      <c r="F49" t="s">
+        <v>266</v>
+      </c>
+      <c r="G49" s="99" t="s">
+        <v>405</v>
+      </c>
+      <c r="H49" s="99" t="s">
+        <v>395</v>
+      </c>
+      <c r="I49" t="s">
+        <v>312</v>
+      </c>
+      <c r="J49" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B50" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C50" s="89" t="str" cm="1">
+        <f t="array" ref="C50">UPPER(INDEX(_xlfn.TEXTSPLIT($F50, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D50" t="s">
+        <v>239</v>
+      </c>
+      <c r="E50" t="s">
+        <v>24</v>
+      </c>
+      <c r="F50" t="s">
+        <v>266</v>
+      </c>
+      <c r="G50" s="99" t="s">
+        <v>406</v>
+      </c>
+      <c r="H50" s="99" t="s">
+        <v>396</v>
+      </c>
+      <c r="I50" t="s">
+        <v>312</v>
+      </c>
+      <c r="J50" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B51" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C51" s="89" t="str" cm="1">
+        <f t="array" ref="C51">UPPER(INDEX(_xlfn.TEXTSPLIT($F51, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D51" t="s">
+        <v>239</v>
+      </c>
+      <c r="E51" t="s">
+        <v>24</v>
+      </c>
+      <c r="F51" t="s">
+        <v>266</v>
+      </c>
+      <c r="G51" s="99" t="s">
+        <v>407</v>
+      </c>
+      <c r="H51" s="99" t="s">
+        <v>397</v>
+      </c>
+      <c r="I51" t="s">
+        <v>312</v>
+      </c>
+      <c r="J51" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B52" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C52" s="89" t="str" cm="1">
+        <f t="array" ref="C52">UPPER(INDEX(_xlfn.TEXTSPLIT($F52, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D52" t="s">
+        <v>239</v>
+      </c>
+      <c r="E52" t="s">
+        <v>24</v>
+      </c>
+      <c r="F52" t="s">
+        <v>266</v>
+      </c>
+      <c r="G52" s="99" t="s">
+        <v>408</v>
+      </c>
+      <c r="H52" s="99" t="s">
+        <v>398</v>
+      </c>
+      <c r="I52" t="s">
+        <v>312</v>
+      </c>
+      <c r="J52" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B53" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C53" s="89" t="str" cm="1">
+        <f t="array" ref="C53">UPPER(INDEX(_xlfn.TEXTSPLIT($F53, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D53" t="s">
+        <v>239</v>
+      </c>
+      <c r="E53" t="s">
+        <v>24</v>
+      </c>
+      <c r="F53" t="s">
+        <v>266</v>
+      </c>
+      <c r="G53" s="99" t="s">
+        <v>409</v>
+      </c>
+      <c r="H53" s="99" t="s">
+        <v>399</v>
+      </c>
+      <c r="I53" t="s">
+        <v>312</v>
+      </c>
+      <c r="J53" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B54" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C54" s="89" t="str" cm="1">
+        <f t="array" ref="C54">UPPER(INDEX(_xlfn.TEXTSPLIT($F54, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D54" t="s">
+        <v>239</v>
+      </c>
+      <c r="E54" t="s">
+        <v>24</v>
+      </c>
+      <c r="F54" t="s">
+        <v>266</v>
+      </c>
+      <c r="G54" s="99" t="s">
+        <v>410</v>
+      </c>
+      <c r="H54" s="99" t="s">
+        <v>400</v>
+      </c>
+      <c r="I54" t="s">
+        <v>312</v>
+      </c>
+      <c r="J54" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B55" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C55" s="89" t="str" cm="1">
+        <f t="array" ref="C55">UPPER(INDEX(_xlfn.TEXTSPLIT($F55, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D55" t="s">
+        <v>239</v>
+      </c>
+      <c r="E55" t="s">
+        <v>24</v>
+      </c>
+      <c r="F55" t="s">
+        <v>266</v>
+      </c>
+      <c r="G55" s="99" t="s">
+        <v>411</v>
+      </c>
+      <c r="H55" s="99" t="s">
+        <v>401</v>
+      </c>
+      <c r="I55" t="s">
+        <v>312</v>
+      </c>
+      <c r="J55" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B56" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C56" s="89" t="str" cm="1">
+        <f t="array" ref="C56">UPPER(INDEX(_xlfn.TEXTSPLIT($F56, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D56" t="s">
+        <v>239</v>
+      </c>
+      <c r="E56" t="s">
+        <v>24</v>
+      </c>
+      <c r="F56" t="s">
+        <v>266</v>
+      </c>
+      <c r="G56" s="99" t="s">
+        <v>412</v>
+      </c>
+      <c r="H56" s="99" t="s">
+        <v>402</v>
+      </c>
+      <c r="I56" t="s">
+        <v>312</v>
+      </c>
+      <c r="J56" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B57" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C57" s="89" t="str" cm="1">
+        <f t="array" ref="C57">UPPER(INDEX(_xlfn.TEXTSPLIT($F57, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D57" t="s">
+        <v>239</v>
+      </c>
+      <c r="E57" t="s">
+        <v>24</v>
+      </c>
+      <c r="F57" t="s">
+        <v>266</v>
+      </c>
+      <c r="G57" t="s">
+        <v>276</v>
+      </c>
+      <c r="H57" t="s">
+        <v>301</v>
+      </c>
+      <c r="I57" t="s">
+        <v>312</v>
+      </c>
+      <c r="J57" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B58" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C58" s="89" t="str" cm="1">
+        <f t="array" ref="C58">UPPER(INDEX(_xlfn.TEXTSPLIT($F58, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D58" t="s">
+        <v>239</v>
+      </c>
+      <c r="E58" t="s">
+        <v>24</v>
+      </c>
+      <c r="F58" t="s">
+        <v>266</v>
+      </c>
+      <c r="G58" t="s">
+        <v>277</v>
+      </c>
+      <c r="H58" t="s">
+        <v>302</v>
+      </c>
+      <c r="I58" t="s">
+        <v>312</v>
+      </c>
+      <c r="J58" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B59" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C59" s="89" t="str" cm="1">
+        <f t="array" ref="C59">UPPER(INDEX(_xlfn.TEXTSPLIT($F59, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D59" t="s">
+        <v>239</v>
+      </c>
+      <c r="E59" t="s">
+        <v>24</v>
+      </c>
+      <c r="F59" t="s">
+        <v>266</v>
+      </c>
+      <c r="G59" t="s">
+        <v>278</v>
+      </c>
+      <c r="H59" t="s">
+        <v>303</v>
+      </c>
+      <c r="I59" t="s">
+        <v>312</v>
+      </c>
+      <c r="J59" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B60" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C60" s="89" t="str" cm="1">
+        <f t="array" ref="C60">UPPER(INDEX(_xlfn.TEXTSPLIT($F60, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D60" t="s">
+        <v>239</v>
+      </c>
+      <c r="E60" t="s">
+        <v>24</v>
+      </c>
+      <c r="F60" t="s">
+        <v>266</v>
+      </c>
+      <c r="G60" t="s">
+        <v>279</v>
+      </c>
+      <c r="H60" t="s">
+        <v>304</v>
+      </c>
+      <c r="I60" t="s">
+        <v>312</v>
+      </c>
+      <c r="J60" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B61" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C61" s="89" t="str" cm="1">
+        <f t="array" ref="C61">UPPER(INDEX(_xlfn.TEXTSPLIT($F61, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D61" t="s">
+        <v>239</v>
+      </c>
+      <c r="E61" t="s">
+        <v>24</v>
+      </c>
+      <c r="F61" t="s">
+        <v>266</v>
+      </c>
+      <c r="G61" t="s">
+        <v>280</v>
+      </c>
+      <c r="H61" t="s">
+        <v>305</v>
+      </c>
+      <c r="I61" t="s">
+        <v>312</v>
+      </c>
+      <c r="J61" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B62" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C62" s="89" t="str" cm="1">
+        <f t="array" ref="C62">UPPER(INDEX(_xlfn.TEXTSPLIT($F62, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D62" t="s">
+        <v>239</v>
+      </c>
+      <c r="E62" t="s">
+        <v>24</v>
+      </c>
+      <c r="F62" t="s">
+        <v>266</v>
+      </c>
+      <c r="G62" t="s">
+        <v>281</v>
+      </c>
+      <c r="H62" t="s">
+        <v>306</v>
+      </c>
+      <c r="I62" t="s">
+        <v>312</v>
+      </c>
+      <c r="J62" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B63" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C63" s="89" t="str" cm="1">
+        <f t="array" ref="C63">UPPER(INDEX(_xlfn.TEXTSPLIT($F63, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D63" t="s">
+        <v>239</v>
+      </c>
+      <c r="E63" t="s">
+        <v>24</v>
+      </c>
+      <c r="F63" t="s">
+        <v>266</v>
+      </c>
+      <c r="G63" t="s">
+        <v>282</v>
+      </c>
+      <c r="H63" t="s">
+        <v>307</v>
+      </c>
+      <c r="I63" t="s">
+        <v>312</v>
+      </c>
+      <c r="J63" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B64" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C64" s="89" t="str" cm="1">
+        <f t="array" ref="C64">UPPER(INDEX(_xlfn.TEXTSPLIT($F64, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D64" t="s">
+        <v>239</v>
+      </c>
+      <c r="E64" t="s">
+        <v>24</v>
+      </c>
+      <c r="F64" t="s">
+        <v>266</v>
+      </c>
+      <c r="G64" t="s">
+        <v>283</v>
+      </c>
+      <c r="H64" t="s">
+        <v>308</v>
+      </c>
+      <c r="I64" t="s">
+        <v>312</v>
+      </c>
+      <c r="J64" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B65" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C65" s="89" t="str" cm="1">
+        <f t="array" ref="C65">UPPER(INDEX(_xlfn.TEXTSPLIT($F65, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D65" t="s">
+        <v>239</v>
+      </c>
+      <c r="E65" t="s">
+        <v>24</v>
+      </c>
+      <c r="F65" t="s">
+        <v>266</v>
+      </c>
+      <c r="G65" t="s">
+        <v>284</v>
+      </c>
+      <c r="H65" t="s">
+        <v>309</v>
+      </c>
+      <c r="I65" t="s">
+        <v>312</v>
+      </c>
+      <c r="J65" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B66" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="C66" s="89" t="str" cm="1">
+        <f t="array" ref="C66">UPPER(INDEX(_xlfn.TEXTSPLIT($F66, "-"), 3))</f>
+        <v>EXT</v>
+      </c>
+      <c r="D66" t="s">
+        <v>239</v>
+      </c>
+      <c r="E66" t="s">
+        <v>24</v>
+      </c>
+      <c r="F66" t="s">
+        <v>266</v>
+      </c>
+      <c r="G66" t="s">
+        <v>285</v>
+      </c>
+      <c r="H66" t="s">
+        <v>310</v>
+      </c>
+      <c r="I66" t="s">
+        <v>312</v>
+      </c>
+      <c r="J66" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B67" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C67" s="102" t="str" cm="1">
+        <f t="array" ref="C67">UPPER(INDEX(_xlfn.TEXTSPLIT($F67, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D67" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E67" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F67" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G67" s="103" t="s">
+        <v>270</v>
+      </c>
+      <c r="H67" s="103" t="s">
+        <v>295</v>
+      </c>
+      <c r="I67" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J67" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B68" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C68" s="102" t="str" cm="1">
+        <f t="array" ref="C68">UPPER(INDEX(_xlfn.TEXTSPLIT($F68, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D68" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E68" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F68" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G68" s="103" t="s">
+        <v>271</v>
+      </c>
+      <c r="H68" s="103" t="s">
+        <v>296</v>
+      </c>
+      <c r="I68" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J68" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B69" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C69" s="102" t="str" cm="1">
+        <f t="array" ref="C69">UPPER(INDEX(_xlfn.TEXTSPLIT($F69, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D69" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E69" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F69" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G69" s="103" t="s">
+        <v>272</v>
+      </c>
+      <c r="H69" s="103" t="s">
+        <v>297</v>
+      </c>
+      <c r="I69" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J69" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B70" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C70" s="102" t="str" cm="1">
+        <f t="array" ref="C70">UPPER(INDEX(_xlfn.TEXTSPLIT($F70, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D70" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E70" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F70" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G70" s="103" t="s">
+        <v>273</v>
+      </c>
+      <c r="H70" s="103" t="s">
+        <v>298</v>
+      </c>
+      <c r="I70" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J70" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B71" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C71" s="102" t="str" cm="1">
+        <f t="array" ref="C71">UPPER(INDEX(_xlfn.TEXTSPLIT($F71, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D71" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E71" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F71" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G71" s="103" t="s">
+        <v>274</v>
+      </c>
+      <c r="H71" s="103" t="s">
+        <v>299</v>
+      </c>
+      <c r="I71" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J71" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B72" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C72" s="102" t="str" cm="1">
+        <f t="array" ref="C72">UPPER(INDEX(_xlfn.TEXTSPLIT($F72, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D72" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E72" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G72" s="103" t="s">
+        <v>413</v>
+      </c>
+      <c r="H72" s="103" t="s">
+        <v>300</v>
+      </c>
+      <c r="I72" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J72" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B73" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C73" s="102" t="str" cm="1">
+        <f t="array" ref="C73">UPPER(INDEX(_xlfn.TEXTSPLIT($F73, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D73" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E73" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F73" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G73" s="103" t="s">
+        <v>315</v>
+      </c>
+      <c r="H73" s="103" t="s">
+        <v>316</v>
+      </c>
+      <c r="I73" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J73" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B74" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C74" s="102" t="str" cm="1">
+        <f t="array" ref="C74">UPPER(INDEX(_xlfn.TEXTSPLIT($F74, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D74" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E74" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F74" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G74" s="103" t="s">
+        <v>414</v>
+      </c>
+      <c r="H74" s="103" t="s">
+        <v>415</v>
+      </c>
+      <c r="I74" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J74" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B75" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C75" s="102" t="str" cm="1">
+        <f t="array" ref="C75">UPPER(INDEX(_xlfn.TEXTSPLIT($F75, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D75" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E75" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F75" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G75" s="103" t="s">
+        <v>286</v>
+      </c>
+      <c r="H75" s="103" t="s">
+        <v>416</v>
+      </c>
+      <c r="I75" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J75" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B76" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C76" s="102" t="str" cm="1">
+        <f t="array" ref="C76">UPPER(INDEX(_xlfn.TEXTSPLIT($F76, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D76" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E76" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F76" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G76" s="103" t="s">
+        <v>287</v>
+      </c>
+      <c r="H76" s="103" t="s">
+        <v>417</v>
+      </c>
+      <c r="I76" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J76" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B77" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C77" s="102" t="str" cm="1">
+        <f t="array" ref="C77">UPPER(INDEX(_xlfn.TEXTSPLIT($F77, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D77" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E77" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F77" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G77" s="103" t="s">
+        <v>288</v>
+      </c>
+      <c r="H77" s="103" t="s">
+        <v>418</v>
+      </c>
+      <c r="I77" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J77" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B78" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C78" s="102" t="str" cm="1">
+        <f t="array" ref="C78">UPPER(INDEX(_xlfn.TEXTSPLIT($F78, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D78" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E78" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F78" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G78" s="103" t="s">
+        <v>289</v>
+      </c>
+      <c r="H78" s="103" t="s">
+        <v>419</v>
+      </c>
+      <c r="I78" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J78" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B79" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C79" s="102" t="str" cm="1">
+        <f t="array" ref="C79">UPPER(INDEX(_xlfn.TEXTSPLIT($F79, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D79" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E79" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F79" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G79" s="103" t="s">
+        <v>290</v>
+      </c>
+      <c r="H79" s="103" t="s">
+        <v>420</v>
+      </c>
+      <c r="I79" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J79" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B80" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C80" s="102" t="str" cm="1">
+        <f t="array" ref="C80">UPPER(INDEX(_xlfn.TEXTSPLIT($F80, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D80" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E80" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F80" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G80" s="103" t="s">
+        <v>291</v>
+      </c>
+      <c r="H80" s="103" t="s">
+        <v>421</v>
+      </c>
+      <c r="I80" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J80" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B81" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C81" s="102" t="str" cm="1">
+        <f t="array" ref="C81">UPPER(INDEX(_xlfn.TEXTSPLIT($F81, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D81" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E81" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F81" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G81" s="103" t="s">
+        <v>292</v>
+      </c>
+      <c r="H81" s="103" t="s">
+        <v>422</v>
+      </c>
+      <c r="I81" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J81" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B82" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C82" s="102" t="str" cm="1">
+        <f t="array" ref="C82">UPPER(INDEX(_xlfn.TEXTSPLIT($F82, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D82" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E82" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F82" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G82" s="103" t="s">
+        <v>293</v>
+      </c>
+      <c r="H82" s="103" t="s">
+        <v>423</v>
+      </c>
+      <c r="I82" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J82" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B83" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C83" s="102" t="str" cm="1">
+        <f t="array" ref="C83">UPPER(INDEX(_xlfn.TEXTSPLIT($F83, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D83" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E83" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F83" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G83" s="103" t="s">
+        <v>431</v>
+      </c>
+      <c r="H83" s="103" t="s">
+        <v>424</v>
+      </c>
+      <c r="I83" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J83" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B84" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C84" s="102" t="str" cm="1">
+        <f t="array" ref="C84">UPPER(INDEX(_xlfn.TEXTSPLIT($F84, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D84" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E84" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F84" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G84" s="103" t="s">
+        <v>432</v>
+      </c>
+      <c r="H84" s="103" t="s">
+        <v>425</v>
+      </c>
+      <c r="I84" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J84" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B85" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C85" s="102" t="str" cm="1">
+        <f t="array" ref="C85">UPPER(INDEX(_xlfn.TEXTSPLIT($F85, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D85" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E85" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F85" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G85" s="103" t="s">
+        <v>433</v>
+      </c>
+      <c r="H85" s="103" t="s">
+        <v>426</v>
+      </c>
+      <c r="I85" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J85" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B86" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C86" s="102" t="str" cm="1">
+        <f t="array" ref="C86">UPPER(INDEX(_xlfn.TEXTSPLIT($F86, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D86" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E86" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F86" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G86" s="103" t="s">
+        <v>434</v>
+      </c>
+      <c r="H86" s="103" t="s">
+        <v>427</v>
+      </c>
+      <c r="I86" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J86" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B87" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C87" s="102" t="str" cm="1">
+        <f t="array" ref="C87">UPPER(INDEX(_xlfn.TEXTSPLIT($F87, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D87" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E87" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F87" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G87" s="103" t="s">
+        <v>435</v>
+      </c>
+      <c r="H87" s="103" t="s">
+        <v>428</v>
+      </c>
+      <c r="I87" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J87" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B88" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C88" s="102" t="str" cm="1">
+        <f t="array" ref="C88">UPPER(INDEX(_xlfn.TEXTSPLIT($F88, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D88" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E88" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F88" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G88" s="103" t="s">
+        <v>436</v>
+      </c>
+      <c r="H88" s="103" t="s">
+        <v>429</v>
+      </c>
+      <c r="I88" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J88" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B89" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C89" s="102" t="str" cm="1">
+        <f t="array" ref="C89">UPPER(INDEX(_xlfn.TEXTSPLIT($F89, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D89" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E89" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F89" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G89" s="103" t="s">
+        <v>437</v>
+      </c>
+      <c r="H89" s="103" t="s">
+        <v>430</v>
+      </c>
+      <c r="I89" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J89" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B90" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C90" s="102" t="str" cm="1">
+        <f t="array" ref="C90">UPPER(INDEX(_xlfn.TEXTSPLIT($F90, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D90" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E90" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F90" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G90" s="103" t="s">
+        <v>276</v>
+      </c>
+      <c r="H90" s="103" t="s">
+        <v>301</v>
+      </c>
+      <c r="I90" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J90" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B91" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C91" s="102" t="str" cm="1">
+        <f t="array" ref="C91">UPPER(INDEX(_xlfn.TEXTSPLIT($F91, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D91" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E91" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F91" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G91" s="103" t="s">
+        <v>277</v>
+      </c>
+      <c r="H91" s="103" t="s">
+        <v>302</v>
+      </c>
+      <c r="I91" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J91" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B92" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C92" s="102" t="str" cm="1">
+        <f t="array" ref="C92">UPPER(INDEX(_xlfn.TEXTSPLIT($F92, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D92" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E92" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F92" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G92" s="103" t="s">
+        <v>278</v>
+      </c>
+      <c r="H92" s="103" t="s">
+        <v>303</v>
+      </c>
+      <c r="I92" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J92" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B93" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C93" s="102" t="str" cm="1">
+        <f t="array" ref="C93">UPPER(INDEX(_xlfn.TEXTSPLIT($F93, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D93" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E93" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F93" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G93" s="103" t="s">
+        <v>279</v>
+      </c>
+      <c r="H93" s="103" t="s">
+        <v>304</v>
+      </c>
+      <c r="I93" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J93" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B94" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C94" s="102" t="str" cm="1">
+        <f t="array" ref="C94">UPPER(INDEX(_xlfn.TEXTSPLIT($F94, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D94" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E94" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F94" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G94" s="103" t="s">
+        <v>280</v>
+      </c>
+      <c r="H94" s="103" t="s">
+        <v>305</v>
+      </c>
+      <c r="I94" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J94" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B95" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C95" s="102" t="str" cm="1">
+        <f t="array" ref="C95">UPPER(INDEX(_xlfn.TEXTSPLIT($F95, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D95" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E95" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F95" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G95" s="103" t="s">
+        <v>281</v>
+      </c>
+      <c r="H95" s="103" t="s">
+        <v>306</v>
+      </c>
+      <c r="I95" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J95" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B96" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C96" s="102" t="str" cm="1">
+        <f t="array" ref="C96">UPPER(INDEX(_xlfn.TEXTSPLIT($F96, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D96" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E96" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F96" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G96" s="103" t="s">
+        <v>282</v>
+      </c>
+      <c r="H96" s="103" t="s">
+        <v>307</v>
+      </c>
+      <c r="I96" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J96" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B97" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C97" s="102" t="str" cm="1">
+        <f t="array" ref="C97">UPPER(INDEX(_xlfn.TEXTSPLIT($F97, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D97" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E97" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F97" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G97" s="103" t="s">
+        <v>283</v>
+      </c>
+      <c r="H97" s="103" t="s">
+        <v>308</v>
+      </c>
+      <c r="I97" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J97" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B98" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C98" s="102" t="str" cm="1">
+        <f t="array" ref="C98">UPPER(INDEX(_xlfn.TEXTSPLIT($F98, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D98" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E98" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F98" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G98" s="103" t="s">
+        <v>284</v>
+      </c>
+      <c r="H98" s="103" t="s">
+        <v>309</v>
+      </c>
+      <c r="I98" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J98" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B99" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C99" s="102" t="str" cm="1">
+        <f t="array" ref="C99">UPPER(INDEX(_xlfn.TEXTSPLIT($F99, "-"), 3))</f>
+        <v>INT</v>
+      </c>
+      <c r="D99" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E99" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F99" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G99" s="103" t="s">
+        <v>285</v>
+      </c>
+      <c r="H99" s="103" t="s">
+        <v>310</v>
+      </c>
+      <c r="I99" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="J99" s="103" t="s">
+        <v>314</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16413697-3740-4555-9E10-C39D5D5DCDBB}">
   <dimension ref="A1:P36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -6973,7 +10850,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD1A3252-EF11-4361-BCDB-10417C7A0940}">
   <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -7392,7 +11269,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33E6DC6D-4CAC-4686-B15B-DE2A4B4502D8}">
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -7635,345 +11512,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BC862D-08E7-4593-9A34-4D2B508CF25B}">
-  <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="58" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" s="58" t="s">
-        <v>136</v>
-      </c>
-      <c r="D1" s="58" t="s">
-        <v>111</v>
-      </c>
-      <c r="E1" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="F1" s="59" t="s">
-        <v>137</v>
-      </c>
-      <c r="G1" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="H1" s="58" t="s">
-        <v>120</v>
-      </c>
-      <c r="I1" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="J1" s="59" t="s">
-        <v>123</v>
-      </c>
-      <c r="K1" s="59" t="s">
-        <v>141</v>
-      </c>
-      <c r="L1" s="59" t="s">
-        <v>142</v>
-      </c>
-      <c r="M1" s="59" t="s">
-        <v>157</v>
-      </c>
-      <c r="N1" s="59" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="56" t="s">
-        <v>121</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>148</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>154</v>
-      </c>
-      <c r="E2" s="56" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" s="56">
-        <v>80</v>
-      </c>
-      <c r="G2" s="56" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="I2" s="56">
-        <v>80</v>
-      </c>
-      <c r="J2" s="56" t="s">
-        <v>124</v>
-      </c>
-      <c r="K2" s="56">
-        <v>4</v>
-      </c>
-      <c r="L2" s="56" t="s">
-        <v>143</v>
-      </c>
-      <c r="M2" s="56" t="b">
-        <v>1</v>
-      </c>
-      <c r="N2" s="56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="56" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="D3" s="56" t="s">
-        <v>154</v>
-      </c>
-      <c r="E3" s="56" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="56">
-        <v>8080</v>
-      </c>
-      <c r="G3" s="56" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="I3" s="56">
-        <v>8080</v>
-      </c>
-      <c r="J3" s="56" t="s">
-        <v>132</v>
-      </c>
-      <c r="K3" s="56">
-        <v>4</v>
-      </c>
-      <c r="L3" s="56" t="s">
-        <v>143</v>
-      </c>
-      <c r="M3" s="56" t="b">
-        <v>1</v>
-      </c>
-      <c r="N3" s="56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="56" t="s">
-        <v>134</v>
-      </c>
-      <c r="C4" s="56" t="s">
-        <v>150</v>
-      </c>
-      <c r="D4" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="E4" s="56" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" s="56">
-        <v>443</v>
-      </c>
-      <c r="G4" s="56" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="I4" s="56">
-        <v>443</v>
-      </c>
-      <c r="J4" s="56" t="s">
-        <v>127</v>
-      </c>
-      <c r="K4" s="56">
-        <v>4</v>
-      </c>
-      <c r="L4" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="M4" s="56" t="b">
-        <v>1</v>
-      </c>
-      <c r="N4" s="56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="56" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="56" t="s">
-        <v>151</v>
-      </c>
-      <c r="D5" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="E5" s="56" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" s="56">
-        <v>22</v>
-      </c>
-      <c r="G5" s="56" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="I5" s="56">
-        <v>22</v>
-      </c>
-      <c r="J5" s="56" t="s">
-        <v>156</v>
-      </c>
-      <c r="K5" s="56">
-        <v>4</v>
-      </c>
-      <c r="L5" s="56" t="s">
-        <v>153</v>
-      </c>
-      <c r="M5" s="56" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" s="56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="N6" s="1"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="N7" s="1"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="N8" s="1"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="N9" s="1"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="N10" s="1"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="N11" s="1"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8121,15 +11663,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8153,17 +11706,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C17A5ED-23AE-4882-ABB8-F85E501AFA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4BC459-5AE0-4496-BC06-A8F21438C160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="VM_Datadisk" sheetId="14" r:id="rId4"/>
     <sheet name="NSG" sheetId="2" r:id="rId5"/>
     <sheet name="UDR" sheetId="15" r:id="rId6"/>
-    <sheet name="NSG_Rule" sheetId="3" r:id="rId7"/>
+    <sheet name="NSG_Rule" sheetId="3" state="hidden" r:id="rId7"/>
     <sheet name="LB" sheetId="6" r:id="rId8"/>
     <sheet name="LB_Probe" sheetId="10" r:id="rId9"/>
     <sheet name="LB_Rule" sheetId="11" r:id="rId10"/>
@@ -3632,7 +3632,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3930,19 +3930,16 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6686,2972 +6683,2972 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B1" s="100" t="s">
+      <c r="B1" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="101" t="s">
+      <c r="C1" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="58" t="s">
         <v>107</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="E1" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="47" t="s">
+      <c r="F1" s="58" t="s">
         <v>269</v>
       </c>
-      <c r="G1" s="47" t="s">
+      <c r="G1" s="58" t="s">
         <v>268</v>
       </c>
-      <c r="H1" s="47" t="s">
+      <c r="H1" s="58" t="s">
         <v>294</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="I1" s="58" t="s">
         <v>311</v>
       </c>
-      <c r="J1" s="46" t="s">
+      <c r="J1" s="58" t="s">
         <v>313</v>
       </c>
       <c r="K1" s="46"/>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C2" s="89" t="str" cm="1">
+      <c r="B2" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2" s="96" t="str" cm="1">
         <f t="array" ref="C2">UPPER(INDEX(_xlfn.TEXTSPLIT($F2, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G2" s="99" t="s">
+      <c r="G2" s="100" t="s">
         <v>270</v>
       </c>
-      <c r="H2" s="99" t="s">
+      <c r="H2" s="100" t="s">
         <v>295</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B3" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C3" s="89" t="str" cm="1">
+      <c r="B3" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3" s="96" t="str" cm="1">
         <f t="array" ref="C3">UPPER(INDEX(_xlfn.TEXTSPLIT($F3, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G3" s="99" t="s">
+      <c r="G3" s="100" t="s">
         <v>271</v>
       </c>
-      <c r="H3" s="99" t="s">
+      <c r="H3" s="100" t="s">
         <v>296</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C4" s="89" t="str" cm="1">
+      <c r="B4" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C4" s="96" t="str" cm="1">
         <f t="array" ref="C4">UPPER(INDEX(_xlfn.TEXTSPLIT($F4, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G4" s="99" t="s">
+      <c r="G4" s="100" t="s">
         <v>272</v>
       </c>
-      <c r="H4" s="99" t="s">
+      <c r="H4" s="100" t="s">
         <v>297</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C5" s="89" t="str" cm="1">
+      <c r="B5" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C5" s="96" t="str" cm="1">
         <f t="array" ref="C5">UPPER(INDEX(_xlfn.TEXTSPLIT($F5, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G5" s="99" t="s">
+      <c r="G5" s="100" t="s">
         <v>273</v>
       </c>
-      <c r="H5" s="99" t="s">
+      <c r="H5" s="100" t="s">
         <v>298</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C6" s="89" t="str" cm="1">
+      <c r="B6" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C6" s="96" t="str" cm="1">
         <f t="array" ref="C6">UPPER(INDEX(_xlfn.TEXTSPLIT($F6, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G6" s="99" t="s">
+      <c r="G6" s="100" t="s">
         <v>274</v>
       </c>
-      <c r="H6" s="99" t="s">
+      <c r="H6" s="100" t="s">
         <v>299</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C7" s="89" t="str" cm="1">
+      <c r="B7" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C7" s="96" t="str" cm="1">
         <f t="array" ref="C7">UPPER(INDEX(_xlfn.TEXTSPLIT($F7, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G7" s="99" t="s">
+      <c r="G7" s="100" t="s">
         <v>275</v>
       </c>
-      <c r="H7" s="99" t="s">
+      <c r="H7" s="100" t="s">
         <v>300</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C8" s="89" t="str" cm="1">
+      <c r="B8" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C8" s="96" t="str" cm="1">
         <f t="array" ref="C8">UPPER(INDEX(_xlfn.TEXTSPLIT($F8, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G8" s="99" t="s">
+      <c r="G8" s="100" t="s">
         <v>315</v>
       </c>
-      <c r="H8" s="99" t="s">
+      <c r="H8" s="100" t="s">
         <v>316</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C9" s="89" t="str" cm="1">
+      <c r="B9" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="96" t="str" cm="1">
         <f t="array" ref="C9">UPPER(INDEX(_xlfn.TEXTSPLIT($F9, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G9" s="99" t="s">
+      <c r="G9" s="100" t="s">
         <v>317</v>
       </c>
-      <c r="H9" s="99" t="s">
+      <c r="H9" s="100" t="s">
         <v>344</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C10" s="89" t="str" cm="1">
+      <c r="B10" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C10" s="96" t="str" cm="1">
         <f t="array" ref="C10">UPPER(INDEX(_xlfn.TEXTSPLIT($F10, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G10" s="99" t="s">
+      <c r="G10" s="100" t="s">
         <v>318</v>
       </c>
-      <c r="H10" s="99" t="s">
+      <c r="H10" s="100" t="s">
         <v>345</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C11" s="89" t="str" cm="1">
+      <c r="B11" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C11" s="96" t="str" cm="1">
         <f t="array" ref="C11">UPPER(INDEX(_xlfn.TEXTSPLIT($F11, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G11" s="99" t="s">
+      <c r="G11" s="100" t="s">
         <v>319</v>
       </c>
-      <c r="H11" s="99" t="s">
+      <c r="H11" s="100" t="s">
         <v>346</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C12" s="89" t="str" cm="1">
+      <c r="B12" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="96" t="str" cm="1">
         <f t="array" ref="C12">UPPER(INDEX(_xlfn.TEXTSPLIT($F12, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G12" s="99" t="s">
+      <c r="G12" s="100" t="s">
         <v>320</v>
       </c>
-      <c r="H12" s="99" t="s">
+      <c r="H12" s="100" t="s">
         <v>347</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C13" s="89" t="str" cm="1">
+      <c r="B13" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="96" t="str" cm="1">
         <f t="array" ref="C13">UPPER(INDEX(_xlfn.TEXTSPLIT($F13, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G13" s="99" t="s">
+      <c r="G13" s="100" t="s">
         <v>321</v>
       </c>
-      <c r="H13" s="99" t="s">
+      <c r="H13" s="100" t="s">
         <v>348</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C14" s="89" t="str" cm="1">
+      <c r="B14" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C14" s="96" t="str" cm="1">
         <f t="array" ref="C14">UPPER(INDEX(_xlfn.TEXTSPLIT($F14, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G14" s="99" t="s">
+      <c r="G14" s="100" t="s">
         <v>322</v>
       </c>
-      <c r="H14" s="99" t="s">
+      <c r="H14" s="100" t="s">
         <v>349</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C15" s="89" t="str" cm="1">
+      <c r="B15" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C15" s="96" t="str" cm="1">
         <f t="array" ref="C15">UPPER(INDEX(_xlfn.TEXTSPLIT($F15, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G15" s="99" t="s">
+      <c r="G15" s="100" t="s">
         <v>323</v>
       </c>
-      <c r="H15" s="99" t="s">
+      <c r="H15" s="100" t="s">
         <v>350</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C16" s="89" t="str" cm="1">
+      <c r="B16" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C16" s="96" t="str" cm="1">
         <f t="array" ref="C16">UPPER(INDEX(_xlfn.TEXTSPLIT($F16, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G16" s="99" t="s">
+      <c r="G16" s="100" t="s">
         <v>324</v>
       </c>
-      <c r="H16" s="99" t="s">
+      <c r="H16" s="100" t="s">
         <v>351</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C17" s="89" t="str" cm="1">
+      <c r="B17" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C17" s="96" t="str" cm="1">
         <f t="array" ref="C17">UPPER(INDEX(_xlfn.TEXTSPLIT($F17, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G17" s="99" t="s">
+      <c r="G17" s="100" t="s">
         <v>325</v>
       </c>
-      <c r="H17" s="99" t="s">
+      <c r="H17" s="100" t="s">
         <v>352</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C18" s="89" t="str" cm="1">
+      <c r="B18" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C18" s="96" t="str" cm="1">
         <f t="array" ref="C18">UPPER(INDEX(_xlfn.TEXTSPLIT($F18, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G18" s="99" t="s">
+      <c r="G18" s="100" t="s">
         <v>326</v>
       </c>
-      <c r="H18" s="99" t="s">
+      <c r="H18" s="100" t="s">
         <v>353</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C19" s="89" t="str" cm="1">
+      <c r="B19" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C19" s="96" t="str" cm="1">
         <f t="array" ref="C19">UPPER(INDEX(_xlfn.TEXTSPLIT($F19, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G19" s="99" t="s">
+      <c r="G19" s="100" t="s">
         <v>327</v>
       </c>
-      <c r="H19" s="99" t="s">
+      <c r="H19" s="100" t="s">
         <v>354</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C20" s="89" t="str" cm="1">
+      <c r="B20" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C20" s="96" t="str" cm="1">
         <f t="array" ref="C20">UPPER(INDEX(_xlfn.TEXTSPLIT($F20, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G20" s="99" t="s">
+      <c r="G20" s="100" t="s">
         <v>328</v>
       </c>
-      <c r="H20" s="99" t="s">
+      <c r="H20" s="100" t="s">
         <v>355</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C21" s="89" t="str" cm="1">
+      <c r="B21" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C21" s="96" t="str" cm="1">
         <f t="array" ref="C21">UPPER(INDEX(_xlfn.TEXTSPLIT($F21, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G21" s="99" t="s">
+      <c r="G21" s="100" t="s">
         <v>329</v>
       </c>
-      <c r="H21" s="99" t="s">
+      <c r="H21" s="100" t="s">
         <v>369</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C22" s="89" t="str" cm="1">
+      <c r="B22" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C22" s="96" t="str" cm="1">
         <f t="array" ref="C22">UPPER(INDEX(_xlfn.TEXTSPLIT($F22, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G22" s="99" t="s">
+      <c r="G22" s="100" t="s">
         <v>330</v>
       </c>
-      <c r="H22" s="99" t="s">
+      <c r="H22" s="100" t="s">
         <v>356</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C23" s="89" t="str" cm="1">
+      <c r="B23" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C23" s="96" t="str" cm="1">
         <f t="array" ref="C23">UPPER(INDEX(_xlfn.TEXTSPLIT($F23, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G23" s="99" t="s">
+      <c r="G23" s="100" t="s">
         <v>331</v>
       </c>
-      <c r="H23" s="99" t="s">
+      <c r="H23" s="100" t="s">
         <v>357</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C24" s="89" t="str" cm="1">
+      <c r="B24" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C24" s="96" t="str" cm="1">
         <f t="array" ref="C24">UPPER(INDEX(_xlfn.TEXTSPLIT($F24, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G24" s="99" t="s">
+      <c r="G24" s="100" t="s">
         <v>332</v>
       </c>
-      <c r="H24" s="99" t="s">
+      <c r="H24" s="100" t="s">
         <v>358</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C25" s="89" t="str" cm="1">
+      <c r="B25" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C25" s="96" t="str" cm="1">
         <f t="array" ref="C25">UPPER(INDEX(_xlfn.TEXTSPLIT($F25, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G25" s="99" t="s">
+      <c r="G25" s="100" t="s">
         <v>333</v>
       </c>
-      <c r="H25" s="99" t="s">
+      <c r="H25" s="100" t="s">
         <v>359</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C26" s="89" t="str" cm="1">
+      <c r="B26" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C26" s="96" t="str" cm="1">
         <f t="array" ref="C26">UPPER(INDEX(_xlfn.TEXTSPLIT($F26, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G26" s="99" t="s">
+      <c r="G26" s="100" t="s">
         <v>334</v>
       </c>
-      <c r="H26" s="99" t="s">
+      <c r="H26" s="100" t="s">
         <v>360</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C27" s="89" t="str" cm="1">
+      <c r="B27" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C27" s="96" t="str" cm="1">
         <f t="array" ref="C27">UPPER(INDEX(_xlfn.TEXTSPLIT($F27, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G27" s="99" t="s">
+      <c r="G27" s="100" t="s">
         <v>335</v>
       </c>
-      <c r="H27" s="99" t="s">
+      <c r="H27" s="100" t="s">
         <v>361</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B28" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C28" s="89" t="str" cm="1">
+      <c r="B28" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C28" s="96" t="str" cm="1">
         <f t="array" ref="C28">UPPER(INDEX(_xlfn.TEXTSPLIT($F28, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G28" s="99" t="s">
+      <c r="G28" s="100" t="s">
         <v>336</v>
       </c>
-      <c r="H28" s="99" t="s">
+      <c r="H28" s="100" t="s">
         <v>362</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B29" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C29" s="89" t="str" cm="1">
+      <c r="B29" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C29" s="96" t="str" cm="1">
         <f t="array" ref="C29">UPPER(INDEX(_xlfn.TEXTSPLIT($F29, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G29" s="99" t="s">
+      <c r="G29" s="100" t="s">
         <v>337</v>
       </c>
-      <c r="H29" s="99" t="s">
+      <c r="H29" s="100" t="s">
         <v>363</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B30" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C30" s="89" t="str" cm="1">
+      <c r="B30" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C30" s="96" t="str" cm="1">
         <f t="array" ref="C30">UPPER(INDEX(_xlfn.TEXTSPLIT($F30, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G30" s="99" t="s">
+      <c r="G30" s="100" t="s">
         <v>338</v>
       </c>
-      <c r="H30" s="99" t="s">
+      <c r="H30" s="100" t="s">
         <v>364</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J30" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B31" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C31" s="89" t="str" cm="1">
+      <c r="B31" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C31" s="96" t="str" cm="1">
         <f t="array" ref="C31">UPPER(INDEX(_xlfn.TEXTSPLIT($F31, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G31" s="99" t="s">
+      <c r="G31" s="100" t="s">
         <v>339</v>
       </c>
-      <c r="H31" s="99" t="s">
+      <c r="H31" s="100" t="s">
         <v>365</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J31" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B32" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C32" s="89" t="str" cm="1">
+      <c r="B32" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C32" s="96" t="str" cm="1">
         <f t="array" ref="C32">UPPER(INDEX(_xlfn.TEXTSPLIT($F32, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G32" s="99" t="s">
+      <c r="G32" s="100" t="s">
         <v>340</v>
       </c>
-      <c r="H32" s="99" t="s">
+      <c r="H32" s="100" t="s">
         <v>366</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J32" t="s">
+      <c r="J32" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B33" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C33" s="89" t="str" cm="1">
+      <c r="B33" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C33" s="96" t="str" cm="1">
         <f t="array" ref="C33">UPPER(INDEX(_xlfn.TEXTSPLIT($F33, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G33" s="99" t="s">
+      <c r="G33" s="100" t="s">
         <v>341</v>
       </c>
-      <c r="H33" s="99" t="s">
+      <c r="H33" s="100" t="s">
         <v>367</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J33" t="s">
+      <c r="J33" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C34" s="89" t="str" cm="1">
+      <c r="B34" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C34" s="96" t="str" cm="1">
         <f t="array" ref="C34">UPPER(INDEX(_xlfn.TEXTSPLIT($F34, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G34" s="99" t="s">
+      <c r="G34" s="100" t="s">
         <v>342</v>
       </c>
-      <c r="H34" s="99" t="s">
+      <c r="H34" s="100" t="s">
         <v>368</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J34" t="s">
+      <c r="J34" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B35" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C35" s="89" t="str" cm="1">
+      <c r="B35" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C35" s="96" t="str" cm="1">
         <f t="array" ref="C35">UPPER(INDEX(_xlfn.TEXTSPLIT($F35, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G35" s="99" t="s">
+      <c r="G35" s="100" t="s">
         <v>343</v>
       </c>
-      <c r="H35" s="99" t="s">
+      <c r="H35" s="100" t="s">
         <v>381</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J35" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B36" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C36" s="89" t="str" cm="1">
+      <c r="B36" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C36" s="96" t="str" cm="1">
         <f t="array" ref="C36">UPPER(INDEX(_xlfn.TEXTSPLIT($F36, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G36" s="99" t="s">
+      <c r="G36" s="100" t="s">
         <v>370</v>
       </c>
-      <c r="H36" s="99" t="s">
+      <c r="H36" s="100" t="s">
         <v>382</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J36" t="s">
+      <c r="J36" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B37" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C37" s="89" t="str" cm="1">
+      <c r="B37" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C37" s="96" t="str" cm="1">
         <f t="array" ref="C37">UPPER(INDEX(_xlfn.TEXTSPLIT($F37, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G37" s="99" t="s">
+      <c r="G37" s="100" t="s">
         <v>371</v>
       </c>
-      <c r="H37" s="99" t="s">
+      <c r="H37" s="100" t="s">
         <v>383</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J37" t="s">
+      <c r="J37" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B38" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C38" s="89" t="str" cm="1">
+      <c r="B38" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C38" s="96" t="str" cm="1">
         <f t="array" ref="C38">UPPER(INDEX(_xlfn.TEXTSPLIT($F38, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G38" s="99" t="s">
+      <c r="G38" s="100" t="s">
         <v>372</v>
       </c>
-      <c r="H38" s="99" t="s">
+      <c r="H38" s="100" t="s">
         <v>384</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J38" t="s">
+      <c r="J38" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B39" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C39" s="89" t="str" cm="1">
+      <c r="B39" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C39" s="96" t="str" cm="1">
         <f t="array" ref="C39">UPPER(INDEX(_xlfn.TEXTSPLIT($F39, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G39" s="99" t="s">
+      <c r="G39" s="100" t="s">
         <v>373</v>
       </c>
-      <c r="H39" s="99" t="s">
+      <c r="H39" s="100" t="s">
         <v>385</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I39" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J39" t="s">
+      <c r="J39" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B40" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C40" s="89" t="str" cm="1">
+      <c r="B40" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C40" s="96" t="str" cm="1">
         <f t="array" ref="C40">UPPER(INDEX(_xlfn.TEXTSPLIT($F40, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G40" s="99" t="s">
+      <c r="G40" s="100" t="s">
         <v>374</v>
       </c>
-      <c r="H40" s="99" t="s">
+      <c r="H40" s="100" t="s">
         <v>386</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J40" t="s">
+      <c r="J40" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B41" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C41" s="89" t="str" cm="1">
+      <c r="B41" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C41" s="96" t="str" cm="1">
         <f t="array" ref="C41">UPPER(INDEX(_xlfn.TEXTSPLIT($F41, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G41" s="99" t="s">
+      <c r="G41" s="100" t="s">
         <v>375</v>
       </c>
-      <c r="H41" s="99" t="s">
+      <c r="H41" s="100" t="s">
         <v>387</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I41" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J41" t="s">
+      <c r="J41" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B42" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C42" s="89" t="str" cm="1">
+      <c r="B42" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C42" s="96" t="str" cm="1">
         <f t="array" ref="C42">UPPER(INDEX(_xlfn.TEXTSPLIT($F42, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G42" s="99" t="s">
+      <c r="G42" s="100" t="s">
         <v>376</v>
       </c>
-      <c r="H42" s="99" t="s">
+      <c r="H42" s="100" t="s">
         <v>388</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I42" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J42" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B43" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C43" s="89" t="str" cm="1">
+      <c r="B43" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C43" s="96" t="str" cm="1">
         <f t="array" ref="C43">UPPER(INDEX(_xlfn.TEXTSPLIT($F43, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G43" s="99" t="s">
+      <c r="G43" s="100" t="s">
         <v>377</v>
       </c>
-      <c r="H43" s="99" t="s">
+      <c r="H43" s="100" t="s">
         <v>389</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J43" t="s">
+      <c r="J43" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B44" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C44" s="89" t="str" cm="1">
+      <c r="B44" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C44" s="96" t="str" cm="1">
         <f t="array" ref="C44">UPPER(INDEX(_xlfn.TEXTSPLIT($F44, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G44" s="99" t="s">
+      <c r="G44" s="100" t="s">
         <v>378</v>
       </c>
-      <c r="H44" s="99" t="s">
+      <c r="H44" s="100" t="s">
         <v>390</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J44" t="s">
+      <c r="J44" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B45" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C45" s="89" t="str" cm="1">
+      <c r="B45" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C45" s="96" t="str" cm="1">
         <f t="array" ref="C45">UPPER(INDEX(_xlfn.TEXTSPLIT($F45, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G45" s="99" t="s">
+      <c r="G45" s="100" t="s">
         <v>379</v>
       </c>
-      <c r="H45" s="99" t="s">
+      <c r="H45" s="100" t="s">
         <v>391</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J45" t="s">
+      <c r="J45" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B46" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C46" s="89" t="str" cm="1">
+      <c r="B46" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C46" s="96" t="str" cm="1">
         <f t="array" ref="C46">UPPER(INDEX(_xlfn.TEXTSPLIT($F46, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G46" s="99" t="s">
+      <c r="G46" s="100" t="s">
         <v>380</v>
       </c>
-      <c r="H46" s="99" t="s">
+      <c r="H46" s="100" t="s">
         <v>392</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I46" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J46" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B47" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C47" s="89" t="str" cm="1">
+      <c r="B47" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C47" s="96" t="str" cm="1">
         <f t="array" ref="C47">UPPER(INDEX(_xlfn.TEXTSPLIT($F47, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G47" s="99" t="s">
+      <c r="G47" s="100" t="s">
         <v>403</v>
       </c>
-      <c r="H47" s="99" t="s">
+      <c r="H47" s="100" t="s">
         <v>393</v>
       </c>
-      <c r="I47" t="s">
+      <c r="I47" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J47" t="s">
+      <c r="J47" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B48" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C48" s="89" t="str" cm="1">
+      <c r="B48" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C48" s="96" t="str" cm="1">
         <f t="array" ref="C48">UPPER(INDEX(_xlfn.TEXTSPLIT($F48, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G48" s="99" t="s">
+      <c r="G48" s="100" t="s">
         <v>404</v>
       </c>
-      <c r="H48" s="99" t="s">
+      <c r="H48" s="100" t="s">
         <v>394</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J48" t="s">
+      <c r="J48" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B49" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C49" s="89" t="str" cm="1">
+      <c r="B49" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C49" s="96" t="str" cm="1">
         <f t="array" ref="C49">UPPER(INDEX(_xlfn.TEXTSPLIT($F49, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G49" s="99" t="s">
+      <c r="G49" s="100" t="s">
         <v>405</v>
       </c>
-      <c r="H49" s="99" t="s">
+      <c r="H49" s="100" t="s">
         <v>395</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I49" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J49" t="s">
+      <c r="J49" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B50" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C50" s="89" t="str" cm="1">
+      <c r="B50" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C50" s="96" t="str" cm="1">
         <f t="array" ref="C50">UPPER(INDEX(_xlfn.TEXTSPLIT($F50, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G50" s="99" t="s">
+      <c r="G50" s="100" t="s">
         <v>406</v>
       </c>
-      <c r="H50" s="99" t="s">
+      <c r="H50" s="100" t="s">
         <v>396</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I50" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J50" t="s">
+      <c r="J50" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B51" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C51" s="89" t="str" cm="1">
+      <c r="B51" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C51" s="96" t="str" cm="1">
         <f t="array" ref="C51">UPPER(INDEX(_xlfn.TEXTSPLIT($F51, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G51" s="99" t="s">
+      <c r="G51" s="100" t="s">
         <v>407</v>
       </c>
-      <c r="H51" s="99" t="s">
+      <c r="H51" s="100" t="s">
         <v>397</v>
       </c>
-      <c r="I51" t="s">
+      <c r="I51" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J51" t="s">
+      <c r="J51" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B52" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C52" s="89" t="str" cm="1">
+      <c r="B52" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C52" s="96" t="str" cm="1">
         <f t="array" ref="C52">UPPER(INDEX(_xlfn.TEXTSPLIT($F52, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G52" s="99" t="s">
+      <c r="G52" s="100" t="s">
         <v>408</v>
       </c>
-      <c r="H52" s="99" t="s">
+      <c r="H52" s="100" t="s">
         <v>398</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I52" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J52" t="s">
+      <c r="J52" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B53" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C53" s="89" t="str" cm="1">
+      <c r="B53" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C53" s="96" t="str" cm="1">
         <f t="array" ref="C53">UPPER(INDEX(_xlfn.TEXTSPLIT($F53, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G53" s="99" t="s">
+      <c r="G53" s="100" t="s">
         <v>409</v>
       </c>
-      <c r="H53" s="99" t="s">
+      <c r="H53" s="100" t="s">
         <v>399</v>
       </c>
-      <c r="I53" t="s">
+      <c r="I53" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J53" t="s">
+      <c r="J53" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B54" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C54" s="89" t="str" cm="1">
+      <c r="B54" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C54" s="96" t="str" cm="1">
         <f t="array" ref="C54">UPPER(INDEX(_xlfn.TEXTSPLIT($F54, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G54" s="99" t="s">
+      <c r="G54" s="100" t="s">
         <v>410</v>
       </c>
-      <c r="H54" s="99" t="s">
+      <c r="H54" s="100" t="s">
         <v>400</v>
       </c>
-      <c r="I54" t="s">
+      <c r="I54" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J54" t="s">
+      <c r="J54" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B55" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C55" s="89" t="str" cm="1">
+      <c r="B55" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C55" s="96" t="str" cm="1">
         <f t="array" ref="C55">UPPER(INDEX(_xlfn.TEXTSPLIT($F55, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G55" s="99" t="s">
+      <c r="G55" s="100" t="s">
         <v>411</v>
       </c>
-      <c r="H55" s="99" t="s">
+      <c r="H55" s="100" t="s">
         <v>401</v>
       </c>
-      <c r="I55" t="s">
+      <c r="I55" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J55" t="s">
+      <c r="J55" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B56" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C56" s="89" t="str" cm="1">
+      <c r="B56" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C56" s="96" t="str" cm="1">
         <f t="array" ref="C56">UPPER(INDEX(_xlfn.TEXTSPLIT($F56, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F56" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G56" s="99" t="s">
+      <c r="G56" s="100" t="s">
         <v>412</v>
       </c>
-      <c r="H56" s="99" t="s">
+      <c r="H56" s="100" t="s">
         <v>402</v>
       </c>
-      <c r="I56" t="s">
+      <c r="I56" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J56" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B57" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C57" s="89" t="str" cm="1">
+      <c r="B57" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C57" s="96" t="str" cm="1">
         <f t="array" ref="C57">UPPER(INDEX(_xlfn.TEXTSPLIT($F57, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F57" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G57" t="s">
+      <c r="G57" s="52" t="s">
         <v>276</v>
       </c>
-      <c r="H57" t="s">
+      <c r="H57" s="52" t="s">
         <v>301</v>
       </c>
-      <c r="I57" t="s">
+      <c r="I57" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J57" t="s">
+      <c r="J57" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B58" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C58" s="89" t="str" cm="1">
+      <c r="B58" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C58" s="96" t="str" cm="1">
         <f t="array" ref="C58">UPPER(INDEX(_xlfn.TEXTSPLIT($F58, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G58" t="s">
+      <c r="G58" s="52" t="s">
         <v>277</v>
       </c>
-      <c r="H58" t="s">
+      <c r="H58" s="52" t="s">
         <v>302</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I58" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J58" t="s">
+      <c r="J58" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B59" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C59" s="89" t="str" cm="1">
+      <c r="B59" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C59" s="96" t="str" cm="1">
         <f t="array" ref="C59">UPPER(INDEX(_xlfn.TEXTSPLIT($F59, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F59" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G59" t="s">
+      <c r="G59" s="52" t="s">
         <v>278</v>
       </c>
-      <c r="H59" t="s">
+      <c r="H59" s="52" t="s">
         <v>303</v>
       </c>
-      <c r="I59" t="s">
+      <c r="I59" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J59" t="s">
+      <c r="J59" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B60" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C60" s="89" t="str" cm="1">
+      <c r="B60" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C60" s="96" t="str" cm="1">
         <f t="array" ref="C60">UPPER(INDEX(_xlfn.TEXTSPLIT($F60, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G60" t="s">
+      <c r="G60" s="52" t="s">
         <v>279</v>
       </c>
-      <c r="H60" t="s">
+      <c r="H60" s="52" t="s">
         <v>304</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I60" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J60" t="s">
+      <c r="J60" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B61" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C61" s="89" t="str" cm="1">
+      <c r="B61" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C61" s="96" t="str" cm="1">
         <f t="array" ref="C61">UPPER(INDEX(_xlfn.TEXTSPLIT($F61, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G61" s="52" t="s">
         <v>280</v>
       </c>
-      <c r="H61" t="s">
+      <c r="H61" s="52" t="s">
         <v>305</v>
       </c>
-      <c r="I61" t="s">
+      <c r="I61" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J61" t="s">
+      <c r="J61" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B62" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C62" s="89" t="str" cm="1">
+      <c r="B62" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C62" s="96" t="str" cm="1">
         <f t="array" ref="C62">UPPER(INDEX(_xlfn.TEXTSPLIT($F62, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G62" t="s">
+      <c r="G62" s="52" t="s">
         <v>281</v>
       </c>
-      <c r="H62" t="s">
+      <c r="H62" s="52" t="s">
         <v>306</v>
       </c>
-      <c r="I62" t="s">
+      <c r="I62" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J62" t="s">
+      <c r="J62" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B63" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C63" s="89" t="str" cm="1">
+      <c r="B63" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C63" s="96" t="str" cm="1">
         <f t="array" ref="C63">UPPER(INDEX(_xlfn.TEXTSPLIT($F63, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G63" t="s">
+      <c r="G63" s="52" t="s">
         <v>282</v>
       </c>
-      <c r="H63" t="s">
+      <c r="H63" s="52" t="s">
         <v>307</v>
       </c>
-      <c r="I63" t="s">
+      <c r="I63" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J63" t="s">
+      <c r="J63" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B64" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C64" s="89" t="str" cm="1">
+      <c r="B64" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C64" s="96" t="str" cm="1">
         <f t="array" ref="C64">UPPER(INDEX(_xlfn.TEXTSPLIT($F64, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F64" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G64" t="s">
+      <c r="G64" s="52" t="s">
         <v>283</v>
       </c>
-      <c r="H64" t="s">
+      <c r="H64" s="52" t="s">
         <v>308</v>
       </c>
-      <c r="I64" t="s">
+      <c r="I64" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J64" t="s">
+      <c r="J64" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B65" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C65" s="89" t="str" cm="1">
+      <c r="B65" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C65" s="96" t="str" cm="1">
         <f t="array" ref="C65">UPPER(INDEX(_xlfn.TEXTSPLIT($F65, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F65" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G65" t="s">
+      <c r="G65" s="52" t="s">
         <v>284</v>
       </c>
-      <c r="H65" t="s">
+      <c r="H65" s="52" t="s">
         <v>309</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I65" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J65" t="s">
+      <c r="J65" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B66" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="C66" s="89" t="str" cm="1">
+      <c r="B66" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C66" s="96" t="str" cm="1">
         <f t="array" ref="C66">UPPER(INDEX(_xlfn.TEXTSPLIT($F66, "-"), 3))</f>
         <v>EXT</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F66" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G66" t="s">
+      <c r="G66" s="52" t="s">
         <v>285</v>
       </c>
-      <c r="H66" t="s">
+      <c r="H66" s="52" t="s">
         <v>310</v>
       </c>
-      <c r="I66" t="s">
+      <c r="I66" s="52" t="s">
         <v>312</v>
       </c>
-      <c r="J66" t="s">
+      <c r="J66" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B67" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C67" s="102" t="str" cm="1">
+      <c r="B67" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C67" s="101" t="str" cm="1">
         <f t="array" ref="C67">UPPER(INDEX(_xlfn.TEXTSPLIT($F67, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D67" s="103" t="s">
+      <c r="D67" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E67" s="103" t="s">
+      <c r="E67" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F67" s="103" t="s">
+      <c r="F67" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G67" s="103" t="s">
+      <c r="G67" s="102" t="s">
         <v>270</v>
       </c>
-      <c r="H67" s="103" t="s">
+      <c r="H67" s="102" t="s">
         <v>295</v>
       </c>
-      <c r="I67" s="103" t="s">
+      <c r="I67" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J67" s="103" t="s">
+      <c r="J67" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B68" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C68" s="102" t="str" cm="1">
+      <c r="B68" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C68" s="101" t="str" cm="1">
         <f t="array" ref="C68">UPPER(INDEX(_xlfn.TEXTSPLIT($F68, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D68" s="103" t="s">
+      <c r="D68" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E68" s="103" t="s">
+      <c r="E68" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F68" s="103" t="s">
+      <c r="F68" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G68" s="103" t="s">
+      <c r="G68" s="102" t="s">
         <v>271</v>
       </c>
-      <c r="H68" s="103" t="s">
+      <c r="H68" s="102" t="s">
         <v>296</v>
       </c>
-      <c r="I68" s="103" t="s">
+      <c r="I68" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J68" s="103" t="s">
+      <c r="J68" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B69" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C69" s="102" t="str" cm="1">
+      <c r="B69" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C69" s="101" t="str" cm="1">
         <f t="array" ref="C69">UPPER(INDEX(_xlfn.TEXTSPLIT($F69, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D69" s="103" t="s">
+      <c r="D69" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E69" s="103" t="s">
+      <c r="E69" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F69" s="103" t="s">
+      <c r="F69" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G69" s="103" t="s">
+      <c r="G69" s="102" t="s">
         <v>272</v>
       </c>
-      <c r="H69" s="103" t="s">
+      <c r="H69" s="102" t="s">
         <v>297</v>
       </c>
-      <c r="I69" s="103" t="s">
+      <c r="I69" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J69" s="103" t="s">
+      <c r="J69" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B70" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C70" s="102" t="str" cm="1">
+      <c r="B70" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C70" s="101" t="str" cm="1">
         <f t="array" ref="C70">UPPER(INDEX(_xlfn.TEXTSPLIT($F70, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D70" s="103" t="s">
+      <c r="D70" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E70" s="103" t="s">
+      <c r="E70" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F70" s="103" t="s">
+      <c r="F70" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G70" s="103" t="s">
+      <c r="G70" s="102" t="s">
         <v>273</v>
       </c>
-      <c r="H70" s="103" t="s">
+      <c r="H70" s="102" t="s">
         <v>298</v>
       </c>
-      <c r="I70" s="103" t="s">
+      <c r="I70" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J70" s="103" t="s">
+      <c r="J70" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B71" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C71" s="102" t="str" cm="1">
+      <c r="B71" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C71" s="101" t="str" cm="1">
         <f t="array" ref="C71">UPPER(INDEX(_xlfn.TEXTSPLIT($F71, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D71" s="103" t="s">
+      <c r="D71" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E71" s="103" t="s">
+      <c r="E71" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F71" s="103" t="s">
+      <c r="F71" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G71" s="103" t="s">
+      <c r="G71" s="102" t="s">
         <v>274</v>
       </c>
-      <c r="H71" s="103" t="s">
+      <c r="H71" s="102" t="s">
         <v>299</v>
       </c>
-      <c r="I71" s="103" t="s">
+      <c r="I71" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J71" s="103" t="s">
+      <c r="J71" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B72" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C72" s="102" t="str" cm="1">
+      <c r="B72" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C72" s="101" t="str" cm="1">
         <f t="array" ref="C72">UPPER(INDEX(_xlfn.TEXTSPLIT($F72, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D72" s="103" t="s">
+      <c r="D72" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E72" s="103" t="s">
+      <c r="E72" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F72" s="103" t="s">
+      <c r="F72" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G72" s="103" t="s">
+      <c r="G72" s="102" t="s">
         <v>413</v>
       </c>
-      <c r="H72" s="103" t="s">
+      <c r="H72" s="102" t="s">
         <v>300</v>
       </c>
-      <c r="I72" s="103" t="s">
+      <c r="I72" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J72" s="103" t="s">
+      <c r="J72" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B73" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C73" s="102" t="str" cm="1">
+      <c r="B73" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C73" s="101" t="str" cm="1">
         <f t="array" ref="C73">UPPER(INDEX(_xlfn.TEXTSPLIT($F73, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D73" s="103" t="s">
+      <c r="D73" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E73" s="103" t="s">
+      <c r="E73" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F73" s="103" t="s">
+      <c r="F73" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G73" s="103" t="s">
+      <c r="G73" s="102" t="s">
         <v>315</v>
       </c>
-      <c r="H73" s="103" t="s">
+      <c r="H73" s="102" t="s">
         <v>316</v>
       </c>
-      <c r="I73" s="103" t="s">
+      <c r="I73" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J73" s="103" t="s">
+      <c r="J73" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B74" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C74" s="102" t="str" cm="1">
+      <c r="B74" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C74" s="101" t="str" cm="1">
         <f t="array" ref="C74">UPPER(INDEX(_xlfn.TEXTSPLIT($F74, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D74" s="103" t="s">
+      <c r="D74" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E74" s="103" t="s">
+      <c r="E74" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F74" s="103" t="s">
+      <c r="F74" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G74" s="103" t="s">
+      <c r="G74" s="102" t="s">
         <v>414</v>
       </c>
-      <c r="H74" s="103" t="s">
+      <c r="H74" s="102" t="s">
         <v>415</v>
       </c>
-      <c r="I74" s="103" t="s">
+      <c r="I74" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J74" s="103" t="s">
+      <c r="J74" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B75" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C75" s="102" t="str" cm="1">
+      <c r="B75" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C75" s="101" t="str" cm="1">
         <f t="array" ref="C75">UPPER(INDEX(_xlfn.TEXTSPLIT($F75, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D75" s="103" t="s">
+      <c r="D75" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E75" s="103" t="s">
+      <c r="E75" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F75" s="103" t="s">
+      <c r="F75" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G75" s="103" t="s">
+      <c r="G75" s="102" t="s">
         <v>286</v>
       </c>
-      <c r="H75" s="103" t="s">
+      <c r="H75" s="102" t="s">
         <v>416</v>
       </c>
-      <c r="I75" s="103" t="s">
+      <c r="I75" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J75" s="103" t="s">
+      <c r="J75" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B76" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C76" s="102" t="str" cm="1">
+      <c r="B76" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C76" s="101" t="str" cm="1">
         <f t="array" ref="C76">UPPER(INDEX(_xlfn.TEXTSPLIT($F76, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D76" s="103" t="s">
+      <c r="D76" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E76" s="103" t="s">
+      <c r="E76" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F76" s="103" t="s">
+      <c r="F76" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G76" s="103" t="s">
+      <c r="G76" s="102" t="s">
         <v>287</v>
       </c>
-      <c r="H76" s="103" t="s">
+      <c r="H76" s="102" t="s">
         <v>417</v>
       </c>
-      <c r="I76" s="103" t="s">
+      <c r="I76" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J76" s="103" t="s">
+      <c r="J76" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B77" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C77" s="102" t="str" cm="1">
+      <c r="B77" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C77" s="101" t="str" cm="1">
         <f t="array" ref="C77">UPPER(INDEX(_xlfn.TEXTSPLIT($F77, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D77" s="103" t="s">
+      <c r="D77" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E77" s="103" t="s">
+      <c r="E77" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F77" s="103" t="s">
+      <c r="F77" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G77" s="103" t="s">
+      <c r="G77" s="102" t="s">
         <v>288</v>
       </c>
-      <c r="H77" s="103" t="s">
+      <c r="H77" s="102" t="s">
         <v>418</v>
       </c>
-      <c r="I77" s="103" t="s">
+      <c r="I77" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J77" s="103" t="s">
+      <c r="J77" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B78" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C78" s="102" t="str" cm="1">
+      <c r="B78" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C78" s="101" t="str" cm="1">
         <f t="array" ref="C78">UPPER(INDEX(_xlfn.TEXTSPLIT($F78, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D78" s="103" t="s">
+      <c r="D78" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E78" s="103" t="s">
+      <c r="E78" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F78" s="103" t="s">
+      <c r="F78" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G78" s="103" t="s">
+      <c r="G78" s="102" t="s">
         <v>289</v>
       </c>
-      <c r="H78" s="103" t="s">
+      <c r="H78" s="102" t="s">
         <v>419</v>
       </c>
-      <c r="I78" s="103" t="s">
+      <c r="I78" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J78" s="103" t="s">
+      <c r="J78" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B79" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C79" s="102" t="str" cm="1">
+      <c r="B79" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C79" s="101" t="str" cm="1">
         <f t="array" ref="C79">UPPER(INDEX(_xlfn.TEXTSPLIT($F79, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D79" s="103" t="s">
+      <c r="D79" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E79" s="103" t="s">
+      <c r="E79" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F79" s="103" t="s">
+      <c r="F79" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G79" s="103" t="s">
+      <c r="G79" s="102" t="s">
         <v>290</v>
       </c>
-      <c r="H79" s="103" t="s">
+      <c r="H79" s="102" t="s">
         <v>420</v>
       </c>
-      <c r="I79" s="103" t="s">
+      <c r="I79" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J79" s="103" t="s">
+      <c r="J79" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B80" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C80" s="102" t="str" cm="1">
+      <c r="B80" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C80" s="101" t="str" cm="1">
         <f t="array" ref="C80">UPPER(INDEX(_xlfn.TEXTSPLIT($F80, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D80" s="103" t="s">
+      <c r="D80" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E80" s="103" t="s">
+      <c r="E80" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F80" s="103" t="s">
+      <c r="F80" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G80" s="103" t="s">
+      <c r="G80" s="102" t="s">
         <v>291</v>
       </c>
-      <c r="H80" s="103" t="s">
+      <c r="H80" s="102" t="s">
         <v>421</v>
       </c>
-      <c r="I80" s="103" t="s">
+      <c r="I80" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J80" s="103" t="s">
+      <c r="J80" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B81" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C81" s="102" t="str" cm="1">
+      <c r="B81" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C81" s="101" t="str" cm="1">
         <f t="array" ref="C81">UPPER(INDEX(_xlfn.TEXTSPLIT($F81, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D81" s="103" t="s">
+      <c r="D81" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E81" s="103" t="s">
+      <c r="E81" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F81" s="103" t="s">
+      <c r="F81" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G81" s="103" t="s">
+      <c r="G81" s="102" t="s">
         <v>292</v>
       </c>
-      <c r="H81" s="103" t="s">
+      <c r="H81" s="102" t="s">
         <v>422</v>
       </c>
-      <c r="I81" s="103" t="s">
+      <c r="I81" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J81" s="103" t="s">
+      <c r="J81" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B82" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C82" s="102" t="str" cm="1">
+      <c r="B82" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C82" s="101" t="str" cm="1">
         <f t="array" ref="C82">UPPER(INDEX(_xlfn.TEXTSPLIT($F82, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D82" s="103" t="s">
+      <c r="D82" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E82" s="103" t="s">
+      <c r="E82" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F82" s="103" t="s">
+      <c r="F82" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G82" s="103" t="s">
+      <c r="G82" s="102" t="s">
         <v>293</v>
       </c>
-      <c r="H82" s="103" t="s">
+      <c r="H82" s="102" t="s">
         <v>423</v>
       </c>
-      <c r="I82" s="103" t="s">
+      <c r="I82" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J82" s="103" t="s">
+      <c r="J82" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B83" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C83" s="102" t="str" cm="1">
+      <c r="B83" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C83" s="101" t="str" cm="1">
         <f t="array" ref="C83">UPPER(INDEX(_xlfn.TEXTSPLIT($F83, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D83" s="103" t="s">
+      <c r="D83" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E83" s="103" t="s">
+      <c r="E83" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F83" s="103" t="s">
+      <c r="F83" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G83" s="103" t="s">
+      <c r="G83" s="102" t="s">
         <v>431</v>
       </c>
-      <c r="H83" s="103" t="s">
+      <c r="H83" s="102" t="s">
         <v>424</v>
       </c>
-      <c r="I83" s="103" t="s">
+      <c r="I83" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J83" s="103" t="s">
+      <c r="J83" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B84" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C84" s="102" t="str" cm="1">
+      <c r="B84" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C84" s="101" t="str" cm="1">
         <f t="array" ref="C84">UPPER(INDEX(_xlfn.TEXTSPLIT($F84, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D84" s="103" t="s">
+      <c r="D84" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E84" s="103" t="s">
+      <c r="E84" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F84" s="103" t="s">
+      <c r="F84" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G84" s="103" t="s">
+      <c r="G84" s="102" t="s">
         <v>432</v>
       </c>
-      <c r="H84" s="103" t="s">
+      <c r="H84" s="102" t="s">
         <v>425</v>
       </c>
-      <c r="I84" s="103" t="s">
+      <c r="I84" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J84" s="103" t="s">
+      <c r="J84" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B85" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C85" s="102" t="str" cm="1">
+      <c r="B85" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C85" s="101" t="str" cm="1">
         <f t="array" ref="C85">UPPER(INDEX(_xlfn.TEXTSPLIT($F85, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D85" s="103" t="s">
+      <c r="D85" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E85" s="103" t="s">
+      <c r="E85" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F85" s="103" t="s">
+      <c r="F85" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G85" s="103" t="s">
+      <c r="G85" s="102" t="s">
         <v>433</v>
       </c>
-      <c r="H85" s="103" t="s">
+      <c r="H85" s="102" t="s">
         <v>426</v>
       </c>
-      <c r="I85" s="103" t="s">
+      <c r="I85" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J85" s="103" t="s">
+      <c r="J85" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B86" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C86" s="102" t="str" cm="1">
+      <c r="B86" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C86" s="101" t="str" cm="1">
         <f t="array" ref="C86">UPPER(INDEX(_xlfn.TEXTSPLIT($F86, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D86" s="103" t="s">
+      <c r="D86" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E86" s="103" t="s">
+      <c r="E86" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F86" s="103" t="s">
+      <c r="F86" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G86" s="103" t="s">
+      <c r="G86" s="102" t="s">
         <v>434</v>
       </c>
-      <c r="H86" s="103" t="s">
+      <c r="H86" s="102" t="s">
         <v>427</v>
       </c>
-      <c r="I86" s="103" t="s">
+      <c r="I86" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J86" s="103" t="s">
+      <c r="J86" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B87" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C87" s="102" t="str" cm="1">
+      <c r="B87" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C87" s="101" t="str" cm="1">
         <f t="array" ref="C87">UPPER(INDEX(_xlfn.TEXTSPLIT($F87, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D87" s="103" t="s">
+      <c r="D87" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E87" s="103" t="s">
+      <c r="E87" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F87" s="103" t="s">
+      <c r="F87" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G87" s="103" t="s">
+      <c r="G87" s="102" t="s">
         <v>435</v>
       </c>
-      <c r="H87" s="103" t="s">
+      <c r="H87" s="102" t="s">
         <v>428</v>
       </c>
-      <c r="I87" s="103" t="s">
+      <c r="I87" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J87" s="103" t="s">
+      <c r="J87" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B88" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C88" s="102" t="str" cm="1">
+      <c r="B88" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C88" s="101" t="str" cm="1">
         <f t="array" ref="C88">UPPER(INDEX(_xlfn.TEXTSPLIT($F88, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D88" s="103" t="s">
+      <c r="D88" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E88" s="103" t="s">
+      <c r="E88" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F88" s="103" t="s">
+      <c r="F88" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G88" s="103" t="s">
+      <c r="G88" s="102" t="s">
         <v>436</v>
       </c>
-      <c r="H88" s="103" t="s">
+      <c r="H88" s="102" t="s">
         <v>429</v>
       </c>
-      <c r="I88" s="103" t="s">
+      <c r="I88" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J88" s="103" t="s">
+      <c r="J88" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B89" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C89" s="102" t="str" cm="1">
+      <c r="B89" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C89" s="101" t="str" cm="1">
         <f t="array" ref="C89">UPPER(INDEX(_xlfn.TEXTSPLIT($F89, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D89" s="103" t="s">
+      <c r="D89" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E89" s="103" t="s">
+      <c r="E89" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F89" s="103" t="s">
+      <c r="F89" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G89" s="103" t="s">
+      <c r="G89" s="102" t="s">
         <v>437</v>
       </c>
-      <c r="H89" s="103" t="s">
+      <c r="H89" s="102" t="s">
         <v>430</v>
       </c>
-      <c r="I89" s="103" t="s">
+      <c r="I89" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J89" s="103" t="s">
+      <c r="J89" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B90" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C90" s="102" t="str" cm="1">
+      <c r="B90" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C90" s="101" t="str" cm="1">
         <f t="array" ref="C90">UPPER(INDEX(_xlfn.TEXTSPLIT($F90, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D90" s="103" t="s">
+      <c r="D90" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E90" s="103" t="s">
+      <c r="E90" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F90" s="103" t="s">
+      <c r="F90" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G90" s="103" t="s">
+      <c r="G90" s="102" t="s">
         <v>276</v>
       </c>
-      <c r="H90" s="103" t="s">
+      <c r="H90" s="102" t="s">
         <v>301</v>
       </c>
-      <c r="I90" s="103" t="s">
+      <c r="I90" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J90" s="103" t="s">
+      <c r="J90" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B91" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C91" s="102" t="str" cm="1">
+      <c r="B91" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C91" s="101" t="str" cm="1">
         <f t="array" ref="C91">UPPER(INDEX(_xlfn.TEXTSPLIT($F91, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D91" s="103" t="s">
+      <c r="D91" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E91" s="103" t="s">
+      <c r="E91" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F91" s="103" t="s">
+      <c r="F91" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G91" s="103" t="s">
+      <c r="G91" s="102" t="s">
         <v>277</v>
       </c>
-      <c r="H91" s="103" t="s">
+      <c r="H91" s="102" t="s">
         <v>302</v>
       </c>
-      <c r="I91" s="103" t="s">
+      <c r="I91" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J91" s="103" t="s">
+      <c r="J91" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B92" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C92" s="102" t="str" cm="1">
+      <c r="B92" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C92" s="101" t="str" cm="1">
         <f t="array" ref="C92">UPPER(INDEX(_xlfn.TEXTSPLIT($F92, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D92" s="103" t="s">
+      <c r="D92" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E92" s="103" t="s">
+      <c r="E92" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F92" s="103" t="s">
+      <c r="F92" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G92" s="103" t="s">
+      <c r="G92" s="102" t="s">
         <v>278</v>
       </c>
-      <c r="H92" s="103" t="s">
+      <c r="H92" s="102" t="s">
         <v>303</v>
       </c>
-      <c r="I92" s="103" t="s">
+      <c r="I92" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J92" s="103" t="s">
+      <c r="J92" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B93" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C93" s="102" t="str" cm="1">
+      <c r="B93" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C93" s="101" t="str" cm="1">
         <f t="array" ref="C93">UPPER(INDEX(_xlfn.TEXTSPLIT($F93, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D93" s="103" t="s">
+      <c r="D93" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E93" s="103" t="s">
+      <c r="E93" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F93" s="103" t="s">
+      <c r="F93" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G93" s="103" t="s">
+      <c r="G93" s="102" t="s">
         <v>279</v>
       </c>
-      <c r="H93" s="103" t="s">
+      <c r="H93" s="102" t="s">
         <v>304</v>
       </c>
-      <c r="I93" s="103" t="s">
+      <c r="I93" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J93" s="103" t="s">
+      <c r="J93" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B94" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C94" s="102" t="str" cm="1">
+      <c r="B94" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C94" s="101" t="str" cm="1">
         <f t="array" ref="C94">UPPER(INDEX(_xlfn.TEXTSPLIT($F94, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D94" s="103" t="s">
+      <c r="D94" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E94" s="103" t="s">
+      <c r="E94" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F94" s="103" t="s">
+      <c r="F94" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G94" s="103" t="s">
+      <c r="G94" s="102" t="s">
         <v>280</v>
       </c>
-      <c r="H94" s="103" t="s">
+      <c r="H94" s="102" t="s">
         <v>305</v>
       </c>
-      <c r="I94" s="103" t="s">
+      <c r="I94" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J94" s="103" t="s">
+      <c r="J94" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B95" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C95" s="102" t="str" cm="1">
+      <c r="B95" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C95" s="101" t="str" cm="1">
         <f t="array" ref="C95">UPPER(INDEX(_xlfn.TEXTSPLIT($F95, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D95" s="103" t="s">
+      <c r="D95" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E95" s="103" t="s">
+      <c r="E95" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F95" s="103" t="s">
+      <c r="F95" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G95" s="103" t="s">
+      <c r="G95" s="102" t="s">
         <v>281</v>
       </c>
-      <c r="H95" s="103" t="s">
+      <c r="H95" s="102" t="s">
         <v>306</v>
       </c>
-      <c r="I95" s="103" t="s">
+      <c r="I95" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J95" s="103" t="s">
+      <c r="J95" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B96" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C96" s="102" t="str" cm="1">
+      <c r="B96" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C96" s="101" t="str" cm="1">
         <f t="array" ref="C96">UPPER(INDEX(_xlfn.TEXTSPLIT($F96, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D96" s="103" t="s">
+      <c r="D96" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E96" s="103" t="s">
+      <c r="E96" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F96" s="103" t="s">
+      <c r="F96" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G96" s="103" t="s">
+      <c r="G96" s="102" t="s">
         <v>282</v>
       </c>
-      <c r="H96" s="103" t="s">
+      <c r="H96" s="102" t="s">
         <v>307</v>
       </c>
-      <c r="I96" s="103" t="s">
+      <c r="I96" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J96" s="103" t="s">
+      <c r="J96" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B97" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C97" s="102" t="str" cm="1">
+      <c r="B97" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C97" s="101" t="str" cm="1">
         <f t="array" ref="C97">UPPER(INDEX(_xlfn.TEXTSPLIT($F97, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D97" s="103" t="s">
+      <c r="D97" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E97" s="103" t="s">
+      <c r="E97" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F97" s="103" t="s">
+      <c r="F97" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G97" s="103" t="s">
+      <c r="G97" s="102" t="s">
         <v>283</v>
       </c>
-      <c r="H97" s="103" t="s">
+      <c r="H97" s="102" t="s">
         <v>308</v>
       </c>
-      <c r="I97" s="103" t="s">
+      <c r="I97" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J97" s="103" t="s">
+      <c r="J97" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B98" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C98" s="102" t="str" cm="1">
+      <c r="B98" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C98" s="101" t="str" cm="1">
         <f t="array" ref="C98">UPPER(INDEX(_xlfn.TEXTSPLIT($F98, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D98" s="103" t="s">
+      <c r="D98" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E98" s="103" t="s">
+      <c r="E98" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F98" s="103" t="s">
+      <c r="F98" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G98" s="103" t="s">
+      <c r="G98" s="102" t="s">
         <v>284</v>
       </c>
-      <c r="H98" s="103" t="s">
+      <c r="H98" s="102" t="s">
         <v>309</v>
       </c>
-      <c r="I98" s="103" t="s">
+      <c r="I98" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J98" s="103" t="s">
+      <c r="J98" s="102" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B99" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C99" s="102" t="str" cm="1">
+      <c r="B99" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C99" s="101" t="str" cm="1">
         <f t="array" ref="C99">UPPER(INDEX(_xlfn.TEXTSPLIT($F99, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D99" s="103" t="s">
+      <c r="D99" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="E99" s="103" t="s">
+      <c r="E99" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F99" s="103" t="s">
+      <c r="F99" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="G99" s="103" t="s">
+      <c r="G99" s="102" t="s">
         <v>285</v>
       </c>
-      <c r="H99" s="103" t="s">
+      <c r="H99" s="102" t="s">
         <v>310</v>
       </c>
-      <c r="I99" s="103" t="s">
+      <c r="I99" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="J99" s="103" t="s">
+      <c r="J99" s="102" t="s">
         <v>314</v>
       </c>
     </row>
@@ -10918,7 +10915,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
-        <v>23</v>
+        <v>223</v>
       </c>
       <c r="B2" s="56" t="s">
         <v>91</v>
@@ -10963,7 +10960,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="56" t="s">
-        <v>23</v>
+        <v>223</v>
       </c>
       <c r="B3" s="56" t="s">
         <v>91</v>

--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4BC459-5AE0-4496-BC06-A8F21438C160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE6FBB9-F62F-4A7E-8E77-00C4B60C5C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -2617,10 +2617,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_Base_Image/versions/0.0.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Role2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3184,6 +3180,10 @@
   </si>
   <si>
     <t>hazr-d-dch-ext-vnet_16</t>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_nginx_Base_Image/versions/0.0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3632,7 +3632,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3930,10 +3930,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5980,7 +5977,7 @@
         <v>212</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>258</v>
+        <v>437</v>
       </c>
       <c r="O2" s="1" t="str">
         <f t="shared" ref="O2:O3" si="0">SUBSTITUTE(F2,"hazr-","")&amp;"-osdisk"</f>
@@ -6069,7 +6066,7 @@
         <v>212</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>258</v>
+        <v>437</v>
       </c>
       <c r="O3" s="1" t="str">
         <f t="shared" si="0"/>
@@ -6492,7 +6489,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E1" s="46" t="s">
         <v>33</v>
@@ -6532,7 +6529,7 @@
         <v>239</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>239</v>
@@ -6564,7 +6561,7 @@
         <v>239</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>239</v>
@@ -6596,7 +6593,7 @@
         <v>239</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>239</v>
@@ -6605,7 +6602,7 @@
         <v>241</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="5" t="s">
@@ -6628,7 +6625,7 @@
         <v>239</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>239</v>
@@ -6637,7 +6634,7 @@
         <v>241</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="7" t="s">
@@ -6696,19 +6693,19 @@
         <v>3</v>
       </c>
       <c r="F1" s="58" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G1" s="58" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1" s="58" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I1" s="58" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J1" s="58" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K1" s="46"/>
     </row>
@@ -6727,19 +6724,19 @@
         <v>24</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G2" s="100" t="s">
-        <v>270</v>
-      </c>
-      <c r="H2" s="100" t="s">
-        <v>295</v>
+        <v>265</v>
+      </c>
+      <c r="G2" s="52" t="s">
+        <v>269</v>
+      </c>
+      <c r="H2" s="52" t="s">
+        <v>294</v>
       </c>
       <c r="I2" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J2" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
@@ -6757,19 +6754,19 @@
         <v>24</v>
       </c>
       <c r="F3" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G3" s="100" t="s">
-        <v>271</v>
-      </c>
-      <c r="H3" s="100" t="s">
-        <v>296</v>
+        <v>265</v>
+      </c>
+      <c r="G3" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="H3" s="52" t="s">
+        <v>295</v>
       </c>
       <c r="I3" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J3" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
@@ -6787,19 +6784,19 @@
         <v>24</v>
       </c>
       <c r="F4" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G4" s="100" t="s">
-        <v>272</v>
-      </c>
-      <c r="H4" s="100" t="s">
-        <v>297</v>
+        <v>265</v>
+      </c>
+      <c r="G4" s="52" t="s">
+        <v>271</v>
+      </c>
+      <c r="H4" s="52" t="s">
+        <v>296</v>
       </c>
       <c r="I4" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J4" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
@@ -6817,19 +6814,19 @@
         <v>24</v>
       </c>
       <c r="F5" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G5" s="100" t="s">
-        <v>273</v>
-      </c>
-      <c r="H5" s="100" t="s">
-        <v>298</v>
+        <v>265</v>
+      </c>
+      <c r="G5" s="52" t="s">
+        <v>272</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>297</v>
       </c>
       <c r="I5" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J5" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -6847,19 +6844,19 @@
         <v>24</v>
       </c>
       <c r="F6" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G6" s="100" t="s">
-        <v>274</v>
-      </c>
-      <c r="H6" s="100" t="s">
-        <v>299</v>
+        <v>265</v>
+      </c>
+      <c r="G6" s="52" t="s">
+        <v>273</v>
+      </c>
+      <c r="H6" s="52" t="s">
+        <v>298</v>
       </c>
       <c r="I6" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J6" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
@@ -6877,19 +6874,19 @@
         <v>24</v>
       </c>
       <c r="F7" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G7" s="100" t="s">
-        <v>275</v>
-      </c>
-      <c r="H7" s="100" t="s">
-        <v>300</v>
+        <v>265</v>
+      </c>
+      <c r="G7" s="52" t="s">
+        <v>274</v>
+      </c>
+      <c r="H7" s="52" t="s">
+        <v>299</v>
       </c>
       <c r="I7" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J7" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
@@ -6907,19 +6904,19 @@
         <v>24</v>
       </c>
       <c r="F8" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G8" s="100" t="s">
+        <v>265</v>
+      </c>
+      <c r="G8" s="52" t="s">
+        <v>314</v>
+      </c>
+      <c r="H8" s="52" t="s">
         <v>315</v>
       </c>
-      <c r="H8" s="100" t="s">
-        <v>316</v>
-      </c>
       <c r="I8" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J8" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
@@ -6937,19 +6934,19 @@
         <v>24</v>
       </c>
       <c r="F9" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G9" s="100" t="s">
-        <v>317</v>
-      </c>
-      <c r="H9" s="100" t="s">
-        <v>344</v>
+        <v>265</v>
+      </c>
+      <c r="G9" s="52" t="s">
+        <v>316</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>343</v>
       </c>
       <c r="I9" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J9" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
@@ -6967,19 +6964,19 @@
         <v>24</v>
       </c>
       <c r="F10" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G10" s="100" t="s">
-        <v>318</v>
-      </c>
-      <c r="H10" s="100" t="s">
-        <v>345</v>
+        <v>265</v>
+      </c>
+      <c r="G10" s="52" t="s">
+        <v>317</v>
+      </c>
+      <c r="H10" s="52" t="s">
+        <v>344</v>
       </c>
       <c r="I10" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J10" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
@@ -6997,19 +6994,19 @@
         <v>24</v>
       </c>
       <c r="F11" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G11" s="100" t="s">
-        <v>319</v>
-      </c>
-      <c r="H11" s="100" t="s">
-        <v>346</v>
+        <v>265</v>
+      </c>
+      <c r="G11" s="52" t="s">
+        <v>318</v>
+      </c>
+      <c r="H11" s="52" t="s">
+        <v>345</v>
       </c>
       <c r="I11" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J11" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
@@ -7027,19 +7024,19 @@
         <v>24</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G12" s="100" t="s">
-        <v>320</v>
-      </c>
-      <c r="H12" s="100" t="s">
-        <v>347</v>
+        <v>265</v>
+      </c>
+      <c r="G12" s="52" t="s">
+        <v>319</v>
+      </c>
+      <c r="H12" s="52" t="s">
+        <v>346</v>
       </c>
       <c r="I12" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J12" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
@@ -7057,19 +7054,19 @@
         <v>24</v>
       </c>
       <c r="F13" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G13" s="100" t="s">
-        <v>321</v>
-      </c>
-      <c r="H13" s="100" t="s">
-        <v>348</v>
+        <v>265</v>
+      </c>
+      <c r="G13" s="52" t="s">
+        <v>320</v>
+      </c>
+      <c r="H13" s="52" t="s">
+        <v>347</v>
       </c>
       <c r="I13" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J13" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
@@ -7087,19 +7084,19 @@
         <v>24</v>
       </c>
       <c r="F14" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G14" s="100" t="s">
-        <v>322</v>
-      </c>
-      <c r="H14" s="100" t="s">
-        <v>349</v>
+        <v>265</v>
+      </c>
+      <c r="G14" s="52" t="s">
+        <v>321</v>
+      </c>
+      <c r="H14" s="52" t="s">
+        <v>348</v>
       </c>
       <c r="I14" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J14" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
@@ -7117,19 +7114,19 @@
         <v>24</v>
       </c>
       <c r="F15" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G15" s="100" t="s">
-        <v>323</v>
-      </c>
-      <c r="H15" s="100" t="s">
-        <v>350</v>
+        <v>265</v>
+      </c>
+      <c r="G15" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="H15" s="52" t="s">
+        <v>349</v>
       </c>
       <c r="I15" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J15" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
@@ -7147,19 +7144,19 @@
         <v>24</v>
       </c>
       <c r="F16" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G16" s="100" t="s">
-        <v>324</v>
-      </c>
-      <c r="H16" s="100" t="s">
-        <v>351</v>
+        <v>265</v>
+      </c>
+      <c r="G16" s="52" t="s">
+        <v>323</v>
+      </c>
+      <c r="H16" s="52" t="s">
+        <v>350</v>
       </c>
       <c r="I16" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J16" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
@@ -7177,19 +7174,19 @@
         <v>24</v>
       </c>
       <c r="F17" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G17" s="100" t="s">
-        <v>325</v>
-      </c>
-      <c r="H17" s="100" t="s">
-        <v>352</v>
+        <v>265</v>
+      </c>
+      <c r="G17" s="52" t="s">
+        <v>324</v>
+      </c>
+      <c r="H17" s="52" t="s">
+        <v>351</v>
       </c>
       <c r="I17" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J17" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
@@ -7207,19 +7204,19 @@
         <v>24</v>
       </c>
       <c r="F18" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G18" s="100" t="s">
-        <v>326</v>
-      </c>
-      <c r="H18" s="100" t="s">
-        <v>353</v>
+        <v>265</v>
+      </c>
+      <c r="G18" s="52" t="s">
+        <v>325</v>
+      </c>
+      <c r="H18" s="52" t="s">
+        <v>352</v>
       </c>
       <c r="I18" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J18" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
@@ -7237,19 +7234,19 @@
         <v>24</v>
       </c>
       <c r="F19" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G19" s="100" t="s">
-        <v>327</v>
-      </c>
-      <c r="H19" s="100" t="s">
-        <v>354</v>
+        <v>265</v>
+      </c>
+      <c r="G19" s="52" t="s">
+        <v>326</v>
+      </c>
+      <c r="H19" s="52" t="s">
+        <v>353</v>
       </c>
       <c r="I19" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J19" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
@@ -7267,19 +7264,19 @@
         <v>24</v>
       </c>
       <c r="F20" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G20" s="100" t="s">
-        <v>328</v>
-      </c>
-      <c r="H20" s="100" t="s">
-        <v>355</v>
+        <v>265</v>
+      </c>
+      <c r="G20" s="52" t="s">
+        <v>327</v>
+      </c>
+      <c r="H20" s="52" t="s">
+        <v>354</v>
       </c>
       <c r="I20" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J20" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
@@ -7297,19 +7294,19 @@
         <v>24</v>
       </c>
       <c r="F21" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G21" s="100" t="s">
-        <v>329</v>
-      </c>
-      <c r="H21" s="100" t="s">
-        <v>369</v>
+        <v>265</v>
+      </c>
+      <c r="G21" s="52" t="s">
+        <v>328</v>
+      </c>
+      <c r="H21" s="52" t="s">
+        <v>368</v>
       </c>
       <c r="I21" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J21" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
@@ -7327,19 +7324,19 @@
         <v>24</v>
       </c>
       <c r="F22" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G22" s="100" t="s">
-        <v>330</v>
-      </c>
-      <c r="H22" s="100" t="s">
-        <v>356</v>
+        <v>265</v>
+      </c>
+      <c r="G22" s="52" t="s">
+        <v>329</v>
+      </c>
+      <c r="H22" s="52" t="s">
+        <v>355</v>
       </c>
       <c r="I22" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J22" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
@@ -7357,19 +7354,19 @@
         <v>24</v>
       </c>
       <c r="F23" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G23" s="100" t="s">
-        <v>331</v>
-      </c>
-      <c r="H23" s="100" t="s">
-        <v>357</v>
+        <v>265</v>
+      </c>
+      <c r="G23" s="52" t="s">
+        <v>330</v>
+      </c>
+      <c r="H23" s="52" t="s">
+        <v>356</v>
       </c>
       <c r="I23" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J23" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
@@ -7387,19 +7384,19 @@
         <v>24</v>
       </c>
       <c r="F24" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G24" s="100" t="s">
-        <v>332</v>
-      </c>
-      <c r="H24" s="100" t="s">
-        <v>358</v>
+        <v>265</v>
+      </c>
+      <c r="G24" s="52" t="s">
+        <v>331</v>
+      </c>
+      <c r="H24" s="52" t="s">
+        <v>357</v>
       </c>
       <c r="I24" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J24" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
@@ -7417,19 +7414,19 @@
         <v>24</v>
       </c>
       <c r="F25" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G25" s="100" t="s">
-        <v>333</v>
-      </c>
-      <c r="H25" s="100" t="s">
-        <v>359</v>
+        <v>265</v>
+      </c>
+      <c r="G25" s="52" t="s">
+        <v>332</v>
+      </c>
+      <c r="H25" s="52" t="s">
+        <v>358</v>
       </c>
       <c r="I25" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J25" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
@@ -7447,19 +7444,19 @@
         <v>24</v>
       </c>
       <c r="F26" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G26" s="100" t="s">
-        <v>334</v>
-      </c>
-      <c r="H26" s="100" t="s">
-        <v>360</v>
+        <v>265</v>
+      </c>
+      <c r="G26" s="52" t="s">
+        <v>333</v>
+      </c>
+      <c r="H26" s="52" t="s">
+        <v>359</v>
       </c>
       <c r="I26" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J26" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
@@ -7477,19 +7474,19 @@
         <v>24</v>
       </c>
       <c r="F27" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G27" s="100" t="s">
-        <v>335</v>
-      </c>
-      <c r="H27" s="100" t="s">
-        <v>361</v>
+        <v>265</v>
+      </c>
+      <c r="G27" s="52" t="s">
+        <v>334</v>
+      </c>
+      <c r="H27" s="52" t="s">
+        <v>360</v>
       </c>
       <c r="I27" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J27" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
@@ -7507,19 +7504,19 @@
         <v>24</v>
       </c>
       <c r="F28" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G28" s="100" t="s">
-        <v>336</v>
-      </c>
-      <c r="H28" s="100" t="s">
-        <v>362</v>
+        <v>265</v>
+      </c>
+      <c r="G28" s="52" t="s">
+        <v>335</v>
+      </c>
+      <c r="H28" s="52" t="s">
+        <v>361</v>
       </c>
       <c r="I28" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J28" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
@@ -7537,19 +7534,19 @@
         <v>24</v>
       </c>
       <c r="F29" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G29" s="100" t="s">
-        <v>337</v>
-      </c>
-      <c r="H29" s="100" t="s">
-        <v>363</v>
+        <v>265</v>
+      </c>
+      <c r="G29" s="52" t="s">
+        <v>336</v>
+      </c>
+      <c r="H29" s="52" t="s">
+        <v>362</v>
       </c>
       <c r="I29" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J29" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
@@ -7567,19 +7564,19 @@
         <v>24</v>
       </c>
       <c r="F30" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G30" s="100" t="s">
-        <v>338</v>
-      </c>
-      <c r="H30" s="100" t="s">
-        <v>364</v>
+        <v>265</v>
+      </c>
+      <c r="G30" s="52" t="s">
+        <v>337</v>
+      </c>
+      <c r="H30" s="52" t="s">
+        <v>363</v>
       </c>
       <c r="I30" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J30" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
@@ -7597,19 +7594,19 @@
         <v>24</v>
       </c>
       <c r="F31" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G31" s="100" t="s">
-        <v>339</v>
-      </c>
-      <c r="H31" s="100" t="s">
-        <v>365</v>
+        <v>265</v>
+      </c>
+      <c r="G31" s="52" t="s">
+        <v>338</v>
+      </c>
+      <c r="H31" s="52" t="s">
+        <v>364</v>
       </c>
       <c r="I31" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J31" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
@@ -7627,19 +7624,19 @@
         <v>24</v>
       </c>
       <c r="F32" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G32" s="100" t="s">
-        <v>340</v>
-      </c>
-      <c r="H32" s="100" t="s">
-        <v>366</v>
+        <v>265</v>
+      </c>
+      <c r="G32" s="52" t="s">
+        <v>339</v>
+      </c>
+      <c r="H32" s="52" t="s">
+        <v>365</v>
       </c>
       <c r="I32" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J32" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.3">
@@ -7657,19 +7654,19 @@
         <v>24</v>
       </c>
       <c r="F33" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G33" s="100" t="s">
-        <v>341</v>
-      </c>
-      <c r="H33" s="100" t="s">
-        <v>367</v>
+        <v>265</v>
+      </c>
+      <c r="G33" s="52" t="s">
+        <v>340</v>
+      </c>
+      <c r="H33" s="52" t="s">
+        <v>366</v>
       </c>
       <c r="I33" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J33" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
@@ -7687,19 +7684,19 @@
         <v>24</v>
       </c>
       <c r="F34" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G34" s="100" t="s">
-        <v>342</v>
-      </c>
-      <c r="H34" s="100" t="s">
-        <v>368</v>
+        <v>265</v>
+      </c>
+      <c r="G34" s="52" t="s">
+        <v>341</v>
+      </c>
+      <c r="H34" s="52" t="s">
+        <v>367</v>
       </c>
       <c r="I34" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J34" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.3">
@@ -7717,19 +7714,19 @@
         <v>24</v>
       </c>
       <c r="F35" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G35" s="100" t="s">
-        <v>343</v>
-      </c>
-      <c r="H35" s="100" t="s">
-        <v>381</v>
+        <v>265</v>
+      </c>
+      <c r="G35" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="H35" s="52" t="s">
+        <v>380</v>
       </c>
       <c r="I35" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J35" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.3">
@@ -7747,19 +7744,19 @@
         <v>24</v>
       </c>
       <c r="F36" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G36" s="100" t="s">
-        <v>370</v>
-      </c>
-      <c r="H36" s="100" t="s">
-        <v>382</v>
+        <v>265</v>
+      </c>
+      <c r="G36" s="52" t="s">
+        <v>369</v>
+      </c>
+      <c r="H36" s="52" t="s">
+        <v>381</v>
       </c>
       <c r="I36" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J36" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.3">
@@ -7777,19 +7774,19 @@
         <v>24</v>
       </c>
       <c r="F37" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G37" s="100" t="s">
-        <v>371</v>
-      </c>
-      <c r="H37" s="100" t="s">
-        <v>383</v>
+        <v>265</v>
+      </c>
+      <c r="G37" s="52" t="s">
+        <v>370</v>
+      </c>
+      <c r="H37" s="52" t="s">
+        <v>382</v>
       </c>
       <c r="I37" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J37" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.3">
@@ -7807,19 +7804,19 @@
         <v>24</v>
       </c>
       <c r="F38" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G38" s="100" t="s">
-        <v>372</v>
-      </c>
-      <c r="H38" s="100" t="s">
-        <v>384</v>
+        <v>265</v>
+      </c>
+      <c r="G38" s="52" t="s">
+        <v>371</v>
+      </c>
+      <c r="H38" s="52" t="s">
+        <v>383</v>
       </c>
       <c r="I38" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J38" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.3">
@@ -7837,19 +7834,19 @@
         <v>24</v>
       </c>
       <c r="F39" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G39" s="100" t="s">
-        <v>373</v>
-      </c>
-      <c r="H39" s="100" t="s">
-        <v>385</v>
+        <v>265</v>
+      </c>
+      <c r="G39" s="52" t="s">
+        <v>372</v>
+      </c>
+      <c r="H39" s="52" t="s">
+        <v>384</v>
       </c>
       <c r="I39" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J39" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
@@ -7867,19 +7864,19 @@
         <v>24</v>
       </c>
       <c r="F40" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G40" s="100" t="s">
-        <v>374</v>
-      </c>
-      <c r="H40" s="100" t="s">
-        <v>386</v>
+        <v>265</v>
+      </c>
+      <c r="G40" s="52" t="s">
+        <v>373</v>
+      </c>
+      <c r="H40" s="52" t="s">
+        <v>385</v>
       </c>
       <c r="I40" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J40" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
@@ -7897,19 +7894,19 @@
         <v>24</v>
       </c>
       <c r="F41" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G41" s="100" t="s">
-        <v>375</v>
-      </c>
-      <c r="H41" s="100" t="s">
-        <v>387</v>
+        <v>265</v>
+      </c>
+      <c r="G41" s="52" t="s">
+        <v>374</v>
+      </c>
+      <c r="H41" s="52" t="s">
+        <v>386</v>
       </c>
       <c r="I41" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J41" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.3">
@@ -7927,19 +7924,19 @@
         <v>24</v>
       </c>
       <c r="F42" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G42" s="100" t="s">
-        <v>376</v>
-      </c>
-      <c r="H42" s="100" t="s">
-        <v>388</v>
+        <v>265</v>
+      </c>
+      <c r="G42" s="52" t="s">
+        <v>375</v>
+      </c>
+      <c r="H42" s="52" t="s">
+        <v>387</v>
       </c>
       <c r="I42" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J42" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.3">
@@ -7957,19 +7954,19 @@
         <v>24</v>
       </c>
       <c r="F43" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G43" s="100" t="s">
-        <v>377</v>
-      </c>
-      <c r="H43" s="100" t="s">
-        <v>389</v>
+        <v>265</v>
+      </c>
+      <c r="G43" s="52" t="s">
+        <v>376</v>
+      </c>
+      <c r="H43" s="52" t="s">
+        <v>388</v>
       </c>
       <c r="I43" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J43" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
@@ -7987,19 +7984,19 @@
         <v>24</v>
       </c>
       <c r="F44" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G44" s="100" t="s">
-        <v>378</v>
-      </c>
-      <c r="H44" s="100" t="s">
-        <v>390</v>
+        <v>265</v>
+      </c>
+      <c r="G44" s="52" t="s">
+        <v>377</v>
+      </c>
+      <c r="H44" s="52" t="s">
+        <v>389</v>
       </c>
       <c r="I44" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J44" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.3">
@@ -8017,19 +8014,19 @@
         <v>24</v>
       </c>
       <c r="F45" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G45" s="100" t="s">
-        <v>379</v>
-      </c>
-      <c r="H45" s="100" t="s">
-        <v>391</v>
+        <v>265</v>
+      </c>
+      <c r="G45" s="52" t="s">
+        <v>378</v>
+      </c>
+      <c r="H45" s="52" t="s">
+        <v>390</v>
       </c>
       <c r="I45" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J45" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.3">
@@ -8047,19 +8044,19 @@
         <v>24</v>
       </c>
       <c r="F46" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G46" s="100" t="s">
-        <v>380</v>
-      </c>
-      <c r="H46" s="100" t="s">
-        <v>392</v>
+        <v>265</v>
+      </c>
+      <c r="G46" s="52" t="s">
+        <v>379</v>
+      </c>
+      <c r="H46" s="52" t="s">
+        <v>391</v>
       </c>
       <c r="I46" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J46" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
@@ -8077,19 +8074,19 @@
         <v>24</v>
       </c>
       <c r="F47" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G47" s="100" t="s">
-        <v>403</v>
-      </c>
-      <c r="H47" s="100" t="s">
-        <v>393</v>
+        <v>265</v>
+      </c>
+      <c r="G47" s="52" t="s">
+        <v>402</v>
+      </c>
+      <c r="H47" s="52" t="s">
+        <v>392</v>
       </c>
       <c r="I47" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J47" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
@@ -8107,19 +8104,19 @@
         <v>24</v>
       </c>
       <c r="F48" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G48" s="100" t="s">
-        <v>404</v>
-      </c>
-      <c r="H48" s="100" t="s">
-        <v>394</v>
+        <v>265</v>
+      </c>
+      <c r="G48" s="52" t="s">
+        <v>403</v>
+      </c>
+      <c r="H48" s="52" t="s">
+        <v>393</v>
       </c>
       <c r="I48" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J48" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.3">
@@ -8137,19 +8134,19 @@
         <v>24</v>
       </c>
       <c r="F49" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G49" s="100" t="s">
-        <v>405</v>
-      </c>
-      <c r="H49" s="100" t="s">
-        <v>395</v>
+        <v>265</v>
+      </c>
+      <c r="G49" s="52" t="s">
+        <v>404</v>
+      </c>
+      <c r="H49" s="52" t="s">
+        <v>394</v>
       </c>
       <c r="I49" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J49" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.3">
@@ -8167,19 +8164,19 @@
         <v>24</v>
       </c>
       <c r="F50" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G50" s="100" t="s">
-        <v>406</v>
-      </c>
-      <c r="H50" s="100" t="s">
-        <v>396</v>
+        <v>265</v>
+      </c>
+      <c r="G50" s="52" t="s">
+        <v>405</v>
+      </c>
+      <c r="H50" s="52" t="s">
+        <v>395</v>
       </c>
       <c r="I50" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J50" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.3">
@@ -8197,19 +8194,19 @@
         <v>24</v>
       </c>
       <c r="F51" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G51" s="100" t="s">
-        <v>407</v>
-      </c>
-      <c r="H51" s="100" t="s">
-        <v>397</v>
+        <v>265</v>
+      </c>
+      <c r="G51" s="52" t="s">
+        <v>406</v>
+      </c>
+      <c r="H51" s="52" t="s">
+        <v>396</v>
       </c>
       <c r="I51" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J51" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.3">
@@ -8227,19 +8224,19 @@
         <v>24</v>
       </c>
       <c r="F52" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G52" s="100" t="s">
-        <v>408</v>
-      </c>
-      <c r="H52" s="100" t="s">
-        <v>398</v>
+        <v>265</v>
+      </c>
+      <c r="G52" s="52" t="s">
+        <v>407</v>
+      </c>
+      <c r="H52" s="52" t="s">
+        <v>397</v>
       </c>
       <c r="I52" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J52" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.3">
@@ -8257,19 +8254,19 @@
         <v>24</v>
       </c>
       <c r="F53" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G53" s="100" t="s">
-        <v>409</v>
-      </c>
-      <c r="H53" s="100" t="s">
-        <v>399</v>
+        <v>265</v>
+      </c>
+      <c r="G53" s="52" t="s">
+        <v>408</v>
+      </c>
+      <c r="H53" s="52" t="s">
+        <v>398</v>
       </c>
       <c r="I53" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J53" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.3">
@@ -8287,19 +8284,19 @@
         <v>24</v>
       </c>
       <c r="F54" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G54" s="100" t="s">
-        <v>410</v>
-      </c>
-      <c r="H54" s="100" t="s">
-        <v>400</v>
+        <v>265</v>
+      </c>
+      <c r="G54" s="52" t="s">
+        <v>409</v>
+      </c>
+      <c r="H54" s="52" t="s">
+        <v>399</v>
       </c>
       <c r="I54" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J54" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.3">
@@ -8317,19 +8314,19 @@
         <v>24</v>
       </c>
       <c r="F55" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G55" s="100" t="s">
-        <v>411</v>
-      </c>
-      <c r="H55" s="100" t="s">
-        <v>401</v>
+        <v>265</v>
+      </c>
+      <c r="G55" s="52" t="s">
+        <v>410</v>
+      </c>
+      <c r="H55" s="52" t="s">
+        <v>400</v>
       </c>
       <c r="I55" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J55" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.3">
@@ -8347,19 +8344,19 @@
         <v>24</v>
       </c>
       <c r="F56" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="G56" s="100" t="s">
-        <v>412</v>
-      </c>
-      <c r="H56" s="100" t="s">
-        <v>402</v>
+        <v>265</v>
+      </c>
+      <c r="G56" s="52" t="s">
+        <v>411</v>
+      </c>
+      <c r="H56" s="52" t="s">
+        <v>401</v>
       </c>
       <c r="I56" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J56" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.3">
@@ -8377,19 +8374,19 @@
         <v>24</v>
       </c>
       <c r="F57" s="52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G57" s="52" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H57" s="52" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I57" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J57" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.3">
@@ -8407,19 +8404,19 @@
         <v>24</v>
       </c>
       <c r="F58" s="52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G58" s="52" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H58" s="52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I58" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J58" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.3">
@@ -8437,19 +8434,19 @@
         <v>24</v>
       </c>
       <c r="F59" s="52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G59" s="52" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H59" s="52" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I59" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J59" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.3">
@@ -8467,19 +8464,19 @@
         <v>24</v>
       </c>
       <c r="F60" s="52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G60" s="52" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H60" s="52" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I60" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J60" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.3">
@@ -8497,19 +8494,19 @@
         <v>24</v>
       </c>
       <c r="F61" s="52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G61" s="52" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H61" s="52" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I61" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J61" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.3">
@@ -8527,19 +8524,19 @@
         <v>24</v>
       </c>
       <c r="F62" s="52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G62" s="52" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H62" s="52" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I62" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J62" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.3">
@@ -8557,19 +8554,19 @@
         <v>24</v>
       </c>
       <c r="F63" s="52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G63" s="52" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H63" s="52" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I63" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J63" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.3">
@@ -8587,19 +8584,19 @@
         <v>24</v>
       </c>
       <c r="F64" s="52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G64" s="52" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H64" s="52" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I64" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J64" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.3">
@@ -8617,19 +8614,19 @@
         <v>24</v>
       </c>
       <c r="F65" s="52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G65" s="52" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H65" s="52" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I65" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J65" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.3">
@@ -8647,1009 +8644,1009 @@
         <v>24</v>
       </c>
       <c r="F66" s="52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G66" s="52" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H66" s="52" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I66" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J66" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B67" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C67" s="101" t="str" cm="1">
+      <c r="B67" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C67" s="100" t="str" cm="1">
         <f t="array" ref="C67">UPPER(INDEX(_xlfn.TEXTSPLIT($F67, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D67" s="102" t="s">
+      <c r="D67" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E67" s="102" t="s">
+      <c r="E67" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F67" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G67" s="102" t="s">
-        <v>270</v>
-      </c>
-      <c r="H67" s="102" t="s">
-        <v>295</v>
-      </c>
-      <c r="I67" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J67" s="102" t="s">
-        <v>314</v>
+      <c r="F67" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G67" s="101" t="s">
+        <v>269</v>
+      </c>
+      <c r="H67" s="101" t="s">
+        <v>294</v>
+      </c>
+      <c r="I67" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J67" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B68" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C68" s="101" t="str" cm="1">
+      <c r="B68" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C68" s="100" t="str" cm="1">
         <f t="array" ref="C68">UPPER(INDEX(_xlfn.TEXTSPLIT($F68, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D68" s="102" t="s">
+      <c r="D68" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E68" s="102" t="s">
+      <c r="E68" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F68" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G68" s="102" t="s">
-        <v>271</v>
-      </c>
-      <c r="H68" s="102" t="s">
-        <v>296</v>
-      </c>
-      <c r="I68" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J68" s="102" t="s">
-        <v>314</v>
+      <c r="F68" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G68" s="101" t="s">
+        <v>270</v>
+      </c>
+      <c r="H68" s="101" t="s">
+        <v>295</v>
+      </c>
+      <c r="I68" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J68" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B69" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C69" s="101" t="str" cm="1">
+      <c r="B69" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C69" s="100" t="str" cm="1">
         <f t="array" ref="C69">UPPER(INDEX(_xlfn.TEXTSPLIT($F69, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D69" s="102" t="s">
+      <c r="D69" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E69" s="102" t="s">
+      <c r="E69" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F69" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G69" s="102" t="s">
-        <v>272</v>
-      </c>
-      <c r="H69" s="102" t="s">
-        <v>297</v>
-      </c>
-      <c r="I69" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J69" s="102" t="s">
-        <v>314</v>
+      <c r="F69" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G69" s="101" t="s">
+        <v>271</v>
+      </c>
+      <c r="H69" s="101" t="s">
+        <v>296</v>
+      </c>
+      <c r="I69" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J69" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B70" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C70" s="101" t="str" cm="1">
+      <c r="B70" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C70" s="100" t="str" cm="1">
         <f t="array" ref="C70">UPPER(INDEX(_xlfn.TEXTSPLIT($F70, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D70" s="102" t="s">
+      <c r="D70" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E70" s="102" t="s">
+      <c r="E70" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F70" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G70" s="102" t="s">
-        <v>273</v>
-      </c>
-      <c r="H70" s="102" t="s">
-        <v>298</v>
-      </c>
-      <c r="I70" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J70" s="102" t="s">
-        <v>314</v>
+      <c r="F70" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G70" s="101" t="s">
+        <v>272</v>
+      </c>
+      <c r="H70" s="101" t="s">
+        <v>297</v>
+      </c>
+      <c r="I70" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J70" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B71" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C71" s="101" t="str" cm="1">
+      <c r="B71" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C71" s="100" t="str" cm="1">
         <f t="array" ref="C71">UPPER(INDEX(_xlfn.TEXTSPLIT($F71, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D71" s="102" t="s">
+      <c r="D71" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E71" s="102" t="s">
+      <c r="E71" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F71" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G71" s="102" t="s">
-        <v>274</v>
-      </c>
-      <c r="H71" s="102" t="s">
-        <v>299</v>
-      </c>
-      <c r="I71" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J71" s="102" t="s">
-        <v>314</v>
+      <c r="F71" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G71" s="101" t="s">
+        <v>273</v>
+      </c>
+      <c r="H71" s="101" t="s">
+        <v>298</v>
+      </c>
+      <c r="I71" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J71" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B72" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C72" s="101" t="str" cm="1">
+      <c r="B72" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C72" s="100" t="str" cm="1">
         <f t="array" ref="C72">UPPER(INDEX(_xlfn.TEXTSPLIT($F72, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D72" s="102" t="s">
+      <c r="D72" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E72" s="102" t="s">
+      <c r="E72" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F72" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G72" s="102" t="s">
-        <v>413</v>
-      </c>
-      <c r="H72" s="102" t="s">
-        <v>300</v>
-      </c>
-      <c r="I72" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J72" s="102" t="s">
-        <v>314</v>
+      <c r="F72" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G72" s="101" t="s">
+        <v>412</v>
+      </c>
+      <c r="H72" s="101" t="s">
+        <v>299</v>
+      </c>
+      <c r="I72" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J72" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B73" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C73" s="101" t="str" cm="1">
+      <c r="B73" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C73" s="100" t="str" cm="1">
         <f t="array" ref="C73">UPPER(INDEX(_xlfn.TEXTSPLIT($F73, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D73" s="102" t="s">
+      <c r="D73" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E73" s="102" t="s">
+      <c r="E73" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F73" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G73" s="102" t="s">
+      <c r="F73" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G73" s="101" t="s">
+        <v>314</v>
+      </c>
+      <c r="H73" s="101" t="s">
         <v>315</v>
       </c>
-      <c r="H73" s="102" t="s">
-        <v>316</v>
-      </c>
-      <c r="I73" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J73" s="102" t="s">
-        <v>314</v>
+      <c r="I73" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J73" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B74" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C74" s="101" t="str" cm="1">
+      <c r="B74" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C74" s="100" t="str" cm="1">
         <f t="array" ref="C74">UPPER(INDEX(_xlfn.TEXTSPLIT($F74, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D74" s="102" t="s">
+      <c r="D74" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E74" s="102" t="s">
+      <c r="E74" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F74" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G74" s="102" t="s">
+      <c r="F74" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G74" s="101" t="s">
+        <v>413</v>
+      </c>
+      <c r="H74" s="101" t="s">
         <v>414</v>
       </c>
-      <c r="H74" s="102" t="s">
-        <v>415</v>
-      </c>
-      <c r="I74" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J74" s="102" t="s">
-        <v>314</v>
+      <c r="I74" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J74" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B75" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C75" s="101" t="str" cm="1">
+      <c r="B75" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C75" s="100" t="str" cm="1">
         <f t="array" ref="C75">UPPER(INDEX(_xlfn.TEXTSPLIT($F75, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D75" s="102" t="s">
+      <c r="D75" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E75" s="102" t="s">
+      <c r="E75" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F75" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G75" s="102" t="s">
-        <v>286</v>
-      </c>
-      <c r="H75" s="102" t="s">
-        <v>416</v>
-      </c>
-      <c r="I75" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J75" s="102" t="s">
-        <v>314</v>
+      <c r="F75" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G75" s="101" t="s">
+        <v>285</v>
+      </c>
+      <c r="H75" s="101" t="s">
+        <v>415</v>
+      </c>
+      <c r="I75" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J75" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B76" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C76" s="101" t="str" cm="1">
+      <c r="B76" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C76" s="100" t="str" cm="1">
         <f t="array" ref="C76">UPPER(INDEX(_xlfn.TEXTSPLIT($F76, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D76" s="102" t="s">
+      <c r="D76" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E76" s="102" t="s">
+      <c r="E76" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F76" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G76" s="102" t="s">
-        <v>287</v>
-      </c>
-      <c r="H76" s="102" t="s">
-        <v>417</v>
-      </c>
-      <c r="I76" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J76" s="102" t="s">
-        <v>314</v>
+      <c r="F76" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G76" s="101" t="s">
+        <v>286</v>
+      </c>
+      <c r="H76" s="101" t="s">
+        <v>416</v>
+      </c>
+      <c r="I76" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J76" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B77" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C77" s="101" t="str" cm="1">
+      <c r="B77" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C77" s="100" t="str" cm="1">
         <f t="array" ref="C77">UPPER(INDEX(_xlfn.TEXTSPLIT($F77, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D77" s="102" t="s">
+      <c r="D77" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E77" s="102" t="s">
+      <c r="E77" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F77" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G77" s="102" t="s">
-        <v>288</v>
-      </c>
-      <c r="H77" s="102" t="s">
-        <v>418</v>
-      </c>
-      <c r="I77" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J77" s="102" t="s">
-        <v>314</v>
+      <c r="F77" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G77" s="101" t="s">
+        <v>287</v>
+      </c>
+      <c r="H77" s="101" t="s">
+        <v>417</v>
+      </c>
+      <c r="I77" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J77" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B78" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C78" s="101" t="str" cm="1">
+      <c r="B78" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C78" s="100" t="str" cm="1">
         <f t="array" ref="C78">UPPER(INDEX(_xlfn.TEXTSPLIT($F78, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D78" s="102" t="s">
+      <c r="D78" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E78" s="102" t="s">
+      <c r="E78" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F78" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G78" s="102" t="s">
-        <v>289</v>
-      </c>
-      <c r="H78" s="102" t="s">
-        <v>419</v>
-      </c>
-      <c r="I78" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J78" s="102" t="s">
-        <v>314</v>
+      <c r="F78" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G78" s="101" t="s">
+        <v>288</v>
+      </c>
+      <c r="H78" s="101" t="s">
+        <v>418</v>
+      </c>
+      <c r="I78" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J78" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B79" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C79" s="101" t="str" cm="1">
+      <c r="B79" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C79" s="100" t="str" cm="1">
         <f t="array" ref="C79">UPPER(INDEX(_xlfn.TEXTSPLIT($F79, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D79" s="102" t="s">
+      <c r="D79" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E79" s="102" t="s">
+      <c r="E79" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F79" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G79" s="102" t="s">
-        <v>290</v>
-      </c>
-      <c r="H79" s="102" t="s">
-        <v>420</v>
-      </c>
-      <c r="I79" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J79" s="102" t="s">
-        <v>314</v>
+      <c r="F79" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G79" s="101" t="s">
+        <v>289</v>
+      </c>
+      <c r="H79" s="101" t="s">
+        <v>419</v>
+      </c>
+      <c r="I79" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J79" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B80" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C80" s="101" t="str" cm="1">
+      <c r="B80" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C80" s="100" t="str" cm="1">
         <f t="array" ref="C80">UPPER(INDEX(_xlfn.TEXTSPLIT($F80, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D80" s="102" t="s">
+      <c r="D80" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E80" s="102" t="s">
+      <c r="E80" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F80" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G80" s="102" t="s">
-        <v>291</v>
-      </c>
-      <c r="H80" s="102" t="s">
-        <v>421</v>
-      </c>
-      <c r="I80" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J80" s="102" t="s">
-        <v>314</v>
+      <c r="F80" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G80" s="101" t="s">
+        <v>290</v>
+      </c>
+      <c r="H80" s="101" t="s">
+        <v>420</v>
+      </c>
+      <c r="I80" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J80" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B81" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C81" s="101" t="str" cm="1">
+      <c r="B81" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C81" s="100" t="str" cm="1">
         <f t="array" ref="C81">UPPER(INDEX(_xlfn.TEXTSPLIT($F81, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D81" s="102" t="s">
+      <c r="D81" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E81" s="102" t="s">
+      <c r="E81" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F81" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G81" s="102" t="s">
-        <v>292</v>
-      </c>
-      <c r="H81" s="102" t="s">
-        <v>422</v>
-      </c>
-      <c r="I81" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J81" s="102" t="s">
-        <v>314</v>
+      <c r="F81" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G81" s="101" t="s">
+        <v>291</v>
+      </c>
+      <c r="H81" s="101" t="s">
+        <v>421</v>
+      </c>
+      <c r="I81" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J81" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B82" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C82" s="101" t="str" cm="1">
+      <c r="B82" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C82" s="100" t="str" cm="1">
         <f t="array" ref="C82">UPPER(INDEX(_xlfn.TEXTSPLIT($F82, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D82" s="102" t="s">
+      <c r="D82" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E82" s="102" t="s">
+      <c r="E82" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F82" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G82" s="102" t="s">
-        <v>293</v>
-      </c>
-      <c r="H82" s="102" t="s">
-        <v>423</v>
-      </c>
-      <c r="I82" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J82" s="102" t="s">
-        <v>314</v>
+      <c r="F82" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G82" s="101" t="s">
+        <v>292</v>
+      </c>
+      <c r="H82" s="101" t="s">
+        <v>422</v>
+      </c>
+      <c r="I82" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J82" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B83" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C83" s="101" t="str" cm="1">
+      <c r="B83" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C83" s="100" t="str" cm="1">
         <f t="array" ref="C83">UPPER(INDEX(_xlfn.TEXTSPLIT($F83, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D83" s="102" t="s">
+      <c r="D83" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E83" s="102" t="s">
+      <c r="E83" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F83" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G83" s="102" t="s">
-        <v>431</v>
-      </c>
-      <c r="H83" s="102" t="s">
-        <v>424</v>
-      </c>
-      <c r="I83" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J83" s="102" t="s">
-        <v>314</v>
+      <c r="F83" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G83" s="101" t="s">
+        <v>430</v>
+      </c>
+      <c r="H83" s="101" t="s">
+        <v>423</v>
+      </c>
+      <c r="I83" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J83" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B84" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C84" s="101" t="str" cm="1">
+      <c r="B84" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C84" s="100" t="str" cm="1">
         <f t="array" ref="C84">UPPER(INDEX(_xlfn.TEXTSPLIT($F84, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D84" s="102" t="s">
+      <c r="D84" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E84" s="102" t="s">
+      <c r="E84" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F84" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G84" s="102" t="s">
-        <v>432</v>
-      </c>
-      <c r="H84" s="102" t="s">
-        <v>425</v>
-      </c>
-      <c r="I84" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J84" s="102" t="s">
-        <v>314</v>
+      <c r="F84" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G84" s="101" t="s">
+        <v>431</v>
+      </c>
+      <c r="H84" s="101" t="s">
+        <v>424</v>
+      </c>
+      <c r="I84" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J84" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B85" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C85" s="101" t="str" cm="1">
+      <c r="B85" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C85" s="100" t="str" cm="1">
         <f t="array" ref="C85">UPPER(INDEX(_xlfn.TEXTSPLIT($F85, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D85" s="102" t="s">
+      <c r="D85" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E85" s="102" t="s">
+      <c r="E85" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F85" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G85" s="102" t="s">
-        <v>433</v>
-      </c>
-      <c r="H85" s="102" t="s">
-        <v>426</v>
-      </c>
-      <c r="I85" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J85" s="102" t="s">
-        <v>314</v>
+      <c r="F85" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G85" s="101" t="s">
+        <v>432</v>
+      </c>
+      <c r="H85" s="101" t="s">
+        <v>425</v>
+      </c>
+      <c r="I85" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J85" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B86" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C86" s="101" t="str" cm="1">
+      <c r="B86" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C86" s="100" t="str" cm="1">
         <f t="array" ref="C86">UPPER(INDEX(_xlfn.TEXTSPLIT($F86, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D86" s="102" t="s">
+      <c r="D86" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E86" s="102" t="s">
+      <c r="E86" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F86" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G86" s="102" t="s">
-        <v>434</v>
-      </c>
-      <c r="H86" s="102" t="s">
-        <v>427</v>
-      </c>
-      <c r="I86" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J86" s="102" t="s">
-        <v>314</v>
+      <c r="F86" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G86" s="101" t="s">
+        <v>433</v>
+      </c>
+      <c r="H86" s="101" t="s">
+        <v>426</v>
+      </c>
+      <c r="I86" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J86" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B87" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C87" s="101" t="str" cm="1">
+      <c r="B87" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C87" s="100" t="str" cm="1">
         <f t="array" ref="C87">UPPER(INDEX(_xlfn.TEXTSPLIT($F87, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D87" s="102" t="s">
+      <c r="D87" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E87" s="102" t="s">
+      <c r="E87" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F87" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G87" s="102" t="s">
-        <v>435</v>
-      </c>
-      <c r="H87" s="102" t="s">
-        <v>428</v>
-      </c>
-      <c r="I87" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J87" s="102" t="s">
-        <v>314</v>
+      <c r="F87" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G87" s="101" t="s">
+        <v>434</v>
+      </c>
+      <c r="H87" s="101" t="s">
+        <v>427</v>
+      </c>
+      <c r="I87" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J87" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B88" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C88" s="101" t="str" cm="1">
+      <c r="B88" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C88" s="100" t="str" cm="1">
         <f t="array" ref="C88">UPPER(INDEX(_xlfn.TEXTSPLIT($F88, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D88" s="102" t="s">
+      <c r="D88" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E88" s="102" t="s">
+      <c r="E88" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F88" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G88" s="102" t="s">
-        <v>436</v>
-      </c>
-      <c r="H88" s="102" t="s">
-        <v>429</v>
-      </c>
-      <c r="I88" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J88" s="102" t="s">
-        <v>314</v>
+      <c r="F88" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G88" s="101" t="s">
+        <v>435</v>
+      </c>
+      <c r="H88" s="101" t="s">
+        <v>428</v>
+      </c>
+      <c r="I88" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J88" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B89" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C89" s="101" t="str" cm="1">
+      <c r="B89" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C89" s="100" t="str" cm="1">
         <f t="array" ref="C89">UPPER(INDEX(_xlfn.TEXTSPLIT($F89, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D89" s="102" t="s">
+      <c r="D89" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E89" s="102" t="s">
+      <c r="E89" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F89" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G89" s="102" t="s">
-        <v>437</v>
-      </c>
-      <c r="H89" s="102" t="s">
-        <v>430</v>
-      </c>
-      <c r="I89" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J89" s="102" t="s">
-        <v>314</v>
+      <c r="F89" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G89" s="101" t="s">
+        <v>436</v>
+      </c>
+      <c r="H89" s="101" t="s">
+        <v>429</v>
+      </c>
+      <c r="I89" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J89" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B90" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C90" s="101" t="str" cm="1">
+      <c r="B90" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C90" s="100" t="str" cm="1">
         <f t="array" ref="C90">UPPER(INDEX(_xlfn.TEXTSPLIT($F90, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D90" s="102" t="s">
+      <c r="D90" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E90" s="102" t="s">
+      <c r="E90" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F90" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G90" s="102" t="s">
-        <v>276</v>
-      </c>
-      <c r="H90" s="102" t="s">
-        <v>301</v>
-      </c>
-      <c r="I90" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J90" s="102" t="s">
-        <v>314</v>
+      <c r="F90" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G90" s="101" t="s">
+        <v>275</v>
+      </c>
+      <c r="H90" s="101" t="s">
+        <v>300</v>
+      </c>
+      <c r="I90" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J90" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B91" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C91" s="101" t="str" cm="1">
+      <c r="B91" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C91" s="100" t="str" cm="1">
         <f t="array" ref="C91">UPPER(INDEX(_xlfn.TEXTSPLIT($F91, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D91" s="102" t="s">
+      <c r="D91" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E91" s="102" t="s">
+      <c r="E91" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F91" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G91" s="102" t="s">
-        <v>277</v>
-      </c>
-      <c r="H91" s="102" t="s">
-        <v>302</v>
-      </c>
-      <c r="I91" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J91" s="102" t="s">
-        <v>314</v>
+      <c r="F91" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G91" s="101" t="s">
+        <v>276</v>
+      </c>
+      <c r="H91" s="101" t="s">
+        <v>301</v>
+      </c>
+      <c r="I91" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J91" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B92" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C92" s="101" t="str" cm="1">
+      <c r="B92" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C92" s="100" t="str" cm="1">
         <f t="array" ref="C92">UPPER(INDEX(_xlfn.TEXTSPLIT($F92, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D92" s="102" t="s">
+      <c r="D92" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E92" s="102" t="s">
+      <c r="E92" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F92" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G92" s="102" t="s">
-        <v>278</v>
-      </c>
-      <c r="H92" s="102" t="s">
-        <v>303</v>
-      </c>
-      <c r="I92" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J92" s="102" t="s">
-        <v>314</v>
+      <c r="F92" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G92" s="101" t="s">
+        <v>277</v>
+      </c>
+      <c r="H92" s="101" t="s">
+        <v>302</v>
+      </c>
+      <c r="I92" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J92" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B93" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C93" s="101" t="str" cm="1">
+      <c r="B93" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C93" s="100" t="str" cm="1">
         <f t="array" ref="C93">UPPER(INDEX(_xlfn.TEXTSPLIT($F93, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D93" s="102" t="s">
+      <c r="D93" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E93" s="102" t="s">
+      <c r="E93" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F93" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G93" s="102" t="s">
-        <v>279</v>
-      </c>
-      <c r="H93" s="102" t="s">
-        <v>304</v>
-      </c>
-      <c r="I93" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J93" s="102" t="s">
-        <v>314</v>
+      <c r="F93" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G93" s="101" t="s">
+        <v>278</v>
+      </c>
+      <c r="H93" s="101" t="s">
+        <v>303</v>
+      </c>
+      <c r="I93" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J93" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B94" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C94" s="101" t="str" cm="1">
+      <c r="B94" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C94" s="100" t="str" cm="1">
         <f t="array" ref="C94">UPPER(INDEX(_xlfn.TEXTSPLIT($F94, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D94" s="102" t="s">
+      <c r="D94" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E94" s="102" t="s">
+      <c r="E94" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F94" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G94" s="102" t="s">
-        <v>280</v>
-      </c>
-      <c r="H94" s="102" t="s">
-        <v>305</v>
-      </c>
-      <c r="I94" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J94" s="102" t="s">
-        <v>314</v>
+      <c r="F94" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G94" s="101" t="s">
+        <v>279</v>
+      </c>
+      <c r="H94" s="101" t="s">
+        <v>304</v>
+      </c>
+      <c r="I94" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J94" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B95" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C95" s="101" t="str" cm="1">
+      <c r="B95" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C95" s="100" t="str" cm="1">
         <f t="array" ref="C95">UPPER(INDEX(_xlfn.TEXTSPLIT($F95, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D95" s="102" t="s">
+      <c r="D95" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E95" s="102" t="s">
+      <c r="E95" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F95" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G95" s="102" t="s">
-        <v>281</v>
-      </c>
-      <c r="H95" s="102" t="s">
-        <v>306</v>
-      </c>
-      <c r="I95" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J95" s="102" t="s">
-        <v>314</v>
+      <c r="F95" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G95" s="101" t="s">
+        <v>280</v>
+      </c>
+      <c r="H95" s="101" t="s">
+        <v>305</v>
+      </c>
+      <c r="I95" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J95" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B96" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C96" s="101" t="str" cm="1">
+      <c r="B96" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C96" s="100" t="str" cm="1">
         <f t="array" ref="C96">UPPER(INDEX(_xlfn.TEXTSPLIT($F96, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D96" s="102" t="s">
+      <c r="D96" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E96" s="102" t="s">
+      <c r="E96" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F96" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G96" s="102" t="s">
-        <v>282</v>
-      </c>
-      <c r="H96" s="102" t="s">
-        <v>307</v>
-      </c>
-      <c r="I96" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J96" s="102" t="s">
-        <v>314</v>
+      <c r="F96" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G96" s="101" t="s">
+        <v>281</v>
+      </c>
+      <c r="H96" s="101" t="s">
+        <v>306</v>
+      </c>
+      <c r="I96" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J96" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B97" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C97" s="101" t="str" cm="1">
+      <c r="B97" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C97" s="100" t="str" cm="1">
         <f t="array" ref="C97">UPPER(INDEX(_xlfn.TEXTSPLIT($F97, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D97" s="102" t="s">
+      <c r="D97" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E97" s="102" t="s">
+      <c r="E97" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F97" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G97" s="102" t="s">
-        <v>283</v>
-      </c>
-      <c r="H97" s="102" t="s">
-        <v>308</v>
-      </c>
-      <c r="I97" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J97" s="102" t="s">
-        <v>314</v>
+      <c r="F97" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G97" s="101" t="s">
+        <v>282</v>
+      </c>
+      <c r="H97" s="101" t="s">
+        <v>307</v>
+      </c>
+      <c r="I97" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J97" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B98" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C98" s="101" t="str" cm="1">
+      <c r="B98" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C98" s="100" t="str" cm="1">
         <f t="array" ref="C98">UPPER(INDEX(_xlfn.TEXTSPLIT($F98, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D98" s="102" t="s">
+      <c r="D98" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E98" s="102" t="s">
+      <c r="E98" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F98" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G98" s="102" t="s">
-        <v>284</v>
-      </c>
-      <c r="H98" s="102" t="s">
-        <v>309</v>
-      </c>
-      <c r="I98" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J98" s="102" t="s">
-        <v>314</v>
+      <c r="F98" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G98" s="101" t="s">
+        <v>283</v>
+      </c>
+      <c r="H98" s="101" t="s">
+        <v>308</v>
+      </c>
+      <c r="I98" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J98" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B99" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C99" s="101" t="str" cm="1">
+      <c r="B99" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C99" s="100" t="str" cm="1">
         <f t="array" ref="C99">UPPER(INDEX(_xlfn.TEXTSPLIT($F99, "-"), 3))</f>
         <v>INT</v>
       </c>
-      <c r="D99" s="102" t="s">
+      <c r="D99" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="E99" s="102" t="s">
+      <c r="E99" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F99" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="G99" s="102" t="s">
-        <v>285</v>
-      </c>
-      <c r="H99" s="102" t="s">
-        <v>310</v>
-      </c>
-      <c r="I99" s="102" t="s">
-        <v>312</v>
-      </c>
-      <c r="J99" s="102" t="s">
-        <v>314</v>
+      <c r="F99" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="G99" s="101" t="s">
+        <v>284</v>
+      </c>
+      <c r="H99" s="101" t="s">
+        <v>309</v>
+      </c>
+      <c r="I99" s="101" t="s">
+        <v>311</v>
+      </c>
+      <c r="J99" s="101" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -11510,9 +11507,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11660,26 +11660,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11703,9 +11692,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE6FBB9-F62F-4A7E-8E77-00C4B60C5C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA10B38-1B61-4CF0-A45C-C743C8650F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1654,7 +1654,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="440">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3183,6 +3183,14 @@
   </si>
   <si>
     <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_nginx_Base_Image/versions/0.0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-cs-chtap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.168.21</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5980,7 +5988,7 @@
         <v>437</v>
       </c>
       <c r="O2" s="1" t="str">
-        <f t="shared" ref="O2:O3" si="0">SUBSTITUTE(F2,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" ref="O2:O4" si="0">SUBSTITUTE(F2,"hazr-","")&amp;"-osdisk"</f>
         <v>t-cs-chtweb01-osdisk</v>
       </c>
       <c r="P2" s="1">
@@ -5993,7 +6001,7 @@
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1" t="str">
-        <f t="shared" ref="U2:U3" si="1">SUBSTITUTE(F2,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="U2:U6" si="1">SUBSTITUTE(F2,"hazr-","")&amp;"-nic"</f>
         <v>t-cs-chtweb01-nic</v>
       </c>
       <c r="V2" s="1" t="b">
@@ -6045,7 +6053,7 @@
         <v>252</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>257</v>
+        <v>439</v>
       </c>
       <c r="H3" s="81" t="s">
         <v>211</v>
@@ -6116,34 +6124,89 @@
       <c r="AF3" s="1"/>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="80"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H4" s="81" t="s">
+        <v>211</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2</v>
+      </c>
+      <c r="J4" s="1">
+        <v>8</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="O4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>t-cs-chtap01-osdisk</v>
+      </c>
+      <c r="P4" s="1">
+        <v>64</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
+      <c r="U4" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>t-cs-chtap01-nic</v>
+      </c>
+      <c r="V4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>3</v>
+      </c>
       <c r="AE4" s="1"/>
       <c r="AF4" s="1"/>
     </row>
@@ -6366,7 +6429,7 @@
         <v>252</v>
       </c>
       <c r="G3" s="88" t="str">
-        <f t="shared" ref="G3" si="0">SUBSTITUTE($F3,"hazr-","")&amp;"-disk01"</f>
+        <f t="shared" ref="G3:G4" si="0">SUBSTITUTE($F3,"hazr-","")&amp;"-disk01"</f>
         <v>t-cs-chtintweb01-disk01</v>
       </c>
       <c r="H3" s="88" t="s">
@@ -6404,22 +6467,56 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="96"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88"/>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
+      <c r="B4" s="88" t="s">
+        <v>223</v>
+      </c>
+      <c r="C4" s="88" t="s">
+        <v>214</v>
+      </c>
+      <c r="D4" s="88" t="s">
+        <v>250</v>
+      </c>
+      <c r="E4" s="93" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="95" t="s">
+        <v>438</v>
+      </c>
+      <c r="G4" s="88" t="str">
+        <f t="shared" si="0"/>
+        <v>t-cs-chtap01-disk01</v>
+      </c>
+      <c r="H4" s="88" t="s">
+        <v>213</v>
+      </c>
+      <c r="I4" s="88">
+        <v>128</v>
+      </c>
+      <c r="J4" s="88" t="str">
+        <f>SUBSTITUTE($F4,"hazr-","")&amp;"-disk02"</f>
+        <v>t-cs-chtap01-disk02</v>
+      </c>
+      <c r="K4" s="88" t="s">
+        <v>213</v>
+      </c>
+      <c r="L4" s="88">
+        <v>128</v>
+      </c>
+      <c r="M4" s="88">
+        <v>3</v>
+      </c>
+      <c r="N4" s="88" t="s">
+        <v>235</v>
+      </c>
+      <c r="O4" s="88" t="s">
+        <v>239</v>
+      </c>
+      <c r="P4" s="88" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q4" s="88" t="b">
+        <v>1</v>
+      </c>
       <c r="R4" s="56"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -11507,12 +11604,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11660,15 +11754,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11692,17 +11797,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9499B5E4-2BC7-44D8-8426-5DBB79986918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88D03EB-DD9F-44FE-BC97-D5295DF707B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4444,10 +4444,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_Base_Image/versions/0.0.6</t>
-  </si>
-  <si>
     <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_nginx_Base_Image/versions/0.0.5</t>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_Base_Image/versions/0.0.7</t>
   </si>
 </sst>
 </file>
@@ -4921,7 +4921,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5228,10 +5228,7 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -9543,7 +9540,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" s="102"/>
+      <c r="A2" s="73"/>
       <c r="B2" s="1" t="s">
         <v>189</v>
       </c>
@@ -9582,7 +9579,7 @@
         <v>187</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O2" s="1" t="str">
         <f t="shared" ref="O2:O6" si="0">SUBSTITUTE(F2,"hazr-","")&amp;"-osdisk"</f>
@@ -9631,7 +9628,7 @@
       <c r="AF2" s="1"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" s="102"/>
+      <c r="A3" s="73"/>
       <c r="B3" s="1" t="s">
         <v>189</v>
       </c>
@@ -9670,7 +9667,7 @@
         <v>187</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O3" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9719,7 +9716,7 @@
       <c r="AF3" s="1"/>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A4" s="103"/>
+      <c r="A4" s="102"/>
       <c r="B4" s="1" t="s">
         <v>189</v>
       </c>
@@ -9758,7 +9755,7 @@
         <v>187</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O4" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9845,7 +9842,7 @@
         <v>187</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O5" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9932,7 +9929,7 @@
         <v>187</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O6" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10019,7 +10016,7 @@
         <v>187</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O7" s="1" t="str">
         <f>SUBSTITUTE(F7,"hazr-","")&amp;"-osdisk"</f>
@@ -10106,7 +10103,7 @@
         <v>187</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O8" s="1" t="str">
         <f t="shared" ref="O8:O39" si="1">SUBSTITUTE(F8,"hazr-","")&amp;"-osdisk"</f>
@@ -10193,7 +10190,7 @@
         <v>187</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O9" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10280,7 +10277,7 @@
         <v>187</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O10" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10367,7 +10364,7 @@
         <v>187</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O11" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10454,7 +10451,7 @@
         <v>187</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O12" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10541,7 +10538,7 @@
         <v>187</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O13" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10628,7 +10625,7 @@
         <v>187</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O14" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10715,7 +10712,7 @@
         <v>187</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O15" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10802,7 +10799,7 @@
         <v>187</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O16" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10889,7 +10886,7 @@
         <v>187</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O17" s="1" t="str">
         <f t="shared" si="1"/>
@@ -10976,7 +10973,7 @@
         <v>187</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O18" s="1" t="str">
         <f t="shared" si="1"/>
@@ -11063,7 +11060,7 @@
         <v>187</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O19" s="1" t="str">
         <f t="shared" si="1"/>
@@ -11237,7 +11234,7 @@
         <v>187</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O21" s="1" t="str">
         <f t="shared" si="1"/>
@@ -11324,7 +11321,7 @@
         <v>187</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O22" s="1" t="str">
         <f t="shared" si="1"/>
@@ -11411,7 +11408,7 @@
         <v>187</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O23" s="1" t="str">
         <f t="shared" si="1"/>
@@ -11498,7 +11495,7 @@
         <v>187</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O24" s="1" t="str">
         <f t="shared" si="1"/>
@@ -11585,7 +11582,7 @@
         <v>187</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O25" s="1" t="str">
         <f t="shared" si="1"/>
@@ -11672,7 +11669,7 @@
         <v>187</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O26" s="1" t="str">
         <f t="shared" si="1"/>
@@ -11759,7 +11756,7 @@
         <v>187</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O27" s="1" t="str">
         <f t="shared" si="1"/>
@@ -11846,7 +11843,7 @@
         <v>187</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O28" s="1" t="str">
         <f t="shared" si="1"/>
@@ -11933,7 +11930,7 @@
         <v>187</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O29" s="1" t="str">
         <f t="shared" si="1"/>
@@ -12020,7 +12017,7 @@
         <v>187</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O30" s="1" t="str">
         <f t="shared" si="1"/>
@@ -12107,7 +12104,7 @@
         <v>187</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O31" s="1" t="str">
         <f t="shared" si="1"/>
@@ -12194,7 +12191,7 @@
         <v>187</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O32" s="1" t="str">
         <f t="shared" si="1"/>
@@ -12281,7 +12278,7 @@
         <v>187</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O33" s="1" t="str">
         <f t="shared" si="1"/>
@@ -12368,7 +12365,7 @@
         <v>187</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O34" s="1" t="str">
         <f t="shared" si="1"/>
@@ -12455,7 +12452,7 @@
         <v>187</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O35" s="1" t="str">
         <f t="shared" si="1"/>
@@ -12542,7 +12539,7 @@
         <v>187</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O36" s="1" t="str">
         <f t="shared" si="1"/>
@@ -12629,7 +12626,7 @@
         <v>187</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O37" s="1" t="str">
         <f t="shared" si="1"/>
@@ -12716,7 +12713,7 @@
         <v>187</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O38" s="1" t="str">
         <f t="shared" si="1"/>
@@ -12803,7 +12800,7 @@
         <v>187</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O39" s="1" t="str">
         <f t="shared" si="1"/>
@@ -12890,7 +12887,7 @@
         <v>187</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O40" s="1" t="str">
         <f t="shared" ref="O40:O64" si="2">SUBSTITUTE(F40,"hazr-","")&amp;"-osdisk"</f>
@@ -12977,7 +12974,7 @@
         <v>187</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O41" s="1" t="str">
         <f t="shared" si="2"/>
@@ -13064,7 +13061,7 @@
         <v>187</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O42" s="1" t="str">
         <f t="shared" si="2"/>
@@ -13151,7 +13148,7 @@
         <v>187</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O43" s="1" t="str">
         <f t="shared" si="2"/>
@@ -13238,7 +13235,7 @@
         <v>187</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O44" s="1" t="str">
         <f t="shared" si="2"/>
@@ -13325,7 +13322,7 @@
         <v>187</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O45" s="1" t="str">
         <f t="shared" si="2"/>
@@ -13412,7 +13409,7 @@
         <v>187</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O46" s="1" t="str">
         <f t="shared" si="2"/>
@@ -13499,7 +13496,7 @@
         <v>187</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O47" s="1" t="str">
         <f t="shared" si="2"/>
@@ -13586,7 +13583,7 @@
         <v>187</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O48" s="1" t="str">
         <f t="shared" si="2"/>
@@ -13673,7 +13670,7 @@
         <v>187</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O49" s="1" t="str">
         <f t="shared" si="2"/>
@@ -13760,7 +13757,7 @@
         <v>187</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O50" s="1" t="str">
         <f t="shared" si="2"/>
@@ -13847,7 +13844,7 @@
         <v>187</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O51" s="1" t="str">
         <f t="shared" si="2"/>
@@ -13934,7 +13931,7 @@
         <v>187</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O52" s="1" t="str">
         <f t="shared" si="2"/>
@@ -14021,7 +14018,7 @@
         <v>187</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O53" s="1" t="str">
         <f t="shared" si="2"/>
@@ -14108,7 +14105,7 @@
         <v>187</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O54" s="1" t="str">
         <f t="shared" si="2"/>
@@ -14195,7 +14192,7 @@
         <v>187</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O55" s="1" t="str">
         <f t="shared" si="2"/>
@@ -14282,7 +14279,7 @@
         <v>187</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O56" s="1" t="str">
         <f t="shared" si="2"/>
@@ -14369,7 +14366,7 @@
         <v>187</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O57" s="1" t="str">
         <f t="shared" si="2"/>
@@ -14456,7 +14453,7 @@
         <v>187</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O58" s="1" t="str">
         <f t="shared" si="2"/>
@@ -14543,7 +14540,7 @@
         <v>187</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O59" s="1" t="str">
         <f t="shared" si="2"/>
@@ -14630,7 +14627,7 @@
         <v>187</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O60" s="1" t="str">
         <f t="shared" si="2"/>
@@ -14717,7 +14714,7 @@
         <v>187</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O61" s="1" t="str">
         <f t="shared" si="2"/>
@@ -14804,7 +14801,7 @@
         <v>187</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O62" s="1" t="str">
         <f t="shared" si="2"/>
@@ -14891,7 +14888,7 @@
         <v>187</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O63" s="1" t="str">
         <f t="shared" si="2"/>
@@ -14978,7 +14975,7 @@
         <v>187</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O64" s="1" t="str">
         <f t="shared" si="2"/>
@@ -15065,7 +15062,7 @@
         <v>187</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O65" s="1" t="str">
         <f t="shared" ref="O65:O70" si="3">SUBSTITUTE(F65,"hazr-","")&amp;"-osdisk"</f>
@@ -15152,7 +15149,7 @@
         <v>187</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O66" s="1" t="str">
         <f t="shared" si="3"/>
@@ -15239,7 +15236,7 @@
         <v>187</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O67" s="1" t="str">
         <f t="shared" si="3"/>
@@ -15326,7 +15323,7 @@
         <v>187</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O68" s="1" t="str">
         <f t="shared" si="3"/>
@@ -15413,7 +15410,7 @@
         <v>187</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O69" s="1" t="str">
         <f t="shared" si="3"/>
@@ -15500,7 +15497,7 @@
         <v>187</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O70" s="1" t="str">
         <f t="shared" si="3"/>
@@ -21947,7 +21944,7 @@
         <v>205</v>
       </c>
       <c r="E68" s="84" t="str">
-        <f t="shared" ref="E68:E88" si="2">SUBSTITUTE(I68,"hazr-","")&amp;"-nsg"</f>
+        <f t="shared" ref="E68:E70" si="2">SUBSTITUTE(I68,"hazr-","")&amp;"-nsg"</f>
         <v>t-bdp-crkweb01-nsg</v>
       </c>
       <c r="F68" s="84" t="s">
@@ -30489,12 +30486,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -30642,15 +30636,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -30674,17 +30679,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -30486,9 +30486,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -30636,26 +30639,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -30679,9 +30671,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88D03EB-DD9F-44FE-BC97-D5295DF707B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DF0411-B88E-4AEE-BFE3-7BA8B831E90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9804,6 +9804,7 @@
       <c r="AF4" s="1"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A5" s="102"/>
       <c r="B5" s="1" t="s">
         <v>189</v>
       </c>
@@ -9891,6 +9892,7 @@
       <c r="AF5" s="1"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A6" s="102"/>
       <c r="B6" s="1" t="s">
         <v>189</v>
       </c>
@@ -9978,6 +9980,7 @@
       <c r="AF6" s="1"/>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A7" s="102"/>
       <c r="B7" s="1" t="s">
         <v>189</v>
       </c>
@@ -10065,6 +10068,7 @@
       <c r="AF7" s="1"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A8" s="102"/>
       <c r="B8" s="1" t="s">
         <v>189</v>
       </c>
@@ -10152,6 +10156,7 @@
       <c r="AF8" s="1"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A9" s="102"/>
       <c r="B9" s="1" t="s">
         <v>189</v>
       </c>
@@ -10239,6 +10244,7 @@
       <c r="AF9" s="1"/>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A10" s="102"/>
       <c r="B10" s="1" t="s">
         <v>189</v>
       </c>
@@ -10326,6 +10332,7 @@
       <c r="AF10" s="1"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A11" s="102"/>
       <c r="B11" s="1" t="s">
         <v>189</v>
       </c>
@@ -10413,6 +10420,7 @@
       <c r="AF11" s="1"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A12" s="102"/>
       <c r="B12" s="1" t="s">
         <v>189</v>
       </c>
@@ -10500,6 +10508,7 @@
       <c r="AF12" s="1"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A13" s="102"/>
       <c r="B13" s="1" t="s">
         <v>189</v>
       </c>
@@ -10587,6 +10596,7 @@
       <c r="AF13" s="1"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A14" s="102"/>
       <c r="B14" s="1" t="s">
         <v>189</v>
       </c>
@@ -10674,6 +10684,7 @@
       <c r="AF14" s="1"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A15" s="102"/>
       <c r="B15" s="1" t="s">
         <v>189</v>
       </c>
@@ -10761,6 +10772,7 @@
       <c r="AF15" s="1"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A16" s="102"/>
       <c r="B16" s="1" t="s">
         <v>189</v>
       </c>
@@ -10847,7 +10859,8 @@
       <c r="AE16" s="1"/>
       <c r="AF16" s="1"/>
     </row>
-    <row r="17" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A17" s="102"/>
       <c r="B17" s="1" t="s">
         <v>189</v>
       </c>
@@ -10934,7 +10947,8 @@
       <c r="AE17" s="1"/>
       <c r="AF17" s="1"/>
     </row>
-    <row r="18" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A18" s="102"/>
       <c r="B18" s="1" t="s">
         <v>189</v>
       </c>
@@ -11021,7 +11035,8 @@
       <c r="AE18" s="1"/>
       <c r="AF18" s="1"/>
     </row>
-    <row r="19" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A19" s="102"/>
       <c r="B19" s="1" t="s">
         <v>189</v>
       </c>
@@ -11108,7 +11123,8 @@
       <c r="AE19" s="1"/>
       <c r="AF19" s="1"/>
     </row>
-    <row r="20" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A20" s="102"/>
       <c r="B20" s="1" t="s">
         <v>189</v>
       </c>
@@ -11195,7 +11211,7 @@
       <c r="AE20" s="1"/>
       <c r="AF20" s="1"/>
     </row>
-    <row r="21" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>189</v>
       </c>
@@ -11282,7 +11298,7 @@
       <c r="AE21" s="1"/>
       <c r="AF21" s="1"/>
     </row>
-    <row r="22" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>189</v>
       </c>
@@ -11369,7 +11385,7 @@
       <c r="AE22" s="1"/>
       <c r="AF22" s="1"/>
     </row>
-    <row r="23" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>189</v>
       </c>
@@ -11456,7 +11472,7 @@
       <c r="AE23" s="1"/>
       <c r="AF23" s="1"/>
     </row>
-    <row r="24" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>189</v>
       </c>
@@ -11543,7 +11559,7 @@
       <c r="AE24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>189</v>
       </c>
@@ -11630,7 +11646,7 @@
       <c r="AE25" s="1"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>189</v>
       </c>
@@ -11717,7 +11733,7 @@
       <c r="AE26" s="1"/>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>189</v>
       </c>
@@ -11804,7 +11820,7 @@
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>189</v>
       </c>
@@ -11891,7 +11907,7 @@
       <c r="AE28" s="1"/>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>189</v>
       </c>
@@ -11978,7 +11994,7 @@
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>189</v>
       </c>
@@ -12065,7 +12081,7 @@
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>189</v>
       </c>
@@ -12152,7 +12168,7 @@
       <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>189</v>
       </c>
@@ -30486,12 +30502,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -30639,15 +30652,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -30671,17 +30695,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DF0411-B88E-4AEE-BFE3-7BA8B831E90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C2955B-977B-465A-8F55-1D5727CCCA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">LB!$B$1:$Q$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4454,7 +4455,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4576,6 +4577,14 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="10">
@@ -4921,7 +4930,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5229,6 +5238,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -11212,6 +11230,7 @@
       <c r="AF20" s="1"/>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A21" s="102"/>
       <c r="B21" s="1" t="s">
         <v>189</v>
       </c>
@@ -11299,6 +11318,7 @@
       <c r="AF21" s="1"/>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A22" s="102"/>
       <c r="B22" s="1" t="s">
         <v>189</v>
       </c>
@@ -11386,6 +11406,7 @@
       <c r="AF22" s="1"/>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A23" s="102"/>
       <c r="B23" s="1" t="s">
         <v>189</v>
       </c>
@@ -11473,6 +11494,7 @@
       <c r="AF23" s="1"/>
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A24" s="102"/>
       <c r="B24" s="1" t="s">
         <v>189</v>
       </c>
@@ -11560,6 +11582,7 @@
       <c r="AF24" s="1"/>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A25" s="102"/>
       <c r="B25" s="1" t="s">
         <v>189</v>
       </c>
@@ -11647,6 +11670,7 @@
       <c r="AF25" s="1"/>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A26" s="102"/>
       <c r="B26" s="1" t="s">
         <v>189</v>
       </c>
@@ -11734,6 +11758,7 @@
       <c r="AF26" s="1"/>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A27" s="102"/>
       <c r="B27" s="1" t="s">
         <v>189</v>
       </c>
@@ -11821,6 +11846,7 @@
       <c r="AF27" s="1"/>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A28" s="102"/>
       <c r="B28" s="1" t="s">
         <v>189</v>
       </c>
@@ -11908,6 +11934,7 @@
       <c r="AF28" s="1"/>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A29" s="102"/>
       <c r="B29" s="1" t="s">
         <v>189</v>
       </c>
@@ -11995,6 +12022,7 @@
       <c r="AF29" s="1"/>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A30" s="102"/>
       <c r="B30" s="1" t="s">
         <v>189</v>
       </c>
@@ -12082,6 +12110,7 @@
       <c r="AF30" s="1"/>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A31" s="102"/>
       <c r="B31" s="1" t="s">
         <v>189</v>
       </c>
@@ -12169,6 +12198,7 @@
       <c r="AF31" s="1"/>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A32" s="102"/>
       <c r="B32" s="1" t="s">
         <v>189</v>
       </c>
@@ -12255,7 +12285,8 @@
       <c r="AE32" s="1"/>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A33" s="102"/>
       <c r="B33" s="1" t="s">
         <v>189</v>
       </c>
@@ -12342,7 +12373,8 @@
       <c r="AE33" s="1"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A34" s="102"/>
       <c r="B34" s="1" t="s">
         <v>189</v>
       </c>
@@ -12429,7 +12461,8 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A35" s="102"/>
       <c r="B35" s="1" t="s">
         <v>189</v>
       </c>
@@ -12516,7 +12549,8 @@
       <c r="AE35" s="1"/>
       <c r="AF35" s="1"/>
     </row>
-    <row r="36" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A36" s="102"/>
       <c r="B36" s="1" t="s">
         <v>189</v>
       </c>
@@ -12603,7 +12637,8 @@
       <c r="AE36" s="1"/>
       <c r="AF36" s="1"/>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A37" s="102"/>
       <c r="B37" s="1" t="s">
         <v>189</v>
       </c>
@@ -12690,7 +12725,8 @@
       <c r="AE37" s="1"/>
       <c r="AF37" s="1"/>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A38" s="102"/>
       <c r="B38" s="1" t="s">
         <v>189</v>
       </c>
@@ -12777,7 +12813,8 @@
       <c r="AE38" s="1"/>
       <c r="AF38" s="1"/>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A39" s="102"/>
       <c r="B39" s="1" t="s">
         <v>189</v>
       </c>
@@ -12864,7 +12901,8 @@
       <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
     </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A40" s="102"/>
       <c r="B40" s="1" t="s">
         <v>189</v>
       </c>
@@ -12951,7 +12989,8 @@
       <c r="AE40" s="1"/>
       <c r="AF40" s="1"/>
     </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A41" s="102"/>
       <c r="B41" s="1" t="s">
         <v>189</v>
       </c>
@@ -13038,7 +13077,8 @@
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A42" s="102"/>
       <c r="B42" s="1" t="s">
         <v>189</v>
       </c>
@@ -13125,7 +13165,8 @@
       <c r="AE42" s="1"/>
       <c r="AF42" s="1"/>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A43" s="102"/>
       <c r="B43" s="1" t="s">
         <v>189</v>
       </c>
@@ -13212,7 +13253,8 @@
       <c r="AE43" s="1"/>
       <c r="AF43" s="1"/>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A44" s="102"/>
       <c r="B44" s="1" t="s">
         <v>189</v>
       </c>
@@ -13299,7 +13341,8 @@
       <c r="AE44" s="1"/>
       <c r="AF44" s="1"/>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A45" s="102"/>
       <c r="B45" s="1" t="s">
         <v>189</v>
       </c>
@@ -13386,7 +13429,8 @@
       <c r="AE45" s="1"/>
       <c r="AF45" s="1"/>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A46" s="102"/>
       <c r="B46" s="1" t="s">
         <v>189</v>
       </c>
@@ -13473,7 +13517,8 @@
       <c r="AE46" s="1"/>
       <c r="AF46" s="1"/>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A47" s="102"/>
       <c r="B47" s="1" t="s">
         <v>189</v>
       </c>
@@ -13560,7 +13605,8 @@
       <c r="AE47" s="1"/>
       <c r="AF47" s="1"/>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A48" s="102"/>
       <c r="B48" s="1" t="s">
         <v>189</v>
       </c>
@@ -13647,7 +13693,8 @@
       <c r="AE48" s="1"/>
       <c r="AF48" s="1"/>
     </row>
-    <row r="49" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A49" s="102"/>
       <c r="B49" s="1" t="s">
         <v>189</v>
       </c>
@@ -13734,7 +13781,8 @@
       <c r="AE49" s="1"/>
       <c r="AF49" s="1"/>
     </row>
-    <row r="50" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A50" s="102"/>
       <c r="B50" s="1" t="s">
         <v>189</v>
       </c>
@@ -13821,7 +13869,8 @@
       <c r="AE50" s="1"/>
       <c r="AF50" s="1"/>
     </row>
-    <row r="51" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A51" s="102"/>
       <c r="B51" s="1" t="s">
         <v>189</v>
       </c>
@@ -13908,7 +13957,8 @@
       <c r="AE51" s="1"/>
       <c r="AF51" s="1"/>
     </row>
-    <row r="52" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A52" s="102"/>
       <c r="B52" s="1" t="s">
         <v>189</v>
       </c>
@@ -13995,7 +14045,8 @@
       <c r="AE52" s="1"/>
       <c r="AF52" s="1"/>
     </row>
-    <row r="53" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A53" s="102"/>
       <c r="B53" s="1" t="s">
         <v>189</v>
       </c>
@@ -14082,7 +14133,8 @@
       <c r="AE53" s="1"/>
       <c r="AF53" s="1"/>
     </row>
-    <row r="54" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A54" s="102"/>
       <c r="B54" s="1" t="s">
         <v>189</v>
       </c>
@@ -14169,7 +14221,8 @@
       <c r="AE54" s="1"/>
       <c r="AF54" s="1"/>
     </row>
-    <row r="55" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A55" s="102"/>
       <c r="B55" s="1" t="s">
         <v>189</v>
       </c>
@@ -14256,7 +14309,8 @@
       <c r="AE55" s="1"/>
       <c r="AF55" s="1"/>
     </row>
-    <row r="56" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A56" s="102"/>
       <c r="B56" s="1" t="s">
         <v>189</v>
       </c>
@@ -14343,7 +14397,8 @@
       <c r="AE56" s="1"/>
       <c r="AF56" s="1"/>
     </row>
-    <row r="57" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A57" s="102"/>
       <c r="B57" s="1" t="s">
         <v>189</v>
       </c>
@@ -14430,7 +14485,8 @@
       <c r="AE57" s="1"/>
       <c r="AF57" s="1"/>
     </row>
-    <row r="58" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A58" s="102"/>
       <c r="B58" s="1" t="s">
         <v>189</v>
       </c>
@@ -14517,7 +14573,8 @@
       <c r="AE58" s="1"/>
       <c r="AF58" s="1"/>
     </row>
-    <row r="59" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A59" s="102"/>
       <c r="B59" s="1" t="s">
         <v>189</v>
       </c>
@@ -14604,7 +14661,8 @@
       <c r="AE59" s="1"/>
       <c r="AF59" s="1"/>
     </row>
-    <row r="60" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A60" s="102"/>
       <c r="B60" s="1" t="s">
         <v>189</v>
       </c>
@@ -14691,7 +14749,8 @@
       <c r="AE60" s="1"/>
       <c r="AF60" s="1"/>
     </row>
-    <row r="61" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A61" s="102"/>
       <c r="B61" s="1" t="s">
         <v>189</v>
       </c>
@@ -14778,7 +14837,8 @@
       <c r="AE61" s="1"/>
       <c r="AF61" s="1"/>
     </row>
-    <row r="62" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A62" s="102"/>
       <c r="B62" s="1" t="s">
         <v>189</v>
       </c>
@@ -14865,7 +14925,8 @@
       <c r="AE62" s="1"/>
       <c r="AF62" s="1"/>
     </row>
-    <row r="63" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A63" s="102"/>
       <c r="B63" s="1" t="s">
         <v>189</v>
       </c>
@@ -14952,7 +15013,8 @@
       <c r="AE63" s="1"/>
       <c r="AF63" s="1"/>
     </row>
-    <row r="64" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A64" s="102"/>
       <c r="B64" s="1" t="s">
         <v>189</v>
       </c>
@@ -15039,7 +15101,8 @@
       <c r="AE64" s="1"/>
       <c r="AF64" s="1"/>
     </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A65" s="102"/>
       <c r="B65" s="1" t="s">
         <v>189</v>
       </c>
@@ -15126,7 +15189,8 @@
       <c r="AE65" s="1"/>
       <c r="AF65" s="1"/>
     </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A66" s="102"/>
       <c r="B66" s="1" t="s">
         <v>189</v>
       </c>
@@ -15213,7 +15277,8 @@
       <c r="AE66" s="1"/>
       <c r="AF66" s="1"/>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A67" s="102"/>
       <c r="B67" s="1" t="s">
         <v>189</v>
       </c>
@@ -15300,7 +15365,8 @@
       <c r="AE67" s="1"/>
       <c r="AF67" s="1"/>
     </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A68" s="102"/>
       <c r="B68" s="1" t="s">
         <v>189</v>
       </c>
@@ -15387,7 +15453,8 @@
       <c r="AE68" s="1"/>
       <c r="AF68" s="1"/>
     </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A69" s="102"/>
       <c r="B69" s="1" t="s">
         <v>189</v>
       </c>
@@ -15474,7 +15541,8 @@
       <c r="AE69" s="1"/>
       <c r="AF69" s="1"/>
     </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A70" s="102"/>
       <c r="B70" s="1" t="s">
         <v>189</v>
       </c>
@@ -15813,7 +15881,7 @@
       <c r="R4" s="77"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="78"/>
+      <c r="A5" s="100"/>
       <c r="B5" s="82" t="s">
         <v>189</v>
       </c>
@@ -15868,6 +15936,7 @@
       <c r="R5" s="78"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="103"/>
       <c r="B6" s="93" t="s">
         <v>189</v>
       </c>
@@ -15922,6 +15991,7 @@
       <c r="R6" s="77"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="103"/>
       <c r="B7" s="82" t="s">
         <v>189</v>
       </c>
@@ -15976,6 +16046,7 @@
       <c r="R7" s="78"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="103"/>
       <c r="B8" s="93" t="s">
         <v>189</v>
       </c>
@@ -16030,6 +16101,7 @@
       <c r="R8" s="77"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="103"/>
       <c r="B9" s="82" t="s">
         <v>189</v>
       </c>
@@ -16084,6 +16156,7 @@
       <c r="R9" s="78"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="103"/>
       <c r="B10" s="93" t="s">
         <v>189</v>
       </c>
@@ -16138,6 +16211,7 @@
       <c r="R10" s="77"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="103"/>
       <c r="B11" s="82" t="s">
         <v>189</v>
       </c>
@@ -16192,6 +16266,7 @@
       <c r="R11" s="78"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="103"/>
       <c r="B12" s="93" t="s">
         <v>189</v>
       </c>
@@ -16246,6 +16321,7 @@
       <c r="R12" s="77"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="103"/>
       <c r="B13" s="82" t="s">
         <v>189</v>
       </c>
@@ -16300,6 +16376,7 @@
       <c r="R13" s="78"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="103"/>
       <c r="B14" s="93" t="s">
         <v>189</v>
       </c>
@@ -16354,6 +16431,7 @@
       <c r="R14" s="77"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="103"/>
       <c r="B15" s="82" t="s">
         <v>189</v>
       </c>
@@ -16408,6 +16486,7 @@
       <c r="R15" s="78"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="103"/>
       <c r="B16" s="93" t="s">
         <v>189</v>
       </c>
@@ -16461,7 +16540,8 @@
       </c>
       <c r="R16" s="77"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" s="103"/>
       <c r="B17" s="82" t="s">
         <v>189</v>
       </c>
@@ -16515,7 +16595,8 @@
       </c>
       <c r="R17" s="78"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" s="103"/>
       <c r="B18" s="93" t="s">
         <v>189</v>
       </c>
@@ -16569,7 +16650,8 @@
       </c>
       <c r="R18" s="77"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" s="103"/>
       <c r="B19" s="82" t="s">
         <v>189</v>
       </c>
@@ -16623,7 +16705,8 @@
       </c>
       <c r="R19" s="78"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" s="103"/>
       <c r="B20" s="93" t="s">
         <v>189</v>
       </c>
@@ -16645,7 +16728,7 @@
         <v>t-dis-dfir01-disk01</v>
       </c>
       <c r="H20" s="77" t="s">
-        <v>188</v>
+        <v>720</v>
       </c>
       <c r="I20" s="77" t="s">
         <v>720</v>
@@ -16676,7 +16759,8 @@
       </c>
       <c r="R20" s="77"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" s="103"/>
       <c r="B21" s="82" t="s">
         <v>189</v>
       </c>
@@ -16730,7 +16814,8 @@
       </c>
       <c r="R21" s="78"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" s="103"/>
       <c r="B22" s="93" t="s">
         <v>189</v>
       </c>
@@ -16784,7 +16869,8 @@
       </c>
       <c r="R22" s="77"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" s="103"/>
       <c r="B23" s="82" t="s">
         <v>189</v>
       </c>
@@ -16838,7 +16924,8 @@
       </c>
       <c r="R23" s="78"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" s="103"/>
       <c r="B24" s="93" t="s">
         <v>189</v>
       </c>
@@ -16892,7 +16979,8 @@
       </c>
       <c r="R24" s="77"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A25" s="103"/>
       <c r="B25" s="82" t="s">
         <v>189</v>
       </c>
@@ -16946,7 +17034,8 @@
       </c>
       <c r="R25" s="78"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A26" s="103"/>
       <c r="B26" s="93" t="s">
         <v>189</v>
       </c>
@@ -17000,7 +17089,8 @@
       </c>
       <c r="R26" s="77"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A27" s="103"/>
       <c r="B27" s="82" t="s">
         <v>189</v>
       </c>
@@ -17054,7 +17144,8 @@
       </c>
       <c r="R27" s="78"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A28" s="103"/>
       <c r="B28" s="93" t="s">
         <v>189</v>
       </c>
@@ -17108,7 +17199,8 @@
       </c>
       <c r="R28" s="77"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A29" s="103"/>
       <c r="B29" s="82" t="s">
         <v>189</v>
       </c>
@@ -17162,7 +17254,8 @@
       </c>
       <c r="R29" s="78"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A30" s="103"/>
       <c r="B30" s="93" t="s">
         <v>189</v>
       </c>
@@ -17216,7 +17309,8 @@
       </c>
       <c r="R30" s="77"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A31" s="103"/>
       <c r="B31" s="82" t="s">
         <v>189</v>
       </c>
@@ -17270,7 +17364,8 @@
       </c>
       <c r="R31" s="78"/>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A32" s="103"/>
       <c r="B32" s="93" t="s">
         <v>189</v>
       </c>
@@ -17324,7 +17419,8 @@
       </c>
       <c r="R32" s="77"/>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A33" s="103"/>
       <c r="B33" s="82" t="s">
         <v>189</v>
       </c>
@@ -17378,7 +17474,8 @@
       </c>
       <c r="R33" s="78"/>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A34" s="103"/>
       <c r="B34" s="93" t="s">
         <v>189</v>
       </c>
@@ -17432,7 +17529,8 @@
       </c>
       <c r="R34" s="77"/>
     </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A35" s="103"/>
       <c r="B35" s="82" t="s">
         <v>189</v>
       </c>
@@ -17486,7 +17584,8 @@
       </c>
       <c r="R35" s="78"/>
     </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A36" s="103"/>
       <c r="B36" s="93" t="s">
         <v>189</v>
       </c>
@@ -17540,7 +17639,8 @@
       </c>
       <c r="R36" s="77"/>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A37" s="103"/>
       <c r="B37" s="82" t="s">
         <v>189</v>
       </c>
@@ -17594,7 +17694,8 @@
       </c>
       <c r="R37" s="78"/>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A38" s="103"/>
       <c r="B38" s="93" t="s">
         <v>189</v>
       </c>
@@ -17648,7 +17749,8 @@
       </c>
       <c r="R38" s="77"/>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A39" s="103"/>
       <c r="B39" s="82" t="s">
         <v>189</v>
       </c>
@@ -17702,7 +17804,8 @@
       </c>
       <c r="R39" s="78"/>
     </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A40" s="103"/>
       <c r="B40" s="93" t="s">
         <v>189</v>
       </c>
@@ -17756,7 +17859,8 @@
       </c>
       <c r="R40" s="77"/>
     </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A41" s="103"/>
       <c r="B41" s="82" t="s">
         <v>189</v>
       </c>
@@ -17810,7 +17914,8 @@
       </c>
       <c r="R41" s="78"/>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A42" s="103"/>
       <c r="B42" s="93" t="s">
         <v>189</v>
       </c>
@@ -17864,7 +17969,8 @@
       </c>
       <c r="R42" s="77"/>
     </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A43" s="103"/>
       <c r="B43" s="82" t="s">
         <v>189</v>
       </c>
@@ -17918,7 +18024,8 @@
       </c>
       <c r="R43" s="78"/>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A44" s="103"/>
       <c r="B44" s="93" t="s">
         <v>189</v>
       </c>
@@ -17972,7 +18079,8 @@
       </c>
       <c r="R44" s="77"/>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A45" s="103"/>
       <c r="B45" s="82" t="s">
         <v>189</v>
       </c>
@@ -18026,7 +18134,8 @@
       </c>
       <c r="R45" s="78"/>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A46" s="103"/>
       <c r="B46" s="93" t="s">
         <v>189</v>
       </c>
@@ -18080,7 +18189,8 @@
       </c>
       <c r="R46" s="77"/>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A47" s="103"/>
       <c r="B47" s="82" t="s">
         <v>189</v>
       </c>
@@ -18134,7 +18244,8 @@
       </c>
       <c r="R47" s="78"/>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A48" s="103"/>
       <c r="B48" s="93" t="s">
         <v>189</v>
       </c>
@@ -18188,7 +18299,8 @@
       </c>
       <c r="R48" s="77"/>
     </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A49" s="103"/>
       <c r="B49" s="82" t="s">
         <v>189</v>
       </c>
@@ -18242,7 +18354,8 @@
       </c>
       <c r="R49" s="78"/>
     </row>
-    <row r="50" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A50" s="103"/>
       <c r="B50" s="93" t="s">
         <v>189</v>
       </c>
@@ -18296,7 +18409,8 @@
       </c>
       <c r="R50" s="77"/>
     </row>
-    <row r="51" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A51" s="103"/>
       <c r="B51" s="82" t="s">
         <v>189</v>
       </c>
@@ -18350,7 +18464,8 @@
       </c>
       <c r="R51" s="78"/>
     </row>
-    <row r="52" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A52" s="103"/>
       <c r="B52" s="93" t="s">
         <v>189</v>
       </c>
@@ -18404,7 +18519,8 @@
       </c>
       <c r="R52" s="77"/>
     </row>
-    <row r="53" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A53" s="103"/>
       <c r="B53" s="82" t="s">
         <v>189</v>
       </c>
@@ -18458,7 +18574,8 @@
       </c>
       <c r="R53" s="78"/>
     </row>
-    <row r="54" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A54" s="103"/>
       <c r="B54" s="93" t="s">
         <v>189</v>
       </c>
@@ -18512,7 +18629,8 @@
       </c>
       <c r="R54" s="77"/>
     </row>
-    <row r="55" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A55" s="103"/>
       <c r="B55" s="82" t="s">
         <v>189</v>
       </c>
@@ -18566,7 +18684,8 @@
       </c>
       <c r="R55" s="78"/>
     </row>
-    <row r="56" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A56" s="103"/>
       <c r="B56" s="93" t="s">
         <v>189</v>
       </c>
@@ -18620,7 +18739,8 @@
       </c>
       <c r="R56" s="77"/>
     </row>
-    <row r="57" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A57" s="103"/>
       <c r="B57" s="82" t="s">
         <v>189</v>
       </c>
@@ -18674,7 +18794,8 @@
       </c>
       <c r="R57" s="78"/>
     </row>
-    <row r="58" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A58" s="103"/>
       <c r="B58" s="93" t="s">
         <v>189</v>
       </c>
@@ -18728,7 +18849,8 @@
       </c>
       <c r="R58" s="77"/>
     </row>
-    <row r="59" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A59" s="103"/>
       <c r="B59" s="82" t="s">
         <v>189</v>
       </c>
@@ -18782,7 +18904,8 @@
       </c>
       <c r="R59" s="78"/>
     </row>
-    <row r="60" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A60" s="103"/>
       <c r="B60" s="93" t="s">
         <v>189</v>
       </c>
@@ -18836,7 +18959,8 @@
       </c>
       <c r="R60" s="77"/>
     </row>
-    <row r="61" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A61" s="103"/>
       <c r="B61" s="82" t="s">
         <v>189</v>
       </c>
@@ -18890,7 +19014,8 @@
       </c>
       <c r="R61" s="78"/>
     </row>
-    <row r="62" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A62" s="103"/>
       <c r="B62" s="93" t="s">
         <v>189</v>
       </c>
@@ -18944,7 +19069,8 @@
       </c>
       <c r="R62" s="77"/>
     </row>
-    <row r="63" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A63" s="103"/>
       <c r="B63" s="82" t="s">
         <v>189</v>
       </c>
@@ -18998,7 +19124,8 @@
       </c>
       <c r="R63" s="78"/>
     </row>
-    <row r="64" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A64" s="103"/>
       <c r="B64" s="93" t="s">
         <v>189</v>
       </c>
@@ -19052,7 +19179,8 @@
       </c>
       <c r="R64" s="77"/>
     </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A65" s="103"/>
       <c r="B65" s="82" t="s">
         <v>189</v>
       </c>
@@ -19106,7 +19234,8 @@
       </c>
       <c r="R65" s="78"/>
     </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A66" s="103"/>
       <c r="B66" s="93" t="s">
         <v>189</v>
       </c>
@@ -19160,7 +19289,8 @@
       </c>
       <c r="R66" s="77"/>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A67" s="103"/>
       <c r="B67" s="82" t="s">
         <v>189</v>
       </c>
@@ -19214,7 +19344,8 @@
       </c>
       <c r="R67" s="78"/>
     </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A68" s="103"/>
       <c r="B68" s="93" t="s">
         <v>189</v>
       </c>
@@ -19268,7 +19399,8 @@
       </c>
       <c r="R68" s="77"/>
     </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A69" s="103"/>
       <c r="B69" s="82" t="s">
         <v>189</v>
       </c>
@@ -19322,7 +19454,8 @@
       </c>
       <c r="R69" s="78"/>
     </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A70" s="103"/>
       <c r="B70" s="93" t="s">
         <v>189</v>
       </c>
@@ -19438,7 +19571,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="75"/>
+      <c r="A2" s="105"/>
       <c r="B2" s="84" t="s">
         <v>189</v>
       </c>
@@ -19477,7 +19610,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="75"/>
+      <c r="A3" s="105"/>
       <c r="B3" s="86" t="s">
         <v>189</v>
       </c>
@@ -19516,7 +19649,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="75"/>
+      <c r="A4" s="105"/>
       <c r="B4" s="84" t="s">
         <v>189</v>
       </c>
@@ -19555,6 +19688,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="102"/>
       <c r="B5" s="86" t="s">
         <v>189</v>
       </c>
@@ -19593,6 +19727,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="102"/>
       <c r="B6" s="84" t="s">
         <v>189</v>
       </c>
@@ -19631,6 +19766,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="102"/>
       <c r="B7" s="86" t="s">
         <v>189</v>
       </c>
@@ -19669,6 +19805,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="102"/>
       <c r="B8" s="84" t="s">
         <v>189</v>
       </c>
@@ -19707,6 +19844,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="102"/>
       <c r="B9" s="86" t="s">
         <v>189</v>
       </c>
@@ -19745,6 +19883,7 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="102"/>
       <c r="B10" s="84" t="s">
         <v>189</v>
       </c>
@@ -19783,6 +19922,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="102"/>
       <c r="B11" s="86" t="s">
         <v>189</v>
       </c>
@@ -19821,6 +19961,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="102"/>
       <c r="B12" s="84" t="s">
         <v>189</v>
       </c>
@@ -19859,6 +20000,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="102"/>
       <c r="B13" s="86" t="s">
         <v>189</v>
       </c>
@@ -19897,6 +20039,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="102"/>
       <c r="B14" s="84" t="s">
         <v>189</v>
       </c>
@@ -19935,6 +20078,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="102"/>
       <c r="B15" s="86" t="s">
         <v>189</v>
       </c>
@@ -19973,6 +20117,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="102"/>
       <c r="B16" s="84" t="s">
         <v>189</v>
       </c>
@@ -20010,7 +20155,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="102"/>
       <c r="B17" s="86" t="s">
         <v>189</v>
       </c>
@@ -20048,7 +20194,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="102"/>
       <c r="B18" s="84" t="s">
         <v>189</v>
       </c>
@@ -20086,7 +20233,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="102"/>
       <c r="B19" s="86" t="s">
         <v>189</v>
       </c>
@@ -20124,7 +20272,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="102"/>
       <c r="B20" s="84" t="s">
         <v>189</v>
       </c>
@@ -20162,7 +20311,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="102"/>
       <c r="B21" s="86" t="s">
         <v>189</v>
       </c>
@@ -20200,7 +20350,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="102"/>
       <c r="B22" s="84" t="s">
         <v>189</v>
       </c>
@@ -20238,7 +20389,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="102"/>
       <c r="B23" s="86" t="s">
         <v>189</v>
       </c>
@@ -20276,7 +20428,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="102"/>
       <c r="B24" s="84" t="s">
         <v>189</v>
       </c>
@@ -20314,7 +20467,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="102"/>
       <c r="B25" s="86" t="s">
         <v>189</v>
       </c>
@@ -20352,7 +20506,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="102"/>
       <c r="B26" s="84" t="s">
         <v>189</v>
       </c>
@@ -20390,7 +20545,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="102"/>
       <c r="B27" s="86" t="s">
         <v>189</v>
       </c>
@@ -20428,7 +20584,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="102"/>
       <c r="B28" s="84" t="s">
         <v>189</v>
       </c>
@@ -20466,7 +20623,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="102"/>
       <c r="B29" s="86" t="s">
         <v>189</v>
       </c>
@@ -20504,7 +20662,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="102"/>
       <c r="B30" s="84" t="s">
         <v>189</v>
       </c>
@@ -20542,7 +20701,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="102"/>
       <c r="B31" s="86" t="s">
         <v>189</v>
       </c>
@@ -20580,7 +20740,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="102"/>
       <c r="B32" s="84" t="s">
         <v>189</v>
       </c>
@@ -20618,7 +20779,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="102"/>
       <c r="B33" s="86" t="s">
         <v>189</v>
       </c>
@@ -20656,7 +20818,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="102"/>
       <c r="B34" s="84" t="s">
         <v>189</v>
       </c>
@@ -20694,7 +20857,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="102"/>
       <c r="B35" s="86" t="s">
         <v>189</v>
       </c>
@@ -20732,7 +20896,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="102"/>
       <c r="B36" s="84" t="s">
         <v>189</v>
       </c>
@@ -20770,7 +20935,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="102"/>
       <c r="B37" s="86" t="s">
         <v>189</v>
       </c>
@@ -20808,7 +20974,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="102"/>
       <c r="B38" s="84" t="s">
         <v>189</v>
       </c>
@@ -20846,7 +21013,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="102"/>
       <c r="B39" s="86" t="s">
         <v>189</v>
       </c>
@@ -20884,7 +21052,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="102"/>
       <c r="B40" s="84" t="s">
         <v>189</v>
       </c>
@@ -20922,7 +21091,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="102"/>
       <c r="B41" s="86" t="s">
         <v>189</v>
       </c>
@@ -20960,7 +21130,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="102"/>
       <c r="B42" s="84" t="s">
         <v>189</v>
       </c>
@@ -20998,7 +21169,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="102"/>
       <c r="B43" s="86" t="s">
         <v>189</v>
       </c>
@@ -21036,7 +21208,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="102"/>
       <c r="B44" s="84" t="s">
         <v>189</v>
       </c>
@@ -21074,7 +21247,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="102"/>
       <c r="B45" s="86" t="s">
         <v>189</v>
       </c>
@@ -21112,7 +21286,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="102"/>
       <c r="B46" s="84" t="s">
         <v>189</v>
       </c>
@@ -21150,7 +21325,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="102"/>
       <c r="B47" s="86" t="s">
         <v>189</v>
       </c>
@@ -21188,7 +21364,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="102"/>
       <c r="B48" s="84" t="s">
         <v>189</v>
       </c>
@@ -21226,7 +21403,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="102"/>
       <c r="B49" s="86" t="s">
         <v>189</v>
       </c>
@@ -21264,7 +21442,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="102"/>
       <c r="B50" s="84" t="s">
         <v>189</v>
       </c>
@@ -21302,7 +21481,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="102"/>
       <c r="B51" s="86" t="s">
         <v>189</v>
       </c>
@@ -21340,7 +21520,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="102"/>
       <c r="B52" s="84" t="s">
         <v>189</v>
       </c>
@@ -21378,7 +21559,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="102"/>
       <c r="B53" s="86" t="s">
         <v>189</v>
       </c>
@@ -21416,7 +21598,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="102"/>
       <c r="B54" s="84" t="s">
         <v>189</v>
       </c>
@@ -21454,7 +21637,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="102"/>
       <c r="B55" s="86" t="s">
         <v>189</v>
       </c>
@@ -21492,7 +21676,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="102"/>
       <c r="B56" s="84" t="s">
         <v>189</v>
       </c>
@@ -21530,7 +21715,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="102"/>
       <c r="B57" s="86" t="s">
         <v>189</v>
       </c>
@@ -21568,7 +21754,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="102"/>
       <c r="B58" s="84" t="s">
         <v>189</v>
       </c>
@@ -21606,7 +21793,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="102"/>
       <c r="B59" s="86" t="s">
         <v>189</v>
       </c>
@@ -21644,7 +21832,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="102"/>
       <c r="B60" s="84" t="s">
         <v>189</v>
       </c>
@@ -21682,7 +21871,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="102"/>
       <c r="B61" s="86" t="s">
         <v>189</v>
       </c>
@@ -21720,7 +21910,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="102"/>
       <c r="B62" s="84" t="s">
         <v>189</v>
       </c>
@@ -21758,7 +21949,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="102"/>
       <c r="B63" s="86" t="s">
         <v>189</v>
       </c>
@@ -21796,7 +21988,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="102"/>
       <c r="B64" s="84" t="s">
         <v>189</v>
       </c>
@@ -21834,7 +22027,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" s="102"/>
       <c r="B65" s="86" t="s">
         <v>189</v>
       </c>
@@ -21872,7 +22066,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="102"/>
       <c r="B66" s="84" t="s">
         <v>189</v>
       </c>
@@ -21910,7 +22105,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="102"/>
       <c r="B67" s="86" t="s">
         <v>189</v>
       </c>
@@ -21948,7 +22144,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="102"/>
       <c r="B68" s="84" t="s">
         <v>189</v>
       </c>
@@ -21986,7 +22183,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="102"/>
       <c r="B69" s="86" t="s">
         <v>189</v>
       </c>
@@ -22024,7 +22222,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="102"/>
       <c r="B70" s="84" t="s">
         <v>189</v>
       </c>
@@ -22062,7 +22261,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" s="102"/>
       <c r="B71" s="86" t="s">
         <v>189</v>
       </c>
@@ -22093,7 +22293,8 @@
         <v>794</v>
       </c>
     </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="102"/>
       <c r="B72" s="84" t="s">
         <v>189</v>
       </c>
@@ -22124,7 +22325,8 @@
         <v>794</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="102"/>
       <c r="B73" s="86" t="s">
         <v>189</v>
       </c>
@@ -22155,7 +22357,8 @@
         <v>794</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="102"/>
       <c r="B74" s="84" t="s">
         <v>189</v>
       </c>
@@ -22186,7 +22389,8 @@
         <v>794</v>
       </c>
     </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" s="102"/>
       <c r="B75" s="86" t="s">
         <v>189</v>
       </c>
@@ -22217,7 +22421,8 @@
         <v>794</v>
       </c>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="102"/>
       <c r="B76" s="84" t="s">
         <v>189</v>
       </c>
@@ -22248,7 +22453,8 @@
         <v>794</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="102"/>
       <c r="B77" s="86" t="s">
         <v>189</v>
       </c>
@@ -22279,7 +22485,8 @@
         <v>794</v>
       </c>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" s="102"/>
       <c r="B78" s="84" t="s">
         <v>189</v>
       </c>
@@ -22310,7 +22517,8 @@
         <v>794</v>
       </c>
     </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" s="102"/>
       <c r="B79" s="86" t="s">
         <v>189</v>
       </c>
@@ -22341,7 +22549,8 @@
         <v>794</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="102"/>
       <c r="B80" s="84" t="s">
         <v>189</v>
       </c>
@@ -22372,7 +22581,8 @@
         <v>794</v>
       </c>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" s="102"/>
       <c r="B81" s="86" t="s">
         <v>189</v>
       </c>
@@ -22403,7 +22613,8 @@
         <v>794</v>
       </c>
     </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" s="102"/>
       <c r="B82" s="84" t="s">
         <v>189</v>
       </c>
@@ -22434,7 +22645,8 @@
         <v>794</v>
       </c>
     </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" s="104"/>
       <c r="B83" s="86" t="s">
         <v>189</v>
       </c>
@@ -22465,7 +22677,8 @@
         <v>794</v>
       </c>
     </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" s="104"/>
       <c r="B84" s="84" t="s">
         <v>189</v>
       </c>
@@ -22496,7 +22709,8 @@
         <v>794</v>
       </c>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" s="102"/>
       <c r="B85" s="86" t="s">
         <v>189</v>
       </c>
@@ -22527,7 +22741,8 @@
         <v>794</v>
       </c>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A86" s="102"/>
       <c r="B86" s="84" t="s">
         <v>189</v>
       </c>
@@ -22558,7 +22773,8 @@
         <v>794</v>
       </c>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A87" s="102"/>
       <c r="B87" s="86" t="s">
         <v>189</v>
       </c>
@@ -22589,7 +22805,8 @@
         <v>794</v>
       </c>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A88" s="102"/>
       <c r="B88" s="84" t="s">
         <v>189</v>
       </c>
@@ -25064,7 +25281,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD1A3252-EF11-4361-BCDB-10417C7A0940}">
-  <dimension ref="B1:AB66"/>
+  <dimension ref="B1:AB55"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.25" customWidth="1"/>
@@ -28805,204 +29022,6 @@
       <c r="O55" s="1"/>
       <c r="P55" s="1"/>
       <c r="Q55" s="1"/>
-    </row>
-    <row r="56" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1"/>
-      <c r="Q56" s="1"/>
-    </row>
-    <row r="57" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-      <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
-    </row>
-    <row r="58" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1"/>
-      <c r="Q58" s="1"/>
-    </row>
-    <row r="59" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
-      <c r="P59" s="1"/>
-      <c r="Q59" s="1"/>
-    </row>
-    <row r="60" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
-      <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
-      <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
-    </row>
-    <row r="61" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
-      <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1"/>
-      <c r="Q61" s="1"/>
-    </row>
-    <row r="62" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
-    </row>
-    <row r="63" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="1"/>
-      <c r="M63" s="1"/>
-      <c r="N63" s="1"/>
-      <c r="O63" s="1"/>
-      <c r="P63" s="1"/>
-      <c r="Q63" s="1"/>
-    </row>
-    <row r="64" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-      <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
-      <c r="P64" s="1"/>
-      <c r="Q64" s="1"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
-      <c r="L65" s="1"/>
-      <c r="M65" s="1"/>
-      <c r="N65" s="1"/>
-      <c r="O65" s="1"/>
-      <c r="P65" s="1"/>
-      <c r="Q65" s="1"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1"/>
-      <c r="Q66" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCD2AAD-95D3-4EC3-960E-CD3CA4D4FD33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0A8F91-35F7-4569-8B22-8B3BC6CF2003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1657,7 +1657,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4605" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4603" uniqueCount="743">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4293,10 +4293,6 @@
   </si>
   <si>
     <t>hazr-l-comm-double-des</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-l-common-rg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4779,7 +4775,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5104,46 +5100,11 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="33">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -6117,6 +6078,38 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -6131,46 +6124,46 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF72" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF72" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
   <autoFilter ref="B1:AF72" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="31">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="29">
       <calculatedColumnFormula array="1">UPPER(INDEX(_xlfn.TEXTSPLIT($D2, "-"), 3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="27"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="26"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="25"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="20"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="19">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="25"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="24"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="23"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="17">
       <calculatedColumnFormula>SUBSTITUTE(F2,"hazr-","")&amp;"-osdisk"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="18"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="17"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="16"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="15"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="13">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="15"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="14"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="13"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="11">
       <calculatedColumnFormula>SUBSTITUTE(F2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{6FD9A0A6-7008-49AB-B2C9-4BEDF1811434}" name="EnableAcceleratedNetworking" dataDxfId="12"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="10"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="9"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="8"/>
-    <tableColumn id="28" xr3:uid="{73185387-6B41-497F-9EB6-5675CC43B3E3}" name="UseOsDiskDoubleEncryption " dataDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{804782E7-599A-496A-B10D-EFCB52F3E7DB}" name="DESRG" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{1ED2A695-2028-4644-8B0B-7B32A8F548C4}" name="DESName" dataDxfId="5"/>
-    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="4"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="3"/>
-    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="2"/>
+    <tableColumn id="27" xr3:uid="{6FD9A0A6-7008-49AB-B2C9-4BEDF1811434}" name="EnableAcceleratedNetworking" dataDxfId="10"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="7"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="6"/>
+    <tableColumn id="28" xr3:uid="{73185387-6B41-497F-9EB6-5675CC43B3E3}" name="UseOsDiskDoubleEncryption " dataDxfId="5"/>
+    <tableColumn id="21" xr3:uid="{804782E7-599A-496A-B10D-EFCB52F3E7DB}" name="DESRG" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{1ED2A695-2028-4644-8B0B-7B32A8F548C4}" name="DESName" dataDxfId="3"/>
+    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="1"/>
+    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9778,7 +9771,7 @@
     <col min="20" max="21" width="21" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="28.125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="9" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="16.875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="18.75" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="27.75" bestFit="1" customWidth="1"/>
@@ -15726,7 +15719,7 @@
       <c r="S67" s="74"/>
       <c r="T67" s="74"/>
       <c r="U67" s="74" t="str">
-        <f t="shared" ref="U67:U70" si="5">SUBSTITUTE(F67,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="U67:U72" si="5">SUBSTITUTE(F67,"hazr-","")&amp;"-nic"</f>
         <v>t-doip-adm01-nic</v>
       </c>
       <c r="V67" s="74" t="b">
@@ -16034,7 +16027,7 @@
         <f t="array" ref="C71">UPPER(INDEX(_xlfn.TEXTSPLIT($D71, "-"), 3))</f>
         <v>MON</v>
       </c>
-      <c r="D71" s="108" t="s">
+      <c r="D71" s="74" t="s">
         <v>729</v>
       </c>
       <c r="E71" s="74" t="s">
@@ -16067,7 +16060,7 @@
       <c r="N71" s="74" t="s">
         <v>728</v>
       </c>
-      <c r="O71" s="108" t="str">
+      <c r="O71" s="74" t="str">
         <f>SUBSTITUTE(F71,"hazr-","")&amp;"-osdisk"</f>
         <v>l-mon-whtap01-osdisk</v>
       </c>
@@ -16077,11 +16070,12 @@
       <c r="Q71" s="74" t="s">
         <v>188</v>
       </c>
-      <c r="R71" s="108"/>
+      <c r="R71" s="74"/>
       <c r="S71" s="74"/>
-      <c r="T71" s="108"/>
-      <c r="U71" s="74" t="s">
-        <v>739</v>
+      <c r="T71" s="74"/>
+      <c r="U71" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>l-mon-whtap01-nic</v>
       </c>
       <c r="V71" s="74" t="b">
         <v>1</v>
@@ -16102,7 +16096,7 @@
         <v>1</v>
       </c>
       <c r="AB71" s="74" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="AC71" s="74" t="s">
         <v>742</v>
@@ -16121,7 +16115,7 @@
         <f t="array" ref="C72">UPPER(INDEX(_xlfn.TEXTSPLIT($D72, "-"), 3))</f>
         <v>MON</v>
       </c>
-      <c r="D72" s="108" t="s">
+      <c r="D72" s="74" t="s">
         <v>729</v>
       </c>
       <c r="E72" s="74" t="s">
@@ -16154,7 +16148,7 @@
       <c r="N72" s="74" t="s">
         <v>728</v>
       </c>
-      <c r="O72" s="108" t="str">
+      <c r="O72" s="74" t="str">
         <f>SUBSTITUTE(F72,"hazr-","")&amp;"-osdisk"</f>
         <v>l-mon-whtap02-osdisk</v>
       </c>
@@ -16164,11 +16158,12 @@
       <c r="Q72" s="74" t="s">
         <v>188</v>
       </c>
-      <c r="R72" s="108"/>
+      <c r="R72" s="74"/>
       <c r="S72" s="74"/>
-      <c r="T72" s="108"/>
-      <c r="U72" s="74" t="s">
-        <v>740</v>
+      <c r="T72" s="74"/>
+      <c r="U72" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>l-mon-whtap02-nic</v>
       </c>
       <c r="V72" s="74" t="b">
         <v>1</v>
@@ -16189,7 +16184,7 @@
         <v>1</v>
       </c>
       <c r="AB72" s="73" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="AC72" s="73" t="s">
         <v>741</v>
@@ -20127,7 +20122,7 @@
         <v>201</v>
       </c>
       <c r="O71" s="74" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="P71" s="74" t="s">
         <v>742</v>
@@ -20180,7 +20175,7 @@
         <v>201</v>
       </c>
       <c r="O72" s="73" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="P72" s="73" t="s">
         <v>741</v>
@@ -22987,7 +22982,7 @@
         <v>205</v>
       </c>
       <c r="E72" s="80" t="str">
-        <f t="shared" ref="E72:E90" si="4">SUBSTITUTE(H72,"-sbn","")&amp;"-nsg"</f>
+        <f t="shared" ref="E72:E88" si="4">SUBSTITUTE(H72,"-sbn","")&amp;"-nsg"</f>
         <v>t-dis-pe-nsg</v>
       </c>
       <c r="F72" s="80" t="s">
@@ -31276,12 +31271,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31429,15 +31421,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31461,17 +31464,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0A8F91-35F7-4569-8B22-8B3BC6CF2003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE0B8F3-D623-4AB9-9513-006859E696CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1657,7 +1657,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4603" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4640" uniqueCount="749">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4294,6 +4294,28 @@
   <si>
     <t>hazr-l-comm-double-des</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEMP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-l-mon-whtap03</t>
+  </si>
+  <si>
+    <t>hazr-l-mon-whtap03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.155.161.70</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>l-mon-whtap03-nic</t>
   </si>
 </sst>
 </file>
@@ -4775,7 +4797,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5098,6 +5120,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6124,8 +6158,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF72" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
-  <autoFilter ref="B1:AF72" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF73" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
+  <autoFilter ref="B1:AF73" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="30"/>
     <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="29">
@@ -9747,7 +9781,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF72"/>
+  <dimension ref="A1:AF73"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
@@ -9757,7 +9791,7 @@
     <col min="5" max="5" width="12.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.75" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.875" bestFit="1" customWidth="1"/>
@@ -11493,7 +11527,7 @@
         <v>293</v>
       </c>
       <c r="E20" s="74" t="s">
-        <v>24</v>
+        <v>744</v>
       </c>
       <c r="F20" s="74" t="s">
         <v>665</v>
@@ -16021,7 +16055,7 @@
     </row>
     <row r="71" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B71" s="74" t="s">
-        <v>23</v>
+        <v>743</v>
       </c>
       <c r="C71" s="74" t="str" cm="1">
         <f t="array" ref="C71">UPPER(INDEX(_xlfn.TEXTSPLIT($D71, "-"), 3))</f>
@@ -16109,7 +16143,7 @@
     </row>
     <row r="72" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B72" s="74" t="s">
-        <v>23</v>
+        <v>743</v>
       </c>
       <c r="C72" s="74" t="str" cm="1">
         <f t="array" ref="C72">UPPER(INDEX(_xlfn.TEXTSPLIT($D72, "-"), 3))</f>
@@ -16194,6 +16228,93 @@
       </c>
       <c r="AE72" s="74"/>
       <c r="AF72" s="74"/>
+    </row>
+    <row r="73" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B73" s="108" t="s">
+        <v>743</v>
+      </c>
+      <c r="C73" s="109" t="s">
+        <v>738</v>
+      </c>
+      <c r="D73" s="109" t="s">
+        <v>729</v>
+      </c>
+      <c r="E73" s="108" t="s">
+        <v>24</v>
+      </c>
+      <c r="F73" s="108" t="s">
+        <v>746</v>
+      </c>
+      <c r="G73" s="108" t="s">
+        <v>747</v>
+      </c>
+      <c r="H73" s="110" t="s">
+        <v>186</v>
+      </c>
+      <c r="I73" s="108">
+        <v>2</v>
+      </c>
+      <c r="J73" s="108">
+        <v>8</v>
+      </c>
+      <c r="K73" s="108" t="s">
+        <v>190</v>
+      </c>
+      <c r="L73" s="111" t="s">
+        <v>185</v>
+      </c>
+      <c r="M73" s="111" t="s">
+        <v>730</v>
+      </c>
+      <c r="N73" s="74" t="s">
+        <v>728</v>
+      </c>
+      <c r="O73" s="109" t="str">
+        <f>SUBSTITUTE(F73,"hazr-","")&amp;"-osdisk"</f>
+        <v>l-mon-whtap03-osdisk</v>
+      </c>
+      <c r="P73" s="108">
+        <v>64</v>
+      </c>
+      <c r="Q73" s="108" t="s">
+        <v>188</v>
+      </c>
+      <c r="R73" s="109"/>
+      <c r="S73" s="108"/>
+      <c r="T73" s="109"/>
+      <c r="U73" s="109" t="str">
+        <f>SUBSTITUTE(F73,"hazr-","")&amp;"-nic"</f>
+        <v>l-mon-whtap03-nic</v>
+      </c>
+      <c r="V73" s="108" t="b">
+        <v>1</v>
+      </c>
+      <c r="W73" s="108" t="b">
+        <v>1</v>
+      </c>
+      <c r="X73" s="108" t="s">
+        <v>737</v>
+      </c>
+      <c r="Y73" s="108" t="s">
+        <v>289</v>
+      </c>
+      <c r="Z73" s="108" t="s">
+        <v>734</v>
+      </c>
+      <c r="AA73" s="108" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB73" s="108" t="s">
+        <v>737</v>
+      </c>
+      <c r="AC73" s="108" t="s">
+        <v>742</v>
+      </c>
+      <c r="AD73" s="108">
+        <v>3</v>
+      </c>
+      <c r="AE73" s="108"/>
+      <c r="AF73" s="108"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -16210,7 +16331,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:R72"/>
+  <dimension ref="A1:R73"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.25" style="75" customWidth="1"/>
@@ -16578,7 +16699,7 @@
         <v>652</v>
       </c>
       <c r="G7" s="74" t="str">
-        <f t="shared" ref="G7:G71" si="2">SUBSTITUTE($F7,"hazr-","")&amp;"-disk01"</f>
+        <f t="shared" ref="G7:G73" si="2">SUBSTITUTE($F7,"hazr-","")&amp;"-disk01"</f>
         <v>t-dis-bbiweb01-disk01</v>
       </c>
       <c r="H7" s="74" t="s">
@@ -19997,7 +20118,7 @@
         <v>128</v>
       </c>
       <c r="J69" s="74" t="str">
-        <f t="shared" ref="J69:J72" si="3">SUBSTITUTE($F69,"hazr-","")&amp;"-disk02"</f>
+        <f t="shared" ref="J69:J73" si="3">SUBSTITUTE($F69,"hazr-","")&amp;"-disk02"</f>
         <v>t-bdp-crkap01-disk02</v>
       </c>
       <c r="K69" s="74" t="s">
@@ -20184,6 +20305,59 @@
         <v>1</v>
       </c>
       <c r="R72" s="73"/>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B73" s="78" t="s">
+        <v>23</v>
+      </c>
+      <c r="C73" s="74" t="str" cm="1">
+        <f t="array" ref="C73">UPPER(INDEX(_xlfn.TEXTSPLIT($D73, "-"), 3))</f>
+        <v>MON</v>
+      </c>
+      <c r="D73" s="78" t="s">
+        <v>729</v>
+      </c>
+      <c r="E73" s="90" t="s">
+        <v>24</v>
+      </c>
+      <c r="F73" s="74" t="s">
+        <v>745</v>
+      </c>
+      <c r="G73" s="74" t="str">
+        <f>SUBSTITUTE($F73,"hazr-","")&amp;"-disk01"</f>
+        <v>l-mon-whtap03-disk01</v>
+      </c>
+      <c r="H73" s="74" t="s">
+        <v>188</v>
+      </c>
+      <c r="I73" s="74">
+        <v>128</v>
+      </c>
+      <c r="J73" s="74" t="s">
+        <v>720</v>
+      </c>
+      <c r="K73" s="74" t="s">
+        <v>720</v>
+      </c>
+      <c r="L73" s="74" t="s">
+        <v>720</v>
+      </c>
+      <c r="M73" s="74">
+        <v>3</v>
+      </c>
+      <c r="N73" s="74" t="s">
+        <v>201</v>
+      </c>
+      <c r="O73" s="74" t="s">
+        <v>737</v>
+      </c>
+      <c r="P73" s="74" t="s">
+        <v>742</v>
+      </c>
+      <c r="Q73" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R73" s="74"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -20196,7 +20370,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.5" customWidth="1"/>
@@ -23296,14 +23470,14 @@
       </c>
       <c r="C82" s="80" t="str" cm="1">
         <f t="array" ref="C82">UPPER(INDEX(_xlfn.TEXTSPLIT($E82, "-"), 2))</f>
-        <v>COM</v>
+        <v>DIP</v>
       </c>
       <c r="D82" s="80" t="s">
         <v>205</v>
       </c>
       <c r="E82" s="80" t="str">
         <f t="shared" si="4"/>
-        <v>t-com-pe-nsg</v>
+        <v>t-dip-pe-nsg</v>
       </c>
       <c r="F82" s="80" t="s">
         <v>205</v>
@@ -23312,7 +23486,7 @@
         <v>627</v>
       </c>
       <c r="H82" s="73" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="I82" s="73"/>
       <c r="J82" s="73"/>
@@ -23584,6 +23758,43 @@
         <v>740</v>
       </c>
       <c r="L90" s="73" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B91" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="C91" s="82" t="str" cm="1">
+        <f t="array" ref="C91">UPPER(INDEX(_xlfn.TEXTSPLIT($D91, "-"), 3))</f>
+        <v>MON</v>
+      </c>
+      <c r="D91" s="82" t="s">
+        <v>729</v>
+      </c>
+      <c r="E91" s="82" t="str">
+        <f>SUBSTITUTE(I91,"hazr-","")&amp;"-nsg"</f>
+        <v>l-mon-whtap03-nsg</v>
+      </c>
+      <c r="F91" s="82" t="s">
+        <v>729</v>
+      </c>
+      <c r="G91" s="74" t="s">
+        <v>289</v>
+      </c>
+      <c r="H91" s="74" t="s">
+        <v>734</v>
+      </c>
+      <c r="I91" s="74" t="s">
+        <v>746</v>
+      </c>
+      <c r="J91" s="74" t="s">
+        <v>729</v>
+      </c>
+      <c r="K91" s="74" t="s">
+        <v>748</v>
+      </c>
+      <c r="L91" s="74" t="s">
         <v>721</v>
       </c>
     </row>
@@ -31271,9 +31482,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31421,26 +31635,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31464,9 +31667,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E25A80B-217F-4258-8AD8-6CFF080DA683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>

--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E25A80B-217F-4258-8AD8-6CFF080DA683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3B1D33-DC7E-4E7E-B287-A3FC23DCE856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -4454,7 +4454,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4791,27 +4791,11 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="34">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5841,46 +5825,46 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF73" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF73" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
   <autoFilter ref="B1:AF73" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="31">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="30">
       <calculatedColumnFormula array="1">UPPER(INDEX(_xlfn.TEXTSPLIT($D2, "-"), 3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="27"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="26"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="25"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="20"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="19">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="26"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="25"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="24"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="18">
       <calculatedColumnFormula>SUBSTITUTE(F2,"hazr-","")&amp;"-osdisk"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="18"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="17"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="16"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="15"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="13">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="17"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="16"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="15"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="14"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="12">
       <calculatedColumnFormula>SUBSTITUTE(F2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{6FD9A0A6-7008-49AB-B2C9-4BEDF1811434}" name="EnableAcceleratedNetworking" dataDxfId="12"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="10"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="9"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="8"/>
-    <tableColumn id="28" xr3:uid="{73185387-6B41-497F-9EB6-5675CC43B3E3}" name="UseOsDiskDoubleEncryption " dataDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{804782E7-599A-496A-B10D-EFCB52F3E7DB}" name="DESRG" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{1ED2A695-2028-4644-8B0B-7B32A8F548C4}" name="DESName" dataDxfId="5"/>
-    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="4"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="3"/>
-    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="2"/>
+    <tableColumn id="27" xr3:uid="{6FD9A0A6-7008-49AB-B2C9-4BEDF1811434}" name="EnableAcceleratedNetworking" dataDxfId="11"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="9"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="8"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="7"/>
+    <tableColumn id="28" xr3:uid="{73185387-6B41-497F-9EB6-5675CC43B3E3}" name="UseOsDiskDoubleEncryption " dataDxfId="6"/>
+    <tableColumn id="21" xr3:uid="{804782E7-599A-496A-B10D-EFCB52F3E7DB}" name="DESRG" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{1ED2A695-2028-4644-8B0B-7B32A8F548C4}" name="DESName" dataDxfId="4"/>
+    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="2"/>
+    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6826,7 +6810,7 @@
   <cols>
     <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.5" bestFit="1" customWidth="1"/>
@@ -6893,118 +6877,118 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B2" s="112" t="str" cm="1">
+      <c r="A2" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" s="74" t="str" cm="1">
         <f t="array" ref="B2">UPPER(INDEX(_xlfn.TEXTSPLIT($C2, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="C2" s="112" t="s">
+      <c r="C2" s="74" t="s">
         <v>391</v>
       </c>
-      <c r="D2" s="112" t="s">
+      <c r="D2" s="74" t="s">
         <v>363</v>
       </c>
-      <c r="E2" s="112" t="str">
-        <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-rule"</f>
-        <v>t-dtg-web-lb-rule</v>
-      </c>
-      <c r="F2" s="112" t="str">
+      <c r="E2" s="74" t="str">
+        <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-rule"&amp;M2</f>
+        <v>t-dtg-web-lb-rule8080</v>
+      </c>
+      <c r="F2" s="74" t="str">
         <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-web-lb-fe</v>
       </c>
-      <c r="G2" s="112" t="s">
+      <c r="G2" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="112">
+      <c r="H2" s="74">
         <v>8080</v>
       </c>
-      <c r="I2" s="112" t="b">
+      <c r="I2" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J2" s="112" t="str">
+      <c r="J2" s="74" t="str">
         <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-web-lb-bp</v>
       </c>
-      <c r="K2" s="112">
+      <c r="K2" s="74">
         <v>8080</v>
       </c>
-      <c r="L2" s="112" t="str">
+      <c r="L2" s="74" t="str">
         <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-pb"&amp;IF(M2="", "", M2)</f>
         <v>t-dtg-web-lb-pb8080</v>
       </c>
-      <c r="M2" s="112">
+      <c r="M2" s="74">
         <v>8080</v>
       </c>
-      <c r="N2" s="112">
+      <c r="N2" s="74">
         <v>4</v>
       </c>
-      <c r="O2" s="112" t="s">
+      <c r="O2" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P2" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="112" t="b">
+      <c r="P2" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B3" s="112" t="str" cm="1">
+      <c r="A3" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" s="74" t="str" cm="1">
         <f t="array" ref="B3">UPPER(INDEX(_xlfn.TEXTSPLIT($C3, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="C3" s="112" t="s">
+      <c r="C3" s="74" t="s">
         <v>391</v>
       </c>
-      <c r="D3" s="112" t="s">
+      <c r="D3" s="74" t="s">
         <v>363</v>
       </c>
-      <c r="E3" s="112" t="str">
-        <f>SUBSTITUTE(D3, "hazr-", "")&amp;"-rule"</f>
-        <v>t-dtg-web-lb-rule</v>
-      </c>
-      <c r="F3" s="112" t="str">
+      <c r="E3" s="74" t="str">
+        <f t="shared" ref="E3:E66" si="0">SUBSTITUTE(D3, "hazr-", "")&amp;"-rule"&amp;M3</f>
+        <v>t-dtg-web-lb-rule8081</v>
+      </c>
+      <c r="F3" s="74" t="str">
         <f>SUBSTITUTE(D3, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-web-lb-fe</v>
       </c>
-      <c r="G3" s="112" t="s">
+      <c r="G3" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H3" s="112">
+      <c r="H3" s="74">
         <v>8081</v>
       </c>
-      <c r="I3" s="112" t="b">
+      <c r="I3" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J3" s="112" t="str">
+      <c r="J3" s="74" t="str">
         <f>SUBSTITUTE(D3, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-web-lb-bp</v>
       </c>
-      <c r="K3" s="112">
+      <c r="K3" s="74">
         <v>8081</v>
       </c>
-      <c r="L3" s="112" t="str">
-        <f t="shared" ref="L3:L66" si="0">SUBSTITUTE(D3, "hazr-", "")&amp;"-pb"&amp;IF(M3="", "", M3)</f>
+      <c r="L3" s="74" t="str">
+        <f t="shared" ref="L3:L66" si="1">SUBSTITUTE(D3, "hazr-", "")&amp;"-pb"&amp;IF(M3="", "", M3)</f>
         <v>t-dtg-web-lb-pb8081</v>
       </c>
-      <c r="M3" s="112">
+      <c r="M3" s="74">
         <v>8081</v>
       </c>
-      <c r="N3" s="112">
+      <c r="N3" s="74">
         <v>4</v>
       </c>
-      <c r="O3" s="112" t="s">
+      <c r="O3" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P3" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="112" t="b">
+      <c r="P3" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7023,8 +7007,8 @@
         <v>360</v>
       </c>
       <c r="E4" s="84" t="str">
-        <f>SUBSTITUTE(D4, "hazr-", "")&amp;"-rule"</f>
-        <v>t-dtg-mq-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dtg-mq-lb-rule1883</v>
       </c>
       <c r="F4" s="84" t="str">
         <f>SUBSTITUTE(D4, "hazr-", "")&amp;"-fe"</f>
@@ -7047,7 +7031,7 @@
         <v>1883</v>
       </c>
       <c r="L4" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dtg-mq-lb-pb1883</v>
       </c>
       <c r="M4" s="84">
@@ -7081,8 +7065,8 @@
         <v>360</v>
       </c>
       <c r="E5" s="84" t="str">
-        <f>SUBSTITUTE(D5, "hazr-", "")&amp;"-rule"</f>
-        <v>t-dtg-mq-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dtg-mq-lb-rule1884</v>
       </c>
       <c r="F5" s="84" t="str">
         <f>SUBSTITUTE(D5, "hazr-", "")&amp;"-fe"</f>
@@ -7105,7 +7089,7 @@
         <v>1884</v>
       </c>
       <c r="L5" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dtg-mq-lb-pb1884</v>
       </c>
       <c r="M5" s="84">
@@ -7139,8 +7123,8 @@
         <v>356</v>
       </c>
       <c r="E6" s="86" t="str">
-        <f t="shared" ref="E6:E50" si="1">SUBSTITUTE(D6, "hazr-", "")&amp;"-rule"</f>
-        <v>t-dtg-ingap-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dtg-ingap-lb-rule8081</v>
       </c>
       <c r="F6" s="86" t="str">
         <f t="shared" ref="F6:F50" si="2">SUBSTITUTE(D6, "hazr-", "")&amp;"-fe"</f>
@@ -7163,7 +7147,7 @@
         <v>8081</v>
       </c>
       <c r="L6" s="86" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dtg-ingap-lb-pb8081</v>
       </c>
       <c r="M6" s="86">
@@ -7197,8 +7181,8 @@
         <v>359</v>
       </c>
       <c r="E7" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-geoap-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dtg-geoap-lb-rule8089</v>
       </c>
       <c r="F7" s="84" t="str">
         <f t="shared" si="2"/>
@@ -7221,7 +7205,7 @@
         <v>8089</v>
       </c>
       <c r="L7" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dtg-geoap-lb-pb8089</v>
       </c>
       <c r="M7" s="84">
@@ -7255,8 +7239,8 @@
         <v>359</v>
       </c>
       <c r="E8" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-geoap-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dtg-geoap-lb-rule9089</v>
       </c>
       <c r="F8" s="84" t="str">
         <f t="shared" si="2"/>
@@ -7279,7 +7263,7 @@
         <v>9089</v>
       </c>
       <c r="L8" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dtg-geoap-lb-pb9089</v>
       </c>
       <c r="M8" s="84">
@@ -7299,118 +7283,118 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B9" s="112" t="str" cm="1">
+      <c r="A9" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="74" t="str" cm="1">
         <f t="array" ref="B9">UPPER(INDEX(_xlfn.TEXTSPLIT($C9, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="74" t="s">
         <v>391</v>
       </c>
-      <c r="D9" s="112" t="s">
+      <c r="D9" s="74" t="s">
         <v>358</v>
       </c>
-      <c r="E9" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-extgeoap-lb-rule</v>
-      </c>
-      <c r="F9" s="112" t="str">
+      <c r="E9" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dtg-extgeoap-lb-rule3660</v>
+      </c>
+      <c r="F9" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dtg-extgeoap-lb-fe</v>
       </c>
-      <c r="G9" s="112" t="s">
+      <c r="G9" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="112">
+      <c r="H9" s="74">
         <v>3660</v>
       </c>
-      <c r="I9" s="112" t="b">
+      <c r="I9" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="112" t="str">
+      <c r="J9" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dtg-extgeoap-lb-bp</v>
       </c>
-      <c r="K9" s="112">
+      <c r="K9" s="74">
         <v>3660</v>
       </c>
-      <c r="L9" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L9" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dtg-extgeoap-lb-pb3660</v>
       </c>
-      <c r="M9" s="112">
+      <c r="M9" s="74">
         <v>3660</v>
       </c>
-      <c r="N9" s="112">
+      <c r="N9" s="74">
         <v>4</v>
       </c>
-      <c r="O9" s="112" t="s">
+      <c r="O9" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P9" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="112" t="b">
+      <c r="P9" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="112" t="str" cm="1">
+      <c r="A10" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="74" t="str" cm="1">
         <f t="array" ref="B10">UPPER(INDEX(_xlfn.TEXTSPLIT($C10, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="C10" s="112" t="s">
+      <c r="C10" s="74" t="s">
         <v>391</v>
       </c>
-      <c r="D10" s="112" t="s">
+      <c r="D10" s="74" t="s">
         <v>358</v>
       </c>
-      <c r="E10" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-extgeoap-lb-rule</v>
-      </c>
-      <c r="F10" s="112" t="str">
+      <c r="E10" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dtg-extgeoap-lb-rule3661</v>
+      </c>
+      <c r="F10" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dtg-extgeoap-lb-fe</v>
       </c>
-      <c r="G10" s="112" t="s">
+      <c r="G10" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="112">
+      <c r="H10" s="74">
         <v>3661</v>
       </c>
-      <c r="I10" s="112" t="b">
+      <c r="I10" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J10" s="112" t="str">
+      <c r="J10" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dtg-extgeoap-lb-bp</v>
       </c>
-      <c r="K10" s="112">
+      <c r="K10" s="74">
         <v>3661</v>
       </c>
-      <c r="L10" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L10" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dtg-extgeoap-lb-pb3661</v>
       </c>
-      <c r="M10" s="112">
+      <c r="M10" s="74">
         <v>3661</v>
       </c>
-      <c r="N10" s="112">
+      <c r="N10" s="74">
         <v>4</v>
       </c>
-      <c r="O10" s="112" t="s">
+      <c r="O10" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P10" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="112" t="b">
+      <c r="P10" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7429,8 +7413,8 @@
         <v>369</v>
       </c>
       <c r="E11" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-dprweb-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dtg-dprweb-lb-rule443</v>
       </c>
       <c r="F11" s="84" t="str">
         <f t="shared" si="2"/>
@@ -7453,7 +7437,7 @@
         <v>443</v>
       </c>
       <c r="L11" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dtg-dprweb-lb-pb443</v>
       </c>
       <c r="M11" s="84">
@@ -7487,8 +7471,8 @@
         <v>370</v>
       </c>
       <c r="E12" s="86" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-dprap-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dtg-dprap-lb-rule8082</v>
       </c>
       <c r="F12" s="86" t="str">
         <f t="shared" si="2"/>
@@ -7511,7 +7495,7 @@
         <v>8082</v>
       </c>
       <c r="L12" s="86" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dtg-dprap-lb-pb8082</v>
       </c>
       <c r="M12" s="86">
@@ -7545,8 +7529,8 @@
         <v>368</v>
       </c>
       <c r="E13" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-diosweb-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dtg-diosweb-lb-rule443</v>
       </c>
       <c r="F13" s="84" t="str">
         <f t="shared" si="2"/>
@@ -7569,7 +7553,7 @@
         <v>443</v>
       </c>
       <c r="L13" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dtg-diosweb-lb-pb443</v>
       </c>
       <c r="M13" s="84">
@@ -7603,8 +7587,8 @@
         <v>367</v>
       </c>
       <c r="E14" s="86" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-diosap-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dtg-diosap-lb-rule8080</v>
       </c>
       <c r="F14" s="86" t="str">
         <f t="shared" si="2"/>
@@ -7627,7 +7611,7 @@
         <v>8080</v>
       </c>
       <c r="L14" s="86" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dtg-diosap-lb-pb8080</v>
       </c>
       <c r="M14" s="86">
@@ -7661,8 +7645,8 @@
         <v>366</v>
       </c>
       <c r="E15" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdsvadm-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dtg-cdsvadm-lb-rule9100</v>
       </c>
       <c r="F15" s="84" t="str">
         <f t="shared" si="2"/>
@@ -7685,7 +7669,7 @@
         <v>9100</v>
       </c>
       <c r="L15" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dtg-cdsvadm-lb-pb9100</v>
       </c>
       <c r="M15" s="84">
@@ -7719,8 +7703,8 @@
         <v>366</v>
       </c>
       <c r="E16" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdsvadm-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dtg-cdsvadm-lb-rule9300</v>
       </c>
       <c r="F16" s="84" t="str">
         <f t="shared" si="2"/>
@@ -7743,7 +7727,7 @@
         <v>9300</v>
       </c>
       <c r="L16" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dtg-cdsvadm-lb-pb9300</v>
       </c>
       <c r="M16" s="84">
@@ -7777,8 +7761,8 @@
         <v>366</v>
       </c>
       <c r="E17" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdsvadm-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dtg-cdsvadm-lb-rule9105</v>
       </c>
       <c r="F17" s="84" t="str">
         <f t="shared" si="2"/>
@@ -7801,7 +7785,7 @@
         <v>9105</v>
       </c>
       <c r="L17" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dtg-cdsvadm-lb-pb9105</v>
       </c>
       <c r="M17" s="84">
@@ -7835,8 +7819,8 @@
         <v>366</v>
       </c>
       <c r="E18" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdsvadm-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dtg-cdsvadm-lb-rule9003</v>
       </c>
       <c r="F18" s="84" t="str">
         <f t="shared" si="2"/>
@@ -7859,7 +7843,7 @@
         <v>9003</v>
       </c>
       <c r="L18" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dtg-cdsvadm-lb-pb9003</v>
       </c>
       <c r="M18" s="84">
@@ -7893,8 +7877,8 @@
         <v>366</v>
       </c>
       <c r="E19" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdsvadm-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dtg-cdsvadm-lb-rule8088</v>
       </c>
       <c r="F19" s="84" t="str">
         <f t="shared" si="2"/>
@@ -7917,7 +7901,7 @@
         <v>8088</v>
       </c>
       <c r="L19" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dtg-cdsvadm-lb-pb8088</v>
       </c>
       <c r="M19" s="84">
@@ -7950,10 +7934,7 @@
       <c r="D20" s="86" t="s">
         <v>365</v>
       </c>
-      <c r="E20" s="86" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdstap-lb-rule</v>
-      </c>
+      <c r="E20" s="86"/>
       <c r="F20" s="86" t="str">
         <f t="shared" si="2"/>
         <v>t-dtg-cdstap-lb-fe</v>
@@ -8000,8 +7981,8 @@
         <v>364</v>
       </c>
       <c r="E21" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdmlap-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dtg-cdmlap-lb-rule9305</v>
       </c>
       <c r="F21" s="84" t="str">
         <f t="shared" si="2"/>
@@ -8024,7 +8005,7 @@
         <v>9305</v>
       </c>
       <c r="L21" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dtg-cdmlap-lb-pb9305</v>
       </c>
       <c r="M21" s="84">
@@ -8058,8 +8039,8 @@
         <v>364</v>
       </c>
       <c r="E22" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdmlap-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dtg-cdmlap-lb-rule9306</v>
       </c>
       <c r="F22" s="84" t="str">
         <f t="shared" si="2"/>
@@ -8082,7 +8063,7 @@
         <v>9306</v>
       </c>
       <c r="L22" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dtg-cdmlap-lb-pb9306</v>
       </c>
       <c r="M22" s="84">
@@ -8102,118 +8083,118 @@
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B23" s="112" t="str" cm="1">
+      <c r="A23" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B23" s="74" t="str" cm="1">
         <f t="array" ref="B23">UPPER(INDEX(_xlfn.TEXTSPLIT($C23, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="C23" s="112" t="s">
+      <c r="C23" s="74" t="s">
         <v>391</v>
       </c>
-      <c r="D23" s="112" t="s">
+      <c r="D23" s="74" t="s">
         <v>357</v>
       </c>
-      <c r="E23" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-ap-lb-rule</v>
-      </c>
-      <c r="F23" s="112" t="str">
+      <c r="E23" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dtg-ap-lb-rule8080</v>
+      </c>
+      <c r="F23" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dtg-ap-lb-fe</v>
       </c>
-      <c r="G23" s="112" t="s">
+      <c r="G23" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H23" s="112">
+      <c r="H23" s="74">
         <v>8080</v>
       </c>
-      <c r="I23" s="112" t="b">
+      <c r="I23" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J23" s="112" t="str">
+      <c r="J23" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dtg-ap-lb-bp</v>
       </c>
-      <c r="K23" s="112">
+      <c r="K23" s="74">
         <v>8080</v>
       </c>
-      <c r="L23" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L23" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dtg-ap-lb-pb8080</v>
       </c>
-      <c r="M23" s="112">
+      <c r="M23" s="74">
         <v>8080</v>
       </c>
-      <c r="N23" s="112">
+      <c r="N23" s="74">
         <v>4</v>
       </c>
-      <c r="O23" s="112" t="s">
+      <c r="O23" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P23" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="112" t="b">
+      <c r="P23" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B24" s="112" t="str" cm="1">
+      <c r="A24" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B24" s="74" t="str" cm="1">
         <f t="array" ref="B24">UPPER(INDEX(_xlfn.TEXTSPLIT($C24, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="C24" s="112" t="s">
+      <c r="C24" s="74" t="s">
         <v>391</v>
       </c>
-      <c r="D24" s="112" t="s">
+      <c r="D24" s="74" t="s">
         <v>357</v>
       </c>
-      <c r="E24" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-ap-lb-rule</v>
-      </c>
-      <c r="F24" s="112" t="str">
+      <c r="E24" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dtg-ap-lb-rule9087</v>
+      </c>
+      <c r="F24" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dtg-ap-lb-fe</v>
       </c>
-      <c r="G24" s="112" t="s">
+      <c r="G24" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H24" s="112">
+      <c r="H24" s="74">
         <v>9087</v>
       </c>
-      <c r="I24" s="112" t="b">
+      <c r="I24" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J24" s="112" t="str">
+      <c r="J24" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dtg-ap-lb-bp</v>
       </c>
-      <c r="K24" s="112">
+      <c r="K24" s="74">
         <v>9087</v>
       </c>
-      <c r="L24" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L24" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dtg-ap-lb-pb9087</v>
       </c>
-      <c r="M24" s="112">
+      <c r="M24" s="74">
         <v>9087</v>
       </c>
-      <c r="N24" s="112">
+      <c r="N24" s="74">
         <v>4</v>
       </c>
-      <c r="O24" s="112" t="s">
+      <c r="O24" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P24" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="112" t="b">
+      <c r="P24" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8232,8 +8213,8 @@
         <v>361</v>
       </c>
       <c r="E25" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-admweb-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dtg-admweb-lb-rule8088</v>
       </c>
       <c r="F25" s="84" t="str">
         <f t="shared" si="2"/>
@@ -8256,7 +8237,7 @@
         <v>8088</v>
       </c>
       <c r="L25" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dtg-admweb-lb-pb8088</v>
       </c>
       <c r="M25" s="84">
@@ -8276,118 +8257,118 @@
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B26" s="112" t="str" cm="1">
+      <c r="A26" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B26" s="74" t="str" cm="1">
         <f t="array" ref="B26">UPPER(INDEX(_xlfn.TEXTSPLIT($C26, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="C26" s="112" t="s">
+      <c r="C26" s="74" t="s">
         <v>391</v>
       </c>
-      <c r="D26" s="112" t="s">
+      <c r="D26" s="74" t="s">
         <v>362</v>
       </c>
-      <c r="E26" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-admap-lb-rule</v>
-      </c>
-      <c r="F26" s="112" t="str">
+      <c r="E26" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dtg-admap-lb-rule8085</v>
+      </c>
+      <c r="F26" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dtg-admap-lb-fe</v>
       </c>
-      <c r="G26" s="112" t="s">
+      <c r="G26" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H26" s="112">
+      <c r="H26" s="74">
         <v>8085</v>
       </c>
-      <c r="I26" s="112" t="b">
+      <c r="I26" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J26" s="112" t="str">
+      <c r="J26" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dtg-admap-lb-bp</v>
       </c>
-      <c r="K26" s="112">
+      <c r="K26" s="74">
         <v>8085</v>
       </c>
-      <c r="L26" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L26" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dtg-admap-lb-pb8085</v>
       </c>
-      <c r="M26" s="112">
+      <c r="M26" s="74">
         <v>8085</v>
       </c>
-      <c r="N26" s="112">
+      <c r="N26" s="74">
         <v>4</v>
       </c>
-      <c r="O26" s="112" t="s">
+      <c r="O26" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P26" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="112" t="b">
+      <c r="P26" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B27" s="112" t="str" cm="1">
+      <c r="A27" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B27" s="74" t="str" cm="1">
         <f t="array" ref="B27">UPPER(INDEX(_xlfn.TEXTSPLIT($C27, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="C27" s="112" t="s">
+      <c r="C27" s="74" t="s">
         <v>391</v>
       </c>
-      <c r="D27" s="112" t="s">
+      <c r="D27" s="74" t="s">
         <v>362</v>
       </c>
-      <c r="E27" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-admap-lb-rule</v>
-      </c>
-      <c r="F27" s="112" t="str">
+      <c r="E27" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dtg-admap-lb-rule8087</v>
+      </c>
+      <c r="F27" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dtg-admap-lb-fe</v>
       </c>
-      <c r="G27" s="112" t="s">
+      <c r="G27" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H27" s="112">
+      <c r="H27" s="74">
         <v>8087</v>
       </c>
-      <c r="I27" s="112" t="b">
+      <c r="I27" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J27" s="112" t="str">
+      <c r="J27" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dtg-admap-lb-bp</v>
       </c>
-      <c r="K27" s="112">
+      <c r="K27" s="74">
         <v>8087</v>
       </c>
-      <c r="L27" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L27" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dtg-admap-lb-pb8087</v>
       </c>
-      <c r="M27" s="112">
+      <c r="M27" s="74">
         <v>8087</v>
       </c>
-      <c r="N27" s="112">
+      <c r="N27" s="74">
         <v>4</v>
       </c>
-      <c r="O27" s="112" t="s">
+      <c r="O27" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P27" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q27" s="112" t="b">
+      <c r="P27" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8405,10 +8386,7 @@
       <c r="D28" s="84" t="s">
         <v>385</v>
       </c>
-      <c r="E28" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-doip-web-lb-rule</v>
-      </c>
+      <c r="E28" s="84"/>
       <c r="F28" s="84" t="str">
         <f t="shared" si="2"/>
         <v>t-doip-web-lb-fe</v>
@@ -8454,10 +8432,7 @@
       <c r="D29" s="86" t="s">
         <v>386</v>
       </c>
-      <c r="E29" s="86" t="str">
-        <f t="shared" si="1"/>
-        <v>t-doip-ap-lb-rule</v>
-      </c>
+      <c r="E29" s="86"/>
       <c r="F29" s="86" t="str">
         <f t="shared" si="2"/>
         <v>t-doip-ap-lb-fe</v>
@@ -8503,10 +8478,7 @@
       <c r="D30" s="84" t="s">
         <v>387</v>
       </c>
-      <c r="E30" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-doip-adm-lb-rule</v>
-      </c>
+      <c r="E30" s="84"/>
       <c r="F30" s="84" t="str">
         <f t="shared" si="2"/>
         <v>t-doip-adm-lb-fe</v>
@@ -8539,118 +8511,118 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B31" s="112" t="str" cm="1">
+      <c r="A31" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B31" s="74" t="str" cm="1">
         <f t="array" ref="B31">UPPER(INDEX(_xlfn.TEXTSPLIT($C31, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="C31" s="112" t="s">
+      <c r="C31" s="74" t="s">
         <v>289</v>
       </c>
-      <c r="D31" s="112" t="s">
+      <c r="D31" s="74" t="s">
         <v>292</v>
       </c>
-      <c r="E31" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-web-lb-rule</v>
-      </c>
-      <c r="F31" s="112" t="str">
+      <c r="E31" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dis-web-lb-rule80</v>
+      </c>
+      <c r="F31" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dis-web-lb-fe</v>
       </c>
-      <c r="G31" s="112" t="s">
+      <c r="G31" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H31" s="112">
+      <c r="H31" s="74">
         <v>80</v>
       </c>
-      <c r="I31" s="112" t="b">
+      <c r="I31" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J31" s="112" t="str">
+      <c r="J31" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dis-web-lb-bp</v>
       </c>
-      <c r="K31" s="112">
+      <c r="K31" s="74">
         <v>80</v>
       </c>
-      <c r="L31" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L31" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dis-web-lb-pb80</v>
       </c>
-      <c r="M31" s="112">
+      <c r="M31" s="74">
         <v>80</v>
       </c>
-      <c r="N31" s="112">
+      <c r="N31" s="74">
         <v>4</v>
       </c>
-      <c r="O31" s="112" t="s">
+      <c r="O31" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P31" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="112" t="b">
+      <c r="P31" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B32" s="112" t="str" cm="1">
+      <c r="A32" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B32" s="74" t="str" cm="1">
         <f t="array" ref="B32">UPPER(INDEX(_xlfn.TEXTSPLIT($C32, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="C32" s="112" t="s">
+      <c r="C32" s="74" t="s">
         <v>289</v>
       </c>
-      <c r="D32" s="112" t="s">
+      <c r="D32" s="74" t="s">
         <v>292</v>
       </c>
-      <c r="E32" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-web-lb-rule</v>
-      </c>
-      <c r="F32" s="112" t="str">
+      <c r="E32" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dis-web-lb-rule443</v>
+      </c>
+      <c r="F32" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dis-web-lb-fe</v>
       </c>
-      <c r="G32" s="112" t="s">
+      <c r="G32" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H32" s="112">
+      <c r="H32" s="74">
         <v>443</v>
       </c>
-      <c r="I32" s="112" t="b">
+      <c r="I32" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J32" s="112" t="str">
+      <c r="J32" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dis-web-lb-bp</v>
       </c>
-      <c r="K32" s="112">
+      <c r="K32" s="74">
         <v>443</v>
       </c>
-      <c r="L32" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L32" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dis-web-lb-pb443</v>
       </c>
-      <c r="M32" s="112">
+      <c r="M32" s="74">
         <v>443</v>
       </c>
-      <c r="N32" s="112">
+      <c r="N32" s="74">
         <v>4</v>
       </c>
-      <c r="O32" s="112" t="s">
+      <c r="O32" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P32" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="112" t="b">
+      <c r="P32" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8669,8 +8641,8 @@
         <v>350</v>
       </c>
       <c r="E33" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-walkweb-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dis-walkweb-lb-rule443</v>
       </c>
       <c r="F33" s="84" t="str">
         <f t="shared" si="2"/>
@@ -8693,7 +8665,7 @@
         <v>443</v>
       </c>
       <c r="L33" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dis-walkweb-lb-pb443</v>
       </c>
       <c r="M33" s="84">
@@ -8713,60 +8685,60 @@
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A34" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B34" s="112" t="str" cm="1">
+      <c r="A34" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B34" s="74" t="str" cm="1">
         <f t="array" ref="B34">UPPER(INDEX(_xlfn.TEXTSPLIT($C34, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="C34" s="112" t="s">
+      <c r="C34" s="74" t="s">
         <v>205</v>
       </c>
-      <c r="D34" s="112" t="s">
+      <c r="D34" s="74" t="s">
         <v>348</v>
       </c>
-      <c r="E34" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-walkap-lb-rule</v>
-      </c>
-      <c r="F34" s="112" t="str">
+      <c r="E34" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dis-walkap-lb-rule8080</v>
+      </c>
+      <c r="F34" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dis-walkap-lb-fe</v>
       </c>
-      <c r="G34" s="112" t="s">
+      <c r="G34" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H34" s="112">
+      <c r="H34" s="74">
         <v>8080</v>
       </c>
-      <c r="I34" s="112" t="b">
+      <c r="I34" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J34" s="112" t="str">
+      <c r="J34" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dis-walkap-lb-bp</v>
       </c>
-      <c r="K34" s="112">
+      <c r="K34" s="74">
         <v>8080</v>
       </c>
-      <c r="L34" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L34" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dis-walkap-lb-pb8080</v>
       </c>
-      <c r="M34" s="112">
+      <c r="M34" s="74">
         <v>8080</v>
       </c>
-      <c r="N34" s="112">
+      <c r="N34" s="74">
         <v>4</v>
       </c>
-      <c r="O34" s="112" t="s">
+      <c r="O34" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P34" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="112" t="b">
+      <c r="P34" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8785,8 +8757,8 @@
         <v>351</v>
       </c>
       <c r="E35" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-drvmsgap-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dis-drvmsgap-lb-rule8080</v>
       </c>
       <c r="F35" s="84" t="str">
         <f t="shared" si="2"/>
@@ -8809,7 +8781,7 @@
         <v>8080</v>
       </c>
       <c r="L35" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dis-drvmsgap-lb-pb8080</v>
       </c>
       <c r="M35" s="84">
@@ -8829,60 +8801,60 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A36" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B36" s="112" t="str" cm="1">
+      <c r="A36" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B36" s="74" t="str" cm="1">
         <f t="array" ref="B36">UPPER(INDEX(_xlfn.TEXTSPLIT($C36, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="C36" s="112" t="s">
+      <c r="C36" s="74" t="s">
         <v>289</v>
       </c>
-      <c r="D36" s="112" t="s">
+      <c r="D36" s="74" t="s">
         <v>349</v>
       </c>
-      <c r="E36" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-drvcltap-lb-rule</v>
-      </c>
-      <c r="F36" s="112" t="str">
+      <c r="E36" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dis-drvcltap-lb-rule8081</v>
+      </c>
+      <c r="F36" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dis-drvcltap-lb-fe</v>
       </c>
-      <c r="G36" s="112" t="s">
+      <c r="G36" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H36" s="112">
+      <c r="H36" s="74">
         <v>8081</v>
       </c>
-      <c r="I36" s="112" t="b">
+      <c r="I36" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J36" s="112" t="str">
+      <c r="J36" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dis-drvcltap-lb-bp</v>
       </c>
-      <c r="K36" s="112">
+      <c r="K36" s="74">
         <v>8081</v>
       </c>
-      <c r="L36" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L36" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dis-drvcltap-lb-pb8081</v>
       </c>
-      <c r="M36" s="112">
+      <c r="M36" s="74">
         <v>8081</v>
       </c>
-      <c r="N36" s="112">
+      <c r="N36" s="74">
         <v>4</v>
       </c>
-      <c r="O36" s="112" t="s">
+      <c r="O36" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P36" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="112" t="b">
+      <c r="P36" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8901,8 +8873,8 @@
         <v>354</v>
       </c>
       <c r="E37" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-cmsweb-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dis-cmsweb-lb-rule80</v>
       </c>
       <c r="F37" s="84" t="str">
         <f t="shared" si="2"/>
@@ -8925,7 +8897,7 @@
         <v>80</v>
       </c>
       <c r="L37" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dis-cmsweb-lb-pb80</v>
       </c>
       <c r="M37" s="84">
@@ -8945,60 +8917,60 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A38" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B38" s="112" t="str" cm="1">
+      <c r="A38" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B38" s="74" t="str" cm="1">
         <f t="array" ref="B38">UPPER(INDEX(_xlfn.TEXTSPLIT($C38, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="C38" s="112" t="s">
+      <c r="C38" s="74" t="s">
         <v>289</v>
       </c>
-      <c r="D38" s="112" t="s">
+      <c r="D38" s="74" t="s">
         <v>354</v>
       </c>
-      <c r="E38" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-cmsweb-lb-rule</v>
-      </c>
-      <c r="F38" s="112" t="str">
+      <c r="E38" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dis-cmsweb-lb-rule443</v>
+      </c>
+      <c r="F38" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dis-cmsweb-lb-fe</v>
       </c>
-      <c r="G38" s="112" t="s">
+      <c r="G38" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H38" s="112">
+      <c r="H38" s="74">
         <v>443</v>
       </c>
-      <c r="I38" s="112" t="b">
+      <c r="I38" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J38" s="112" t="str">
+      <c r="J38" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dis-cmsweb-lb-bp</v>
       </c>
-      <c r="K38" s="112">
+      <c r="K38" s="74">
         <v>443</v>
       </c>
-      <c r="L38" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L38" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dis-cmsweb-lb-pb443</v>
       </c>
-      <c r="M38" s="112">
+      <c r="M38" s="74">
         <v>443</v>
       </c>
-      <c r="N38" s="112">
+      <c r="N38" s="74">
         <v>4</v>
       </c>
-      <c r="O38" s="112" t="s">
+      <c r="O38" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P38" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q38" s="112" t="b">
+      <c r="P38" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9017,8 +8989,8 @@
         <v>353</v>
       </c>
       <c r="E39" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-cmsap-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dis-cmsap-lb-rule4001</v>
       </c>
       <c r="F39" s="84" t="str">
         <f t="shared" si="2"/>
@@ -9041,7 +9013,7 @@
         <v>4001</v>
       </c>
       <c r="L39" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dis-cmsap-lb-pb4001</v>
       </c>
       <c r="M39" s="84">
@@ -9061,60 +9033,60 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A40" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B40" s="112" t="str" cm="1">
+      <c r="A40" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B40" s="74" t="str" cm="1">
         <f t="array" ref="B40">UPPER(INDEX(_xlfn.TEXTSPLIT($C40, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="C40" s="112" t="s">
+      <c r="C40" s="74" t="s">
         <v>205</v>
       </c>
-      <c r="D40" s="112" t="s">
+      <c r="D40" s="74" t="s">
         <v>352</v>
       </c>
-      <c r="E40" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-cmsadm-lb-rule</v>
-      </c>
-      <c r="F40" s="112" t="str">
+      <c r="E40" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dis-cmsadm-lb-rule443</v>
+      </c>
+      <c r="F40" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dis-cmsadm-lb-fe</v>
       </c>
-      <c r="G40" s="112" t="s">
+      <c r="G40" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H40" s="112">
+      <c r="H40" s="74">
         <v>443</v>
       </c>
-      <c r="I40" s="112" t="b">
+      <c r="I40" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J40" s="112" t="str">
+      <c r="J40" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dis-cmsadm-lb-bp</v>
       </c>
-      <c r="K40" s="112">
+      <c r="K40" s="74">
         <v>443</v>
       </c>
-      <c r="L40" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L40" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dis-cmsadm-lb-pb443</v>
       </c>
-      <c r="M40" s="112">
+      <c r="M40" s="74">
         <v>443</v>
       </c>
-      <c r="N40" s="112">
+      <c r="N40" s="74">
         <v>4</v>
       </c>
-      <c r="O40" s="112" t="s">
+      <c r="O40" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P40" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q40" s="112" t="b">
+      <c r="P40" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9133,8 +9105,8 @@
         <v>355</v>
       </c>
       <c r="E41" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-cmbsap-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dis-cmbsap-lb-rule8080</v>
       </c>
       <c r="F41" s="84" t="str">
         <f t="shared" si="2"/>
@@ -9157,7 +9129,7 @@
         <v>8080</v>
       </c>
       <c r="L41" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dis-cmbsap-lb-pb8080</v>
       </c>
       <c r="M41" s="84">
@@ -9177,60 +9149,60 @@
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A42" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B42" s="112" t="str" cm="1">
+      <c r="A42" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B42" s="74" t="str" cm="1">
         <f t="array" ref="B42">UPPER(INDEX(_xlfn.TEXTSPLIT($C42, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="C42" s="112" t="s">
+      <c r="C42" s="74" t="s">
         <v>205</v>
       </c>
-      <c r="D42" s="112" t="s">
+      <c r="D42" s="74" t="s">
         <v>345</v>
       </c>
-      <c r="E42" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-bbiweb-lb-rule</v>
-      </c>
-      <c r="F42" s="112" t="str">
+      <c r="E42" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dis-bbiweb-lb-rule443</v>
+      </c>
+      <c r="F42" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dis-bbiweb-lb-fe</v>
       </c>
-      <c r="G42" s="112" t="s">
+      <c r="G42" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H42" s="112">
+      <c r="H42" s="74">
         <v>443</v>
       </c>
-      <c r="I42" s="112" t="b">
+      <c r="I42" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J42" s="112" t="str">
+      <c r="J42" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dis-bbiweb-lb-bp</v>
       </c>
-      <c r="K42" s="112">
+      <c r="K42" s="74">
         <v>443</v>
       </c>
-      <c r="L42" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L42" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dis-bbiweb-lb-pb443</v>
       </c>
-      <c r="M42" s="112">
+      <c r="M42" s="74">
         <v>443</v>
       </c>
-      <c r="N42" s="112">
+      <c r="N42" s="74">
         <v>4</v>
       </c>
-      <c r="O42" s="112" t="s">
+      <c r="O42" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P42" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q42" s="112" t="b">
+      <c r="P42" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9249,8 +9221,8 @@
         <v>347</v>
       </c>
       <c r="E43" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-bbimsgap-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dis-bbimsgap-lb-rule20030</v>
       </c>
       <c r="F43" s="84" t="str">
         <f t="shared" si="2"/>
@@ -9273,7 +9245,7 @@
         <v>20030</v>
       </c>
       <c r="L43" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dis-bbimsgap-lb-pb20030</v>
       </c>
       <c r="M43" s="84">
@@ -9293,176 +9265,176 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A44" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B44" s="112" t="str" cm="1">
+      <c r="A44" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B44" s="74" t="str" cm="1">
         <f t="array" ref="B44">UPPER(INDEX(_xlfn.TEXTSPLIT($C44, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="C44" s="112" t="s">
+      <c r="C44" s="74" t="s">
         <v>205</v>
       </c>
-      <c r="D44" s="112" t="s">
+      <c r="D44" s="74" t="s">
         <v>346</v>
       </c>
-      <c r="E44" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-bbicltap-lb-rule</v>
-      </c>
-      <c r="F44" s="112" t="str">
+      <c r="E44" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dis-bbicltap-lb-rule20000</v>
+      </c>
+      <c r="F44" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dis-bbicltap-lb-fe</v>
       </c>
-      <c r="G44" s="112" t="s">
+      <c r="G44" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H44" s="112">
+      <c r="H44" s="74">
         <v>20000</v>
       </c>
-      <c r="I44" s="112" t="b">
+      <c r="I44" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J44" s="112" t="str">
+      <c r="J44" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dis-bbicltap-lb-bp</v>
       </c>
-      <c r="K44" s="112">
+      <c r="K44" s="74">
         <v>20000</v>
       </c>
-      <c r="L44" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L44" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dis-bbicltap-lb-pb20000</v>
       </c>
-      <c r="M44" s="112">
+      <c r="M44" s="74">
         <v>20000</v>
       </c>
-      <c r="N44" s="112">
+      <c r="N44" s="74">
         <v>4</v>
       </c>
-      <c r="O44" s="112" t="s">
+      <c r="O44" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P44" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q44" s="112" t="b">
+      <c r="P44" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A45" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B45" s="112" t="str" cm="1">
+      <c r="A45" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B45" s="74" t="str" cm="1">
         <f t="array" ref="B45">UPPER(INDEX(_xlfn.TEXTSPLIT($C45, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="C45" s="112" t="s">
+      <c r="C45" s="74" t="s">
         <v>205</v>
       </c>
-      <c r="D45" s="112" t="s">
+      <c r="D45" s="74" t="s">
         <v>346</v>
       </c>
-      <c r="E45" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-bbicltap-lb-rule</v>
-      </c>
-      <c r="F45" s="112" t="str">
+      <c r="E45" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dis-bbicltap-lb-rule21000</v>
+      </c>
+      <c r="F45" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dis-bbicltap-lb-fe</v>
       </c>
-      <c r="G45" s="112" t="s">
+      <c r="G45" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H45" s="112">
+      <c r="H45" s="74">
         <v>21000</v>
       </c>
-      <c r="I45" s="112" t="b">
+      <c r="I45" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J45" s="112" t="str">
+      <c r="J45" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dis-bbicltap-lb-bp</v>
       </c>
-      <c r="K45" s="112">
+      <c r="K45" s="74">
         <v>21000</v>
       </c>
-      <c r="L45" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L45" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dis-bbicltap-lb-pb21000</v>
       </c>
-      <c r="M45" s="112">
+      <c r="M45" s="74">
         <v>21000</v>
       </c>
-      <c r="N45" s="112">
+      <c r="N45" s="74">
         <v>4</v>
       </c>
-      <c r="O45" s="112" t="s">
+      <c r="O45" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P45" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q45" s="112" t="b">
+      <c r="P45" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A46" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B46" s="112" t="str" cm="1">
+      <c r="A46" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B46" s="74" t="str" cm="1">
         <f t="array" ref="B46">UPPER(INDEX(_xlfn.TEXTSPLIT($C46, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="C46" s="112" t="s">
+      <c r="C46" s="74" t="s">
         <v>205</v>
       </c>
-      <c r="D46" s="112" t="s">
+      <c r="D46" s="74" t="s">
         <v>346</v>
       </c>
-      <c r="E46" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-bbicltap-lb-rule</v>
-      </c>
-      <c r="F46" s="112" t="str">
+      <c r="E46" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dis-bbicltap-lb-rule22000</v>
+      </c>
+      <c r="F46" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dis-bbicltap-lb-fe</v>
       </c>
-      <c r="G46" s="112" t="s">
+      <c r="G46" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H46" s="112">
+      <c r="H46" s="74">
         <v>22000</v>
       </c>
-      <c r="I46" s="112" t="b">
+      <c r="I46" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J46" s="112" t="str">
+      <c r="J46" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dis-bbicltap-lb-bp</v>
       </c>
-      <c r="K46" s="112">
+      <c r="K46" s="74">
         <v>22000</v>
       </c>
-      <c r="L46" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L46" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dis-bbicltap-lb-pb22000</v>
       </c>
-      <c r="M46" s="112">
+      <c r="M46" s="74">
         <v>22000</v>
       </c>
-      <c r="N46" s="112">
+      <c r="N46" s="74">
         <v>4</v>
       </c>
-      <c r="O46" s="112" t="s">
+      <c r="O46" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P46" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q46" s="112" t="b">
+      <c r="P46" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q46" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9481,8 +9453,8 @@
         <v>290</v>
       </c>
       <c r="E47" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-ap-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dis-ap-lb-rule8080</v>
       </c>
       <c r="F47" s="84" t="str">
         <f t="shared" si="2"/>
@@ -9505,7 +9477,7 @@
         <v>8080</v>
       </c>
       <c r="L47" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dis-ap-lb-pb8080</v>
       </c>
       <c r="M47" s="84">
@@ -9525,60 +9497,60 @@
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A48" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B48" s="112" t="str" cm="1">
+      <c r="A48" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B48" s="74" t="str" cm="1">
         <f t="array" ref="B48">UPPER(INDEX(_xlfn.TEXTSPLIT($C48, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="C48" s="112" t="s">
+      <c r="C48" s="74" t="s">
         <v>205</v>
       </c>
-      <c r="D48" s="112" t="s">
+      <c r="D48" s="74" t="s">
         <v>344</v>
       </c>
-      <c r="E48" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-adm-lb-rule</v>
-      </c>
-      <c r="F48" s="112" t="str">
+      <c r="E48" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dis-adm-lb-rule443</v>
+      </c>
+      <c r="F48" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dis-adm-lb-fe</v>
       </c>
-      <c r="G48" s="112" t="s">
+      <c r="G48" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H48" s="112">
+      <c r="H48" s="74">
         <v>443</v>
       </c>
-      <c r="I48" s="112" t="b">
+      <c r="I48" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J48" s="112" t="str">
+      <c r="J48" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dis-adm-lb-bp</v>
       </c>
-      <c r="K48" s="112">
+      <c r="K48" s="74">
         <v>443</v>
       </c>
-      <c r="L48" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L48" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dis-adm-lb-pb443</v>
       </c>
-      <c r="M48" s="112">
+      <c r="M48" s="74">
         <v>443</v>
       </c>
-      <c r="N48" s="112">
+      <c r="N48" s="74">
         <v>4</v>
       </c>
-      <c r="O48" s="112" t="s">
+      <c r="O48" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P48" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q48" s="112" t="b">
+      <c r="P48" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9597,8 +9569,8 @@
         <v>379</v>
       </c>
       <c r="E49" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-web-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dip-web-lb-rule443</v>
       </c>
       <c r="F49" s="84" t="str">
         <f t="shared" si="2"/>
@@ -9621,7 +9593,7 @@
         <v>443</v>
       </c>
       <c r="L49" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dip-web-lb-pb443</v>
       </c>
       <c r="M49" s="84">
@@ -9641,60 +9613,60 @@
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A50" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B50" s="112" t="str" cm="1">
+      <c r="A50" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B50" s="74" t="str" cm="1">
         <f t="array" ref="B50">UPPER(INDEX(_xlfn.TEXTSPLIT($C50, "-"), 3))</f>
         <v>DIP</v>
       </c>
-      <c r="C50" s="112" t="s">
+      <c r="C50" s="74" t="s">
         <v>630</v>
       </c>
-      <c r="D50" s="112" t="s">
+      <c r="D50" s="74" t="s">
         <v>379</v>
       </c>
-      <c r="E50" s="112" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-web-lb-rule</v>
-      </c>
-      <c r="F50" s="112" t="str">
+      <c r="E50" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dip-web-lb-rule9100</v>
+      </c>
+      <c r="F50" s="74" t="str">
         <f t="shared" si="2"/>
         <v>t-dip-web-lb-fe</v>
       </c>
-      <c r="G50" s="112" t="s">
+      <c r="G50" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H50" s="112">
+      <c r="H50" s="74">
         <v>9100</v>
       </c>
-      <c r="I50" s="112" t="b">
+      <c r="I50" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J50" s="112" t="str">
+      <c r="J50" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-dip-web-lb-bp</v>
       </c>
-      <c r="K50" s="112">
+      <c r="K50" s="74">
         <v>9100</v>
       </c>
-      <c r="L50" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L50" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dip-web-lb-pb9100</v>
       </c>
-      <c r="M50" s="112">
+      <c r="M50" s="74">
         <v>9100</v>
       </c>
-      <c r="N50" s="112">
+      <c r="N50" s="74">
         <v>4</v>
       </c>
-      <c r="O50" s="112" t="s">
+      <c r="O50" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P50" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q50" s="112" t="b">
+      <c r="P50" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9713,8 +9685,8 @@
         <v>378</v>
       </c>
       <c r="E51" s="84" t="str">
-        <f>SUBSTITUTE(D51, "hazr-", "")&amp;"-rule"</f>
-        <v>t-dip-mqweb-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dip-mqweb-lb-rule8883</v>
       </c>
       <c r="F51" s="84" t="str">
         <f>SUBSTITUTE(D51, "hazr-", "")&amp;"-fe"</f>
@@ -9737,7 +9709,7 @@
         <v>8883</v>
       </c>
       <c r="L51" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dip-mqweb-lb-pb8883</v>
       </c>
       <c r="M51" s="84">
@@ -9771,8 +9743,8 @@
         <v>378</v>
       </c>
       <c r="E52" s="84" t="str">
-        <f>SUBSTITUTE(D52, "hazr-", "")&amp;"-rule"</f>
-        <v>t-dip-mqweb-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dip-mqweb-lb-rule1884</v>
       </c>
       <c r="F52" s="84" t="str">
         <f>SUBSTITUTE(D52, "hazr-", "")&amp;"-fe"</f>
@@ -9795,7 +9767,7 @@
         <v>1884</v>
       </c>
       <c r="L52" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dip-mqweb-lb-pb1884</v>
       </c>
       <c r="M52" s="84">
@@ -9829,8 +9801,8 @@
         <v>378</v>
       </c>
       <c r="E53" s="84" t="str">
-        <f>SUBSTITUTE(D53, "hazr-", "")&amp;"-rule"</f>
-        <v>t-dip-mqweb-lb-rule</v>
+        <f t="shared" si="0"/>
+        <v>t-dip-mqweb-lb-rule9100</v>
       </c>
       <c r="F53" s="84" t="str">
         <f>SUBSTITUTE(D53, "hazr-", "")&amp;"-fe"</f>
@@ -9853,7 +9825,7 @@
         <v>9100</v>
       </c>
       <c r="L53" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dip-mqweb-lb-pb9100</v>
       </c>
       <c r="M53" s="84">
@@ -9873,234 +9845,234 @@
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A54" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B54" s="112" t="str" cm="1">
+      <c r="A54" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B54" s="74" t="str" cm="1">
         <f t="array" ref="B54">UPPER(INDEX(_xlfn.TEXTSPLIT($C54, "-"), 3))</f>
         <v>DIP</v>
       </c>
-      <c r="C54" s="112" t="s">
+      <c r="C54" s="74" t="s">
         <v>630</v>
       </c>
-      <c r="D54" s="112" t="s">
+      <c r="D54" s="74" t="s">
         <v>377</v>
       </c>
-      <c r="E54" s="112" t="str">
-        <f>SUBSTITUTE(D54, "hazr-", "")&amp;"-rule"</f>
-        <v>t-dip-mqap-lb-rule</v>
-      </c>
-      <c r="F54" s="112" t="str">
+      <c r="E54" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dip-mqap-lb-rule1883</v>
+      </c>
+      <c r="F54" s="74" t="str">
         <f>SUBSTITUTE(D54, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-mqap-lb-fe</v>
       </c>
-      <c r="G54" s="112" t="s">
+      <c r="G54" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H54" s="112">
+      <c r="H54" s="74">
         <v>1883</v>
       </c>
-      <c r="I54" s="112" t="b">
+      <c r="I54" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J54" s="112" t="str">
+      <c r="J54" s="74" t="str">
         <f>SUBSTITUTE(D54, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-mqap-lb-bp</v>
       </c>
-      <c r="K54" s="112">
+      <c r="K54" s="74">
         <v>1883</v>
       </c>
-      <c r="L54" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L54" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dip-mqap-lb-pb1883</v>
       </c>
-      <c r="M54" s="112">
+      <c r="M54" s="74">
         <v>1883</v>
       </c>
-      <c r="N54" s="112">
+      <c r="N54" s="74">
         <v>4</v>
       </c>
-      <c r="O54" s="112" t="s">
+      <c r="O54" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P54" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q54" s="112" t="b">
+      <c r="P54" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A55" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B55" s="112" t="str" cm="1">
+      <c r="A55" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B55" s="74" t="str" cm="1">
         <f t="array" ref="B55">UPPER(INDEX(_xlfn.TEXTSPLIT($C55, "-"), 3))</f>
         <v>DIP</v>
       </c>
-      <c r="C55" s="112" t="s">
+      <c r="C55" s="74" t="s">
         <v>630</v>
       </c>
-      <c r="D55" s="112" t="s">
+      <c r="D55" s="74" t="s">
         <v>377</v>
       </c>
-      <c r="E55" s="112" t="str">
-        <f t="shared" ref="E55:E88" si="4">SUBSTITUTE(D55, "hazr-", "")&amp;"-rule"</f>
-        <v>t-dip-mqap-lb-rule</v>
-      </c>
-      <c r="F55" s="112" t="str">
-        <f t="shared" ref="F55:F88" si="5">SUBSTITUTE(D55, "hazr-", "")&amp;"-fe"</f>
+      <c r="E55" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dip-mqap-lb-rule1884</v>
+      </c>
+      <c r="F55" s="74" t="str">
+        <f t="shared" ref="F55:F88" si="4">SUBSTITUTE(D55, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-mqap-lb-fe</v>
       </c>
-      <c r="G55" s="112" t="s">
+      <c r="G55" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H55" s="112">
+      <c r="H55" s="74">
         <v>1884</v>
       </c>
-      <c r="I55" s="112" t="b">
+      <c r="I55" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J55" s="112" t="str">
+      <c r="J55" s="74" t="str">
         <f>SUBSTITUTE(D55, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-mqap-lb-bp</v>
       </c>
-      <c r="K55" s="112">
+      <c r="K55" s="74">
         <v>1884</v>
       </c>
-      <c r="L55" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L55" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dip-mqap-lb-pb1884</v>
       </c>
-      <c r="M55" s="112">
+      <c r="M55" s="74">
         <v>1884</v>
       </c>
-      <c r="N55" s="112">
+      <c r="N55" s="74">
         <v>4</v>
       </c>
-      <c r="O55" s="112" t="s">
+      <c r="O55" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P55" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q55" s="112" t="b">
+      <c r="P55" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A56" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B56" s="112" t="str" cm="1">
+      <c r="A56" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B56" s="74" t="str" cm="1">
         <f t="array" ref="B56">UPPER(INDEX(_xlfn.TEXTSPLIT($C56, "-"), 3))</f>
         <v>DIP</v>
       </c>
-      <c r="C56" s="112" t="s">
+      <c r="C56" s="74" t="s">
         <v>630</v>
       </c>
-      <c r="D56" s="112" t="s">
+      <c r="D56" s="74" t="s">
         <v>377</v>
       </c>
-      <c r="E56" s="112" t="str">
+      <c r="E56" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dip-mqap-lb-rule18083</v>
+      </c>
+      <c r="F56" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-mqap-lb-rule</v>
-      </c>
-      <c r="F56" s="112" t="str">
-        <f t="shared" si="5"/>
         <v>t-dip-mqap-lb-fe</v>
       </c>
-      <c r="G56" s="112" t="s">
+      <c r="G56" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H56" s="112">
+      <c r="H56" s="74">
         <v>18083</v>
       </c>
-      <c r="I56" s="112" t="b">
+      <c r="I56" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J56" s="112" t="str">
-        <f t="shared" ref="J56:J88" si="6">SUBSTITUTE(D56, "hazr-", "")&amp;"-bp"</f>
+      <c r="J56" s="74" t="str">
+        <f t="shared" ref="J56:J88" si="5">SUBSTITUTE(D56, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-mqap-lb-bp</v>
       </c>
-      <c r="K56" s="112">
+      <c r="K56" s="74">
         <v>18083</v>
       </c>
-      <c r="L56" s="112" t="str">
-        <f t="shared" si="0"/>
+      <c r="L56" s="74" t="str">
+        <f t="shared" si="1"/>
         <v>t-dip-mqap-lb-pb18083</v>
       </c>
-      <c r="M56" s="112">
+      <c r="M56" s="74">
         <v>18083</v>
       </c>
-      <c r="N56" s="112">
+      <c r="N56" s="74">
         <v>4</v>
       </c>
-      <c r="O56" s="112" t="s">
+      <c r="O56" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P56" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q56" s="112" t="b">
+      <c r="P56" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A57" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B57" s="112" t="str" cm="1">
+      <c r="A57" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B57" s="74" t="str" cm="1">
         <f t="array" ref="B57">UPPER(INDEX(_xlfn.TEXTSPLIT($C57, "-"), 3))</f>
         <v>DIP</v>
       </c>
-      <c r="C57" s="112" t="s">
+      <c r="C57" s="74" t="s">
         <v>630</v>
       </c>
-      <c r="D57" s="112" t="s">
+      <c r="D57" s="74" t="s">
         <v>377</v>
       </c>
-      <c r="E57" s="112" t="str">
+      <c r="E57" s="74" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dip-mqap-lb-rule9100</v>
+      </c>
+      <c r="F57" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-mqap-lb-rule</v>
-      </c>
-      <c r="F57" s="112" t="str">
+        <v>t-dip-mqap-lb-fe</v>
+      </c>
+      <c r="G57" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H57" s="74">
+        <v>9100</v>
+      </c>
+      <c r="I57" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dip-mqap-lb-fe</v>
-      </c>
-      <c r="G57" s="112" t="s">
-        <v>57</v>
-      </c>
-      <c r="H57" s="112">
+        <v>t-dip-mqap-lb-bp</v>
+      </c>
+      <c r="K57" s="74">
         <v>9100</v>
       </c>
-      <c r="I57" s="112" t="b">
-        <v>0</v>
-      </c>
-      <c r="J57" s="112" t="str">
-        <f t="shared" si="6"/>
-        <v>t-dip-mqap-lb-bp</v>
-      </c>
-      <c r="K57" s="112">
+      <c r="L57" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dip-mqap-lb-pb9100</v>
+      </c>
+      <c r="M57" s="74">
         <v>9100</v>
       </c>
-      <c r="L57" s="112" t="str">
-        <f t="shared" si="0"/>
-        <v>t-dip-mqap-lb-pb9100</v>
-      </c>
-      <c r="M57" s="112">
-        <v>9100</v>
-      </c>
-      <c r="N57" s="112">
+      <c r="N57" s="74">
         <v>4</v>
       </c>
-      <c r="O57" s="112" t="s">
+      <c r="O57" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P57" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q57" s="112" t="b">
+      <c r="P57" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10119,11 +10091,11 @@
         <v>376</v>
       </c>
       <c r="E58" s="84" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dip-geoap-lb-rule3660</v>
+      </c>
+      <c r="F58" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-geoap-lb-rule</v>
-      </c>
-      <c r="F58" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-dip-geoap-lb-fe</v>
       </c>
       <c r="G58" s="84" t="s">
@@ -10136,14 +10108,14 @@
         <v>0</v>
       </c>
       <c r="J58" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-dip-geoap-lb-bp</v>
       </c>
       <c r="K58" s="84">
         <v>3660</v>
       </c>
       <c r="L58" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dip-geoap-lb-pb3660</v>
       </c>
       <c r="M58" s="84">
@@ -10177,11 +10149,11 @@
         <v>376</v>
       </c>
       <c r="E59" s="84" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dip-geoap-lb-rule3661</v>
+      </c>
+      <c r="F59" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-geoap-lb-rule</v>
-      </c>
-      <c r="F59" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-dip-geoap-lb-fe</v>
       </c>
       <c r="G59" s="84" t="s">
@@ -10194,14 +10166,14 @@
         <v>0</v>
       </c>
       <c r="J59" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-dip-geoap-lb-bp</v>
       </c>
       <c r="K59" s="84">
         <v>3661</v>
       </c>
       <c r="L59" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dip-geoap-lb-pb3661</v>
       </c>
       <c r="M59" s="84">
@@ -10235,11 +10207,11 @@
         <v>376</v>
       </c>
       <c r="E60" s="84" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dip-geoap-lb-rule3670</v>
+      </c>
+      <c r="F60" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-geoap-lb-rule</v>
-      </c>
-      <c r="F60" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-dip-geoap-lb-fe</v>
       </c>
       <c r="G60" s="84" t="s">
@@ -10252,14 +10224,14 @@
         <v>0</v>
       </c>
       <c r="J60" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-dip-geoap-lb-bp</v>
       </c>
       <c r="K60" s="84">
         <v>3670</v>
       </c>
       <c r="L60" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dip-geoap-lb-pb3670</v>
       </c>
       <c r="M60" s="84">
@@ -10293,11 +10265,11 @@
         <v>376</v>
       </c>
       <c r="E61" s="84" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dip-geoap-lb-rule3671</v>
+      </c>
+      <c r="F61" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-geoap-lb-rule</v>
-      </c>
-      <c r="F61" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-dip-geoap-lb-fe</v>
       </c>
       <c r="G61" s="84" t="s">
@@ -10310,14 +10282,14 @@
         <v>0</v>
       </c>
       <c r="J61" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-dip-geoap-lb-bp</v>
       </c>
       <c r="K61" s="84">
         <v>3671</v>
       </c>
       <c r="L61" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dip-geoap-lb-pb3671</v>
       </c>
       <c r="M61" s="84">
@@ -10351,11 +10323,11 @@
         <v>376</v>
       </c>
       <c r="E62" s="84" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dip-geoap-lb-rule9100</v>
+      </c>
+      <c r="F62" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-geoap-lb-rule</v>
-      </c>
-      <c r="F62" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-dip-geoap-lb-fe</v>
       </c>
       <c r="G62" s="84" t="s">
@@ -10368,14 +10340,14 @@
         <v>0</v>
       </c>
       <c r="J62" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-dip-geoap-lb-bp</v>
       </c>
       <c r="K62" s="84">
         <v>9100</v>
       </c>
       <c r="L62" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dip-geoap-lb-pb9100</v>
       </c>
       <c r="M62" s="84">
@@ -10395,51 +10367,48 @@
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A63" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B63" s="112" t="str" cm="1">
+      <c r="A63" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B63" s="74" t="str" cm="1">
         <f t="array" ref="B63">UPPER(INDEX(_xlfn.TEXTSPLIT($C63, "-"), 3))</f>
         <v>DIP</v>
       </c>
-      <c r="C63" s="112" t="s">
+      <c r="C63" s="74" t="s">
         <v>630</v>
       </c>
-      <c r="D63" s="112" t="s">
+      <c r="D63" s="74" t="s">
         <v>375</v>
       </c>
-      <c r="E63" s="112" t="str">
+      <c r="E63" s="74"/>
+      <c r="F63" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-flk-lb-rule</v>
-      </c>
-      <c r="F63" s="112" t="str">
+        <v>t-dip-flk-lb-fe</v>
+      </c>
+      <c r="G63" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H63" s="74"/>
+      <c r="I63" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J63" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dip-flk-lb-fe</v>
-      </c>
-      <c r="G63" s="112" t="s">
-        <v>57</v>
-      </c>
-      <c r="H63" s="112"/>
-      <c r="I63" s="112" t="b">
-        <v>0</v>
-      </c>
-      <c r="J63" s="112" t="str">
-        <f t="shared" si="6"/>
         <v>t-dip-flk-lb-bp</v>
       </c>
-      <c r="K63" s="112"/>
-      <c r="L63" s="112"/>
-      <c r="M63" s="112"/>
-      <c r="N63" s="112">
+      <c r="K63" s="74"/>
+      <c r="L63" s="74"/>
+      <c r="M63" s="74"/>
+      <c r="N63" s="74">
         <v>4</v>
       </c>
-      <c r="O63" s="112" t="s">
+      <c r="O63" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P63" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q63" s="112" t="b">
+      <c r="P63" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10458,11 +10427,11 @@
         <v>374</v>
       </c>
       <c r="E64" s="84" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dip-ap-lb-rule443</v>
+      </c>
+      <c r="F64" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-ap-lb-rule</v>
-      </c>
-      <c r="F64" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-fe</v>
       </c>
       <c r="G64" s="84" t="s">
@@ -10475,14 +10444,14 @@
         <v>0</v>
       </c>
       <c r="J64" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-bp</v>
       </c>
       <c r="K64" s="84">
         <v>443</v>
       </c>
       <c r="L64" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dip-ap-lb-pb443</v>
       </c>
       <c r="M64" s="84">
@@ -10516,11 +10485,11 @@
         <v>374</v>
       </c>
       <c r="E65" s="84" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dip-ap-lb-rule8100</v>
+      </c>
+      <c r="F65" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-ap-lb-rule</v>
-      </c>
-      <c r="F65" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-fe</v>
       </c>
       <c r="G65" s="84" t="s">
@@ -10533,14 +10502,14 @@
         <v>0</v>
       </c>
       <c r="J65" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-bp</v>
       </c>
       <c r="K65" s="84">
         <v>8100</v>
       </c>
       <c r="L65" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dip-ap-lb-pb8100</v>
       </c>
       <c r="M65" s="84">
@@ -10574,11 +10543,11 @@
         <v>374</v>
       </c>
       <c r="E66" s="84" t="str">
+        <f t="shared" si="0"/>
+        <v>t-dip-ap-lb-rule8200</v>
+      </c>
+      <c r="F66" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-ap-lb-rule</v>
-      </c>
-      <c r="F66" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-fe</v>
       </c>
       <c r="G66" s="84" t="s">
@@ -10591,14 +10560,14 @@
         <v>0</v>
       </c>
       <c r="J66" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-bp</v>
       </c>
       <c r="K66" s="84">
         <v>8200</v>
       </c>
       <c r="L66" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>t-dip-ap-lb-pb8200</v>
       </c>
       <c r="M66" s="84">
@@ -10632,11 +10601,11 @@
         <v>374</v>
       </c>
       <c r="E67" s="84" t="str">
+        <f t="shared" ref="E67:E88" si="6">SUBSTITUTE(D67, "hazr-", "")&amp;"-rule"&amp;M67</f>
+        <v>t-dip-ap-lb-rule8300</v>
+      </c>
+      <c r="F67" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-ap-lb-rule</v>
-      </c>
-      <c r="F67" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-fe</v>
       </c>
       <c r="G67" s="84" t="s">
@@ -10649,7 +10618,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-bp</v>
       </c>
       <c r="K67" s="84">
@@ -10690,11 +10659,11 @@
         <v>374</v>
       </c>
       <c r="E68" s="84" t="str">
+        <f t="shared" si="6"/>
+        <v>t-dip-ap-lb-rule8400</v>
+      </c>
+      <c r="F68" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-ap-lb-rule</v>
-      </c>
-      <c r="F68" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-fe</v>
       </c>
       <c r="G68" s="84" t="s">
@@ -10707,7 +10676,7 @@
         <v>0</v>
       </c>
       <c r="J68" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-bp</v>
       </c>
       <c r="K68" s="84">
@@ -10748,11 +10717,11 @@
         <v>374</v>
       </c>
       <c r="E69" s="84" t="str">
+        <f t="shared" si="6"/>
+        <v>t-dip-ap-lb-rule9100</v>
+      </c>
+      <c r="F69" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-ap-lb-rule</v>
-      </c>
-      <c r="F69" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-fe</v>
       </c>
       <c r="G69" s="84" t="s">
@@ -10765,7 +10734,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-bp</v>
       </c>
       <c r="K69" s="84">
@@ -10806,11 +10775,11 @@
         <v>374</v>
       </c>
       <c r="E70" s="84" t="str">
+        <f t="shared" si="6"/>
+        <v>t-dip-ap-lb-rule9113</v>
+      </c>
+      <c r="F70" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-ap-lb-rule</v>
-      </c>
-      <c r="F70" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-fe</v>
       </c>
       <c r="G70" s="84" t="s">
@@ -10823,7 +10792,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-bp</v>
       </c>
       <c r="K70" s="84">
@@ -10850,292 +10819,292 @@
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A71" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B71" s="112" t="str" cm="1">
+      <c r="A71" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B71" s="74" t="str" cm="1">
         <f t="array" ref="B71">UPPER(INDEX(_xlfn.TEXTSPLIT($C71, "-"), 3))</f>
         <v>DIP</v>
       </c>
-      <c r="C71" s="112" t="s">
+      <c r="C71" s="74" t="s">
         <v>630</v>
       </c>
-      <c r="D71" s="112" t="s">
+      <c r="D71" s="74" t="s">
         <v>373</v>
       </c>
-      <c r="E71" s="112" t="str">
+      <c r="E71" s="74" t="str">
+        <f t="shared" si="6"/>
+        <v>t-dip-adm-lb-rule443</v>
+      </c>
+      <c r="F71" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-adm-lb-rule</v>
-      </c>
-      <c r="F71" s="112" t="str">
+        <v>t-dip-adm-lb-fe</v>
+      </c>
+      <c r="G71" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H71" s="74">
+        <v>443</v>
+      </c>
+      <c r="I71" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dip-adm-lb-fe</v>
-      </c>
-      <c r="G71" s="112" t="s">
-        <v>57</v>
-      </c>
-      <c r="H71" s="112">
+        <v>t-dip-adm-lb-bp</v>
+      </c>
+      <c r="K71" s="74">
         <v>443</v>
       </c>
-      <c r="I71" s="112" t="b">
-        <v>0</v>
-      </c>
-      <c r="J71" s="112" t="str">
-        <f t="shared" si="6"/>
-        <v>t-dip-adm-lb-bp</v>
-      </c>
-      <c r="K71" s="112">
-        <v>443</v>
-      </c>
-      <c r="L71" s="112" t="str">
+      <c r="L71" s="74" t="str">
         <f t="shared" si="7"/>
         <v>t-dip-adm-lb-pb443</v>
       </c>
-      <c r="M71" s="112">
+      <c r="M71" s="74">
         <v>443</v>
       </c>
-      <c r="N71" s="112">
+      <c r="N71" s="74">
         <v>4</v>
       </c>
-      <c r="O71" s="112" t="s">
+      <c r="O71" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P71" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q71" s="112" t="b">
+      <c r="P71" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A72" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B72" s="112" t="str" cm="1">
+      <c r="A72" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B72" s="74" t="str" cm="1">
         <f t="array" ref="B72">UPPER(INDEX(_xlfn.TEXTSPLIT($C72, "-"), 3))</f>
         <v>DIP</v>
       </c>
-      <c r="C72" s="112" t="s">
+      <c r="C72" s="74" t="s">
         <v>630</v>
       </c>
-      <c r="D72" s="112" t="s">
+      <c r="D72" s="74" t="s">
         <v>373</v>
       </c>
-      <c r="E72" s="112" t="str">
+      <c r="E72" s="74" t="str">
+        <f t="shared" si="6"/>
+        <v>t-dip-adm-lb-rule8085</v>
+      </c>
+      <c r="F72" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-adm-lb-rule</v>
-      </c>
-      <c r="F72" s="112" t="str">
+        <v>t-dip-adm-lb-fe</v>
+      </c>
+      <c r="G72" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H72" s="74">
+        <v>8085</v>
+      </c>
+      <c r="I72" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dip-adm-lb-fe</v>
-      </c>
-      <c r="G72" s="112" t="s">
-        <v>57</v>
-      </c>
-      <c r="H72" s="112">
+        <v>t-dip-adm-lb-bp</v>
+      </c>
+      <c r="K72" s="74">
         <v>8085</v>
       </c>
-      <c r="I72" s="112" t="b">
-        <v>0</v>
-      </c>
-      <c r="J72" s="112" t="str">
-        <f t="shared" si="6"/>
-        <v>t-dip-adm-lb-bp</v>
-      </c>
-      <c r="K72" s="112">
-        <v>8085</v>
-      </c>
-      <c r="L72" s="112" t="str">
+      <c r="L72" s="74" t="str">
         <f t="shared" si="7"/>
         <v>t-dip-adm-lb-pb8085</v>
       </c>
-      <c r="M72" s="112">
+      <c r="M72" s="74">
         <v>8085</v>
       </c>
-      <c r="N72" s="112">
+      <c r="N72" s="74">
         <v>4</v>
       </c>
-      <c r="O72" s="112" t="s">
+      <c r="O72" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P72" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q72" s="112" t="b">
+      <c r="P72" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A73" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B73" s="112" t="str" cm="1">
+      <c r="A73" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B73" s="74" t="str" cm="1">
         <f t="array" ref="B73">UPPER(INDEX(_xlfn.TEXTSPLIT($C73, "-"), 3))</f>
         <v>DIP</v>
       </c>
-      <c r="C73" s="112" t="s">
+      <c r="C73" s="74" t="s">
         <v>630</v>
       </c>
-      <c r="D73" s="112" t="s">
+      <c r="D73" s="74" t="s">
         <v>373</v>
       </c>
-      <c r="E73" s="112" t="str">
+      <c r="E73" s="74" t="str">
+        <f t="shared" si="6"/>
+        <v>t-dip-adm-lb-rule8900</v>
+      </c>
+      <c r="F73" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-adm-lb-rule</v>
-      </c>
-      <c r="F73" s="112" t="str">
+        <v>t-dip-adm-lb-fe</v>
+      </c>
+      <c r="G73" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H73" s="74">
+        <v>8900</v>
+      </c>
+      <c r="I73" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dip-adm-lb-fe</v>
-      </c>
-      <c r="G73" s="112" t="s">
-        <v>57</v>
-      </c>
-      <c r="H73" s="112">
+        <v>t-dip-adm-lb-bp</v>
+      </c>
+      <c r="K73" s="74">
         <v>8900</v>
       </c>
-      <c r="I73" s="112" t="b">
-        <v>0</v>
-      </c>
-      <c r="J73" s="112" t="str">
-        <f t="shared" si="6"/>
-        <v>t-dip-adm-lb-bp</v>
-      </c>
-      <c r="K73" s="112">
-        <v>8900</v>
-      </c>
-      <c r="L73" s="112" t="str">
+      <c r="L73" s="74" t="str">
         <f t="shared" si="7"/>
         <v>t-dip-adm-lb-pb8900</v>
       </c>
-      <c r="M73" s="112">
+      <c r="M73" s="74">
         <v>8900</v>
       </c>
-      <c r="N73" s="112">
+      <c r="N73" s="74">
         <v>4</v>
       </c>
-      <c r="O73" s="112" t="s">
+      <c r="O73" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P73" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q73" s="112" t="b">
+      <c r="P73" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A74" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B74" s="112" t="str" cm="1">
+      <c r="A74" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B74" s="74" t="str" cm="1">
         <f t="array" ref="B74">UPPER(INDEX(_xlfn.TEXTSPLIT($C74, "-"), 3))</f>
         <v>DIP</v>
       </c>
-      <c r="C74" s="112" t="s">
+      <c r="C74" s="74" t="s">
         <v>630</v>
       </c>
-      <c r="D74" s="112" t="s">
+      <c r="D74" s="74" t="s">
         <v>373</v>
       </c>
-      <c r="E74" s="112" t="str">
+      <c r="E74" s="74" t="str">
+        <f t="shared" si="6"/>
+        <v>t-dip-adm-lb-rule8901</v>
+      </c>
+      <c r="F74" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-adm-lb-rule</v>
-      </c>
-      <c r="F74" s="112" t="str">
+        <v>t-dip-adm-lb-fe</v>
+      </c>
+      <c r="G74" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H74" s="74">
+        <v>8901</v>
+      </c>
+      <c r="I74" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dip-adm-lb-fe</v>
-      </c>
-      <c r="G74" s="112" t="s">
-        <v>57</v>
-      </c>
-      <c r="H74" s="112">
+        <v>t-dip-adm-lb-bp</v>
+      </c>
+      <c r="K74" s="74">
         <v>8901</v>
       </c>
-      <c r="I74" s="112" t="b">
-        <v>0</v>
-      </c>
-      <c r="J74" s="112" t="str">
-        <f t="shared" si="6"/>
-        <v>t-dip-adm-lb-bp</v>
-      </c>
-      <c r="K74" s="112">
-        <v>8901</v>
-      </c>
-      <c r="L74" s="112" t="str">
+      <c r="L74" s="74" t="str">
         <f t="shared" si="7"/>
         <v>t-dip-adm-lb-pb8901</v>
       </c>
-      <c r="M74" s="112">
+      <c r="M74" s="74">
         <v>8901</v>
       </c>
-      <c r="N74" s="112">
+      <c r="N74" s="74">
         <v>4</v>
       </c>
-      <c r="O74" s="112" t="s">
+      <c r="O74" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P74" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q74" s="112" t="b">
+      <c r="P74" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q74" s="74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A75" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B75" s="112" t="str" cm="1">
+      <c r="A75" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B75" s="74" t="str" cm="1">
         <f t="array" ref="B75">UPPER(INDEX(_xlfn.TEXTSPLIT($C75, "-"), 3))</f>
         <v>DIP</v>
       </c>
-      <c r="C75" s="112" t="s">
+      <c r="C75" s="74" t="s">
         <v>630</v>
       </c>
-      <c r="D75" s="112" t="s">
+      <c r="D75" s="74" t="s">
         <v>373</v>
       </c>
-      <c r="E75" s="112" t="str">
+      <c r="E75" s="74" t="str">
+        <f t="shared" si="6"/>
+        <v>t-dip-adm-lb-rule9100</v>
+      </c>
+      <c r="F75" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-dip-adm-lb-rule</v>
-      </c>
-      <c r="F75" s="112" t="str">
+        <v>t-dip-adm-lb-fe</v>
+      </c>
+      <c r="G75" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H75" s="74">
+        <v>9100</v>
+      </c>
+      <c r="I75" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dip-adm-lb-fe</v>
-      </c>
-      <c r="G75" s="112" t="s">
-        <v>57</v>
-      </c>
-      <c r="H75" s="112">
+        <v>t-dip-adm-lb-bp</v>
+      </c>
+      <c r="K75" s="74">
         <v>9100</v>
       </c>
-      <c r="I75" s="112" t="b">
-        <v>0</v>
-      </c>
-      <c r="J75" s="112" t="str">
-        <f t="shared" si="6"/>
-        <v>t-dip-adm-lb-bp</v>
-      </c>
-      <c r="K75" s="112">
-        <v>9100</v>
-      </c>
-      <c r="L75" s="112" t="str">
+      <c r="L75" s="74" t="str">
         <f t="shared" si="7"/>
         <v>t-dip-adm-lb-pb9100</v>
       </c>
-      <c r="M75" s="112">
+      <c r="M75" s="74">
         <v>9100</v>
       </c>
-      <c r="N75" s="112">
+      <c r="N75" s="74">
         <v>4</v>
       </c>
-      <c r="O75" s="112" t="s">
+      <c r="O75" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P75" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q75" s="112" t="b">
+      <c r="P75" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q75" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11153,12 +11122,9 @@
       <c r="D76" s="84" t="s">
         <v>383</v>
       </c>
-      <c r="E76" s="84" t="str">
+      <c r="E76" s="84"/>
+      <c r="F76" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-cs-chtweb-lb-rule</v>
-      </c>
-      <c r="F76" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-cs-chtweb-lb-fe</v>
       </c>
       <c r="G76" s="84" t="s">
@@ -11169,7 +11135,7 @@
         <v>0</v>
       </c>
       <c r="J76" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-cs-chtweb-lb-bp</v>
       </c>
       <c r="K76" s="84"/>
@@ -11189,51 +11155,48 @@
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A77" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B77" s="112" t="str" cm="1">
+      <c r="A77" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B77" s="74" t="str" cm="1">
         <f t="array" ref="B77">UPPER(INDEX(_xlfn.TEXTSPLIT($C77, "-"), 3))</f>
         <v>CS</v>
       </c>
-      <c r="C77" s="112" t="s">
+      <c r="C77" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="D77" s="112" t="s">
+      <c r="D77" s="74" t="s">
         <v>384</v>
       </c>
-      <c r="E77" s="112" t="str">
+      <c r="E77" s="74"/>
+      <c r="F77" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-cs-chtintweb-lb-rule</v>
-      </c>
-      <c r="F77" s="112" t="str">
+        <v>t-cs-chtintweb-lb-fe</v>
+      </c>
+      <c r="G77" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H77" s="74"/>
+      <c r="I77" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-cs-chtintweb-lb-fe</v>
-      </c>
-      <c r="G77" s="112" t="s">
-        <v>57</v>
-      </c>
-      <c r="H77" s="112"/>
-      <c r="I77" s="112" t="b">
-        <v>0</v>
-      </c>
-      <c r="J77" s="112" t="str">
-        <f t="shared" si="6"/>
         <v>t-cs-chtintweb-lb-bp</v>
       </c>
-      <c r="K77" s="112"/>
-      <c r="L77" s="112"/>
-      <c r="M77" s="112"/>
-      <c r="N77" s="112">
+      <c r="K77" s="74"/>
+      <c r="L77" s="74"/>
+      <c r="M77" s="74"/>
+      <c r="N77" s="74">
         <v>4</v>
       </c>
-      <c r="O77" s="112" t="s">
+      <c r="O77" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P77" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q77" s="112" t="b">
+      <c r="P77" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q77" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11251,12 +11214,9 @@
       <c r="D78" s="84" t="s">
         <v>382</v>
       </c>
-      <c r="E78" s="84" t="str">
+      <c r="E78" s="84"/>
+      <c r="F78" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-cs-chtap-lb-rule</v>
-      </c>
-      <c r="F78" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-cs-chtap-lb-fe</v>
       </c>
       <c r="G78" s="84" t="s">
@@ -11267,7 +11227,7 @@
         <v>0</v>
       </c>
       <c r="J78" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-cs-chtap-lb-bp</v>
       </c>
       <c r="K78" s="84"/>
@@ -11287,118 +11247,118 @@
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A79" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B79" s="112" t="str" cm="1">
+      <c r="A79" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B79" s="74" t="str" cm="1">
         <f t="array" ref="B79">UPPER(INDEX(_xlfn.TEXTSPLIT($C79, "-"), 3))</f>
         <v>COM</v>
       </c>
-      <c r="C79" s="112" t="s">
+      <c r="C79" s="74" t="s">
         <v>394</v>
       </c>
-      <c r="D79" s="112" t="s">
+      <c r="D79" s="74" t="s">
         <v>381</v>
       </c>
-      <c r="E79" s="112" t="str">
+      <c r="E79" s="74" t="str">
+        <f t="shared" si="6"/>
+        <v>t-com-proxy-lb-rule443</v>
+      </c>
+      <c r="F79" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-com-proxy-lb-rule</v>
-      </c>
-      <c r="F79" s="112" t="str">
+        <v>t-com-proxy-lb-fe</v>
+      </c>
+      <c r="G79" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H79" s="74">
+        <v>443</v>
+      </c>
+      <c r="I79" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-com-proxy-lb-fe</v>
-      </c>
-      <c r="G79" s="112" t="s">
-        <v>57</v>
-      </c>
-      <c r="H79" s="112">
+        <v>t-com-proxy-lb-bp</v>
+      </c>
+      <c r="K79" s="74">
         <v>443</v>
       </c>
-      <c r="I79" s="112" t="b">
-        <v>0</v>
-      </c>
-      <c r="J79" s="112" t="str">
-        <f t="shared" si="6"/>
-        <v>t-com-proxy-lb-bp</v>
-      </c>
-      <c r="K79" s="112">
-        <v>443</v>
-      </c>
-      <c r="L79" s="112" t="str">
+      <c r="L79" s="74" t="str">
         <f t="shared" si="7"/>
         <v>t-com-proxy-lb-pb443</v>
       </c>
-      <c r="M79" s="112">
+      <c r="M79" s="74">
         <v>443</v>
       </c>
-      <c r="N79" s="112">
+      <c r="N79" s="74">
         <v>4</v>
       </c>
-      <c r="O79" s="112" t="s">
+      <c r="O79" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P79" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q79" s="112" t="b">
+      <c r="P79" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q79" s="74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A80" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B80" s="112" t="str" cm="1">
+      <c r="A80" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B80" s="74" t="str" cm="1">
         <f t="array" ref="B80">UPPER(INDEX(_xlfn.TEXTSPLIT($C80, "-"), 3))</f>
         <v>COM</v>
       </c>
-      <c r="C80" s="112" t="s">
+      <c r="C80" s="74" t="s">
         <v>204</v>
       </c>
-      <c r="D80" s="112" t="s">
+      <c r="D80" s="74" t="s">
         <v>381</v>
       </c>
-      <c r="E80" s="112" t="str">
+      <c r="E80" s="74" t="str">
+        <f t="shared" si="6"/>
+        <v>t-com-proxy-lb-rule8080</v>
+      </c>
+      <c r="F80" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-com-proxy-lb-rule</v>
-      </c>
-      <c r="F80" s="112" t="str">
+        <v>t-com-proxy-lb-fe</v>
+      </c>
+      <c r="G80" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H80" s="74">
+        <v>8080</v>
+      </c>
+      <c r="I80" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-com-proxy-lb-fe</v>
-      </c>
-      <c r="G80" s="112" t="s">
-        <v>57</v>
-      </c>
-      <c r="H80" s="112">
+        <v>t-com-proxy-lb-bp</v>
+      </c>
+      <c r="K80" s="74">
         <v>8080</v>
       </c>
-      <c r="I80" s="112" t="b">
-        <v>0</v>
-      </c>
-      <c r="J80" s="112" t="str">
-        <f t="shared" si="6"/>
-        <v>t-com-proxy-lb-bp</v>
-      </c>
-      <c r="K80" s="112">
-        <v>8080</v>
-      </c>
-      <c r="L80" s="112" t="str">
+      <c r="L80" s="74" t="str">
         <f t="shared" si="7"/>
         <v>t-com-proxy-lb-pb8080</v>
       </c>
-      <c r="M80" s="112">
+      <c r="M80" s="74">
         <v>8080</v>
       </c>
-      <c r="N80" s="112">
+      <c r="N80" s="74">
         <v>4</v>
       </c>
-      <c r="O80" s="112" t="s">
+      <c r="O80" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P80" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q80" s="112" t="b">
+      <c r="P80" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q80" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11417,11 +11377,11 @@
         <v>380</v>
       </c>
       <c r="E81" s="84" t="str">
+        <f t="shared" si="6"/>
+        <v>t-com-auth-lb-rule8088</v>
+      </c>
+      <c r="F81" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-com-auth-lb-rule</v>
-      </c>
-      <c r="F81" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-com-auth-lb-fe</v>
       </c>
       <c r="G81" s="84" t="s">
@@ -11434,7 +11394,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-com-auth-lb-bp</v>
       </c>
       <c r="K81" s="84">
@@ -11475,11 +11435,11 @@
         <v>380</v>
       </c>
       <c r="E82" s="84" t="str">
+        <f t="shared" si="6"/>
+        <v>t-com-auth-lb-rule9003</v>
+      </c>
+      <c r="F82" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-com-auth-lb-rule</v>
-      </c>
-      <c r="F82" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-com-auth-lb-fe</v>
       </c>
       <c r="G82" s="84" t="s">
@@ -11492,7 +11452,7 @@
         <v>0</v>
       </c>
       <c r="J82" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-com-auth-lb-bp</v>
       </c>
       <c r="K82" s="84">
@@ -11533,11 +11493,11 @@
         <v>380</v>
       </c>
       <c r="E83" s="84" t="str">
+        <f t="shared" si="6"/>
+        <v>t-com-auth-lb-rule9005</v>
+      </c>
+      <c r="F83" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-com-auth-lb-rule</v>
-      </c>
-      <c r="F83" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-com-auth-lb-fe</v>
       </c>
       <c r="G83" s="84" t="s">
@@ -11550,7 +11510,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-com-auth-lb-bp</v>
       </c>
       <c r="K83" s="84">
@@ -11577,60 +11537,60 @@
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A84" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B84" s="112" t="str" cm="1">
+      <c r="A84" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B84" s="74" t="str" cm="1">
         <f t="array" ref="B84">UPPER(INDEX(_xlfn.TEXTSPLIT($C84, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="C84" s="112" t="s">
+      <c r="C84" s="74" t="s">
         <v>392</v>
       </c>
-      <c r="D84" s="112" t="s">
+      <c r="D84" s="74" t="s">
         <v>372</v>
       </c>
-      <c r="E84" s="112" t="str">
+      <c r="E84" s="74" t="str">
+        <f t="shared" si="6"/>
+        <v>t-bdp-slap-lb-rule443</v>
+      </c>
+      <c r="F84" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-bdp-slap-lb-rule</v>
-      </c>
-      <c r="F84" s="112" t="str">
+        <v>t-bdp-slap-lb-fe</v>
+      </c>
+      <c r="G84" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H84" s="74">
+        <v>443</v>
+      </c>
+      <c r="I84" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-bdp-slap-lb-fe</v>
-      </c>
-      <c r="G84" s="112" t="s">
-        <v>57</v>
-      </c>
-      <c r="H84" s="112">
+        <v>t-bdp-slap-lb-bp</v>
+      </c>
+      <c r="K84" s="74">
         <v>443</v>
       </c>
-      <c r="I84" s="112" t="b">
-        <v>0</v>
-      </c>
-      <c r="J84" s="112" t="str">
-        <f t="shared" si="6"/>
-        <v>t-bdp-slap-lb-bp</v>
-      </c>
-      <c r="K84" s="112">
-        <v>443</v>
-      </c>
-      <c r="L84" s="112" t="str">
+      <c r="L84" s="74" t="str">
         <f t="shared" si="7"/>
         <v>t-bdp-slap-lb-pb443</v>
       </c>
-      <c r="M84" s="112">
+      <c r="M84" s="74">
         <v>443</v>
       </c>
-      <c r="N84" s="112">
+      <c r="N84" s="74">
         <v>4</v>
       </c>
-      <c r="O84" s="112" t="s">
+      <c r="O84" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P84" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q84" s="112" t="b">
+      <c r="P84" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q84" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11649,11 +11609,11 @@
         <v>371</v>
       </c>
       <c r="E85" s="84" t="str">
+        <f t="shared" si="6"/>
+        <v>t-bdp-cxmadm-lb-rule443</v>
+      </c>
+      <c r="F85" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-bdp-cxmadm-lb-rule</v>
-      </c>
-      <c r="F85" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-bdp-cxmadm-lb-fe</v>
       </c>
       <c r="G85" s="84" t="s">
@@ -11666,7 +11626,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-bdp-cxmadm-lb-bp</v>
       </c>
       <c r="K85" s="84">
@@ -11693,60 +11653,60 @@
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A86" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B86" s="112" t="str" cm="1">
+      <c r="A86" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B86" s="74" t="str" cm="1">
         <f t="array" ref="B86">UPPER(INDEX(_xlfn.TEXTSPLIT($C86, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="C86" s="112" t="s">
+      <c r="C86" s="74" t="s">
         <v>207</v>
       </c>
-      <c r="D86" s="112" t="s">
+      <c r="D86" s="74" t="s">
         <v>388</v>
       </c>
-      <c r="E86" s="112" t="str">
+      <c r="E86" s="74" t="str">
+        <f t="shared" si="6"/>
+        <v>t-bdp-crkweb-lb-rule443</v>
+      </c>
+      <c r="F86" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-bdp-crkweb-lb-rule</v>
-      </c>
-      <c r="F86" s="112" t="str">
+        <v>t-bdp-crkweb-lb-fe</v>
+      </c>
+      <c r="G86" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H86" s="74">
+        <v>443</v>
+      </c>
+      <c r="I86" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J86" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-bdp-crkweb-lb-fe</v>
-      </c>
-      <c r="G86" s="112" t="s">
-        <v>57</v>
-      </c>
-      <c r="H86" s="112">
+        <v>t-bdp-crkweb-lb-bp</v>
+      </c>
+      <c r="K86" s="74">
         <v>443</v>
       </c>
-      <c r="I86" s="112" t="b">
-        <v>0</v>
-      </c>
-      <c r="J86" s="112" t="str">
-        <f t="shared" si="6"/>
-        <v>t-bdp-crkweb-lb-bp</v>
-      </c>
-      <c r="K86" s="112">
-        <v>443</v>
-      </c>
-      <c r="L86" s="112" t="str">
+      <c r="L86" s="74" t="str">
         <f t="shared" si="7"/>
         <v>t-bdp-crkweb-lb-pb443</v>
       </c>
-      <c r="M86" s="112">
+      <c r="M86" s="74">
         <v>443</v>
       </c>
-      <c r="N86" s="112">
+      <c r="N86" s="74">
         <v>4</v>
       </c>
-      <c r="O86" s="112" t="s">
+      <c r="O86" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P86" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q86" s="112" t="b">
+      <c r="P86" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q86" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11765,11 +11725,11 @@
         <v>390</v>
       </c>
       <c r="E87" s="84" t="str">
+        <f t="shared" si="6"/>
+        <v>t-bdp-crkml-lb-rule8082</v>
+      </c>
+      <c r="F87" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-bdp-crkml-lb-rule</v>
-      </c>
-      <c r="F87" s="84" t="str">
-        <f t="shared" si="5"/>
         <v>t-bdp-crkml-lb-fe</v>
       </c>
       <c r="G87" s="84" t="s">
@@ -11782,7 +11742,7 @@
         <v>0</v>
       </c>
       <c r="J87" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>t-bdp-crkml-lb-bp</v>
       </c>
       <c r="K87" s="84">
@@ -11809,60 +11769,60 @@
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A88" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B88" s="112" t="str" cm="1">
+      <c r="A88" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B88" s="74" t="str" cm="1">
         <f t="array" ref="B88">UPPER(INDEX(_xlfn.TEXTSPLIT($C88, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="C88" s="112" t="s">
+      <c r="C88" s="74" t="s">
         <v>207</v>
       </c>
-      <c r="D88" s="112" t="s">
+      <c r="D88" s="74" t="s">
         <v>389</v>
       </c>
-      <c r="E88" s="112" t="str">
+      <c r="E88" s="74" t="str">
+        <f t="shared" si="6"/>
+        <v>t-bdp-crkap-lb-rule8085</v>
+      </c>
+      <c r="F88" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-bdp-crkap-lb-rule</v>
-      </c>
-      <c r="F88" s="112" t="str">
+        <v>t-bdp-crkap-lb-fe</v>
+      </c>
+      <c r="G88" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H88" s="74">
+        <v>8085</v>
+      </c>
+      <c r="I88" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J88" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-bdp-crkap-lb-fe</v>
-      </c>
-      <c r="G88" s="112" t="s">
-        <v>57</v>
-      </c>
-      <c r="H88" s="112">
+        <v>t-bdp-crkap-lb-bp</v>
+      </c>
+      <c r="K88" s="74">
         <v>8085</v>
       </c>
-      <c r="I88" s="112" t="b">
-        <v>0</v>
-      </c>
-      <c r="J88" s="112" t="str">
-        <f t="shared" si="6"/>
-        <v>t-bdp-crkap-lb-bp</v>
-      </c>
-      <c r="K88" s="112">
-        <v>8085</v>
-      </c>
-      <c r="L88" s="112" t="str">
+      <c r="L88" s="74" t="str">
         <f t="shared" si="7"/>
         <v>t-bdp-crkap-lb-pb8085</v>
       </c>
-      <c r="M88" s="112">
+      <c r="M88" s="74">
         <v>8085</v>
       </c>
-      <c r="N88" s="112">
+      <c r="N88" s="74">
         <v>4</v>
       </c>
-      <c r="O88" s="112" t="s">
+      <c r="O88" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P88" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q88" s="112" t="b">
+      <c r="P88" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q88" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26198,7 +26158,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -31336,66 +31296,66 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B2" s="112" t="str" cm="1">
+      <c r="A2" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" s="74" t="str" cm="1">
         <f t="array" ref="B2">UPPER(INDEX(_xlfn.TEXTSPLIT($C2, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="C2" s="112" t="s">
+      <c r="C2" s="74" t="s">
         <v>391</v>
       </c>
-      <c r="D2" s="112" t="s">
+      <c r="D2" s="74" t="s">
         <v>363</v>
       </c>
-      <c r="E2" s="113" t="str">
-        <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-pb"&amp;G2</f>
+      <c r="E2" s="88" t="str">
+        <f t="shared" ref="E2:E33" si="0">SUBSTITUTE(D2, "hazr-", "")&amp;"-pb"&amp;G2</f>
         <v>t-dtg-web-lb-pb8080</v>
       </c>
-      <c r="F2" s="112" t="s">
+      <c r="F2" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="112">
+      <c r="G2" s="74">
         <v>8080</v>
       </c>
-      <c r="H2" s="112"/>
-      <c r="I2" s="112">
+      <c r="H2" s="74"/>
+      <c r="I2" s="74">
         <v>5</v>
       </c>
-      <c r="J2" s="112">
+      <c r="J2" s="74">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B3" s="112" t="str" cm="1">
+      <c r="A3" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" s="74" t="str" cm="1">
         <f t="array" ref="B3">UPPER(INDEX(_xlfn.TEXTSPLIT($C3, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="C3" s="112" t="s">
+      <c r="C3" s="74" t="s">
         <v>391</v>
       </c>
-      <c r="D3" s="112" t="s">
+      <c r="D3" s="74" t="s">
         <v>363</v>
       </c>
-      <c r="E3" s="113" t="str">
-        <f>SUBSTITUTE(D3, "hazr-", "")&amp;"-pb"&amp;G3</f>
+      <c r="E3" s="88" t="str">
+        <f t="shared" si="0"/>
         <v>t-dtg-web-lb-pb8081</v>
       </c>
-      <c r="F3" s="112" t="s">
+      <c r="F3" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="112">
+      <c r="G3" s="74">
         <v>8081</v>
       </c>
-      <c r="H3" s="112"/>
-      <c r="I3" s="112">
+      <c r="H3" s="74"/>
+      <c r="I3" s="74">
         <v>5</v>
       </c>
-      <c r="J3" s="112">
+      <c r="J3" s="74">
         <v>2</v>
       </c>
     </row>
@@ -31414,7 +31374,7 @@
         <v>360</v>
       </c>
       <c r="E4" s="85" t="str">
-        <f>SUBSTITUTE(D4, "hazr-", "")&amp;"-pb"&amp;G4</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-mq-lb-pb1883</v>
       </c>
       <c r="F4" s="84" t="s">
@@ -31446,7 +31406,7 @@
         <v>360</v>
       </c>
       <c r="E5" s="85" t="str">
-        <f>SUBSTITUTE(D5, "hazr-", "")&amp;"-pb"&amp;G5</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-mq-lb-pb1884</v>
       </c>
       <c r="F5" s="84" t="s">
@@ -31478,7 +31438,7 @@
         <v>356</v>
       </c>
       <c r="E6" s="86" t="str">
-        <f>SUBSTITUTE(D6, "hazr-", "")&amp;"-pb"&amp;G6</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-ingap-lb-pb8081</v>
       </c>
       <c r="F6" s="86" t="s">
@@ -31510,7 +31470,7 @@
         <v>359</v>
       </c>
       <c r="E7" s="84" t="str">
-        <f>SUBSTITUTE(D7, "hazr-", "")&amp;"-pb"&amp;G7</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-geoap-lb-pb8089</v>
       </c>
       <c r="F7" s="84" t="s">
@@ -31542,7 +31502,7 @@
         <v>359</v>
       </c>
       <c r="E8" s="84" t="str">
-        <f>SUBSTITUTE(D8, "hazr-", "")&amp;"-pb"&amp;G8</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-geoap-lb-pb9089</v>
       </c>
       <c r="F8" s="84" t="s">
@@ -31560,66 +31520,66 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B9" s="112" t="str" cm="1">
+      <c r="A9" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="74" t="str" cm="1">
         <f t="array" ref="B9">UPPER(INDEX(_xlfn.TEXTSPLIT($C9, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="74" t="s">
         <v>391</v>
       </c>
-      <c r="D9" s="112" t="s">
+      <c r="D9" s="74" t="s">
         <v>358</v>
       </c>
-      <c r="E9" s="113" t="str">
-        <f>SUBSTITUTE(D9, "hazr-", "")&amp;"-pb"&amp;G9</f>
+      <c r="E9" s="88" t="str">
+        <f t="shared" si="0"/>
         <v>t-dtg-extgeoap-lb-pb3660</v>
       </c>
-      <c r="F9" s="112" t="s">
+      <c r="F9" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="112">
+      <c r="G9" s="74">
         <v>3660</v>
       </c>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112">
+      <c r="H9" s="74"/>
+      <c r="I9" s="74">
         <v>5</v>
       </c>
-      <c r="J9" s="112">
+      <c r="J9" s="74">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="112" t="str" cm="1">
+      <c r="A10" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="74" t="str" cm="1">
         <f t="array" ref="B10">UPPER(INDEX(_xlfn.TEXTSPLIT($C10, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="C10" s="112" t="s">
+      <c r="C10" s="74" t="s">
         <v>391</v>
       </c>
-      <c r="D10" s="112" t="s">
+      <c r="D10" s="74" t="s">
         <v>358</v>
       </c>
-      <c r="E10" s="113" t="str">
-        <f>SUBSTITUTE(D10, "hazr-", "")&amp;"-pb"&amp;G10</f>
+      <c r="E10" s="88" t="str">
+        <f t="shared" si="0"/>
         <v>t-dtg-extgeoap-lb-pb3661</v>
       </c>
-      <c r="F10" s="112" t="s">
+      <c r="F10" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="112">
+      <c r="G10" s="74">
         <v>3661</v>
       </c>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112">
+      <c r="H10" s="74"/>
+      <c r="I10" s="74">
         <v>5</v>
       </c>
-      <c r="J10" s="112">
+      <c r="J10" s="74">
         <v>2</v>
       </c>
     </row>
@@ -31638,7 +31598,7 @@
         <v>369</v>
       </c>
       <c r="E11" s="85" t="str">
-        <f>SUBSTITUTE(D11, "hazr-", "")&amp;"-pb"&amp;G11</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-dprweb-lb-pb443</v>
       </c>
       <c r="F11" s="84" t="s">
@@ -31670,7 +31630,7 @@
         <v>370</v>
       </c>
       <c r="E12" s="86" t="str">
-        <f>SUBSTITUTE(D12, "hazr-", "")&amp;"-pb"&amp;G12</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-dprap-lb-pb8082</v>
       </c>
       <c r="F12" s="86" t="s">
@@ -31702,7 +31662,7 @@
         <v>368</v>
       </c>
       <c r="E13" s="85" t="str">
-        <f>SUBSTITUTE(D13, "hazr-", "")&amp;"-pb"&amp;G13</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-diosweb-lb-pb443</v>
       </c>
       <c r="F13" s="84" t="s">
@@ -31734,7 +31694,7 @@
         <v>367</v>
       </c>
       <c r="E14" s="86" t="str">
-        <f>SUBSTITUTE(D14, "hazr-", "")&amp;"-pb"&amp;G14</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-diosap-lb-pb8080</v>
       </c>
       <c r="F14" s="86" t="s">
@@ -31768,7 +31728,7 @@
         <v>366</v>
       </c>
       <c r="E15" s="85" t="str">
-        <f>SUBSTITUTE(D15, "hazr-", "")&amp;"-pb"&amp;G15</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-cdsvadm-lb-pb9100</v>
       </c>
       <c r="F15" s="84" t="s">
@@ -31800,7 +31760,7 @@
         <v>366</v>
       </c>
       <c r="E16" s="85" t="str">
-        <f>SUBSTITUTE(D16, "hazr-", "")&amp;"-pb"&amp;G16</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-cdsvadm-lb-pb9300</v>
       </c>
       <c r="F16" s="84" t="s">
@@ -31832,7 +31792,7 @@
         <v>366</v>
       </c>
       <c r="E17" s="85" t="str">
-        <f>SUBSTITUTE(D17, "hazr-", "")&amp;"-pb"&amp;G17</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-cdsvadm-lb-pb9105</v>
       </c>
       <c r="F17" s="84" t="s">
@@ -31864,7 +31824,7 @@
         <v>366</v>
       </c>
       <c r="E18" s="85" t="str">
-        <f>SUBSTITUTE(D18, "hazr-", "")&amp;"-pb"&amp;G18</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-cdsvadm-lb-pb9003</v>
       </c>
       <c r="F18" s="84" t="s">
@@ -31896,7 +31856,7 @@
         <v>366</v>
       </c>
       <c r="E19" s="85" t="str">
-        <f>SUBSTITUTE(D19, "hazr-", "")&amp;"-pb"&amp;G19</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-cdsvadm-lb-pb8088</v>
       </c>
       <c r="F19" s="84" t="s">
@@ -31928,7 +31888,7 @@
         <v>365</v>
       </c>
       <c r="E20" s="86" t="str">
-        <f>SUBSTITUTE(D20, "hazr-", "")&amp;"-pb"&amp;G20</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-cdstap-lb-pb</v>
       </c>
       <c r="F20" s="86"/>
@@ -31956,7 +31916,7 @@
         <v>364</v>
       </c>
       <c r="E21" s="85" t="str">
-        <f>SUBSTITUTE(D21, "hazr-", "")&amp;"-pb"&amp;G21</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-cdmlap-lb-pb9305</v>
       </c>
       <c r="F21" s="84" t="s">
@@ -31988,7 +31948,7 @@
         <v>364</v>
       </c>
       <c r="E22" s="85" t="str">
-        <f>SUBSTITUTE(D22, "hazr-", "")&amp;"-pb"&amp;G22</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-cdmlap-lb-pb9306</v>
       </c>
       <c r="F22" s="84" t="s">
@@ -32020,7 +31980,7 @@
         <v>357</v>
       </c>
       <c r="E23" s="84" t="str">
-        <f>SUBSTITUTE(D23, "hazr-", "")&amp;"-pb"&amp;G23</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-ap-lb-pb8080</v>
       </c>
       <c r="F23" s="84" t="s">
@@ -32052,7 +32012,7 @@
         <v>357</v>
       </c>
       <c r="E24" s="84" t="str">
-        <f>SUBSTITUTE(D24, "hazr-", "")&amp;"-pb"&amp;G24</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-ap-lb-pb9087</v>
       </c>
       <c r="F24" s="84" t="s">
@@ -32070,34 +32030,34 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B25" s="112" t="str" cm="1">
+      <c r="A25" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B25" s="74" t="str" cm="1">
         <f t="array" ref="B25">UPPER(INDEX(_xlfn.TEXTSPLIT($C25, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="C25" s="112" t="s">
+      <c r="C25" s="74" t="s">
         <v>391</v>
       </c>
-      <c r="D25" s="112" t="s">
+      <c r="D25" s="74" t="s">
         <v>361</v>
       </c>
-      <c r="E25" s="113" t="str">
-        <f>SUBSTITUTE(D25, "hazr-", "")&amp;"-pb"&amp;G25</f>
+      <c r="E25" s="88" t="str">
+        <f t="shared" si="0"/>
         <v>t-dtg-admweb-lb-pb8088</v>
       </c>
-      <c r="F25" s="112" t="s">
+      <c r="F25" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="G25" s="112">
+      <c r="G25" s="74">
         <v>8088</v>
       </c>
-      <c r="H25" s="112"/>
-      <c r="I25" s="112">
+      <c r="H25" s="74"/>
+      <c r="I25" s="74">
         <v>5</v>
       </c>
-      <c r="J25" s="112">
+      <c r="J25" s="74">
         <v>2</v>
       </c>
     </row>
@@ -32116,7 +32076,7 @@
         <v>362</v>
       </c>
       <c r="E26" s="84" t="str">
-        <f>SUBSTITUTE(D26, "hazr-", "")&amp;"-pb"&amp;G26</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-admap-lb-pb8085</v>
       </c>
       <c r="F26" s="84" t="s">
@@ -32148,7 +32108,7 @@
         <v>362</v>
       </c>
       <c r="E27" s="84" t="str">
-        <f>SUBSTITUTE(D27, "hazr-", "")&amp;"-pb"&amp;G27</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-admap-lb-pb8087</v>
       </c>
       <c r="F27" s="84" t="s">
@@ -32180,7 +32140,7 @@
         <v>385</v>
       </c>
       <c r="E28" s="85" t="str">
-        <f>SUBSTITUTE(D28, "hazr-", "")&amp;"-pb"&amp;G28</f>
+        <f t="shared" si="0"/>
         <v>t-doip-web-lb-pb</v>
       </c>
       <c r="F28" s="84"/>
@@ -32208,7 +32168,7 @@
         <v>386</v>
       </c>
       <c r="E29" s="86" t="str">
-        <f>SUBSTITUTE(D29, "hazr-", "")&amp;"-pb"&amp;G29</f>
+        <f t="shared" si="0"/>
         <v>t-doip-ap-lb-pb</v>
       </c>
       <c r="F29" s="86"/>
@@ -32236,7 +32196,7 @@
         <v>387</v>
       </c>
       <c r="E30" s="85" t="str">
-        <f>SUBSTITUTE(D30, "hazr-", "")&amp;"-pb"&amp;G30</f>
+        <f t="shared" si="0"/>
         <v>t-doip-adm-lb-pb</v>
       </c>
       <c r="F30" s="84"/>
@@ -32264,7 +32224,7 @@
         <v>292</v>
       </c>
       <c r="E31" s="85" t="str">
-        <f>SUBSTITUTE(D31, "hazr-", "")&amp;"-pb"&amp;G31</f>
+        <f t="shared" si="0"/>
         <v>t-dis-web-lb-pb80</v>
       </c>
       <c r="F31" s="84" t="s">
@@ -32296,7 +32256,7 @@
         <v>292</v>
       </c>
       <c r="E32" s="85" t="str">
-        <f>SUBSTITUTE(D32, "hazr-", "")&amp;"-pb"&amp;G32</f>
+        <f t="shared" si="0"/>
         <v>t-dis-web-lb-pb443</v>
       </c>
       <c r="F32" s="84" t="s">
@@ -32314,34 +32274,34 @@
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B33" s="112" t="str" cm="1">
+      <c r="A33" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B33" s="74" t="str" cm="1">
         <f t="array" ref="B33">UPPER(INDEX(_xlfn.TEXTSPLIT($C33, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="C33" s="112" t="s">
+      <c r="C33" s="74" t="s">
         <v>289</v>
       </c>
-      <c r="D33" s="112" t="s">
+      <c r="D33" s="74" t="s">
         <v>350</v>
       </c>
-      <c r="E33" s="113" t="str">
-        <f>SUBSTITUTE(D33, "hazr-", "")&amp;"-pb"&amp;G33</f>
+      <c r="E33" s="88" t="str">
+        <f t="shared" si="0"/>
         <v>t-dis-walkweb-lb-pb443</v>
       </c>
-      <c r="F33" s="112" t="s">
+      <c r="F33" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="G33" s="112">
+      <c r="G33" s="74">
         <v>443</v>
       </c>
-      <c r="H33" s="112"/>
-      <c r="I33" s="112">
+      <c r="H33" s="74"/>
+      <c r="I33" s="74">
         <v>5</v>
       </c>
-      <c r="J33" s="112">
+      <c r="J33" s="74">
         <v>2</v>
       </c>
     </row>
@@ -32360,7 +32320,7 @@
         <v>348</v>
       </c>
       <c r="E34" s="86" t="str">
-        <f>SUBSTITUTE(D34, "hazr-", "")&amp;"-pb"&amp;G34</f>
+        <f t="shared" ref="E34:E65" si="1">SUBSTITUTE(D34, "hazr-", "")&amp;"-pb"&amp;G34</f>
         <v>t-dis-walkap-lb-pb8080</v>
       </c>
       <c r="F34" s="86" t="s">
@@ -32394,7 +32354,7 @@
         <v>351</v>
       </c>
       <c r="E35" s="86" t="str">
-        <f>SUBSTITUTE(D35, "hazr-", "")&amp;"-pb"&amp;G35</f>
+        <f t="shared" si="1"/>
         <v>t-dis-drvmsgap-lb-pb8080</v>
       </c>
       <c r="F35" s="86" t="s">
@@ -32428,7 +32388,7 @@
         <v>349</v>
       </c>
       <c r="E36" s="85" t="str">
-        <f>SUBSTITUTE(D36, "hazr-", "")&amp;"-pb"&amp;G36</f>
+        <f t="shared" si="1"/>
         <v>t-dis-drvcltap-lb-pb8081</v>
       </c>
       <c r="F36" s="84" t="s">
@@ -32448,66 +32408,66 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B37" s="112" t="str" cm="1">
+      <c r="A37" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B37" s="74" t="str" cm="1">
         <f t="array" ref="B37">UPPER(INDEX(_xlfn.TEXTSPLIT($C37, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="C37" s="112" t="s">
+      <c r="C37" s="74" t="s">
         <v>289</v>
       </c>
-      <c r="D37" s="112" t="s">
+      <c r="D37" s="74" t="s">
         <v>354</v>
       </c>
-      <c r="E37" s="113" t="str">
-        <f>SUBSTITUTE(D37, "hazr-", "")&amp;"-pb"&amp;G37</f>
+      <c r="E37" s="88" t="str">
+        <f t="shared" si="1"/>
         <v>t-dis-cmsweb-lb-pb80</v>
       </c>
-      <c r="F37" s="112" t="s">
+      <c r="F37" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="G37" s="112">
+      <c r="G37" s="74">
         <v>80</v>
       </c>
-      <c r="H37" s="112"/>
-      <c r="I37" s="112">
+      <c r="H37" s="74"/>
+      <c r="I37" s="74">
         <v>5</v>
       </c>
-      <c r="J37" s="112">
+      <c r="J37" s="74">
         <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B38" s="112" t="str" cm="1">
+      <c r="A38" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B38" s="74" t="str" cm="1">
         <f t="array" ref="B38">UPPER(INDEX(_xlfn.TEXTSPLIT($C38, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="C38" s="112" t="s">
+      <c r="C38" s="74" t="s">
         <v>289</v>
       </c>
-      <c r="D38" s="112" t="s">
+      <c r="D38" s="74" t="s">
         <v>354</v>
       </c>
-      <c r="E38" s="113" t="str">
-        <f>SUBSTITUTE(D38, "hazr-", "")&amp;"-pb"&amp;G38</f>
+      <c r="E38" s="88" t="str">
+        <f t="shared" si="1"/>
         <v>t-dis-cmsweb-lb-pb443</v>
       </c>
-      <c r="F38" s="112" t="s">
+      <c r="F38" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="G38" s="112">
+      <c r="G38" s="74">
         <v>443</v>
       </c>
-      <c r="H38" s="112"/>
-      <c r="I38" s="112">
+      <c r="H38" s="74"/>
+      <c r="I38" s="74">
         <v>5</v>
       </c>
-      <c r="J38" s="112">
+      <c r="J38" s="74">
         <v>2</v>
       </c>
     </row>
@@ -32526,7 +32486,7 @@
         <v>353</v>
       </c>
       <c r="E39" s="85" t="str">
-        <f>SUBSTITUTE(D39, "hazr-", "")&amp;"-pb"&amp;G39</f>
+        <f t="shared" si="1"/>
         <v>t-dis-cmsap-lb-pb4001</v>
       </c>
       <c r="F39" s="84" t="s">
@@ -32544,68 +32504,68 @@
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B40" s="112" t="str" cm="1">
+      <c r="A40" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B40" s="74" t="str" cm="1">
         <f t="array" ref="B40">UPPER(INDEX(_xlfn.TEXTSPLIT($C40, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="C40" s="112" t="s">
+      <c r="C40" s="74" t="s">
         <v>289</v>
       </c>
-      <c r="D40" s="112" t="s">
+      <c r="D40" s="74" t="s">
         <v>352</v>
       </c>
-      <c r="E40" s="113" t="str">
-        <f>SUBSTITUTE(D40, "hazr-", "")&amp;"-pb"&amp;G40</f>
+      <c r="E40" s="88" t="str">
+        <f t="shared" si="1"/>
         <v>t-dis-cmsadm-lb-pb443</v>
       </c>
-      <c r="F40" s="112" t="s">
+      <c r="F40" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="G40" s="112">
+      <c r="G40" s="74">
         <v>443</v>
       </c>
-      <c r="H40" s="112"/>
-      <c r="I40" s="112">
+      <c r="H40" s="74"/>
+      <c r="I40" s="74">
         <v>5</v>
       </c>
-      <c r="J40" s="112">
+      <c r="J40" s="74">
         <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B41" s="112" t="str" cm="1">
+      <c r="A41" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B41" s="74" t="str" cm="1">
         <f t="array" ref="B41">UPPER(INDEX(_xlfn.TEXTSPLIT($C41, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="C41" s="112" t="s">
+      <c r="C41" s="74" t="s">
         <v>289</v>
       </c>
-      <c r="D41" s="112" t="s">
+      <c r="D41" s="74" t="s">
         <v>355</v>
       </c>
-      <c r="E41" s="113" t="str">
-        <f>SUBSTITUTE(D41, "hazr-", "")&amp;"-pb"&amp;G41</f>
+      <c r="E41" s="88" t="str">
+        <f t="shared" si="1"/>
         <v>t-dis-cmbsap-lb-pb8080</v>
       </c>
-      <c r="F41" s="112" t="s">
+      <c r="F41" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="G41" s="112">
+      <c r="G41" s="74">
         <v>8080</v>
       </c>
-      <c r="H41" s="112" t="s">
+      <c r="H41" s="74" t="s">
         <v>628</v>
       </c>
-      <c r="I41" s="112">
+      <c r="I41" s="74">
         <v>5</v>
       </c>
-      <c r="J41" s="112">
+      <c r="J41" s="74">
         <v>2</v>
       </c>
     </row>
@@ -32624,7 +32584,7 @@
         <v>345</v>
       </c>
       <c r="E42" s="85" t="str">
-        <f>SUBSTITUTE(D42, "hazr-", "")&amp;"-pb"&amp;G42</f>
+        <f t="shared" si="1"/>
         <v>t-dis-bbiweb-lb-pb443</v>
       </c>
       <c r="F42" s="84" t="s">
@@ -32656,7 +32616,7 @@
         <v>347</v>
       </c>
       <c r="E43" s="85" t="str">
-        <f>SUBSTITUTE(D43, "hazr-", "")&amp;"-pb"&amp;G43</f>
+        <f t="shared" si="1"/>
         <v>t-dis-bbimsgap-lb-pb20030</v>
       </c>
       <c r="F43" s="84" t="s">
@@ -32690,7 +32650,7 @@
         <v>346</v>
       </c>
       <c r="E44" s="86" t="str">
-        <f>SUBSTITUTE(D44, "hazr-", "")&amp;"-pb"&amp;G44</f>
+        <f t="shared" si="1"/>
         <v>t-dis-bbicltap-lb-pb20000</v>
       </c>
       <c r="F44" s="86" t="s">
@@ -32724,7 +32684,7 @@
         <v>346</v>
       </c>
       <c r="E45" s="86" t="str">
-        <f>SUBSTITUTE(D45, "hazr-", "")&amp;"-pb"&amp;G45</f>
+        <f t="shared" si="1"/>
         <v>t-dis-bbicltap-lb-pb21000</v>
       </c>
       <c r="F45" s="86" t="s">
@@ -32758,7 +32718,7 @@
         <v>346</v>
       </c>
       <c r="E46" s="86" t="str">
-        <f>SUBSTITUTE(D46, "hazr-", "")&amp;"-pb"&amp;G46</f>
+        <f t="shared" si="1"/>
         <v>t-dis-bbicltap-lb-pb22000</v>
       </c>
       <c r="F46" s="86" t="s">
@@ -32792,7 +32752,7 @@
         <v>290</v>
       </c>
       <c r="E47" s="85" t="str">
-        <f>SUBSTITUTE(D47, "hazr-", "")&amp;"-pb"&amp;G47</f>
+        <f t="shared" si="1"/>
         <v>t-dis-ap-lb-pb8080</v>
       </c>
       <c r="F47" s="84" t="s">
@@ -32824,7 +32784,7 @@
         <v>344</v>
       </c>
       <c r="E48" s="85" t="str">
-        <f>SUBSTITUTE(D48, "hazr-", "")&amp;"-pb"&amp;G48</f>
+        <f t="shared" si="1"/>
         <v>t-dis-adm-lb-pb443</v>
       </c>
       <c r="F48" s="84" t="s">
@@ -32856,7 +32816,7 @@
         <v>379</v>
       </c>
       <c r="E49" s="86" t="str">
-        <f>SUBSTITUTE(D49, "hazr-", "")&amp;"-pb"&amp;G49</f>
+        <f t="shared" si="1"/>
         <v>t-dip-web-lb-pb443</v>
       </c>
       <c r="F49" s="86" t="s">
@@ -32890,7 +32850,7 @@
         <v>379</v>
       </c>
       <c r="E50" s="86" t="str">
-        <f>SUBSTITUTE(D50, "hazr-", "")&amp;"-pb"&amp;G50</f>
+        <f t="shared" si="1"/>
         <v>t-dip-web-lb-pb9100</v>
       </c>
       <c r="F50" s="86" t="s">
@@ -32924,7 +32884,7 @@
         <v>378</v>
       </c>
       <c r="E51" s="85" t="str">
-        <f>SUBSTITUTE(D51, "hazr-", "")&amp;"-pb"&amp;G51</f>
+        <f t="shared" si="1"/>
         <v>t-dip-mqweb-lb-pb8883</v>
       </c>
       <c r="F51" s="84" t="s">
@@ -32958,7 +32918,7 @@
         <v>378</v>
       </c>
       <c r="E52" s="85" t="str">
-        <f>SUBSTITUTE(D52, "hazr-", "")&amp;"-pb"&amp;G52</f>
+        <f t="shared" si="1"/>
         <v>t-dip-mqweb-lb-pb1884</v>
       </c>
       <c r="F52" s="84" t="s">
@@ -32992,7 +32952,7 @@
         <v>378</v>
       </c>
       <c r="E53" s="85" t="str">
-        <f>SUBSTITUTE(D53, "hazr-", "")&amp;"-pb"&amp;G53</f>
+        <f t="shared" si="1"/>
         <v>t-dip-mqweb-lb-pb9100</v>
       </c>
       <c r="F53" s="84" t="s">
@@ -33026,7 +32986,7 @@
         <v>377</v>
       </c>
       <c r="E54" s="86" t="str">
-        <f>SUBSTITUTE(D54, "hazr-", "")&amp;"-pb"&amp;G54</f>
+        <f t="shared" si="1"/>
         <v>t-dip-mqap-lb-pb1883</v>
       </c>
       <c r="F54" s="86" t="s">
@@ -33060,7 +33020,7 @@
         <v>377</v>
       </c>
       <c r="E55" s="86" t="str">
-        <f>SUBSTITUTE(D55, "hazr-", "")&amp;"-pb"&amp;G55</f>
+        <f t="shared" si="1"/>
         <v>t-dip-mqap-lb-pb1884</v>
       </c>
       <c r="F55" s="86" t="s">
@@ -33094,7 +33054,7 @@
         <v>377</v>
       </c>
       <c r="E56" s="86" t="str">
-        <f>SUBSTITUTE(D56, "hazr-", "")&amp;"-pb"&amp;G56</f>
+        <f t="shared" si="1"/>
         <v>t-dip-mqap-lb-pb18083</v>
       </c>
       <c r="F56" s="86" t="s">
@@ -33128,7 +33088,7 @@
         <v>377</v>
       </c>
       <c r="E57" s="86" t="str">
-        <f>SUBSTITUTE(D57, "hazr-", "")&amp;"-pb"&amp;G57</f>
+        <f t="shared" si="1"/>
         <v>t-dip-mqap-lb-pb9100</v>
       </c>
       <c r="F57" s="86" t="s">
@@ -33162,7 +33122,7 @@
         <v>376</v>
       </c>
       <c r="E58" s="85" t="str">
-        <f>SUBSTITUTE(D58, "hazr-", "")&amp;"-pb"&amp;G58</f>
+        <f t="shared" si="1"/>
         <v>t-dip-geoap-lb-pb3660</v>
       </c>
       <c r="F58" s="84" t="s">
@@ -33196,7 +33156,7 @@
         <v>376</v>
       </c>
       <c r="E59" s="85" t="str">
-        <f>SUBSTITUTE(D59, "hazr-", "")&amp;"-pb"&amp;G59</f>
+        <f t="shared" si="1"/>
         <v>t-dip-geoap-lb-pb3661</v>
       </c>
       <c r="F59" s="84" t="s">
@@ -33230,7 +33190,7 @@
         <v>376</v>
       </c>
       <c r="E60" s="85" t="str">
-        <f>SUBSTITUTE(D60, "hazr-", "")&amp;"-pb"&amp;G60</f>
+        <f t="shared" si="1"/>
         <v>t-dip-geoap-lb-pb3670</v>
       </c>
       <c r="F60" s="84" t="s">
@@ -33264,7 +33224,7 @@
         <v>376</v>
       </c>
       <c r="E61" s="85" t="str">
-        <f>SUBSTITUTE(D61, "hazr-", "")&amp;"-pb"&amp;G61</f>
+        <f t="shared" si="1"/>
         <v>t-dip-geoap-lb-pb3671</v>
       </c>
       <c r="F61" s="84" t="s">
@@ -33298,7 +33258,7 @@
         <v>376</v>
       </c>
       <c r="E62" s="85" t="str">
-        <f>SUBSTITUTE(D62, "hazr-", "")&amp;"-pb"&amp;G62</f>
+        <f t="shared" si="1"/>
         <v>t-dip-geoap-lb-pb9100</v>
       </c>
       <c r="F62" s="84" t="s">
@@ -33332,7 +33292,7 @@
         <v>375</v>
       </c>
       <c r="E63" s="86" t="str">
-        <f>SUBSTITUTE(D63, "hazr-", "")&amp;"-pb"&amp;G63</f>
+        <f t="shared" si="1"/>
         <v>t-dip-flk-lb-pb</v>
       </c>
       <c r="F63" s="86"/>
@@ -33360,7 +33320,7 @@
         <v>374</v>
       </c>
       <c r="E64" s="85" t="str">
-        <f>SUBSTITUTE(D64, "hazr-", "")&amp;"-pb"&amp;G64</f>
+        <f t="shared" si="1"/>
         <v>t-dip-ap-lb-pb443</v>
       </c>
       <c r="F64" s="84" t="s">
@@ -33394,7 +33354,7 @@
         <v>374</v>
       </c>
       <c r="E65" s="85" t="str">
-        <f>SUBSTITUTE(D65, "hazr-", "")&amp;"-pb"&amp;G65</f>
+        <f t="shared" si="1"/>
         <v>t-dip-ap-lb-pb8100</v>
       </c>
       <c r="F65" s="84" t="s">
@@ -33428,7 +33388,7 @@
         <v>374</v>
       </c>
       <c r="E66" s="85" t="str">
-        <f>SUBSTITUTE(D66, "hazr-", "")&amp;"-pb"&amp;G66</f>
+        <f t="shared" ref="E66:E97" si="2">SUBSTITUTE(D66, "hazr-", "")&amp;"-pb"&amp;G66</f>
         <v>t-dip-ap-lb-pb8200</v>
       </c>
       <c r="F66" s="84" t="s">
@@ -33462,7 +33422,7 @@
         <v>374</v>
       </c>
       <c r="E67" s="85" t="str">
-        <f>SUBSTITUTE(D67, "hazr-", "")&amp;"-pb"&amp;G67</f>
+        <f t="shared" si="2"/>
         <v>t-dip-ap-lb-pb8300</v>
       </c>
       <c r="F67" s="84" t="s">
@@ -33496,7 +33456,7 @@
         <v>374</v>
       </c>
       <c r="E68" s="85" t="str">
-        <f>SUBSTITUTE(D68, "hazr-", "")&amp;"-pb"&amp;G68</f>
+        <f t="shared" si="2"/>
         <v>t-dip-ap-lb-pb8400</v>
       </c>
       <c r="F68" s="84" t="s">
@@ -33530,7 +33490,7 @@
         <v>374</v>
       </c>
       <c r="E69" s="85" t="str">
-        <f>SUBSTITUTE(D69, "hazr-", "")&amp;"-pb"&amp;G69</f>
+        <f t="shared" si="2"/>
         <v>t-dip-ap-lb-pb9100</v>
       </c>
       <c r="F69" s="84" t="s">
@@ -33564,7 +33524,7 @@
         <v>374</v>
       </c>
       <c r="E70" s="85" t="str">
-        <f>SUBSTITUTE(D70, "hazr-", "")&amp;"-pb"&amp;G70</f>
+        <f t="shared" si="2"/>
         <v>t-dip-ap-lb-pb9113</v>
       </c>
       <c r="F70" s="84" t="s">
@@ -33598,7 +33558,7 @@
         <v>373</v>
       </c>
       <c r="E71" s="86" t="str">
-        <f>SUBSTITUTE(D71, "hazr-", "")&amp;"-pb"&amp;G71</f>
+        <f t="shared" si="2"/>
         <v>t-dip-adm-lb-pb443</v>
       </c>
       <c r="F71" s="86" t="s">
@@ -33632,7 +33592,7 @@
         <v>373</v>
       </c>
       <c r="E72" s="86" t="str">
-        <f>SUBSTITUTE(D72, "hazr-", "")&amp;"-pb"&amp;G72</f>
+        <f t="shared" si="2"/>
         <v>t-dip-adm-lb-pb8085</v>
       </c>
       <c r="F72" s="86" t="s">
@@ -33666,7 +33626,7 @@
         <v>373</v>
       </c>
       <c r="E73" s="86" t="str">
-        <f>SUBSTITUTE(D73, "hazr-", "")&amp;"-pb"&amp;G73</f>
+        <f t="shared" si="2"/>
         <v>t-dip-adm-lb-pb8900</v>
       </c>
       <c r="F73" s="86" t="s">
@@ -33700,7 +33660,7 @@
         <v>373</v>
       </c>
       <c r="E74" s="86" t="str">
-        <f>SUBSTITUTE(D74, "hazr-", "")&amp;"-pb"&amp;G74</f>
+        <f t="shared" si="2"/>
         <v>t-dip-adm-lb-pb8901</v>
       </c>
       <c r="F74" s="86" t="s">
@@ -33734,7 +33694,7 @@
         <v>373</v>
       </c>
       <c r="E75" s="86" t="str">
-        <f>SUBSTITUTE(D75, "hazr-", "")&amp;"-pb"&amp;G75</f>
+        <f t="shared" si="2"/>
         <v>t-dip-adm-lb-pb9100</v>
       </c>
       <c r="F75" s="86" t="s">
@@ -33754,30 +33714,30 @@
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B76" s="112" t="str" cm="1">
+      <c r="A76" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B76" s="74" t="str" cm="1">
         <f t="array" ref="B76">UPPER(INDEX(_xlfn.TEXTSPLIT($C76, "-"), 3))</f>
         <v>CS</v>
       </c>
-      <c r="C76" s="112" t="s">
+      <c r="C76" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="D76" s="112" t="s">
+      <c r="D76" s="74" t="s">
         <v>383</v>
       </c>
-      <c r="E76" s="113" t="str">
-        <f>SUBSTITUTE(D76, "hazr-", "")&amp;"-pb"&amp;G76</f>
+      <c r="E76" s="88" t="str">
+        <f t="shared" si="2"/>
         <v>t-cs-chtweb-lb-pb</v>
       </c>
-      <c r="F76" s="112"/>
-      <c r="G76" s="112"/>
-      <c r="H76" s="112"/>
-      <c r="I76" s="112">
+      <c r="F76" s="74"/>
+      <c r="G76" s="74"/>
+      <c r="H76" s="74"/>
+      <c r="I76" s="74">
         <v>5</v>
       </c>
-      <c r="J76" s="112">
+      <c r="J76" s="74">
         <v>2</v>
       </c>
     </row>
@@ -33796,7 +33756,7 @@
         <v>384</v>
       </c>
       <c r="E77" s="85" t="str">
-        <f>SUBSTITUTE(D77, "hazr-", "")&amp;"-pb"&amp;G77</f>
+        <f t="shared" si="2"/>
         <v>t-cs-chtintweb-lb-pb</v>
       </c>
       <c r="F77" s="84"/>
@@ -33824,7 +33784,7 @@
         <v>382</v>
       </c>
       <c r="E78" s="86" t="str">
-        <f>SUBSTITUTE(D78, "hazr-", "")&amp;"-pb"&amp;G78</f>
+        <f t="shared" si="2"/>
         <v>t-cs-chtap-lb-pb</v>
       </c>
       <c r="F78" s="86"/>
@@ -33852,7 +33812,7 @@
         <v>381</v>
       </c>
       <c r="E79" s="85" t="str">
-        <f>SUBSTITUTE(D79, "hazr-", "")&amp;"-pb"&amp;G79</f>
+        <f t="shared" si="2"/>
         <v>t-com-proxy-lb-pb443</v>
       </c>
       <c r="F79" s="84" t="s">
@@ -33886,7 +33846,7 @@
         <v>381</v>
       </c>
       <c r="E80" s="85" t="str">
-        <f>SUBSTITUTE(D80, "hazr-", "")&amp;"-pb"&amp;G80</f>
+        <f t="shared" si="2"/>
         <v>t-com-proxy-lb-pb8080</v>
       </c>
       <c r="F80" s="84" t="s">
@@ -33920,7 +33880,7 @@
         <v>380</v>
       </c>
       <c r="E81" s="85" t="str">
-        <f>SUBSTITUTE(D81, "hazr-", "")&amp;"-pb"&amp;G81</f>
+        <f t="shared" si="2"/>
         <v>t-com-auth-lb-pb8088</v>
       </c>
       <c r="F81" s="84" t="s">
@@ -33954,7 +33914,7 @@
         <v>380</v>
       </c>
       <c r="E82" s="85" t="str">
-        <f>SUBSTITUTE(D82, "hazr-", "")&amp;"-pb"&amp;G82</f>
+        <f t="shared" si="2"/>
         <v>t-com-auth-lb-pb9003</v>
       </c>
       <c r="F82" s="84" t="s">
@@ -33988,7 +33948,7 @@
         <v>380</v>
       </c>
       <c r="E83" s="85" t="str">
-        <f>SUBSTITUTE(D83, "hazr-", "")&amp;"-pb"&amp;G83</f>
+        <f t="shared" si="2"/>
         <v>t-com-auth-lb-pb9005</v>
       </c>
       <c r="F83" s="84" t="s">
@@ -34022,7 +33982,7 @@
         <v>372</v>
       </c>
       <c r="E84" s="85" t="str">
-        <f>SUBSTITUTE(D84, "hazr-", "")&amp;"-pb"&amp;G84</f>
+        <f t="shared" si="2"/>
         <v>t-bdp-slap-lb-pb443</v>
       </c>
       <c r="F84" s="84" t="s">
@@ -34056,7 +34016,7 @@
         <v>371</v>
       </c>
       <c r="E85" s="86" t="str">
-        <f>SUBSTITUTE(D85, "hazr-", "")&amp;"-pb"&amp;G85</f>
+        <f t="shared" si="2"/>
         <v>t-bdp-cxmadm-lb-pb443</v>
       </c>
       <c r="F85" s="86" t="s">
@@ -34076,34 +34036,34 @@
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B86" s="112" t="str" cm="1">
+      <c r="A86" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B86" s="74" t="str" cm="1">
         <f t="array" ref="B86">UPPER(INDEX(_xlfn.TEXTSPLIT($C86, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="C86" s="112" t="s">
+      <c r="C86" s="74" t="s">
         <v>392</v>
       </c>
-      <c r="D86" s="112" t="s">
+      <c r="D86" s="74" t="s">
         <v>388</v>
       </c>
-      <c r="E86" s="113" t="str">
-        <f>SUBSTITUTE(D86, "hazr-", "")&amp;"-pb"&amp;G86</f>
+      <c r="E86" s="88" t="str">
+        <f t="shared" si="2"/>
         <v>t-bdp-crkweb-lb-pb443</v>
       </c>
-      <c r="F86" s="112" t="s">
+      <c r="F86" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="G86" s="112">
+      <c r="G86" s="74">
         <v>443</v>
       </c>
-      <c r="H86" s="112"/>
-      <c r="I86" s="112">
+      <c r="H86" s="74"/>
+      <c r="I86" s="74">
         <v>5</v>
       </c>
-      <c r="J86" s="112">
+      <c r="J86" s="74">
         <v>2</v>
       </c>
     </row>
@@ -34122,7 +34082,7 @@
         <v>390</v>
       </c>
       <c r="E87" s="85" t="str">
-        <f>SUBSTITUTE(D87, "hazr-", "")&amp;"-pb"&amp;G87</f>
+        <f t="shared" si="2"/>
         <v>t-bdp-crkml-lb-pb8082</v>
       </c>
       <c r="F87" s="84" t="s">
@@ -34154,7 +34114,7 @@
         <v>389</v>
       </c>
       <c r="E88" s="86" t="str">
-        <f>SUBSTITUTE(D88, "hazr-", "")&amp;"-pb"&amp;G88</f>
+        <f t="shared" si="2"/>
         <v>t-bdp-crkap-lb-pb8085</v>
       </c>
       <c r="F88" s="86" t="s">
@@ -34178,12 +34138,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -34331,15 +34288,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34363,17 +34331,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3B1D33-DC7E-4E7E-B287-A3FC23DCE856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FE903F-F1A6-4E5B-8097-133FF63573C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">LB!$B$1:$Q$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">LB_Probe!$A$1:$J$88</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">LB_Rule!$A$1:$Q$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">LB_Rule!$A$1:$R$88</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1573,7 +1573,7 @@
     <author>zenithn</author>
   </authors>
   <commentList>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{6D097393-523D-44A5-B559-F99AED6EE617}">
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{6D097393-523D-44A5-B559-F99AED6EE617}">
       <text>
         <r>
           <rPr>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4782" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4783" uniqueCount="633">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3967,6 +3967,10 @@
   </si>
   <si>
     <t>hazr-t-cs-rg</t>
+  </si>
+  <si>
+    <t>OldRuleName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6805,25 +6809,26 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BC862D-08E7-4593-9A34-4D2B508CF25B}">
-  <dimension ref="A1:Q88"/>
+  <dimension ref="A1:R88"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22" customWidth="1"/>
-    <col min="20" max="20" width="13.875" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22" customWidth="1"/>
+    <col min="21" max="21" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
@@ -6840,43 +6845,46 @@
         <v>118</v>
       </c>
       <c r="F1" s="77" t="s">
+        <v>632</v>
+      </c>
+      <c r="G1" s="77" t="s">
         <v>104</v>
       </c>
-      <c r="G1" s="79" t="s">
+      <c r="H1" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="H1" s="79" t="s">
+      <c r="I1" s="79" t="s">
         <v>119</v>
       </c>
-      <c r="I1" s="102" t="s">
+      <c r="J1" s="102" t="s">
         <v>130</v>
       </c>
-      <c r="J1" s="77" t="s">
+      <c r="K1" s="77" t="s">
         <v>110</v>
       </c>
-      <c r="K1" s="79" t="s">
+      <c r="L1" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="L1" s="102" t="s">
+      <c r="M1" s="102" t="s">
         <v>112</v>
       </c>
-      <c r="M1" s="72" t="s">
+      <c r="N1" s="72" t="s">
         <v>629</v>
       </c>
-      <c r="N1" s="102" t="s">
+      <c r="O1" s="102" t="s">
         <v>123</v>
       </c>
-      <c r="O1" s="79" t="s">
+      <c r="P1" s="79" t="s">
         <v>124</v>
       </c>
-      <c r="P1" s="102" t="s">
+      <c r="Q1" s="102" t="s">
         <v>129</v>
       </c>
-      <c r="Q1" s="102" t="s">
+      <c r="R1" s="102" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="74" t="s">
         <v>185</v>
       </c>
@@ -6891,50 +6899,54 @@
         <v>363</v>
       </c>
       <c r="E2" s="74" t="str">
-        <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-rule"&amp;M2</f>
+        <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-rule"&amp;N2</f>
         <v>t-dtg-web-lb-rule8080</v>
       </c>
       <c r="F2" s="74" t="str">
+        <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-rule"</f>
+        <v>t-dtg-web-lb-rule</v>
+      </c>
+      <c r="G2" s="74" t="str">
         <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-web-lb-fe</v>
       </c>
-      <c r="G2" s="74" t="s">
+      <c r="H2" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="74">
+      <c r="I2" s="74">
         <v>8080</v>
       </c>
-      <c r="I2" s="74" t="b">
+      <c r="J2" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J2" s="74" t="str">
+      <c r="K2" s="74" t="str">
         <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-web-lb-bp</v>
       </c>
-      <c r="K2" s="74">
+      <c r="L2" s="74">
         <v>8080</v>
       </c>
-      <c r="L2" s="74" t="str">
-        <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-pb"&amp;IF(M2="", "", M2)</f>
+      <c r="M2" s="74" t="str">
+        <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-pb"&amp;IF(N2="", "", N2)</f>
         <v>t-dtg-web-lb-pb8080</v>
       </c>
-      <c r="M2" s="74">
+      <c r="N2" s="74">
         <v>8080</v>
       </c>
-      <c r="N2" s="74">
+      <c r="O2" s="74">
         <v>4</v>
       </c>
-      <c r="O2" s="74" t="s">
+      <c r="P2" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P2" s="74" t="b">
-        <v>1</v>
-      </c>
       <c r="Q2" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="74" t="s">
         <v>185</v>
       </c>
@@ -6949,50 +6961,54 @@
         <v>363</v>
       </c>
       <c r="E3" s="74" t="str">
-        <f t="shared" ref="E3:E66" si="0">SUBSTITUTE(D3, "hazr-", "")&amp;"-rule"&amp;M3</f>
+        <f t="shared" ref="E3:F66" si="0">SUBSTITUTE(D3, "hazr-", "")&amp;"-rule"&amp;N3</f>
         <v>t-dtg-web-lb-rule8081</v>
       </c>
       <c r="F3" s="74" t="str">
+        <f t="shared" ref="F3:F66" si="1">SUBSTITUTE(D3, "hazr-", "")&amp;"-rule"</f>
+        <v>t-dtg-web-lb-rule</v>
+      </c>
+      <c r="G3" s="74" t="str">
         <f>SUBSTITUTE(D3, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-web-lb-fe</v>
       </c>
-      <c r="G3" s="74" t="s">
+      <c r="H3" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H3" s="74">
+      <c r="I3" s="74">
         <v>8081</v>
       </c>
-      <c r="I3" s="74" t="b">
+      <c r="J3" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J3" s="74" t="str">
+      <c r="K3" s="74" t="str">
         <f>SUBSTITUTE(D3, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-web-lb-bp</v>
       </c>
-      <c r="K3" s="74">
+      <c r="L3" s="74">
         <v>8081</v>
       </c>
-      <c r="L3" s="74" t="str">
-        <f t="shared" ref="L3:L66" si="1">SUBSTITUTE(D3, "hazr-", "")&amp;"-pb"&amp;IF(M3="", "", M3)</f>
+      <c r="M3" s="74" t="str">
+        <f t="shared" ref="M3:M66" si="2">SUBSTITUTE(D3, "hazr-", "")&amp;"-pb"&amp;IF(N3="", "", N3)</f>
         <v>t-dtg-web-lb-pb8081</v>
       </c>
-      <c r="M3" s="74">
+      <c r="N3" s="74">
         <v>8081</v>
       </c>
-      <c r="N3" s="74">
+      <c r="O3" s="74">
         <v>4</v>
       </c>
-      <c r="O3" s="74" t="s">
+      <c r="P3" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P3" s="74" t="b">
-        <v>1</v>
-      </c>
       <c r="Q3" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="84" t="s">
         <v>185</v>
       </c>
@@ -7010,47 +7026,51 @@
         <f t="shared" si="0"/>
         <v>t-dtg-mq-lb-rule1883</v>
       </c>
-      <c r="F4" s="84" t="str">
+      <c r="F4" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-mq-lb-rule</v>
+      </c>
+      <c r="G4" s="84" t="str">
         <f>SUBSTITUTE(D4, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-mq-lb-fe</v>
       </c>
-      <c r="G4" s="84" t="s">
+      <c r="H4" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="84">
+      <c r="I4" s="84">
         <v>1883</v>
       </c>
-      <c r="I4" s="84" t="b">
+      <c r="J4" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J4" s="84" t="str">
+      <c r="K4" s="84" t="str">
         <f>SUBSTITUTE(D4, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-mq-lb-bp</v>
       </c>
-      <c r="K4" s="84">
+      <c r="L4" s="84">
         <v>1883</v>
       </c>
-      <c r="L4" s="84" t="str">
-        <f t="shared" si="1"/>
+      <c r="M4" s="84" t="str">
+        <f t="shared" si="2"/>
         <v>t-dtg-mq-lb-pb1883</v>
       </c>
-      <c r="M4" s="84">
+      <c r="N4" s="84">
         <v>1883</v>
       </c>
-      <c r="N4" s="84">
+      <c r="O4" s="84">
         <v>4</v>
       </c>
-      <c r="O4" s="84" t="s">
+      <c r="P4" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P4" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q4" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="84" t="s">
         <v>185</v>
       </c>
@@ -7068,47 +7088,51 @@
         <f t="shared" si="0"/>
         <v>t-dtg-mq-lb-rule1884</v>
       </c>
-      <c r="F5" s="84" t="str">
+      <c r="F5" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-mq-lb-rule</v>
+      </c>
+      <c r="G5" s="84" t="str">
         <f>SUBSTITUTE(D5, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-mq-lb-fe</v>
       </c>
-      <c r="G5" s="84" t="s">
+      <c r="H5" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="84">
+      <c r="I5" s="84">
         <v>1884</v>
       </c>
-      <c r="I5" s="84" t="b">
+      <c r="J5" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J5" s="84" t="str">
+      <c r="K5" s="84" t="str">
         <f>SUBSTITUTE(D5, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-mq-lb-bp</v>
       </c>
-      <c r="K5" s="84">
+      <c r="L5" s="84">
         <v>1884</v>
       </c>
-      <c r="L5" s="84" t="str">
-        <f t="shared" si="1"/>
+      <c r="M5" s="84" t="str">
+        <f t="shared" si="2"/>
         <v>t-dtg-mq-lb-pb1884</v>
       </c>
-      <c r="M5" s="84">
+      <c r="N5" s="84">
         <v>1884</v>
       </c>
-      <c r="N5" s="84">
+      <c r="O5" s="84">
         <v>4</v>
       </c>
-      <c r="O5" s="84" t="s">
+      <c r="P5" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P5" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q5" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="86" t="s">
         <v>185</v>
       </c>
@@ -7126,47 +7150,51 @@
         <f t="shared" si="0"/>
         <v>t-dtg-ingap-lb-rule8081</v>
       </c>
-      <c r="F6" s="86" t="str">
-        <f t="shared" ref="F6:F50" si="2">SUBSTITUTE(D6, "hazr-", "")&amp;"-fe"</f>
+      <c r="F6" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-ingap-lb-rule</v>
+      </c>
+      <c r="G6" s="86" t="str">
+        <f t="shared" ref="G6:G50" si="3">SUBSTITUTE(D6, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-ingap-lb-fe</v>
       </c>
-      <c r="G6" s="86" t="s">
+      <c r="H6" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="H6" s="86">
+      <c r="I6" s="86">
         <v>8081</v>
       </c>
-      <c r="I6" s="86" t="b">
+      <c r="J6" s="86" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="86" t="str">
+      <c r="K6" s="86" t="str">
         <f>SUBSTITUTE(D6, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-ingap-lb-bp</v>
       </c>
-      <c r="K6" s="86">
+      <c r="L6" s="86">
         <v>8081</v>
       </c>
-      <c r="L6" s="86" t="str">
-        <f t="shared" si="1"/>
+      <c r="M6" s="86" t="str">
+        <f t="shared" si="2"/>
         <v>t-dtg-ingap-lb-pb8081</v>
       </c>
-      <c r="M6" s="86">
+      <c r="N6" s="86">
         <v>8081</v>
       </c>
-      <c r="N6" s="86">
+      <c r="O6" s="86">
         <v>4</v>
       </c>
-      <c r="O6" s="86" t="s">
+      <c r="P6" s="86" t="s">
         <v>125</v>
       </c>
-      <c r="P6" s="86" t="b">
-        <v>1</v>
-      </c>
       <c r="Q6" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" s="86" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="84" t="s">
         <v>185</v>
       </c>
@@ -7184,47 +7212,51 @@
         <f t="shared" si="0"/>
         <v>t-dtg-geoap-lb-rule8089</v>
       </c>
-      <c r="F7" s="84" t="str">
+      <c r="F7" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-geoap-lb-rule</v>
+      </c>
+      <c r="G7" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-geoap-lb-fe</v>
+      </c>
+      <c r="H7" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="84">
+        <v>8089</v>
+      </c>
+      <c r="J7" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="84" t="str">
+        <f t="shared" ref="K7:K50" si="4">SUBSTITUTE(D7, "hazr-", "")&amp;"-bp"</f>
+        <v>t-dtg-geoap-lb-bp</v>
+      </c>
+      <c r="L7" s="84">
+        <v>8089</v>
+      </c>
+      <c r="M7" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-geoap-lb-fe</v>
-      </c>
-      <c r="G7" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" s="84">
+        <v>t-dtg-geoap-lb-pb8089</v>
+      </c>
+      <c r="N7" s="84">
         <v>8089</v>
       </c>
-      <c r="I7" s="84" t="b">
+      <c r="O7" s="84">
+        <v>4</v>
+      </c>
+      <c r="P7" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q7" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J7" s="84" t="str">
-        <f t="shared" ref="J7:J50" si="3">SUBSTITUTE(D7, "hazr-", "")&amp;"-bp"</f>
-        <v>t-dtg-geoap-lb-bp</v>
-      </c>
-      <c r="K7" s="84">
-        <v>8089</v>
-      </c>
-      <c r="L7" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-geoap-lb-pb8089</v>
-      </c>
-      <c r="M7" s="84">
-        <v>8089</v>
-      </c>
-      <c r="N7" s="84">
-        <v>4</v>
-      </c>
-      <c r="O7" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P7" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="84" t="s">
         <v>185</v>
       </c>
@@ -7242,47 +7274,51 @@
         <f t="shared" si="0"/>
         <v>t-dtg-geoap-lb-rule9089</v>
       </c>
-      <c r="F8" s="84" t="str">
+      <c r="F8" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-geoap-lb-rule</v>
+      </c>
+      <c r="G8" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-geoap-lb-fe</v>
+      </c>
+      <c r="H8" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="84">
+        <v>9089</v>
+      </c>
+      <c r="J8" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-geoap-lb-bp</v>
+      </c>
+      <c r="L8" s="84">
+        <v>9089</v>
+      </c>
+      <c r="M8" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-geoap-lb-fe</v>
-      </c>
-      <c r="G8" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="84">
+        <v>t-dtg-geoap-lb-pb9089</v>
+      </c>
+      <c r="N8" s="84">
         <v>9089</v>
       </c>
-      <c r="I8" s="84" t="b">
+      <c r="O8" s="84">
+        <v>4</v>
+      </c>
+      <c r="P8" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q8" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J8" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-geoap-lb-bp</v>
-      </c>
-      <c r="K8" s="84">
-        <v>9089</v>
-      </c>
-      <c r="L8" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-geoap-lb-pb9089</v>
-      </c>
-      <c r="M8" s="84">
-        <v>9089</v>
-      </c>
-      <c r="N8" s="84">
-        <v>4</v>
-      </c>
-      <c r="O8" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P8" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="74" t="s">
         <v>185</v>
       </c>
@@ -7301,46 +7337,50 @@
         <v>t-dtg-extgeoap-lb-rule3660</v>
       </c>
       <c r="F9" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-extgeoap-lb-rule</v>
+      </c>
+      <c r="G9" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-extgeoap-lb-fe</v>
+      </c>
+      <c r="H9" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" s="74">
+        <v>3660</v>
+      </c>
+      <c r="J9" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-extgeoap-lb-bp</v>
+      </c>
+      <c r="L9" s="74">
+        <v>3660</v>
+      </c>
+      <c r="M9" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-extgeoap-lb-fe</v>
-      </c>
-      <c r="G9" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H9" s="74">
+        <v>t-dtg-extgeoap-lb-pb3660</v>
+      </c>
+      <c r="N9" s="74">
         <v>3660</v>
       </c>
-      <c r="I9" s="74" t="b">
+      <c r="O9" s="74">
+        <v>4</v>
+      </c>
+      <c r="P9" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q9" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-extgeoap-lb-bp</v>
-      </c>
-      <c r="K9" s="74">
-        <v>3660</v>
-      </c>
-      <c r="L9" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-extgeoap-lb-pb3660</v>
-      </c>
-      <c r="M9" s="74">
-        <v>3660</v>
-      </c>
-      <c r="N9" s="74">
-        <v>4</v>
-      </c>
-      <c r="O9" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P9" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
         <v>185</v>
       </c>
@@ -7359,46 +7399,50 @@
         <v>t-dtg-extgeoap-lb-rule3661</v>
       </c>
       <c r="F10" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-extgeoap-lb-rule</v>
+      </c>
+      <c r="G10" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-extgeoap-lb-fe</v>
+      </c>
+      <c r="H10" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="74">
+        <v>3661</v>
+      </c>
+      <c r="J10" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-extgeoap-lb-bp</v>
+      </c>
+      <c r="L10" s="74">
+        <v>3661</v>
+      </c>
+      <c r="M10" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-extgeoap-lb-fe</v>
-      </c>
-      <c r="G10" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" s="74">
+        <v>t-dtg-extgeoap-lb-pb3661</v>
+      </c>
+      <c r="N10" s="74">
         <v>3661</v>
       </c>
-      <c r="I10" s="74" t="b">
+      <c r="O10" s="74">
+        <v>4</v>
+      </c>
+      <c r="P10" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q10" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J10" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-extgeoap-lb-bp</v>
-      </c>
-      <c r="K10" s="74">
-        <v>3661</v>
-      </c>
-      <c r="L10" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-extgeoap-lb-pb3661</v>
-      </c>
-      <c r="M10" s="74">
-        <v>3661</v>
-      </c>
-      <c r="N10" s="74">
-        <v>4</v>
-      </c>
-      <c r="O10" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P10" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="84" t="s">
         <v>185</v>
       </c>
@@ -7416,47 +7460,51 @@
         <f t="shared" si="0"/>
         <v>t-dtg-dprweb-lb-rule443</v>
       </c>
-      <c r="F11" s="84" t="str">
+      <c r="F11" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-dprweb-lb-rule</v>
+      </c>
+      <c r="G11" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-dprweb-lb-fe</v>
+      </c>
+      <c r="H11" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="84">
+        <v>443</v>
+      </c>
+      <c r="J11" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-dprweb-lb-bp</v>
+      </c>
+      <c r="L11" s="84">
+        <v>443</v>
+      </c>
+      <c r="M11" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-dprweb-lb-fe</v>
-      </c>
-      <c r="G11" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" s="84">
+        <v>t-dtg-dprweb-lb-pb443</v>
+      </c>
+      <c r="N11" s="84">
         <v>443</v>
       </c>
-      <c r="I11" s="84" t="b">
+      <c r="O11" s="84">
+        <v>4</v>
+      </c>
+      <c r="P11" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q11" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J11" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-dprweb-lb-bp</v>
-      </c>
-      <c r="K11" s="84">
-        <v>443</v>
-      </c>
-      <c r="L11" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-dprweb-lb-pb443</v>
-      </c>
-      <c r="M11" s="84">
-        <v>443</v>
-      </c>
-      <c r="N11" s="84">
-        <v>4</v>
-      </c>
-      <c r="O11" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P11" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="86" t="s">
         <v>185</v>
       </c>
@@ -7474,47 +7522,51 @@
         <f t="shared" si="0"/>
         <v>t-dtg-dprap-lb-rule8082</v>
       </c>
-      <c r="F12" s="86" t="str">
+      <c r="F12" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-dprap-lb-rule</v>
+      </c>
+      <c r="G12" s="86" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-dprap-lb-fe</v>
+      </c>
+      <c r="H12" s="86" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="86">
+        <v>8082</v>
+      </c>
+      <c r="J12" s="86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="86" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-dprap-lb-bp</v>
+      </c>
+      <c r="L12" s="86">
+        <v>8082</v>
+      </c>
+      <c r="M12" s="86" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-dprap-lb-fe</v>
-      </c>
-      <c r="G12" s="86" t="s">
-        <v>57</v>
-      </c>
-      <c r="H12" s="86">
+        <v>t-dtg-dprap-lb-pb8082</v>
+      </c>
+      <c r="N12" s="86">
         <v>8082</v>
       </c>
-      <c r="I12" s="86" t="b">
+      <c r="O12" s="86">
+        <v>4</v>
+      </c>
+      <c r="P12" s="86" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q12" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" s="86" t="b">
         <v>0</v>
       </c>
-      <c r="J12" s="86" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-dprap-lb-bp</v>
-      </c>
-      <c r="K12" s="86">
-        <v>8082</v>
-      </c>
-      <c r="L12" s="86" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-dprap-lb-pb8082</v>
-      </c>
-      <c r="M12" s="86">
-        <v>8082</v>
-      </c>
-      <c r="N12" s="86">
-        <v>4</v>
-      </c>
-      <c r="O12" s="86" t="s">
-        <v>125</v>
-      </c>
-      <c r="P12" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="86" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="84" t="s">
         <v>185</v>
       </c>
@@ -7532,47 +7584,51 @@
         <f t="shared" si="0"/>
         <v>t-dtg-diosweb-lb-rule443</v>
       </c>
-      <c r="F13" s="84" t="str">
+      <c r="F13" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-diosweb-lb-rule</v>
+      </c>
+      <c r="G13" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-diosweb-lb-fe</v>
+      </c>
+      <c r="H13" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I13" s="84">
+        <v>443</v>
+      </c>
+      <c r="J13" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-diosweb-lb-bp</v>
+      </c>
+      <c r="L13" s="84">
+        <v>443</v>
+      </c>
+      <c r="M13" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-diosweb-lb-fe</v>
-      </c>
-      <c r="G13" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H13" s="84">
+        <v>t-dtg-diosweb-lb-pb443</v>
+      </c>
+      <c r="N13" s="84">
         <v>443</v>
       </c>
-      <c r="I13" s="84" t="b">
+      <c r="O13" s="84">
+        <v>4</v>
+      </c>
+      <c r="P13" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q13" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J13" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-diosweb-lb-bp</v>
-      </c>
-      <c r="K13" s="84">
-        <v>443</v>
-      </c>
-      <c r="L13" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-diosweb-lb-pb443</v>
-      </c>
-      <c r="M13" s="84">
-        <v>443</v>
-      </c>
-      <c r="N13" s="84">
-        <v>4</v>
-      </c>
-      <c r="O13" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P13" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="86" t="s">
         <v>185</v>
       </c>
@@ -7590,47 +7646,51 @@
         <f t="shared" si="0"/>
         <v>t-dtg-diosap-lb-rule8080</v>
       </c>
-      <c r="F14" s="86" t="str">
+      <c r="F14" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-diosap-lb-rule</v>
+      </c>
+      <c r="G14" s="86" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-diosap-lb-fe</v>
+      </c>
+      <c r="H14" s="86" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" s="86">
+        <v>8080</v>
+      </c>
+      <c r="J14" s="86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="86" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-diosap-lb-bp</v>
+      </c>
+      <c r="L14" s="86">
+        <v>8080</v>
+      </c>
+      <c r="M14" s="86" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-diosap-lb-fe</v>
-      </c>
-      <c r="G14" s="86" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="86">
+        <v>t-dtg-diosap-lb-pb8080</v>
+      </c>
+      <c r="N14" s="86">
         <v>8080</v>
       </c>
-      <c r="I14" s="86" t="b">
+      <c r="O14" s="86">
+        <v>4</v>
+      </c>
+      <c r="P14" s="86" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q14" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" s="86" t="b">
         <v>0</v>
       </c>
-      <c r="J14" s="86" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-diosap-lb-bp</v>
-      </c>
-      <c r="K14" s="86">
-        <v>8080</v>
-      </c>
-      <c r="L14" s="86" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-diosap-lb-pb8080</v>
-      </c>
-      <c r="M14" s="86">
-        <v>8080</v>
-      </c>
-      <c r="N14" s="86">
-        <v>4</v>
-      </c>
-      <c r="O14" s="86" t="s">
-        <v>125</v>
-      </c>
-      <c r="P14" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="86" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="84" t="s">
         <v>185</v>
       </c>
@@ -7648,47 +7708,51 @@
         <f t="shared" si="0"/>
         <v>t-dtg-cdsvadm-lb-rule9100</v>
       </c>
-      <c r="F15" s="84" t="str">
+      <c r="F15" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-cdsvadm-lb-rule</v>
+      </c>
+      <c r="G15" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-cdsvadm-lb-fe</v>
+      </c>
+      <c r="H15" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I15" s="84">
+        <v>9100</v>
+      </c>
+      <c r="J15" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-cdsvadm-lb-bp</v>
+      </c>
+      <c r="L15" s="84">
+        <v>9100</v>
+      </c>
+      <c r="M15" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-cdsvadm-lb-fe</v>
-      </c>
-      <c r="G15" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H15" s="84">
+        <v>t-dtg-cdsvadm-lb-pb9100</v>
+      </c>
+      <c r="N15" s="84">
         <v>9100</v>
       </c>
-      <c r="I15" s="84" t="b">
+      <c r="O15" s="84">
+        <v>4</v>
+      </c>
+      <c r="P15" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q15" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J15" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-cdsvadm-lb-bp</v>
-      </c>
-      <c r="K15" s="84">
-        <v>9100</v>
-      </c>
-      <c r="L15" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdsvadm-lb-pb9100</v>
-      </c>
-      <c r="M15" s="84">
-        <v>9100</v>
-      </c>
-      <c r="N15" s="84">
-        <v>4</v>
-      </c>
-      <c r="O15" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P15" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="84" t="s">
         <v>185</v>
       </c>
@@ -7706,47 +7770,51 @@
         <f t="shared" si="0"/>
         <v>t-dtg-cdsvadm-lb-rule9300</v>
       </c>
-      <c r="F16" s="84" t="str">
+      <c r="F16" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-cdsvadm-lb-rule</v>
+      </c>
+      <c r="G16" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-cdsvadm-lb-fe</v>
+      </c>
+      <c r="H16" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I16" s="84">
+        <v>9300</v>
+      </c>
+      <c r="J16" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-cdsvadm-lb-bp</v>
+      </c>
+      <c r="L16" s="84">
+        <v>9300</v>
+      </c>
+      <c r="M16" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-cdsvadm-lb-fe</v>
-      </c>
-      <c r="G16" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="84">
+        <v>t-dtg-cdsvadm-lb-pb9300</v>
+      </c>
+      <c r="N16" s="84">
         <v>9300</v>
       </c>
-      <c r="I16" s="84" t="b">
+      <c r="O16" s="84">
+        <v>4</v>
+      </c>
+      <c r="P16" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q16" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J16" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-cdsvadm-lb-bp</v>
-      </c>
-      <c r="K16" s="84">
-        <v>9300</v>
-      </c>
-      <c r="L16" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdsvadm-lb-pb9300</v>
-      </c>
-      <c r="M16" s="84">
-        <v>9300</v>
-      </c>
-      <c r="N16" s="84">
-        <v>4</v>
-      </c>
-      <c r="O16" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P16" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="84" t="s">
         <v>185</v>
       </c>
@@ -7764,47 +7832,51 @@
         <f t="shared" si="0"/>
         <v>t-dtg-cdsvadm-lb-rule9105</v>
       </c>
-      <c r="F17" s="84" t="str">
+      <c r="F17" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-cdsvadm-lb-rule</v>
+      </c>
+      <c r="G17" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-cdsvadm-lb-fe</v>
+      </c>
+      <c r="H17" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17" s="84">
+        <v>9105</v>
+      </c>
+      <c r="J17" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-cdsvadm-lb-bp</v>
+      </c>
+      <c r="L17" s="84">
+        <v>9105</v>
+      </c>
+      <c r="M17" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-cdsvadm-lb-fe</v>
-      </c>
-      <c r="G17" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17" s="84">
+        <v>t-dtg-cdsvadm-lb-pb9105</v>
+      </c>
+      <c r="N17" s="84">
         <v>9105</v>
       </c>
-      <c r="I17" s="84" t="b">
+      <c r="O17" s="84">
+        <v>4</v>
+      </c>
+      <c r="P17" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q17" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J17" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-cdsvadm-lb-bp</v>
-      </c>
-      <c r="K17" s="84">
-        <v>9105</v>
-      </c>
-      <c r="L17" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdsvadm-lb-pb9105</v>
-      </c>
-      <c r="M17" s="84">
-        <v>9105</v>
-      </c>
-      <c r="N17" s="84">
-        <v>4</v>
-      </c>
-      <c r="O17" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P17" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="84" t="s">
         <v>185</v>
       </c>
@@ -7822,47 +7894,51 @@
         <f t="shared" si="0"/>
         <v>t-dtg-cdsvadm-lb-rule9003</v>
       </c>
-      <c r="F18" s="84" t="str">
+      <c r="F18" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-cdsvadm-lb-rule</v>
+      </c>
+      <c r="G18" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-cdsvadm-lb-fe</v>
+      </c>
+      <c r="H18" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I18" s="84">
+        <v>9003</v>
+      </c>
+      <c r="J18" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-cdsvadm-lb-bp</v>
+      </c>
+      <c r="L18" s="84">
+        <v>9003</v>
+      </c>
+      <c r="M18" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-cdsvadm-lb-fe</v>
-      </c>
-      <c r="G18" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H18" s="84">
+        <v>t-dtg-cdsvadm-lb-pb9003</v>
+      </c>
+      <c r="N18" s="84">
         <v>9003</v>
       </c>
-      <c r="I18" s="84" t="b">
+      <c r="O18" s="84">
+        <v>4</v>
+      </c>
+      <c r="P18" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q18" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J18" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-cdsvadm-lb-bp</v>
-      </c>
-      <c r="K18" s="84">
-        <v>9003</v>
-      </c>
-      <c r="L18" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdsvadm-lb-pb9003</v>
-      </c>
-      <c r="M18" s="84">
-        <v>9003</v>
-      </c>
-      <c r="N18" s="84">
-        <v>4</v>
-      </c>
-      <c r="O18" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P18" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="84" t="s">
         <v>185</v>
       </c>
@@ -7880,47 +7956,51 @@
         <f t="shared" si="0"/>
         <v>t-dtg-cdsvadm-lb-rule8088</v>
       </c>
-      <c r="F19" s="84" t="str">
+      <c r="F19" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-cdsvadm-lb-rule</v>
+      </c>
+      <c r="G19" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-cdsvadm-lb-fe</v>
+      </c>
+      <c r="H19" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I19" s="84">
+        <v>8088</v>
+      </c>
+      <c r="J19" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-cdsvadm-lb-bp</v>
+      </c>
+      <c r="L19" s="84">
+        <v>8088</v>
+      </c>
+      <c r="M19" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-cdsvadm-lb-fe</v>
-      </c>
-      <c r="G19" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H19" s="84">
+        <v>t-dtg-cdsvadm-lb-pb8088</v>
+      </c>
+      <c r="N19" s="84">
         <v>8088</v>
       </c>
-      <c r="I19" s="84" t="b">
+      <c r="O19" s="84">
+        <v>4</v>
+      </c>
+      <c r="P19" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q19" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J19" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-cdsvadm-lb-bp</v>
-      </c>
-      <c r="K19" s="84">
-        <v>8088</v>
-      </c>
-      <c r="L19" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdsvadm-lb-pb8088</v>
-      </c>
-      <c r="M19" s="84">
-        <v>8088</v>
-      </c>
-      <c r="N19" s="84">
-        <v>4</v>
-      </c>
-      <c r="O19" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P19" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="86" t="s">
         <v>185</v>
       </c>
@@ -7935,38 +8015,42 @@
         <v>365</v>
       </c>
       <c r="E20" s="86"/>
-      <c r="F20" s="86" t="str">
-        <f t="shared" si="2"/>
+      <c r="F20" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-cdstap-lb-rule</v>
+      </c>
+      <c r="G20" s="86" t="str">
+        <f t="shared" si="3"/>
         <v>t-dtg-cdstap-lb-fe</v>
       </c>
-      <c r="G20" s="86" t="s">
+      <c r="H20" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86" t="b">
+      <c r="I20" s="86"/>
+      <c r="J20" s="86" t="b">
         <v>0</v>
       </c>
-      <c r="J20" s="86" t="str">
-        <f t="shared" si="3"/>
+      <c r="K20" s="86" t="str">
+        <f t="shared" si="4"/>
         <v>t-dtg-cdstap-lb-bp</v>
       </c>
-      <c r="K20" s="86"/>
       <c r="L20" s="86"/>
       <c r="M20" s="86"/>
-      <c r="N20" s="86">
+      <c r="N20" s="86"/>
+      <c r="O20" s="86">
         <v>4</v>
       </c>
-      <c r="O20" s="86" t="s">
+      <c r="P20" s="86" t="s">
         <v>125</v>
       </c>
-      <c r="P20" s="86" t="b">
-        <v>1</v>
-      </c>
       <c r="Q20" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" s="86" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="84" t="s">
         <v>185</v>
       </c>
@@ -7984,47 +8068,51 @@
         <f t="shared" si="0"/>
         <v>t-dtg-cdmlap-lb-rule9305</v>
       </c>
-      <c r="F21" s="84" t="str">
+      <c r="F21" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-cdmlap-lb-rule</v>
+      </c>
+      <c r="G21" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-cdmlap-lb-fe</v>
+      </c>
+      <c r="H21" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I21" s="84">
+        <v>9305</v>
+      </c>
+      <c r="J21" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-cdmlap-lb-bp</v>
+      </c>
+      <c r="L21" s="84">
+        <v>9305</v>
+      </c>
+      <c r="M21" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-cdmlap-lb-fe</v>
-      </c>
-      <c r="G21" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H21" s="84">
+        <v>t-dtg-cdmlap-lb-pb9305</v>
+      </c>
+      <c r="N21" s="84">
         <v>9305</v>
       </c>
-      <c r="I21" s="84" t="b">
+      <c r="O21" s="84">
+        <v>4</v>
+      </c>
+      <c r="P21" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q21" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J21" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-cdmlap-lb-bp</v>
-      </c>
-      <c r="K21" s="84">
-        <v>9305</v>
-      </c>
-      <c r="L21" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdmlap-lb-pb9305</v>
-      </c>
-      <c r="M21" s="84">
-        <v>9305</v>
-      </c>
-      <c r="N21" s="84">
-        <v>4</v>
-      </c>
-      <c r="O21" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P21" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="84" t="s">
         <v>185</v>
       </c>
@@ -8042,47 +8130,51 @@
         <f t="shared" si="0"/>
         <v>t-dtg-cdmlap-lb-rule9306</v>
       </c>
-      <c r="F22" s="84" t="str">
+      <c r="F22" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-cdmlap-lb-rule</v>
+      </c>
+      <c r="G22" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-cdmlap-lb-fe</v>
+      </c>
+      <c r="H22" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I22" s="84">
+        <v>9306</v>
+      </c>
+      <c r="J22" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-cdmlap-lb-bp</v>
+      </c>
+      <c r="L22" s="84">
+        <v>9306</v>
+      </c>
+      <c r="M22" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-cdmlap-lb-fe</v>
-      </c>
-      <c r="G22" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H22" s="84">
+        <v>t-dtg-cdmlap-lb-pb9306</v>
+      </c>
+      <c r="N22" s="84">
         <v>9306</v>
       </c>
-      <c r="I22" s="84" t="b">
+      <c r="O22" s="84">
+        <v>4</v>
+      </c>
+      <c r="P22" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q22" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J22" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-cdmlap-lb-bp</v>
-      </c>
-      <c r="K22" s="84">
-        <v>9306</v>
-      </c>
-      <c r="L22" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdmlap-lb-pb9306</v>
-      </c>
-      <c r="M22" s="84">
-        <v>9306</v>
-      </c>
-      <c r="N22" s="84">
-        <v>4</v>
-      </c>
-      <c r="O22" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P22" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
         <v>185</v>
       </c>
@@ -8101,46 +8193,50 @@
         <v>t-dtg-ap-lb-rule8080</v>
       </c>
       <c r="F23" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-ap-lb-rule</v>
+      </c>
+      <c r="G23" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-ap-lb-fe</v>
+      </c>
+      <c r="H23" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I23" s="74">
+        <v>8080</v>
+      </c>
+      <c r="J23" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-ap-lb-bp</v>
+      </c>
+      <c r="L23" s="74">
+        <v>8080</v>
+      </c>
+      <c r="M23" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-ap-lb-fe</v>
-      </c>
-      <c r="G23" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H23" s="74">
+        <v>t-dtg-ap-lb-pb8080</v>
+      </c>
+      <c r="N23" s="74">
         <v>8080</v>
       </c>
-      <c r="I23" s="74" t="b">
+      <c r="O23" s="74">
+        <v>4</v>
+      </c>
+      <c r="P23" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q23" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J23" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-ap-lb-bp</v>
-      </c>
-      <c r="K23" s="74">
-        <v>8080</v>
-      </c>
-      <c r="L23" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-ap-lb-pb8080</v>
-      </c>
-      <c r="M23" s="74">
-        <v>8080</v>
-      </c>
-      <c r="N23" s="74">
-        <v>4</v>
-      </c>
-      <c r="O23" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P23" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
         <v>185</v>
       </c>
@@ -8159,46 +8255,50 @@
         <v>t-dtg-ap-lb-rule9087</v>
       </c>
       <c r="F24" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-ap-lb-rule</v>
+      </c>
+      <c r="G24" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-ap-lb-fe</v>
+      </c>
+      <c r="H24" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I24" s="74">
+        <v>9087</v>
+      </c>
+      <c r="J24" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-ap-lb-bp</v>
+      </c>
+      <c r="L24" s="74">
+        <v>9087</v>
+      </c>
+      <c r="M24" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-ap-lb-fe</v>
-      </c>
-      <c r="G24" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H24" s="74">
+        <v>t-dtg-ap-lb-pb9087</v>
+      </c>
+      <c r="N24" s="74">
         <v>9087</v>
       </c>
-      <c r="I24" s="74" t="b">
+      <c r="O24" s="74">
+        <v>4</v>
+      </c>
+      <c r="P24" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q24" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J24" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-ap-lb-bp</v>
-      </c>
-      <c r="K24" s="74">
-        <v>9087</v>
-      </c>
-      <c r="L24" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-ap-lb-pb9087</v>
-      </c>
-      <c r="M24" s="74">
-        <v>9087</v>
-      </c>
-      <c r="N24" s="74">
-        <v>4</v>
-      </c>
-      <c r="O24" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P24" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="84" t="s">
         <v>185</v>
       </c>
@@ -8216,47 +8316,51 @@
         <f t="shared" si="0"/>
         <v>t-dtg-admweb-lb-rule8088</v>
       </c>
-      <c r="F25" s="84" t="str">
+      <c r="F25" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-admweb-lb-rule</v>
+      </c>
+      <c r="G25" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-admweb-lb-fe</v>
+      </c>
+      <c r="H25" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I25" s="84">
+        <v>8088</v>
+      </c>
+      <c r="J25" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-admweb-lb-bp</v>
+      </c>
+      <c r="L25" s="84">
+        <v>8088</v>
+      </c>
+      <c r="M25" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-admweb-lb-fe</v>
-      </c>
-      <c r="G25" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H25" s="84">
+        <v>t-dtg-admweb-lb-pb8088</v>
+      </c>
+      <c r="N25" s="84">
         <v>8088</v>
       </c>
-      <c r="I25" s="84" t="b">
+      <c r="O25" s="84">
+        <v>4</v>
+      </c>
+      <c r="P25" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q25" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J25" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-admweb-lb-bp</v>
-      </c>
-      <c r="K25" s="84">
-        <v>8088</v>
-      </c>
-      <c r="L25" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-admweb-lb-pb8088</v>
-      </c>
-      <c r="M25" s="84">
-        <v>8088</v>
-      </c>
-      <c r="N25" s="84">
-        <v>4</v>
-      </c>
-      <c r="O25" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P25" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="74" t="s">
         <v>185</v>
       </c>
@@ -8275,46 +8379,50 @@
         <v>t-dtg-admap-lb-rule8085</v>
       </c>
       <c r="F26" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-admap-lb-rule</v>
+      </c>
+      <c r="G26" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-admap-lb-fe</v>
+      </c>
+      <c r="H26" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I26" s="74">
+        <v>8085</v>
+      </c>
+      <c r="J26" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-admap-lb-bp</v>
+      </c>
+      <c r="L26" s="74">
+        <v>8085</v>
+      </c>
+      <c r="M26" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-admap-lb-fe</v>
-      </c>
-      <c r="G26" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H26" s="74">
+        <v>t-dtg-admap-lb-pb8085</v>
+      </c>
+      <c r="N26" s="74">
         <v>8085</v>
       </c>
-      <c r="I26" s="74" t="b">
+      <c r="O26" s="74">
+        <v>4</v>
+      </c>
+      <c r="P26" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q26" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J26" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-admap-lb-bp</v>
-      </c>
-      <c r="K26" s="74">
-        <v>8085</v>
-      </c>
-      <c r="L26" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-admap-lb-pb8085</v>
-      </c>
-      <c r="M26" s="74">
-        <v>8085</v>
-      </c>
-      <c r="N26" s="74">
-        <v>4</v>
-      </c>
-      <c r="O26" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P26" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="74" t="s">
         <v>185</v>
       </c>
@@ -8333,46 +8441,50 @@
         <v>t-dtg-admap-lb-rule8087</v>
       </c>
       <c r="F27" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dtg-admap-lb-rule</v>
+      </c>
+      <c r="G27" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-admap-lb-fe</v>
+      </c>
+      <c r="H27" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I27" s="74">
+        <v>8087</v>
+      </c>
+      <c r="J27" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-admap-lb-bp</v>
+      </c>
+      <c r="L27" s="74">
+        <v>8087</v>
+      </c>
+      <c r="M27" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-admap-lb-fe</v>
-      </c>
-      <c r="G27" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H27" s="74">
+        <v>t-dtg-admap-lb-pb8087</v>
+      </c>
+      <c r="N27" s="74">
         <v>8087</v>
       </c>
-      <c r="I27" s="74" t="b">
+      <c r="O27" s="74">
+        <v>4</v>
+      </c>
+      <c r="P27" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q27" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J27" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dtg-admap-lb-bp</v>
-      </c>
-      <c r="K27" s="74">
-        <v>8087</v>
-      </c>
-      <c r="L27" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-admap-lb-pb8087</v>
-      </c>
-      <c r="M27" s="74">
-        <v>8087</v>
-      </c>
-      <c r="N27" s="74">
-        <v>4</v>
-      </c>
-      <c r="O27" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P27" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q27" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="84" t="s">
         <v>185</v>
       </c>
@@ -8387,38 +8499,42 @@
         <v>385</v>
       </c>
       <c r="E28" s="84"/>
-      <c r="F28" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="F28" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-doip-web-lb-rule</v>
+      </c>
+      <c r="G28" s="84" t="str">
+        <f t="shared" si="3"/>
         <v>t-doip-web-lb-fe</v>
       </c>
-      <c r="G28" s="84" t="s">
+      <c r="H28" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H28" s="84"/>
-      <c r="I28" s="84" t="b">
+      <c r="I28" s="84"/>
+      <c r="J28" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J28" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="K28" s="84" t="str">
+        <f t="shared" si="4"/>
         <v>t-doip-web-lb-bp</v>
       </c>
-      <c r="K28" s="84"/>
       <c r="L28" s="84"/>
       <c r="M28" s="84"/>
-      <c r="N28" s="84">
+      <c r="N28" s="84"/>
+      <c r="O28" s="84">
         <v>4</v>
       </c>
-      <c r="O28" s="84" t="s">
+      <c r="P28" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P28" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q28" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="86" t="s">
         <v>185</v>
       </c>
@@ -8433,38 +8549,42 @@
         <v>386</v>
       </c>
       <c r="E29" s="86"/>
-      <c r="F29" s="86" t="str">
-        <f t="shared" si="2"/>
+      <c r="F29" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-doip-ap-lb-rule</v>
+      </c>
+      <c r="G29" s="86" t="str">
+        <f t="shared" si="3"/>
         <v>t-doip-ap-lb-fe</v>
       </c>
-      <c r="G29" s="86" t="s">
+      <c r="H29" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="H29" s="86"/>
-      <c r="I29" s="86" t="b">
+      <c r="I29" s="86"/>
+      <c r="J29" s="86" t="b">
         <v>0</v>
       </c>
-      <c r="J29" s="86" t="str">
-        <f t="shared" si="3"/>
+      <c r="K29" s="86" t="str">
+        <f t="shared" si="4"/>
         <v>t-doip-ap-lb-bp</v>
       </c>
-      <c r="K29" s="86"/>
       <c r="L29" s="86"/>
       <c r="M29" s="86"/>
-      <c r="N29" s="86">
+      <c r="N29" s="86"/>
+      <c r="O29" s="86">
         <v>4</v>
       </c>
-      <c r="O29" s="86" t="s">
+      <c r="P29" s="86" t="s">
         <v>125</v>
       </c>
-      <c r="P29" s="86" t="b">
-        <v>1</v>
-      </c>
       <c r="Q29" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" s="86" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="84" t="s">
         <v>185</v>
       </c>
@@ -8479,38 +8599,42 @@
         <v>387</v>
       </c>
       <c r="E30" s="84"/>
-      <c r="F30" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="F30" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-doip-adm-lb-rule</v>
+      </c>
+      <c r="G30" s="84" t="str">
+        <f t="shared" si="3"/>
         <v>t-doip-adm-lb-fe</v>
       </c>
-      <c r="G30" s="84" t="s">
+      <c r="H30" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H30" s="84"/>
-      <c r="I30" s="84" t="b">
+      <c r="I30" s="84"/>
+      <c r="J30" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J30" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="K30" s="84" t="str">
+        <f t="shared" si="4"/>
         <v>t-doip-adm-lb-bp</v>
       </c>
-      <c r="K30" s="84"/>
       <c r="L30" s="84"/>
       <c r="M30" s="84"/>
-      <c r="N30" s="84">
+      <c r="N30" s="84"/>
+      <c r="O30" s="84">
         <v>4</v>
       </c>
-      <c r="O30" s="84" t="s">
+      <c r="P30" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P30" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q30" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="74" t="s">
         <v>185</v>
       </c>
@@ -8529,46 +8653,50 @@
         <v>t-dis-web-lb-rule80</v>
       </c>
       <c r="F31" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-web-lb-rule</v>
+      </c>
+      <c r="G31" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-web-lb-fe</v>
+      </c>
+      <c r="H31" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I31" s="74">
+        <v>80</v>
+      </c>
+      <c r="J31" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-web-lb-bp</v>
+      </c>
+      <c r="L31" s="74">
+        <v>80</v>
+      </c>
+      <c r="M31" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-web-lb-fe</v>
-      </c>
-      <c r="G31" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H31" s="74">
+        <v>t-dis-web-lb-pb80</v>
+      </c>
+      <c r="N31" s="74">
         <v>80</v>
       </c>
-      <c r="I31" s="74" t="b">
+      <c r="O31" s="74">
+        <v>4</v>
+      </c>
+      <c r="P31" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q31" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J31" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-web-lb-bp</v>
-      </c>
-      <c r="K31" s="74">
-        <v>80</v>
-      </c>
-      <c r="L31" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-web-lb-pb80</v>
-      </c>
-      <c r="M31" s="74">
-        <v>80</v>
-      </c>
-      <c r="N31" s="74">
-        <v>4</v>
-      </c>
-      <c r="O31" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P31" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="74" t="s">
         <v>185</v>
       </c>
@@ -8587,46 +8715,50 @@
         <v>t-dis-web-lb-rule443</v>
       </c>
       <c r="F32" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-web-lb-rule</v>
+      </c>
+      <c r="G32" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-web-lb-fe</v>
+      </c>
+      <c r="H32" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I32" s="74">
+        <v>443</v>
+      </c>
+      <c r="J32" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-web-lb-bp</v>
+      </c>
+      <c r="L32" s="74">
+        <v>443</v>
+      </c>
+      <c r="M32" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-web-lb-fe</v>
-      </c>
-      <c r="G32" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H32" s="74">
+        <v>t-dis-web-lb-pb443</v>
+      </c>
+      <c r="N32" s="74">
         <v>443</v>
       </c>
-      <c r="I32" s="74" t="b">
+      <c r="O32" s="74">
+        <v>4</v>
+      </c>
+      <c r="P32" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q32" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J32" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-web-lb-bp</v>
-      </c>
-      <c r="K32" s="74">
-        <v>443</v>
-      </c>
-      <c r="L32" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-web-lb-pb443</v>
-      </c>
-      <c r="M32" s="74">
-        <v>443</v>
-      </c>
-      <c r="N32" s="74">
-        <v>4</v>
-      </c>
-      <c r="O32" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P32" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="84" t="s">
         <v>185</v>
       </c>
@@ -8644,47 +8776,51 @@
         <f t="shared" si="0"/>
         <v>t-dis-walkweb-lb-rule443</v>
       </c>
-      <c r="F33" s="84" t="str">
+      <c r="F33" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-walkweb-lb-rule</v>
+      </c>
+      <c r="G33" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-walkweb-lb-fe</v>
+      </c>
+      <c r="H33" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I33" s="84">
+        <v>443</v>
+      </c>
+      <c r="J33" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-walkweb-lb-bp</v>
+      </c>
+      <c r="L33" s="84">
+        <v>443</v>
+      </c>
+      <c r="M33" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-walkweb-lb-fe</v>
-      </c>
-      <c r="G33" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H33" s="84">
+        <v>t-dis-walkweb-lb-pb443</v>
+      </c>
+      <c r="N33" s="84">
         <v>443</v>
       </c>
-      <c r="I33" s="84" t="b">
+      <c r="O33" s="84">
+        <v>4</v>
+      </c>
+      <c r="P33" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q33" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J33" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-walkweb-lb-bp</v>
-      </c>
-      <c r="K33" s="84">
-        <v>443</v>
-      </c>
-      <c r="L33" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-walkweb-lb-pb443</v>
-      </c>
-      <c r="M33" s="84">
-        <v>443</v>
-      </c>
-      <c r="N33" s="84">
-        <v>4</v>
-      </c>
-      <c r="O33" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P33" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q33" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="74" t="s">
         <v>185</v>
       </c>
@@ -8703,46 +8839,50 @@
         <v>t-dis-walkap-lb-rule8080</v>
       </c>
       <c r="F34" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-walkap-lb-rule</v>
+      </c>
+      <c r="G34" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-walkap-lb-fe</v>
+      </c>
+      <c r="H34" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I34" s="74">
+        <v>8080</v>
+      </c>
+      <c r="J34" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-walkap-lb-bp</v>
+      </c>
+      <c r="L34" s="74">
+        <v>8080</v>
+      </c>
+      <c r="M34" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-walkap-lb-fe</v>
-      </c>
-      <c r="G34" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H34" s="74">
+        <v>t-dis-walkap-lb-pb8080</v>
+      </c>
+      <c r="N34" s="74">
         <v>8080</v>
       </c>
-      <c r="I34" s="74" t="b">
+      <c r="O34" s="74">
+        <v>4</v>
+      </c>
+      <c r="P34" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q34" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J34" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-walkap-lb-bp</v>
-      </c>
-      <c r="K34" s="74">
-        <v>8080</v>
-      </c>
-      <c r="L34" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-walkap-lb-pb8080</v>
-      </c>
-      <c r="M34" s="74">
-        <v>8080</v>
-      </c>
-      <c r="N34" s="74">
-        <v>4</v>
-      </c>
-      <c r="O34" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P34" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="84" t="s">
         <v>185</v>
       </c>
@@ -8760,47 +8900,51 @@
         <f t="shared" si="0"/>
         <v>t-dis-drvmsgap-lb-rule8080</v>
       </c>
-      <c r="F35" s="84" t="str">
+      <c r="F35" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-drvmsgap-lb-rule</v>
+      </c>
+      <c r="G35" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-drvmsgap-lb-fe</v>
+      </c>
+      <c r="H35" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I35" s="84">
+        <v>8080</v>
+      </c>
+      <c r="J35" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-drvmsgap-lb-bp</v>
+      </c>
+      <c r="L35" s="84">
+        <v>8080</v>
+      </c>
+      <c r="M35" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-drvmsgap-lb-fe</v>
-      </c>
-      <c r="G35" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H35" s="84">
+        <v>t-dis-drvmsgap-lb-pb8080</v>
+      </c>
+      <c r="N35" s="84">
         <v>8080</v>
       </c>
-      <c r="I35" s="84" t="b">
+      <c r="O35" s="84">
+        <v>4</v>
+      </c>
+      <c r="P35" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q35" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J35" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-drvmsgap-lb-bp</v>
-      </c>
-      <c r="K35" s="84">
-        <v>8080</v>
-      </c>
-      <c r="L35" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-drvmsgap-lb-pb8080</v>
-      </c>
-      <c r="M35" s="84">
-        <v>8080</v>
-      </c>
-      <c r="N35" s="84">
-        <v>4</v>
-      </c>
-      <c r="O35" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P35" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q35" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="74" t="s">
         <v>185</v>
       </c>
@@ -8819,46 +8963,50 @@
         <v>t-dis-drvcltap-lb-rule8081</v>
       </c>
       <c r="F36" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-drvcltap-lb-rule</v>
+      </c>
+      <c r="G36" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-drvcltap-lb-fe</v>
+      </c>
+      <c r="H36" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I36" s="74">
+        <v>8081</v>
+      </c>
+      <c r="J36" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-drvcltap-lb-bp</v>
+      </c>
+      <c r="L36" s="74">
+        <v>8081</v>
+      </c>
+      <c r="M36" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-drvcltap-lb-fe</v>
-      </c>
-      <c r="G36" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H36" s="74">
+        <v>t-dis-drvcltap-lb-pb8081</v>
+      </c>
+      <c r="N36" s="74">
         <v>8081</v>
       </c>
-      <c r="I36" s="74" t="b">
+      <c r="O36" s="74">
+        <v>4</v>
+      </c>
+      <c r="P36" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q36" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J36" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-drvcltap-lb-bp</v>
-      </c>
-      <c r="K36" s="74">
-        <v>8081</v>
-      </c>
-      <c r="L36" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-drvcltap-lb-pb8081</v>
-      </c>
-      <c r="M36" s="74">
-        <v>8081</v>
-      </c>
-      <c r="N36" s="74">
-        <v>4</v>
-      </c>
-      <c r="O36" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P36" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="84" t="s">
         <v>185</v>
       </c>
@@ -8876,47 +9024,51 @@
         <f t="shared" si="0"/>
         <v>t-dis-cmsweb-lb-rule80</v>
       </c>
-      <c r="F37" s="84" t="str">
+      <c r="F37" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-cmsweb-lb-rule</v>
+      </c>
+      <c r="G37" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-cmsweb-lb-fe</v>
+      </c>
+      <c r="H37" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I37" s="84">
+        <v>80</v>
+      </c>
+      <c r="J37" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-cmsweb-lb-bp</v>
+      </c>
+      <c r="L37" s="84">
+        <v>80</v>
+      </c>
+      <c r="M37" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-cmsweb-lb-fe</v>
-      </c>
-      <c r="G37" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H37" s="84">
+        <v>t-dis-cmsweb-lb-pb80</v>
+      </c>
+      <c r="N37" s="84">
         <v>80</v>
       </c>
-      <c r="I37" s="84" t="b">
+      <c r="O37" s="84">
+        <v>4</v>
+      </c>
+      <c r="P37" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q37" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J37" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-cmsweb-lb-bp</v>
-      </c>
-      <c r="K37" s="84">
-        <v>80</v>
-      </c>
-      <c r="L37" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-cmsweb-lb-pb80</v>
-      </c>
-      <c r="M37" s="84">
-        <v>80</v>
-      </c>
-      <c r="N37" s="84">
-        <v>4</v>
-      </c>
-      <c r="O37" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P37" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q37" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="74" t="s">
         <v>185</v>
       </c>
@@ -8935,46 +9087,50 @@
         <v>t-dis-cmsweb-lb-rule443</v>
       </c>
       <c r="F38" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-cmsweb-lb-rule</v>
+      </c>
+      <c r="G38" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-cmsweb-lb-fe</v>
+      </c>
+      <c r="H38" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I38" s="74">
+        <v>443</v>
+      </c>
+      <c r="J38" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-cmsweb-lb-bp</v>
+      </c>
+      <c r="L38" s="74">
+        <v>443</v>
+      </c>
+      <c r="M38" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-cmsweb-lb-fe</v>
-      </c>
-      <c r="G38" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H38" s="74">
+        <v>t-dis-cmsweb-lb-pb443</v>
+      </c>
+      <c r="N38" s="74">
         <v>443</v>
       </c>
-      <c r="I38" s="74" t="b">
+      <c r="O38" s="74">
+        <v>4</v>
+      </c>
+      <c r="P38" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q38" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J38" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-cmsweb-lb-bp</v>
-      </c>
-      <c r="K38" s="74">
-        <v>443</v>
-      </c>
-      <c r="L38" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-cmsweb-lb-pb443</v>
-      </c>
-      <c r="M38" s="74">
-        <v>443</v>
-      </c>
-      <c r="N38" s="74">
-        <v>4</v>
-      </c>
-      <c r="O38" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P38" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q38" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="84" t="s">
         <v>185</v>
       </c>
@@ -8992,47 +9148,51 @@
         <f t="shared" si="0"/>
         <v>t-dis-cmsap-lb-rule4001</v>
       </c>
-      <c r="F39" s="84" t="str">
+      <c r="F39" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-cmsap-lb-rule</v>
+      </c>
+      <c r="G39" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-cmsap-lb-fe</v>
+      </c>
+      <c r="H39" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I39" s="84">
+        <v>4001</v>
+      </c>
+      <c r="J39" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-cmsap-lb-bp</v>
+      </c>
+      <c r="L39" s="84">
+        <v>4001</v>
+      </c>
+      <c r="M39" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-cmsap-lb-fe</v>
-      </c>
-      <c r="G39" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H39" s="84">
+        <v>t-dis-cmsap-lb-pb4001</v>
+      </c>
+      <c r="N39" s="84">
         <v>4001</v>
       </c>
-      <c r="I39" s="84" t="b">
+      <c r="O39" s="84">
+        <v>4</v>
+      </c>
+      <c r="P39" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q39" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J39" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-cmsap-lb-bp</v>
-      </c>
-      <c r="K39" s="84">
-        <v>4001</v>
-      </c>
-      <c r="L39" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-cmsap-lb-pb4001</v>
-      </c>
-      <c r="M39" s="84">
-        <v>4001</v>
-      </c>
-      <c r="N39" s="84">
-        <v>4</v>
-      </c>
-      <c r="O39" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P39" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q39" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="74" t="s">
         <v>185</v>
       </c>
@@ -9051,46 +9211,50 @@
         <v>t-dis-cmsadm-lb-rule443</v>
       </c>
       <c r="F40" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-cmsadm-lb-rule</v>
+      </c>
+      <c r="G40" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-cmsadm-lb-fe</v>
+      </c>
+      <c r="H40" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I40" s="74">
+        <v>443</v>
+      </c>
+      <c r="J40" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-cmsadm-lb-bp</v>
+      </c>
+      <c r="L40" s="74">
+        <v>443</v>
+      </c>
+      <c r="M40" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-cmsadm-lb-fe</v>
-      </c>
-      <c r="G40" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H40" s="74">
+        <v>t-dis-cmsadm-lb-pb443</v>
+      </c>
+      <c r="N40" s="74">
         <v>443</v>
       </c>
-      <c r="I40" s="74" t="b">
+      <c r="O40" s="74">
+        <v>4</v>
+      </c>
+      <c r="P40" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q40" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J40" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-cmsadm-lb-bp</v>
-      </c>
-      <c r="K40" s="74">
-        <v>443</v>
-      </c>
-      <c r="L40" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-cmsadm-lb-pb443</v>
-      </c>
-      <c r="M40" s="74">
-        <v>443</v>
-      </c>
-      <c r="N40" s="74">
-        <v>4</v>
-      </c>
-      <c r="O40" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P40" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q40" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="84" t="s">
         <v>185</v>
       </c>
@@ -9108,47 +9272,51 @@
         <f t="shared" si="0"/>
         <v>t-dis-cmbsap-lb-rule8080</v>
       </c>
-      <c r="F41" s="84" t="str">
+      <c r="F41" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-cmbsap-lb-rule</v>
+      </c>
+      <c r="G41" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-cmbsap-lb-fe</v>
+      </c>
+      <c r="H41" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I41" s="84">
+        <v>8080</v>
+      </c>
+      <c r="J41" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-cmbsap-lb-bp</v>
+      </c>
+      <c r="L41" s="84">
+        <v>8080</v>
+      </c>
+      <c r="M41" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-cmbsap-lb-fe</v>
-      </c>
-      <c r="G41" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H41" s="84">
+        <v>t-dis-cmbsap-lb-pb8080</v>
+      </c>
+      <c r="N41" s="84">
         <v>8080</v>
       </c>
-      <c r="I41" s="84" t="b">
+      <c r="O41" s="84">
+        <v>4</v>
+      </c>
+      <c r="P41" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q41" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J41" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-cmbsap-lb-bp</v>
-      </c>
-      <c r="K41" s="84">
-        <v>8080</v>
-      </c>
-      <c r="L41" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-cmbsap-lb-pb8080</v>
-      </c>
-      <c r="M41" s="84">
-        <v>8080</v>
-      </c>
-      <c r="N41" s="84">
-        <v>4</v>
-      </c>
-      <c r="O41" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P41" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q41" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="74" t="s">
         <v>185</v>
       </c>
@@ -9167,46 +9335,50 @@
         <v>t-dis-bbiweb-lb-rule443</v>
       </c>
       <c r="F42" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-bbiweb-lb-rule</v>
+      </c>
+      <c r="G42" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-bbiweb-lb-fe</v>
+      </c>
+      <c r="H42" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I42" s="74">
+        <v>443</v>
+      </c>
+      <c r="J42" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-bbiweb-lb-bp</v>
+      </c>
+      <c r="L42" s="74">
+        <v>443</v>
+      </c>
+      <c r="M42" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-bbiweb-lb-fe</v>
-      </c>
-      <c r="G42" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H42" s="74">
+        <v>t-dis-bbiweb-lb-pb443</v>
+      </c>
+      <c r="N42" s="74">
         <v>443</v>
       </c>
-      <c r="I42" s="74" t="b">
+      <c r="O42" s="74">
+        <v>4</v>
+      </c>
+      <c r="P42" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q42" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R42" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J42" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-bbiweb-lb-bp</v>
-      </c>
-      <c r="K42" s="74">
-        <v>443</v>
-      </c>
-      <c r="L42" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-bbiweb-lb-pb443</v>
-      </c>
-      <c r="M42" s="74">
-        <v>443</v>
-      </c>
-      <c r="N42" s="74">
-        <v>4</v>
-      </c>
-      <c r="O42" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P42" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q42" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="84" t="s">
         <v>185</v>
       </c>
@@ -9224,47 +9396,51 @@
         <f t="shared" si="0"/>
         <v>t-dis-bbimsgap-lb-rule20030</v>
       </c>
-      <c r="F43" s="84" t="str">
+      <c r="F43" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-bbimsgap-lb-rule</v>
+      </c>
+      <c r="G43" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-bbimsgap-lb-fe</v>
+      </c>
+      <c r="H43" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I43" s="84">
+        <v>20030</v>
+      </c>
+      <c r="J43" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-bbimsgap-lb-bp</v>
+      </c>
+      <c r="L43" s="84">
+        <v>20030</v>
+      </c>
+      <c r="M43" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-bbimsgap-lb-fe</v>
-      </c>
-      <c r="G43" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H43" s="84">
+        <v>t-dis-bbimsgap-lb-pb20030</v>
+      </c>
+      <c r="N43" s="84">
         <v>20030</v>
       </c>
-      <c r="I43" s="84" t="b">
+      <c r="O43" s="84">
+        <v>4</v>
+      </c>
+      <c r="P43" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q43" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R43" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J43" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-bbimsgap-lb-bp</v>
-      </c>
-      <c r="K43" s="84">
-        <v>20030</v>
-      </c>
-      <c r="L43" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-bbimsgap-lb-pb20030</v>
-      </c>
-      <c r="M43" s="84">
-        <v>20030</v>
-      </c>
-      <c r="N43" s="84">
-        <v>4</v>
-      </c>
-      <c r="O43" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P43" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q43" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="74" t="s">
         <v>185</v>
       </c>
@@ -9283,46 +9459,50 @@
         <v>t-dis-bbicltap-lb-rule20000</v>
       </c>
       <c r="F44" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-bbicltap-lb-rule</v>
+      </c>
+      <c r="G44" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-bbicltap-lb-fe</v>
+      </c>
+      <c r="H44" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I44" s="74">
+        <v>20000</v>
+      </c>
+      <c r="J44" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-bbicltap-lb-bp</v>
+      </c>
+      <c r="L44" s="74">
+        <v>20000</v>
+      </c>
+      <c r="M44" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-bbicltap-lb-fe</v>
-      </c>
-      <c r="G44" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H44" s="74">
+        <v>t-dis-bbicltap-lb-pb20000</v>
+      </c>
+      <c r="N44" s="74">
         <v>20000</v>
       </c>
-      <c r="I44" s="74" t="b">
+      <c r="O44" s="74">
+        <v>4</v>
+      </c>
+      <c r="P44" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q44" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R44" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J44" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-bbicltap-lb-bp</v>
-      </c>
-      <c r="K44" s="74">
-        <v>20000</v>
-      </c>
-      <c r="L44" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-bbicltap-lb-pb20000</v>
-      </c>
-      <c r="M44" s="74">
-        <v>20000</v>
-      </c>
-      <c r="N44" s="74">
-        <v>4</v>
-      </c>
-      <c r="O44" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P44" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q44" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="74" t="s">
         <v>185</v>
       </c>
@@ -9341,46 +9521,50 @@
         <v>t-dis-bbicltap-lb-rule21000</v>
       </c>
       <c r="F45" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-bbicltap-lb-rule</v>
+      </c>
+      <c r="G45" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-bbicltap-lb-fe</v>
+      </c>
+      <c r="H45" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I45" s="74">
+        <v>21000</v>
+      </c>
+      <c r="J45" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-bbicltap-lb-bp</v>
+      </c>
+      <c r="L45" s="74">
+        <v>21000</v>
+      </c>
+      <c r="M45" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-bbicltap-lb-fe</v>
-      </c>
-      <c r="G45" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H45" s="74">
+        <v>t-dis-bbicltap-lb-pb21000</v>
+      </c>
+      <c r="N45" s="74">
         <v>21000</v>
       </c>
-      <c r="I45" s="74" t="b">
+      <c r="O45" s="74">
+        <v>4</v>
+      </c>
+      <c r="P45" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q45" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R45" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J45" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-bbicltap-lb-bp</v>
-      </c>
-      <c r="K45" s="74">
-        <v>21000</v>
-      </c>
-      <c r="L45" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-bbicltap-lb-pb21000</v>
-      </c>
-      <c r="M45" s="74">
-        <v>21000</v>
-      </c>
-      <c r="N45" s="74">
-        <v>4</v>
-      </c>
-      <c r="O45" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P45" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q45" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="74" t="s">
         <v>185</v>
       </c>
@@ -9399,46 +9583,50 @@
         <v>t-dis-bbicltap-lb-rule22000</v>
       </c>
       <c r="F46" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-bbicltap-lb-rule</v>
+      </c>
+      <c r="G46" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-bbicltap-lb-fe</v>
+      </c>
+      <c r="H46" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I46" s="74">
+        <v>22000</v>
+      </c>
+      <c r="J46" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-bbicltap-lb-bp</v>
+      </c>
+      <c r="L46" s="74">
+        <v>22000</v>
+      </c>
+      <c r="M46" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-bbicltap-lb-fe</v>
-      </c>
-      <c r="G46" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H46" s="74">
+        <v>t-dis-bbicltap-lb-pb22000</v>
+      </c>
+      <c r="N46" s="74">
         <v>22000</v>
       </c>
-      <c r="I46" s="74" t="b">
+      <c r="O46" s="74">
+        <v>4</v>
+      </c>
+      <c r="P46" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q46" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R46" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J46" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-bbicltap-lb-bp</v>
-      </c>
-      <c r="K46" s="74">
-        <v>22000</v>
-      </c>
-      <c r="L46" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-bbicltap-lb-pb22000</v>
-      </c>
-      <c r="M46" s="74">
-        <v>22000</v>
-      </c>
-      <c r="N46" s="74">
-        <v>4</v>
-      </c>
-      <c r="O46" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P46" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q46" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" s="84" t="s">
         <v>185</v>
       </c>
@@ -9456,47 +9644,51 @@
         <f t="shared" si="0"/>
         <v>t-dis-ap-lb-rule8080</v>
       </c>
-      <c r="F47" s="84" t="str">
+      <c r="F47" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-ap-lb-rule</v>
+      </c>
+      <c r="G47" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-ap-lb-fe</v>
+      </c>
+      <c r="H47" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I47" s="84">
+        <v>8080</v>
+      </c>
+      <c r="J47" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-ap-lb-bp</v>
+      </c>
+      <c r="L47" s="84">
+        <v>8080</v>
+      </c>
+      <c r="M47" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-ap-lb-fe</v>
-      </c>
-      <c r="G47" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H47" s="84">
+        <v>t-dis-ap-lb-pb8080</v>
+      </c>
+      <c r="N47" s="84">
         <v>8080</v>
       </c>
-      <c r="I47" s="84" t="b">
+      <c r="O47" s="84">
+        <v>4</v>
+      </c>
+      <c r="P47" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q47" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R47" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J47" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-ap-lb-bp</v>
-      </c>
-      <c r="K47" s="84">
-        <v>8080</v>
-      </c>
-      <c r="L47" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-ap-lb-pb8080</v>
-      </c>
-      <c r="M47" s="84">
-        <v>8080</v>
-      </c>
-      <c r="N47" s="84">
-        <v>4</v>
-      </c>
-      <c r="O47" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P47" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q47" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" s="74" t="s">
         <v>185</v>
       </c>
@@ -9515,46 +9707,50 @@
         <v>t-dis-adm-lb-rule443</v>
       </c>
       <c r="F48" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dis-adm-lb-rule</v>
+      </c>
+      <c r="G48" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dis-adm-lb-fe</v>
+      </c>
+      <c r="H48" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I48" s="74">
+        <v>443</v>
+      </c>
+      <c r="J48" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dis-adm-lb-bp</v>
+      </c>
+      <c r="L48" s="74">
+        <v>443</v>
+      </c>
+      <c r="M48" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-adm-lb-fe</v>
-      </c>
-      <c r="G48" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H48" s="74">
+        <v>t-dis-adm-lb-pb443</v>
+      </c>
+      <c r="N48" s="74">
         <v>443</v>
       </c>
-      <c r="I48" s="74" t="b">
+      <c r="O48" s="74">
+        <v>4</v>
+      </c>
+      <c r="P48" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q48" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R48" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J48" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dis-adm-lb-bp</v>
-      </c>
-      <c r="K48" s="74">
-        <v>443</v>
-      </c>
-      <c r="L48" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-adm-lb-pb443</v>
-      </c>
-      <c r="M48" s="74">
-        <v>443</v>
-      </c>
-      <c r="N48" s="74">
-        <v>4</v>
-      </c>
-      <c r="O48" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P48" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q48" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="84" t="s">
         <v>185</v>
       </c>
@@ -9572,47 +9768,51 @@
         <f t="shared" si="0"/>
         <v>t-dip-web-lb-rule443</v>
       </c>
-      <c r="F49" s="84" t="str">
+      <c r="F49" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dip-web-lb-rule</v>
+      </c>
+      <c r="G49" s="84" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dip-web-lb-fe</v>
+      </c>
+      <c r="H49" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I49" s="84">
+        <v>443</v>
+      </c>
+      <c r="J49" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" s="84" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dip-web-lb-bp</v>
+      </c>
+      <c r="L49" s="84">
+        <v>443</v>
+      </c>
+      <c r="M49" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>t-dip-web-lb-fe</v>
-      </c>
-      <c r="G49" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H49" s="84">
+        <v>t-dip-web-lb-pb443</v>
+      </c>
+      <c r="N49" s="84">
         <v>443</v>
       </c>
-      <c r="I49" s="84" t="b">
+      <c r="O49" s="84">
+        <v>4</v>
+      </c>
+      <c r="P49" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q49" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R49" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J49" s="84" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dip-web-lb-bp</v>
-      </c>
-      <c r="K49" s="84">
-        <v>443</v>
-      </c>
-      <c r="L49" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-web-lb-pb443</v>
-      </c>
-      <c r="M49" s="84">
-        <v>443</v>
-      </c>
-      <c r="N49" s="84">
-        <v>4</v>
-      </c>
-      <c r="O49" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P49" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q49" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="74" t="s">
         <v>185</v>
       </c>
@@ -9631,46 +9831,50 @@
         <v>t-dip-web-lb-rule9100</v>
       </c>
       <c r="F50" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dip-web-lb-rule</v>
+      </c>
+      <c r="G50" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dip-web-lb-fe</v>
+      </c>
+      <c r="H50" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I50" s="74">
+        <v>9100</v>
+      </c>
+      <c r="J50" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dip-web-lb-bp</v>
+      </c>
+      <c r="L50" s="74">
+        <v>9100</v>
+      </c>
+      <c r="M50" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dip-web-lb-fe</v>
-      </c>
-      <c r="G50" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H50" s="74">
+        <v>t-dip-web-lb-pb9100</v>
+      </c>
+      <c r="N50" s="74">
         <v>9100</v>
       </c>
-      <c r="I50" s="74" t="b">
+      <c r="O50" s="74">
+        <v>4</v>
+      </c>
+      <c r="P50" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q50" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R50" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J50" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-dip-web-lb-bp</v>
-      </c>
-      <c r="K50" s="74">
-        <v>9100</v>
-      </c>
-      <c r="L50" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-web-lb-pb9100</v>
-      </c>
-      <c r="M50" s="74">
-        <v>9100</v>
-      </c>
-      <c r="N50" s="74">
-        <v>4</v>
-      </c>
-      <c r="O50" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P50" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q50" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="84" t="s">
         <v>185</v>
       </c>
@@ -9688,47 +9892,51 @@
         <f t="shared" si="0"/>
         <v>t-dip-mqweb-lb-rule8883</v>
       </c>
-      <c r="F51" s="84" t="str">
+      <c r="F51" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dip-mqweb-lb-rule</v>
+      </c>
+      <c r="G51" s="84" t="str">
         <f>SUBSTITUTE(D51, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-mqweb-lb-fe</v>
       </c>
-      <c r="G51" s="84" t="s">
+      <c r="H51" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H51" s="84">
+      <c r="I51" s="84">
         <v>8883</v>
       </c>
-      <c r="I51" s="84" t="b">
+      <c r="J51" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J51" s="84" t="str">
+      <c r="K51" s="84" t="str">
         <f>SUBSTITUTE(D51, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-mqweb-lb-bp</v>
       </c>
-      <c r="K51" s="84">
+      <c r="L51" s="84">
         <v>8883</v>
       </c>
-      <c r="L51" s="84" t="str">
-        <f t="shared" si="1"/>
+      <c r="M51" s="84" t="str">
+        <f t="shared" si="2"/>
         <v>t-dip-mqweb-lb-pb8883</v>
       </c>
-      <c r="M51" s="84">
+      <c r="N51" s="84">
         <v>8883</v>
       </c>
-      <c r="N51" s="84">
+      <c r="O51" s="84">
         <v>4</v>
       </c>
-      <c r="O51" s="84" t="s">
+      <c r="P51" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P51" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q51" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R51" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="84" t="s">
         <v>185</v>
       </c>
@@ -9746,47 +9954,51 @@
         <f t="shared" si="0"/>
         <v>t-dip-mqweb-lb-rule1884</v>
       </c>
-      <c r="F52" s="84" t="str">
+      <c r="F52" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dip-mqweb-lb-rule</v>
+      </c>
+      <c r="G52" s="84" t="str">
         <f>SUBSTITUTE(D52, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-mqweb-lb-fe</v>
       </c>
-      <c r="G52" s="84" t="s">
+      <c r="H52" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H52" s="84">
+      <c r="I52" s="84">
         <v>1884</v>
       </c>
-      <c r="I52" s="84" t="b">
+      <c r="J52" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J52" s="84" t="str">
+      <c r="K52" s="84" t="str">
         <f>SUBSTITUTE(D52, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-mqweb-lb-bp</v>
       </c>
-      <c r="K52" s="84">
+      <c r="L52" s="84">
         <v>1884</v>
       </c>
-      <c r="L52" s="84" t="str">
-        <f t="shared" si="1"/>
+      <c r="M52" s="84" t="str">
+        <f t="shared" si="2"/>
         <v>t-dip-mqweb-lb-pb1884</v>
       </c>
-      <c r="M52" s="84">
+      <c r="N52" s="84">
         <v>1884</v>
       </c>
-      <c r="N52" s="84">
+      <c r="O52" s="84">
         <v>4</v>
       </c>
-      <c r="O52" s="84" t="s">
+      <c r="P52" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P52" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q52" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R52" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="84" t="s">
         <v>185</v>
       </c>
@@ -9804,47 +10016,51 @@
         <f t="shared" si="0"/>
         <v>t-dip-mqweb-lb-rule9100</v>
       </c>
-      <c r="F53" s="84" t="str">
+      <c r="F53" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dip-mqweb-lb-rule</v>
+      </c>
+      <c r="G53" s="84" t="str">
         <f>SUBSTITUTE(D53, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-mqweb-lb-fe</v>
       </c>
-      <c r="G53" s="84" t="s">
+      <c r="H53" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H53" s="84">
+      <c r="I53" s="84">
         <v>9100</v>
       </c>
-      <c r="I53" s="84" t="b">
+      <c r="J53" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J53" s="84" t="str">
+      <c r="K53" s="84" t="str">
         <f>SUBSTITUTE(D53, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-mqweb-lb-bp</v>
       </c>
-      <c r="K53" s="84">
+      <c r="L53" s="84">
         <v>9100</v>
       </c>
-      <c r="L53" s="84" t="str">
-        <f t="shared" si="1"/>
+      <c r="M53" s="84" t="str">
+        <f t="shared" si="2"/>
         <v>t-dip-mqweb-lb-pb9100</v>
       </c>
-      <c r="M53" s="84">
+      <c r="N53" s="84">
         <v>9100</v>
       </c>
-      <c r="N53" s="84">
+      <c r="O53" s="84">
         <v>4</v>
       </c>
-      <c r="O53" s="84" t="s">
+      <c r="P53" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P53" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q53" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R53" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" s="74" t="s">
         <v>185</v>
       </c>
@@ -9863,46 +10079,50 @@
         <v>t-dip-mqap-lb-rule1883</v>
       </c>
       <c r="F54" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dip-mqap-lb-rule</v>
+      </c>
+      <c r="G54" s="74" t="str">
         <f>SUBSTITUTE(D54, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-mqap-lb-fe</v>
       </c>
-      <c r="G54" s="74" t="s">
+      <c r="H54" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H54" s="74">
+      <c r="I54" s="74">
         <v>1883</v>
       </c>
-      <c r="I54" s="74" t="b">
+      <c r="J54" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J54" s="74" t="str">
+      <c r="K54" s="74" t="str">
         <f>SUBSTITUTE(D54, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-mqap-lb-bp</v>
       </c>
-      <c r="K54" s="74">
+      <c r="L54" s="74">
         <v>1883</v>
       </c>
-      <c r="L54" s="74" t="str">
-        <f t="shared" si="1"/>
+      <c r="M54" s="74" t="str">
+        <f t="shared" si="2"/>
         <v>t-dip-mqap-lb-pb1883</v>
       </c>
-      <c r="M54" s="74">
+      <c r="N54" s="74">
         <v>1883</v>
       </c>
-      <c r="N54" s="74">
+      <c r="O54" s="74">
         <v>4</v>
       </c>
-      <c r="O54" s="74" t="s">
+      <c r="P54" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P54" s="74" t="b">
-        <v>1</v>
-      </c>
       <c r="Q54" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R54" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" s="74" t="s">
         <v>185</v>
       </c>
@@ -9921,46 +10141,50 @@
         <v>t-dip-mqap-lb-rule1884</v>
       </c>
       <c r="F55" s="74" t="str">
-        <f t="shared" ref="F55:F88" si="4">SUBSTITUTE(D55, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="1"/>
+        <v>t-dip-mqap-lb-rule</v>
+      </c>
+      <c r="G55" s="74" t="str">
+        <f t="shared" ref="G55:G88" si="5">SUBSTITUTE(D55, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-mqap-lb-fe</v>
       </c>
-      <c r="G55" s="74" t="s">
+      <c r="H55" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H55" s="74">
+      <c r="I55" s="74">
         <v>1884</v>
       </c>
-      <c r="I55" s="74" t="b">
+      <c r="J55" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J55" s="74" t="str">
+      <c r="K55" s="74" t="str">
         <f>SUBSTITUTE(D55, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-mqap-lb-bp</v>
       </c>
-      <c r="K55" s="74">
+      <c r="L55" s="74">
         <v>1884</v>
       </c>
-      <c r="L55" s="74" t="str">
-        <f t="shared" si="1"/>
+      <c r="M55" s="74" t="str">
+        <f t="shared" si="2"/>
         <v>t-dip-mqap-lb-pb1884</v>
       </c>
-      <c r="M55" s="74">
+      <c r="N55" s="74">
         <v>1884</v>
       </c>
-      <c r="N55" s="74">
+      <c r="O55" s="74">
         <v>4</v>
       </c>
-      <c r="O55" s="74" t="s">
+      <c r="P55" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P55" s="74" t="b">
-        <v>1</v>
-      </c>
       <c r="Q55" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R55" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="74" t="s">
         <v>185</v>
       </c>
@@ -9979,46 +10203,50 @@
         <v>t-dip-mqap-lb-rule18083</v>
       </c>
       <c r="F56" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
+        <v>t-dip-mqap-lb-rule</v>
+      </c>
+      <c r="G56" s="74" t="str">
+        <f t="shared" si="5"/>
         <v>t-dip-mqap-lb-fe</v>
       </c>
-      <c r="G56" s="74" t="s">
+      <c r="H56" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H56" s="74">
+      <c r="I56" s="74">
         <v>18083</v>
       </c>
-      <c r="I56" s="74" t="b">
+      <c r="J56" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J56" s="74" t="str">
-        <f t="shared" ref="J56:J88" si="5">SUBSTITUTE(D56, "hazr-", "")&amp;"-bp"</f>
+      <c r="K56" s="74" t="str">
+        <f t="shared" ref="K56:K88" si="6">SUBSTITUTE(D56, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-mqap-lb-bp</v>
       </c>
-      <c r="K56" s="74">
+      <c r="L56" s="74">
         <v>18083</v>
       </c>
-      <c r="L56" s="74" t="str">
-        <f t="shared" si="1"/>
+      <c r="M56" s="74" t="str">
+        <f t="shared" si="2"/>
         <v>t-dip-mqap-lb-pb18083</v>
       </c>
-      <c r="M56" s="74">
+      <c r="N56" s="74">
         <v>18083</v>
       </c>
-      <c r="N56" s="74">
+      <c r="O56" s="74">
         <v>4</v>
       </c>
-      <c r="O56" s="74" t="s">
+      <c r="P56" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P56" s="74" t="b">
-        <v>1</v>
-      </c>
       <c r="Q56" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R56" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="74" t="s">
         <v>185</v>
       </c>
@@ -10037,46 +10265,50 @@
         <v>t-dip-mqap-lb-rule9100</v>
       </c>
       <c r="F57" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
+        <v>t-dip-mqap-lb-rule</v>
+      </c>
+      <c r="G57" s="74" t="str">
+        <f t="shared" si="5"/>
         <v>t-dip-mqap-lb-fe</v>
       </c>
-      <c r="G57" s="74" t="s">
+      <c r="H57" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H57" s="74">
+      <c r="I57" s="74">
         <v>9100</v>
       </c>
-      <c r="I57" s="74" t="b">
+      <c r="J57" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J57" s="74" t="str">
-        <f t="shared" si="5"/>
+      <c r="K57" s="74" t="str">
+        <f t="shared" si="6"/>
         <v>t-dip-mqap-lb-bp</v>
       </c>
-      <c r="K57" s="74">
+      <c r="L57" s="74">
         <v>9100</v>
       </c>
-      <c r="L57" s="74" t="str">
-        <f t="shared" si="1"/>
+      <c r="M57" s="74" t="str">
+        <f t="shared" si="2"/>
         <v>t-dip-mqap-lb-pb9100</v>
       </c>
-      <c r="M57" s="74">
+      <c r="N57" s="74">
         <v>9100</v>
       </c>
-      <c r="N57" s="74">
+      <c r="O57" s="74">
         <v>4</v>
       </c>
-      <c r="O57" s="74" t="s">
+      <c r="P57" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P57" s="74" t="b">
-        <v>1</v>
-      </c>
       <c r="Q57" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R57" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="84" t="s">
         <v>185</v>
       </c>
@@ -10094,47 +10326,51 @@
         <f t="shared" si="0"/>
         <v>t-dip-geoap-lb-rule3660</v>
       </c>
-      <c r="F58" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="F58" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dip-geoap-lb-rule</v>
+      </c>
+      <c r="G58" s="84" t="str">
+        <f t="shared" si="5"/>
         <v>t-dip-geoap-lb-fe</v>
       </c>
-      <c r="G58" s="84" t="s">
+      <c r="H58" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H58" s="84">
+      <c r="I58" s="84">
         <v>3660</v>
       </c>
-      <c r="I58" s="84" t="b">
+      <c r="J58" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J58" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="K58" s="84" t="str">
+        <f t="shared" si="6"/>
         <v>t-dip-geoap-lb-bp</v>
       </c>
-      <c r="K58" s="84">
+      <c r="L58" s="84">
         <v>3660</v>
       </c>
-      <c r="L58" s="84" t="str">
-        <f t="shared" si="1"/>
+      <c r="M58" s="84" t="str">
+        <f t="shared" si="2"/>
         <v>t-dip-geoap-lb-pb3660</v>
       </c>
-      <c r="M58" s="84">
+      <c r="N58" s="84">
         <v>3660</v>
       </c>
-      <c r="N58" s="84">
+      <c r="O58" s="84">
         <v>4</v>
       </c>
-      <c r="O58" s="84" t="s">
+      <c r="P58" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P58" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q58" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R58" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="84" t="s">
         <v>185</v>
       </c>
@@ -10152,47 +10388,51 @@
         <f t="shared" si="0"/>
         <v>t-dip-geoap-lb-rule3661</v>
       </c>
-      <c r="F59" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="F59" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dip-geoap-lb-rule</v>
+      </c>
+      <c r="G59" s="84" t="str">
+        <f t="shared" si="5"/>
         <v>t-dip-geoap-lb-fe</v>
       </c>
-      <c r="G59" s="84" t="s">
+      <c r="H59" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H59" s="84">
+      <c r="I59" s="84">
         <v>3661</v>
       </c>
-      <c r="I59" s="84" t="b">
+      <c r="J59" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J59" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="K59" s="84" t="str">
+        <f t="shared" si="6"/>
         <v>t-dip-geoap-lb-bp</v>
       </c>
-      <c r="K59" s="84">
+      <c r="L59" s="84">
         <v>3661</v>
       </c>
-      <c r="L59" s="84" t="str">
-        <f t="shared" si="1"/>
+      <c r="M59" s="84" t="str">
+        <f t="shared" si="2"/>
         <v>t-dip-geoap-lb-pb3661</v>
       </c>
-      <c r="M59" s="84">
+      <c r="N59" s="84">
         <v>3661</v>
       </c>
-      <c r="N59" s="84">
+      <c r="O59" s="84">
         <v>4</v>
       </c>
-      <c r="O59" s="84" t="s">
+      <c r="P59" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P59" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q59" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R59" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="84" t="s">
         <v>185</v>
       </c>
@@ -10210,47 +10450,51 @@
         <f t="shared" si="0"/>
         <v>t-dip-geoap-lb-rule3670</v>
       </c>
-      <c r="F60" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="F60" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dip-geoap-lb-rule</v>
+      </c>
+      <c r="G60" s="84" t="str">
+        <f t="shared" si="5"/>
         <v>t-dip-geoap-lb-fe</v>
       </c>
-      <c r="G60" s="84" t="s">
+      <c r="H60" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H60" s="84">
+      <c r="I60" s="84">
         <v>3670</v>
       </c>
-      <c r="I60" s="84" t="b">
+      <c r="J60" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J60" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="K60" s="84" t="str">
+        <f t="shared" si="6"/>
         <v>t-dip-geoap-lb-bp</v>
       </c>
-      <c r="K60" s="84">
+      <c r="L60" s="84">
         <v>3670</v>
       </c>
-      <c r="L60" s="84" t="str">
-        <f t="shared" si="1"/>
+      <c r="M60" s="84" t="str">
+        <f t="shared" si="2"/>
         <v>t-dip-geoap-lb-pb3670</v>
       </c>
-      <c r="M60" s="84">
+      <c r="N60" s="84">
         <v>3670</v>
       </c>
-      <c r="N60" s="84">
+      <c r="O60" s="84">
         <v>4</v>
       </c>
-      <c r="O60" s="84" t="s">
+      <c r="P60" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P60" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q60" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R60" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="84" t="s">
         <v>185</v>
       </c>
@@ -10268,47 +10512,51 @@
         <f t="shared" si="0"/>
         <v>t-dip-geoap-lb-rule3671</v>
       </c>
-      <c r="F61" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="F61" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dip-geoap-lb-rule</v>
+      </c>
+      <c r="G61" s="84" t="str">
+        <f t="shared" si="5"/>
         <v>t-dip-geoap-lb-fe</v>
       </c>
-      <c r="G61" s="84" t="s">
+      <c r="H61" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H61" s="84">
+      <c r="I61" s="84">
         <v>3671</v>
       </c>
-      <c r="I61" s="84" t="b">
+      <c r="J61" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J61" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="K61" s="84" t="str">
+        <f t="shared" si="6"/>
         <v>t-dip-geoap-lb-bp</v>
       </c>
-      <c r="K61" s="84">
+      <c r="L61" s="84">
         <v>3671</v>
       </c>
-      <c r="L61" s="84" t="str">
-        <f t="shared" si="1"/>
+      <c r="M61" s="84" t="str">
+        <f t="shared" si="2"/>
         <v>t-dip-geoap-lb-pb3671</v>
       </c>
-      <c r="M61" s="84">
+      <c r="N61" s="84">
         <v>3671</v>
       </c>
-      <c r="N61" s="84">
+      <c r="O61" s="84">
         <v>4</v>
       </c>
-      <c r="O61" s="84" t="s">
+      <c r="P61" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P61" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q61" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R61" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="84" t="s">
         <v>185</v>
       </c>
@@ -10326,47 +10574,51 @@
         <f t="shared" si="0"/>
         <v>t-dip-geoap-lb-rule9100</v>
       </c>
-      <c r="F62" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="F62" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dip-geoap-lb-rule</v>
+      </c>
+      <c r="G62" s="84" t="str">
+        <f t="shared" si="5"/>
         <v>t-dip-geoap-lb-fe</v>
       </c>
-      <c r="G62" s="84" t="s">
+      <c r="H62" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H62" s="84">
+      <c r="I62" s="84">
         <v>9100</v>
       </c>
-      <c r="I62" s="84" t="b">
+      <c r="J62" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J62" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="K62" s="84" t="str">
+        <f t="shared" si="6"/>
         <v>t-dip-geoap-lb-bp</v>
       </c>
-      <c r="K62" s="84">
+      <c r="L62" s="84">
         <v>9100</v>
       </c>
-      <c r="L62" s="84" t="str">
-        <f t="shared" si="1"/>
+      <c r="M62" s="84" t="str">
+        <f t="shared" si="2"/>
         <v>t-dip-geoap-lb-pb9100</v>
       </c>
-      <c r="M62" s="84">
+      <c r="N62" s="84">
         <v>9100</v>
       </c>
-      <c r="N62" s="84">
+      <c r="O62" s="84">
         <v>4</v>
       </c>
-      <c r="O62" s="84" t="s">
+      <c r="P62" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P62" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q62" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R62" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="74" t="s">
         <v>185</v>
       </c>
@@ -10382,37 +10634,41 @@
       </c>
       <c r="E63" s="74"/>
       <c r="F63" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
+        <v>t-dip-flk-lb-rule</v>
+      </c>
+      <c r="G63" s="74" t="str">
+        <f t="shared" si="5"/>
         <v>t-dip-flk-lb-fe</v>
       </c>
-      <c r="G63" s="74" t="s">
+      <c r="H63" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H63" s="74"/>
-      <c r="I63" s="74" t="b">
+      <c r="I63" s="74"/>
+      <c r="J63" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J63" s="74" t="str">
-        <f t="shared" si="5"/>
+      <c r="K63" s="74" t="str">
+        <f t="shared" si="6"/>
         <v>t-dip-flk-lb-bp</v>
       </c>
-      <c r="K63" s="74"/>
       <c r="L63" s="74"/>
       <c r="M63" s="74"/>
-      <c r="N63" s="74">
+      <c r="N63" s="74"/>
+      <c r="O63" s="74">
         <v>4</v>
       </c>
-      <c r="O63" s="74" t="s">
+      <c r="P63" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P63" s="74" t="b">
-        <v>1</v>
-      </c>
       <c r="Q63" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R63" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="84" t="s">
         <v>185</v>
       </c>
@@ -10430,47 +10686,51 @@
         <f t="shared" si="0"/>
         <v>t-dip-ap-lb-rule443</v>
       </c>
-      <c r="F64" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="F64" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dip-ap-lb-rule</v>
+      </c>
+      <c r="G64" s="84" t="str">
+        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-fe</v>
       </c>
-      <c r="G64" s="84" t="s">
+      <c r="H64" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H64" s="84">
+      <c r="I64" s="84">
         <v>443</v>
       </c>
-      <c r="I64" s="84" t="b">
+      <c r="J64" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J64" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="K64" s="84" t="str">
+        <f t="shared" si="6"/>
         <v>t-dip-ap-lb-bp</v>
       </c>
-      <c r="K64" s="84">
+      <c r="L64" s="84">
         <v>443</v>
       </c>
-      <c r="L64" s="84" t="str">
-        <f t="shared" si="1"/>
+      <c r="M64" s="84" t="str">
+        <f t="shared" si="2"/>
         <v>t-dip-ap-lb-pb443</v>
       </c>
-      <c r="M64" s="84">
+      <c r="N64" s="84">
         <v>443</v>
       </c>
-      <c r="N64" s="84">
+      <c r="O64" s="84">
         <v>4</v>
       </c>
-      <c r="O64" s="84" t="s">
+      <c r="P64" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P64" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q64" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R64" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" s="84" t="s">
         <v>185</v>
       </c>
@@ -10488,47 +10748,51 @@
         <f t="shared" si="0"/>
         <v>t-dip-ap-lb-rule8100</v>
       </c>
-      <c r="F65" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="F65" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dip-ap-lb-rule</v>
+      </c>
+      <c r="G65" s="84" t="str">
+        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-fe</v>
       </c>
-      <c r="G65" s="84" t="s">
+      <c r="H65" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H65" s="84">
+      <c r="I65" s="84">
         <v>8100</v>
       </c>
-      <c r="I65" s="84" t="b">
+      <c r="J65" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J65" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="K65" s="84" t="str">
+        <f t="shared" si="6"/>
         <v>t-dip-ap-lb-bp</v>
       </c>
-      <c r="K65" s="84">
+      <c r="L65" s="84">
         <v>8100</v>
       </c>
-      <c r="L65" s="84" t="str">
-        <f t="shared" si="1"/>
+      <c r="M65" s="84" t="str">
+        <f t="shared" si="2"/>
         <v>t-dip-ap-lb-pb8100</v>
       </c>
-      <c r="M65" s="84">
+      <c r="N65" s="84">
         <v>8100</v>
       </c>
-      <c r="N65" s="84">
+      <c r="O65" s="84">
         <v>4</v>
       </c>
-      <c r="O65" s="84" t="s">
+      <c r="P65" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P65" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q65" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R65" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" s="84" t="s">
         <v>185</v>
       </c>
@@ -10546,47 +10810,51 @@
         <f t="shared" si="0"/>
         <v>t-dip-ap-lb-rule8200</v>
       </c>
-      <c r="F66" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="F66" s="74" t="str">
+        <f t="shared" si="1"/>
+        <v>t-dip-ap-lb-rule</v>
+      </c>
+      <c r="G66" s="84" t="str">
+        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-fe</v>
       </c>
-      <c r="G66" s="84" t="s">
+      <c r="H66" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H66" s="84">
+      <c r="I66" s="84">
         <v>8200</v>
       </c>
-      <c r="I66" s="84" t="b">
+      <c r="J66" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J66" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="K66" s="84" t="str">
+        <f t="shared" si="6"/>
         <v>t-dip-ap-lb-bp</v>
       </c>
-      <c r="K66" s="84">
+      <c r="L66" s="84">
         <v>8200</v>
       </c>
-      <c r="L66" s="84" t="str">
-        <f t="shared" si="1"/>
+      <c r="M66" s="84" t="str">
+        <f t="shared" si="2"/>
         <v>t-dip-ap-lb-pb8200</v>
       </c>
-      <c r="M66" s="84">
+      <c r="N66" s="84">
         <v>8200</v>
       </c>
-      <c r="N66" s="84">
+      <c r="O66" s="84">
         <v>4</v>
       </c>
-      <c r="O66" s="84" t="s">
+      <c r="P66" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P66" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q66" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R66" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" s="84" t="s">
         <v>185</v>
       </c>
@@ -10601,50 +10869,54 @@
         <v>374</v>
       </c>
       <c r="E67" s="84" t="str">
-        <f t="shared" ref="E67:E88" si="6">SUBSTITUTE(D67, "hazr-", "")&amp;"-rule"&amp;M67</f>
+        <f t="shared" ref="E67:F88" si="7">SUBSTITUTE(D67, "hazr-", "")&amp;"-rule"&amp;N67</f>
         <v>t-dip-ap-lb-rule8300</v>
       </c>
-      <c r="F67" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="F67" s="74" t="str">
+        <f t="shared" ref="F67:F88" si="8">SUBSTITUTE(D67, "hazr-", "")&amp;"-rule"</f>
+        <v>t-dip-ap-lb-rule</v>
+      </c>
+      <c r="G67" s="84" t="str">
+        <f t="shared" si="5"/>
         <v>t-dip-ap-lb-fe</v>
       </c>
-      <c r="G67" s="84" t="s">
+      <c r="H67" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H67" s="84">
+      <c r="I67" s="84">
         <v>8300</v>
       </c>
-      <c r="I67" s="84" t="b">
+      <c r="J67" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J67" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="K67" s="84" t="str">
+        <f t="shared" si="6"/>
         <v>t-dip-ap-lb-bp</v>
       </c>
-      <c r="K67" s="84">
+      <c r="L67" s="84">
         <v>8300</v>
       </c>
-      <c r="L67" s="84" t="str">
-        <f t="shared" ref="L67:L88" si="7">SUBSTITUTE(D67, "hazr-", "")&amp;"-pb"&amp;IF(M67="", "", M67)</f>
+      <c r="M67" s="84" t="str">
+        <f t="shared" ref="M67:M88" si="9">SUBSTITUTE(D67, "hazr-", "")&amp;"-pb"&amp;IF(N67="", "", N67)</f>
         <v>t-dip-ap-lb-pb8300</v>
       </c>
-      <c r="M67" s="84">
+      <c r="N67" s="84">
         <v>8300</v>
       </c>
-      <c r="N67" s="84">
+      <c r="O67" s="84">
         <v>4</v>
       </c>
-      <c r="O67" s="84" t="s">
+      <c r="P67" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P67" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q67" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R67" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" s="84" t="s">
         <v>185</v>
       </c>
@@ -10659,50 +10931,54 @@
         <v>374</v>
       </c>
       <c r="E68" s="84" t="str">
+        <f t="shared" si="7"/>
+        <v>t-dip-ap-lb-rule8400</v>
+      </c>
+      <c r="F68" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-dip-ap-lb-rule</v>
+      </c>
+      <c r="G68" s="84" t="str">
+        <f t="shared" si="5"/>
+        <v>t-dip-ap-lb-fe</v>
+      </c>
+      <c r="H68" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I68" s="84">
+        <v>8400</v>
+      </c>
+      <c r="J68" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" s="84" t="str">
         <f t="shared" si="6"/>
-        <v>t-dip-ap-lb-rule8400</v>
-      </c>
-      <c r="F68" s="84" t="str">
-        <f t="shared" si="4"/>
-        <v>t-dip-ap-lb-fe</v>
-      </c>
-      <c r="G68" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H68" s="84">
+        <v>t-dip-ap-lb-bp</v>
+      </c>
+      <c r="L68" s="84">
         <v>8400</v>
       </c>
-      <c r="I68" s="84" t="b">
+      <c r="M68" s="84" t="str">
+        <f t="shared" si="9"/>
+        <v>t-dip-ap-lb-pb8400</v>
+      </c>
+      <c r="N68" s="84">
+        <v>8400</v>
+      </c>
+      <c r="O68" s="84">
+        <v>4</v>
+      </c>
+      <c r="P68" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q68" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R68" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J68" s="84" t="str">
-        <f t="shared" si="5"/>
-        <v>t-dip-ap-lb-bp</v>
-      </c>
-      <c r="K68" s="84">
-        <v>8400</v>
-      </c>
-      <c r="L68" s="84" t="str">
-        <f t="shared" si="7"/>
-        <v>t-dip-ap-lb-pb8400</v>
-      </c>
-      <c r="M68" s="84">
-        <v>8400</v>
-      </c>
-      <c r="N68" s="84">
-        <v>4</v>
-      </c>
-      <c r="O68" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P68" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q68" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" s="84" t="s">
         <v>185</v>
       </c>
@@ -10717,50 +10993,54 @@
         <v>374</v>
       </c>
       <c r="E69" s="84" t="str">
+        <f t="shared" si="7"/>
+        <v>t-dip-ap-lb-rule9100</v>
+      </c>
+      <c r="F69" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-dip-ap-lb-rule</v>
+      </c>
+      <c r="G69" s="84" t="str">
+        <f t="shared" si="5"/>
+        <v>t-dip-ap-lb-fe</v>
+      </c>
+      <c r="H69" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I69" s="84">
+        <v>9100</v>
+      </c>
+      <c r="J69" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" s="84" t="str">
         <f t="shared" si="6"/>
-        <v>t-dip-ap-lb-rule9100</v>
-      </c>
-      <c r="F69" s="84" t="str">
-        <f t="shared" si="4"/>
-        <v>t-dip-ap-lb-fe</v>
-      </c>
-      <c r="G69" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H69" s="84">
+        <v>t-dip-ap-lb-bp</v>
+      </c>
+      <c r="L69" s="84">
         <v>9100</v>
       </c>
-      <c r="I69" s="84" t="b">
+      <c r="M69" s="84" t="str">
+        <f t="shared" si="9"/>
+        <v>t-dip-ap-lb-pb9100</v>
+      </c>
+      <c r="N69" s="84">
+        <v>9100</v>
+      </c>
+      <c r="O69" s="84">
+        <v>4</v>
+      </c>
+      <c r="P69" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q69" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R69" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J69" s="84" t="str">
-        <f t="shared" si="5"/>
-        <v>t-dip-ap-lb-bp</v>
-      </c>
-      <c r="K69" s="84">
-        <v>9100</v>
-      </c>
-      <c r="L69" s="84" t="str">
-        <f t="shared" si="7"/>
-        <v>t-dip-ap-lb-pb9100</v>
-      </c>
-      <c r="M69" s="84">
-        <v>9100</v>
-      </c>
-      <c r="N69" s="84">
-        <v>4</v>
-      </c>
-      <c r="O69" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P69" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q69" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" s="84" t="s">
         <v>185</v>
       </c>
@@ -10775,50 +11055,54 @@
         <v>374</v>
       </c>
       <c r="E70" s="84" t="str">
+        <f t="shared" si="7"/>
+        <v>t-dip-ap-lb-rule9113</v>
+      </c>
+      <c r="F70" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-dip-ap-lb-rule</v>
+      </c>
+      <c r="G70" s="84" t="str">
+        <f t="shared" si="5"/>
+        <v>t-dip-ap-lb-fe</v>
+      </c>
+      <c r="H70" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I70" s="84">
+        <v>9113</v>
+      </c>
+      <c r="J70" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" s="84" t="str">
         <f t="shared" si="6"/>
-        <v>t-dip-ap-lb-rule9113</v>
-      </c>
-      <c r="F70" s="84" t="str">
-        <f t="shared" si="4"/>
-        <v>t-dip-ap-lb-fe</v>
-      </c>
-      <c r="G70" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H70" s="84">
+        <v>t-dip-ap-lb-bp</v>
+      </c>
+      <c r="L70" s="84">
         <v>9113</v>
       </c>
-      <c r="I70" s="84" t="b">
+      <c r="M70" s="84" t="str">
+        <f t="shared" si="9"/>
+        <v>t-dip-ap-lb-pb9113</v>
+      </c>
+      <c r="N70" s="84">
+        <v>9113</v>
+      </c>
+      <c r="O70" s="84">
+        <v>4</v>
+      </c>
+      <c r="P70" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q70" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R70" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J70" s="84" t="str">
-        <f t="shared" si="5"/>
-        <v>t-dip-ap-lb-bp</v>
-      </c>
-      <c r="K70" s="84">
-        <v>9113</v>
-      </c>
-      <c r="L70" s="84" t="str">
-        <f t="shared" si="7"/>
-        <v>t-dip-ap-lb-pb9113</v>
-      </c>
-      <c r="M70" s="84">
-        <v>9113</v>
-      </c>
-      <c r="N70" s="84">
-        <v>4</v>
-      </c>
-      <c r="O70" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P70" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q70" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71" s="74" t="s">
         <v>185</v>
       </c>
@@ -10833,50 +11117,54 @@
         <v>373</v>
       </c>
       <c r="E71" s="74" t="str">
+        <f t="shared" si="7"/>
+        <v>t-dip-adm-lb-rule443</v>
+      </c>
+      <c r="F71" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-dip-adm-lb-rule</v>
+      </c>
+      <c r="G71" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>t-dip-adm-lb-fe</v>
+      </c>
+      <c r="H71" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I71" s="74">
+        <v>443</v>
+      </c>
+      <c r="J71" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" s="74" t="str">
         <f t="shared" si="6"/>
-        <v>t-dip-adm-lb-rule443</v>
-      </c>
-      <c r="F71" s="74" t="str">
-        <f t="shared" si="4"/>
-        <v>t-dip-adm-lb-fe</v>
-      </c>
-      <c r="G71" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H71" s="74">
+        <v>t-dip-adm-lb-bp</v>
+      </c>
+      <c r="L71" s="74">
         <v>443</v>
       </c>
-      <c r="I71" s="74" t="b">
+      <c r="M71" s="74" t="str">
+        <f t="shared" si="9"/>
+        <v>t-dip-adm-lb-pb443</v>
+      </c>
+      <c r="N71" s="74">
+        <v>443</v>
+      </c>
+      <c r="O71" s="74">
+        <v>4</v>
+      </c>
+      <c r="P71" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q71" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R71" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J71" s="74" t="str">
-        <f t="shared" si="5"/>
-        <v>t-dip-adm-lb-bp</v>
-      </c>
-      <c r="K71" s="74">
-        <v>443</v>
-      </c>
-      <c r="L71" s="74" t="str">
-        <f t="shared" si="7"/>
-        <v>t-dip-adm-lb-pb443</v>
-      </c>
-      <c r="M71" s="74">
-        <v>443</v>
-      </c>
-      <c r="N71" s="74">
-        <v>4</v>
-      </c>
-      <c r="O71" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P71" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q71" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" s="74" t="s">
         <v>185</v>
       </c>
@@ -10891,50 +11179,54 @@
         <v>373</v>
       </c>
       <c r="E72" s="74" t="str">
+        <f t="shared" si="7"/>
+        <v>t-dip-adm-lb-rule8085</v>
+      </c>
+      <c r="F72" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-dip-adm-lb-rule</v>
+      </c>
+      <c r="G72" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>t-dip-adm-lb-fe</v>
+      </c>
+      <c r="H72" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I72" s="74">
+        <v>8085</v>
+      </c>
+      <c r="J72" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" s="74" t="str">
         <f t="shared" si="6"/>
-        <v>t-dip-adm-lb-rule8085</v>
-      </c>
-      <c r="F72" s="74" t="str">
-        <f t="shared" si="4"/>
-        <v>t-dip-adm-lb-fe</v>
-      </c>
-      <c r="G72" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H72" s="74">
+        <v>t-dip-adm-lb-bp</v>
+      </c>
+      <c r="L72" s="74">
         <v>8085</v>
       </c>
-      <c r="I72" s="74" t="b">
+      <c r="M72" s="74" t="str">
+        <f t="shared" si="9"/>
+        <v>t-dip-adm-lb-pb8085</v>
+      </c>
+      <c r="N72" s="74">
+        <v>8085</v>
+      </c>
+      <c r="O72" s="74">
+        <v>4</v>
+      </c>
+      <c r="P72" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q72" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R72" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J72" s="74" t="str">
-        <f t="shared" si="5"/>
-        <v>t-dip-adm-lb-bp</v>
-      </c>
-      <c r="K72" s="74">
-        <v>8085</v>
-      </c>
-      <c r="L72" s="74" t="str">
-        <f t="shared" si="7"/>
-        <v>t-dip-adm-lb-pb8085</v>
-      </c>
-      <c r="M72" s="74">
-        <v>8085</v>
-      </c>
-      <c r="N72" s="74">
-        <v>4</v>
-      </c>
-      <c r="O72" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P72" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q72" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73" s="74" t="s">
         <v>185</v>
       </c>
@@ -10949,50 +11241,54 @@
         <v>373</v>
       </c>
       <c r="E73" s="74" t="str">
+        <f t="shared" si="7"/>
+        <v>t-dip-adm-lb-rule8900</v>
+      </c>
+      <c r="F73" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-dip-adm-lb-rule</v>
+      </c>
+      <c r="G73" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>t-dip-adm-lb-fe</v>
+      </c>
+      <c r="H73" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I73" s="74">
+        <v>8900</v>
+      </c>
+      <c r="J73" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" s="74" t="str">
         <f t="shared" si="6"/>
-        <v>t-dip-adm-lb-rule8900</v>
-      </c>
-      <c r="F73" s="74" t="str">
-        <f t="shared" si="4"/>
-        <v>t-dip-adm-lb-fe</v>
-      </c>
-      <c r="G73" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H73" s="74">
+        <v>t-dip-adm-lb-bp</v>
+      </c>
+      <c r="L73" s="74">
         <v>8900</v>
       </c>
-      <c r="I73" s="74" t="b">
+      <c r="M73" s="74" t="str">
+        <f t="shared" si="9"/>
+        <v>t-dip-adm-lb-pb8900</v>
+      </c>
+      <c r="N73" s="74">
+        <v>8900</v>
+      </c>
+      <c r="O73" s="74">
+        <v>4</v>
+      </c>
+      <c r="P73" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q73" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R73" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J73" s="74" t="str">
-        <f t="shared" si="5"/>
-        <v>t-dip-adm-lb-bp</v>
-      </c>
-      <c r="K73" s="74">
-        <v>8900</v>
-      </c>
-      <c r="L73" s="74" t="str">
-        <f t="shared" si="7"/>
-        <v>t-dip-adm-lb-pb8900</v>
-      </c>
-      <c r="M73" s="74">
-        <v>8900</v>
-      </c>
-      <c r="N73" s="74">
-        <v>4</v>
-      </c>
-      <c r="O73" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P73" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q73" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" s="74" t="s">
         <v>185</v>
       </c>
@@ -11007,50 +11303,54 @@
         <v>373</v>
       </c>
       <c r="E74" s="74" t="str">
+        <f t="shared" si="7"/>
+        <v>t-dip-adm-lb-rule8901</v>
+      </c>
+      <c r="F74" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-dip-adm-lb-rule</v>
+      </c>
+      <c r="G74" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>t-dip-adm-lb-fe</v>
+      </c>
+      <c r="H74" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I74" s="74">
+        <v>8901</v>
+      </c>
+      <c r="J74" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" s="74" t="str">
         <f t="shared" si="6"/>
-        <v>t-dip-adm-lb-rule8901</v>
-      </c>
-      <c r="F74" s="74" t="str">
-        <f t="shared" si="4"/>
-        <v>t-dip-adm-lb-fe</v>
-      </c>
-      <c r="G74" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H74" s="74">
+        <v>t-dip-adm-lb-bp</v>
+      </c>
+      <c r="L74" s="74">
         <v>8901</v>
       </c>
-      <c r="I74" s="74" t="b">
+      <c r="M74" s="74" t="str">
+        <f t="shared" si="9"/>
+        <v>t-dip-adm-lb-pb8901</v>
+      </c>
+      <c r="N74" s="74">
+        <v>8901</v>
+      </c>
+      <c r="O74" s="74">
+        <v>4</v>
+      </c>
+      <c r="P74" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q74" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R74" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J74" s="74" t="str">
-        <f t="shared" si="5"/>
-        <v>t-dip-adm-lb-bp</v>
-      </c>
-      <c r="K74" s="74">
-        <v>8901</v>
-      </c>
-      <c r="L74" s="74" t="str">
-        <f t="shared" si="7"/>
-        <v>t-dip-adm-lb-pb8901</v>
-      </c>
-      <c r="M74" s="74">
-        <v>8901</v>
-      </c>
-      <c r="N74" s="74">
-        <v>4</v>
-      </c>
-      <c r="O74" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P74" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q74" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" s="74" t="s">
         <v>185</v>
       </c>
@@ -11065,50 +11365,54 @@
         <v>373</v>
       </c>
       <c r="E75" s="74" t="str">
+        <f t="shared" si="7"/>
+        <v>t-dip-adm-lb-rule9100</v>
+      </c>
+      <c r="F75" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-dip-adm-lb-rule</v>
+      </c>
+      <c r="G75" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>t-dip-adm-lb-fe</v>
+      </c>
+      <c r="H75" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I75" s="74">
+        <v>9100</v>
+      </c>
+      <c r="J75" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" s="74" t="str">
         <f t="shared" si="6"/>
-        <v>t-dip-adm-lb-rule9100</v>
-      </c>
-      <c r="F75" s="74" t="str">
-        <f t="shared" si="4"/>
-        <v>t-dip-adm-lb-fe</v>
-      </c>
-      <c r="G75" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H75" s="74">
+        <v>t-dip-adm-lb-bp</v>
+      </c>
+      <c r="L75" s="74">
         <v>9100</v>
       </c>
-      <c r="I75" s="74" t="b">
+      <c r="M75" s="74" t="str">
+        <f t="shared" si="9"/>
+        <v>t-dip-adm-lb-pb9100</v>
+      </c>
+      <c r="N75" s="74">
+        <v>9100</v>
+      </c>
+      <c r="O75" s="74">
+        <v>4</v>
+      </c>
+      <c r="P75" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q75" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R75" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J75" s="74" t="str">
-        <f t="shared" si="5"/>
-        <v>t-dip-adm-lb-bp</v>
-      </c>
-      <c r="K75" s="74">
-        <v>9100</v>
-      </c>
-      <c r="L75" s="74" t="str">
-        <f t="shared" si="7"/>
-        <v>t-dip-adm-lb-pb9100</v>
-      </c>
-      <c r="M75" s="74">
-        <v>9100</v>
-      </c>
-      <c r="N75" s="74">
-        <v>4</v>
-      </c>
-      <c r="O75" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P75" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q75" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" s="84" t="s">
         <v>185</v>
       </c>
@@ -11123,38 +11427,42 @@
         <v>383</v>
       </c>
       <c r="E76" s="84"/>
-      <c r="F76" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="F76" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-cs-chtweb-lb-rule</v>
+      </c>
+      <c r="G76" s="84" t="str">
+        <f t="shared" si="5"/>
         <v>t-cs-chtweb-lb-fe</v>
       </c>
-      <c r="G76" s="84" t="s">
+      <c r="H76" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H76" s="84"/>
-      <c r="I76" s="84" t="b">
+      <c r="I76" s="84"/>
+      <c r="J76" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J76" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="K76" s="84" t="str">
+        <f t="shared" si="6"/>
         <v>t-cs-chtweb-lb-bp</v>
       </c>
-      <c r="K76" s="84"/>
       <c r="L76" s="84"/>
       <c r="M76" s="84"/>
-      <c r="N76" s="84">
+      <c r="N76" s="84"/>
+      <c r="O76" s="84">
         <v>4</v>
       </c>
-      <c r="O76" s="84" t="s">
+      <c r="P76" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P76" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q76" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R76" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" s="74" t="s">
         <v>185</v>
       </c>
@@ -11170,37 +11478,41 @@
       </c>
       <c r="E77" s="74"/>
       <c r="F77" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
+        <v>t-cs-chtintweb-lb-rule</v>
+      </c>
+      <c r="G77" s="74" t="str">
+        <f t="shared" si="5"/>
         <v>t-cs-chtintweb-lb-fe</v>
       </c>
-      <c r="G77" s="74" t="s">
+      <c r="H77" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H77" s="74"/>
-      <c r="I77" s="74" t="b">
+      <c r="I77" s="74"/>
+      <c r="J77" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J77" s="74" t="str">
-        <f t="shared" si="5"/>
+      <c r="K77" s="74" t="str">
+        <f t="shared" si="6"/>
         <v>t-cs-chtintweb-lb-bp</v>
       </c>
-      <c r="K77" s="74"/>
       <c r="L77" s="74"/>
       <c r="M77" s="74"/>
-      <c r="N77" s="74">
+      <c r="N77" s="74"/>
+      <c r="O77" s="74">
         <v>4</v>
       </c>
-      <c r="O77" s="74" t="s">
+      <c r="P77" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="P77" s="74" t="b">
-        <v>1</v>
-      </c>
       <c r="Q77" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R77" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" s="84" t="s">
         <v>185</v>
       </c>
@@ -11215,38 +11527,42 @@
         <v>382</v>
       </c>
       <c r="E78" s="84"/>
-      <c r="F78" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="F78" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-cs-chtap-lb-rule</v>
+      </c>
+      <c r="G78" s="84" t="str">
+        <f t="shared" si="5"/>
         <v>t-cs-chtap-lb-fe</v>
       </c>
-      <c r="G78" s="84" t="s">
+      <c r="H78" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H78" s="84"/>
-      <c r="I78" s="84" t="b">
+      <c r="I78" s="84"/>
+      <c r="J78" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J78" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="K78" s="84" t="str">
+        <f t="shared" si="6"/>
         <v>t-cs-chtap-lb-bp</v>
       </c>
-      <c r="K78" s="84"/>
       <c r="L78" s="84"/>
       <c r="M78" s="84"/>
-      <c r="N78" s="84">
+      <c r="N78" s="84"/>
+      <c r="O78" s="84">
         <v>4</v>
       </c>
-      <c r="O78" s="84" t="s">
+      <c r="P78" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="P78" s="84" t="b">
-        <v>1</v>
-      </c>
       <c r="Q78" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R78" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" s="74" t="s">
         <v>185</v>
       </c>
@@ -11261,50 +11577,54 @@
         <v>381</v>
       </c>
       <c r="E79" s="74" t="str">
+        <f t="shared" si="7"/>
+        <v>t-com-proxy-lb-rule443</v>
+      </c>
+      <c r="F79" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-com-proxy-lb-rule</v>
+      </c>
+      <c r="G79" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>t-com-proxy-lb-fe</v>
+      </c>
+      <c r="H79" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I79" s="74">
+        <v>443</v>
+      </c>
+      <c r="J79" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" s="74" t="str">
         <f t="shared" si="6"/>
-        <v>t-com-proxy-lb-rule443</v>
-      </c>
-      <c r="F79" s="74" t="str">
-        <f t="shared" si="4"/>
-        <v>t-com-proxy-lb-fe</v>
-      </c>
-      <c r="G79" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H79" s="74">
+        <v>t-com-proxy-lb-bp</v>
+      </c>
+      <c r="L79" s="74">
         <v>443</v>
       </c>
-      <c r="I79" s="74" t="b">
+      <c r="M79" s="74" t="str">
+        <f t="shared" si="9"/>
+        <v>t-com-proxy-lb-pb443</v>
+      </c>
+      <c r="N79" s="74">
+        <v>443</v>
+      </c>
+      <c r="O79" s="74">
+        <v>4</v>
+      </c>
+      <c r="P79" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q79" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R79" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J79" s="74" t="str">
-        <f t="shared" si="5"/>
-        <v>t-com-proxy-lb-bp</v>
-      </c>
-      <c r="K79" s="74">
-        <v>443</v>
-      </c>
-      <c r="L79" s="74" t="str">
-        <f t="shared" si="7"/>
-        <v>t-com-proxy-lb-pb443</v>
-      </c>
-      <c r="M79" s="74">
-        <v>443</v>
-      </c>
-      <c r="N79" s="74">
-        <v>4</v>
-      </c>
-      <c r="O79" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P79" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q79" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" s="74" t="s">
         <v>185</v>
       </c>
@@ -11319,50 +11639,54 @@
         <v>381</v>
       </c>
       <c r="E80" s="74" t="str">
+        <f t="shared" si="7"/>
+        <v>t-com-proxy-lb-rule8080</v>
+      </c>
+      <c r="F80" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-com-proxy-lb-rule</v>
+      </c>
+      <c r="G80" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>t-com-proxy-lb-fe</v>
+      </c>
+      <c r="H80" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I80" s="74">
+        <v>8080</v>
+      </c>
+      <c r="J80" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" s="74" t="str">
         <f t="shared" si="6"/>
-        <v>t-com-proxy-lb-rule8080</v>
-      </c>
-      <c r="F80" s="74" t="str">
-        <f t="shared" si="4"/>
-        <v>t-com-proxy-lb-fe</v>
-      </c>
-      <c r="G80" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H80" s="74">
+        <v>t-com-proxy-lb-bp</v>
+      </c>
+      <c r="L80" s="74">
         <v>8080</v>
       </c>
-      <c r="I80" s="74" t="b">
+      <c r="M80" s="74" t="str">
+        <f t="shared" si="9"/>
+        <v>t-com-proxy-lb-pb8080</v>
+      </c>
+      <c r="N80" s="74">
+        <v>8080</v>
+      </c>
+      <c r="O80" s="74">
+        <v>4</v>
+      </c>
+      <c r="P80" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q80" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R80" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J80" s="74" t="str">
-        <f t="shared" si="5"/>
-        <v>t-com-proxy-lb-bp</v>
-      </c>
-      <c r="K80" s="74">
-        <v>8080</v>
-      </c>
-      <c r="L80" s="74" t="str">
-        <f t="shared" si="7"/>
-        <v>t-com-proxy-lb-pb8080</v>
-      </c>
-      <c r="M80" s="74">
-        <v>8080</v>
-      </c>
-      <c r="N80" s="74">
-        <v>4</v>
-      </c>
-      <c r="O80" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P80" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q80" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" s="84" t="s">
         <v>185</v>
       </c>
@@ -11377,50 +11701,54 @@
         <v>380</v>
       </c>
       <c r="E81" s="84" t="str">
+        <f t="shared" si="7"/>
+        <v>t-com-auth-lb-rule8088</v>
+      </c>
+      <c r="F81" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-com-auth-lb-rule</v>
+      </c>
+      <c r="G81" s="84" t="str">
+        <f t="shared" si="5"/>
+        <v>t-com-auth-lb-fe</v>
+      </c>
+      <c r="H81" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I81" s="84">
+        <v>8088</v>
+      </c>
+      <c r="J81" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" s="84" t="str">
         <f t="shared" si="6"/>
-        <v>t-com-auth-lb-rule8088</v>
-      </c>
-      <c r="F81" s="84" t="str">
-        <f t="shared" si="4"/>
-        <v>t-com-auth-lb-fe</v>
-      </c>
-      <c r="G81" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H81" s="84">
+        <v>t-com-auth-lb-bp</v>
+      </c>
+      <c r="L81" s="84">
         <v>8088</v>
       </c>
-      <c r="I81" s="84" t="b">
+      <c r="M81" s="84" t="str">
+        <f t="shared" si="9"/>
+        <v>t-com-auth-lb-pb8088</v>
+      </c>
+      <c r="N81" s="84">
+        <v>8088</v>
+      </c>
+      <c r="O81" s="84">
+        <v>4</v>
+      </c>
+      <c r="P81" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q81" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R81" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J81" s="84" t="str">
-        <f t="shared" si="5"/>
-        <v>t-com-auth-lb-bp</v>
-      </c>
-      <c r="K81" s="84">
-        <v>8088</v>
-      </c>
-      <c r="L81" s="84" t="str">
-        <f t="shared" si="7"/>
-        <v>t-com-auth-lb-pb8088</v>
-      </c>
-      <c r="M81" s="84">
-        <v>8088</v>
-      </c>
-      <c r="N81" s="84">
-        <v>4</v>
-      </c>
-      <c r="O81" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P81" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q81" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" s="84" t="s">
         <v>185</v>
       </c>
@@ -11435,50 +11763,54 @@
         <v>380</v>
       </c>
       <c r="E82" s="84" t="str">
+        <f t="shared" si="7"/>
+        <v>t-com-auth-lb-rule9003</v>
+      </c>
+      <c r="F82" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-com-auth-lb-rule</v>
+      </c>
+      <c r="G82" s="84" t="str">
+        <f t="shared" si="5"/>
+        <v>t-com-auth-lb-fe</v>
+      </c>
+      <c r="H82" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I82" s="84">
+        <v>9003</v>
+      </c>
+      <c r="J82" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" s="84" t="str">
         <f t="shared" si="6"/>
-        <v>t-com-auth-lb-rule9003</v>
-      </c>
-      <c r="F82" s="84" t="str">
-        <f t="shared" si="4"/>
-        <v>t-com-auth-lb-fe</v>
-      </c>
-      <c r="G82" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H82" s="84">
+        <v>t-com-auth-lb-bp</v>
+      </c>
+      <c r="L82" s="84">
         <v>9003</v>
       </c>
-      <c r="I82" s="84" t="b">
+      <c r="M82" s="84" t="str">
+        <f t="shared" si="9"/>
+        <v>t-com-auth-lb-pb9003</v>
+      </c>
+      <c r="N82" s="84">
+        <v>9003</v>
+      </c>
+      <c r="O82" s="84">
+        <v>4</v>
+      </c>
+      <c r="P82" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q82" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R82" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J82" s="84" t="str">
-        <f t="shared" si="5"/>
-        <v>t-com-auth-lb-bp</v>
-      </c>
-      <c r="K82" s="84">
-        <v>9003</v>
-      </c>
-      <c r="L82" s="84" t="str">
-        <f t="shared" si="7"/>
-        <v>t-com-auth-lb-pb9003</v>
-      </c>
-      <c r="M82" s="84">
-        <v>9003</v>
-      </c>
-      <c r="N82" s="84">
-        <v>4</v>
-      </c>
-      <c r="O82" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P82" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q82" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" s="84" t="s">
         <v>185</v>
       </c>
@@ -11493,50 +11825,54 @@
         <v>380</v>
       </c>
       <c r="E83" s="84" t="str">
+        <f t="shared" si="7"/>
+        <v>t-com-auth-lb-rule9005</v>
+      </c>
+      <c r="F83" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-com-auth-lb-rule</v>
+      </c>
+      <c r="G83" s="84" t="str">
+        <f t="shared" si="5"/>
+        <v>t-com-auth-lb-fe</v>
+      </c>
+      <c r="H83" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I83" s="84">
+        <v>9005</v>
+      </c>
+      <c r="J83" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" s="84" t="str">
         <f t="shared" si="6"/>
-        <v>t-com-auth-lb-rule9005</v>
-      </c>
-      <c r="F83" s="84" t="str">
-        <f t="shared" si="4"/>
-        <v>t-com-auth-lb-fe</v>
-      </c>
-      <c r="G83" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H83" s="84">
+        <v>t-com-auth-lb-bp</v>
+      </c>
+      <c r="L83" s="84">
         <v>9005</v>
       </c>
-      <c r="I83" s="84" t="b">
+      <c r="M83" s="84" t="str">
+        <f t="shared" si="9"/>
+        <v>t-com-auth-lb-pb9005</v>
+      </c>
+      <c r="N83" s="84">
+        <v>9005</v>
+      </c>
+      <c r="O83" s="84">
+        <v>4</v>
+      </c>
+      <c r="P83" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q83" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R83" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J83" s="84" t="str">
-        <f t="shared" si="5"/>
-        <v>t-com-auth-lb-bp</v>
-      </c>
-      <c r="K83" s="84">
-        <v>9005</v>
-      </c>
-      <c r="L83" s="84" t="str">
-        <f t="shared" si="7"/>
-        <v>t-com-auth-lb-pb9005</v>
-      </c>
-      <c r="M83" s="84">
-        <v>9005</v>
-      </c>
-      <c r="N83" s="84">
-        <v>4</v>
-      </c>
-      <c r="O83" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P83" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q83" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="74" t="s">
         <v>185</v>
       </c>
@@ -11551,50 +11887,54 @@
         <v>372</v>
       </c>
       <c r="E84" s="74" t="str">
+        <f t="shared" si="7"/>
+        <v>t-bdp-slap-lb-rule443</v>
+      </c>
+      <c r="F84" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-bdp-slap-lb-rule</v>
+      </c>
+      <c r="G84" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>t-bdp-slap-lb-fe</v>
+      </c>
+      <c r="H84" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I84" s="74">
+        <v>443</v>
+      </c>
+      <c r="J84" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" s="74" t="str">
         <f t="shared" si="6"/>
-        <v>t-bdp-slap-lb-rule443</v>
-      </c>
-      <c r="F84" s="74" t="str">
-        <f t="shared" si="4"/>
-        <v>t-bdp-slap-lb-fe</v>
-      </c>
-      <c r="G84" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H84" s="74">
+        <v>t-bdp-slap-lb-bp</v>
+      </c>
+      <c r="L84" s="74">
         <v>443</v>
       </c>
-      <c r="I84" s="74" t="b">
+      <c r="M84" s="74" t="str">
+        <f t="shared" si="9"/>
+        <v>t-bdp-slap-lb-pb443</v>
+      </c>
+      <c r="N84" s="74">
+        <v>443</v>
+      </c>
+      <c r="O84" s="74">
+        <v>4</v>
+      </c>
+      <c r="P84" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q84" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R84" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J84" s="74" t="str">
-        <f t="shared" si="5"/>
-        <v>t-bdp-slap-lb-bp</v>
-      </c>
-      <c r="K84" s="74">
-        <v>443</v>
-      </c>
-      <c r="L84" s="74" t="str">
-        <f t="shared" si="7"/>
-        <v>t-bdp-slap-lb-pb443</v>
-      </c>
-      <c r="M84" s="74">
-        <v>443</v>
-      </c>
-      <c r="N84" s="74">
-        <v>4</v>
-      </c>
-      <c r="O84" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P84" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q84" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="84" t="s">
         <v>185</v>
       </c>
@@ -11609,50 +11949,54 @@
         <v>371</v>
       </c>
       <c r="E85" s="84" t="str">
+        <f t="shared" si="7"/>
+        <v>t-bdp-cxmadm-lb-rule443</v>
+      </c>
+      <c r="F85" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-bdp-cxmadm-lb-rule</v>
+      </c>
+      <c r="G85" s="84" t="str">
+        <f t="shared" si="5"/>
+        <v>t-bdp-cxmadm-lb-fe</v>
+      </c>
+      <c r="H85" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I85" s="84">
+        <v>443</v>
+      </c>
+      <c r="J85" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" s="84" t="str">
         <f t="shared" si="6"/>
-        <v>t-bdp-cxmadm-lb-rule443</v>
-      </c>
-      <c r="F85" s="84" t="str">
-        <f t="shared" si="4"/>
-        <v>t-bdp-cxmadm-lb-fe</v>
-      </c>
-      <c r="G85" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H85" s="84">
+        <v>t-bdp-cxmadm-lb-bp</v>
+      </c>
+      <c r="L85" s="84">
         <v>443</v>
       </c>
-      <c r="I85" s="84" t="b">
+      <c r="M85" s="84" t="str">
+        <f t="shared" si="9"/>
+        <v>t-bdp-cxmadm-lb-pb443</v>
+      </c>
+      <c r="N85" s="84">
+        <v>443</v>
+      </c>
+      <c r="O85" s="84">
+        <v>4</v>
+      </c>
+      <c r="P85" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q85" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R85" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J85" s="84" t="str">
-        <f t="shared" si="5"/>
-        <v>t-bdp-cxmadm-lb-bp</v>
-      </c>
-      <c r="K85" s="84">
-        <v>443</v>
-      </c>
-      <c r="L85" s="84" t="str">
-        <f t="shared" si="7"/>
-        <v>t-bdp-cxmadm-lb-pb443</v>
-      </c>
-      <c r="M85" s="84">
-        <v>443</v>
-      </c>
-      <c r="N85" s="84">
-        <v>4</v>
-      </c>
-      <c r="O85" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P85" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q85" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="74" t="s">
         <v>185</v>
       </c>
@@ -11667,50 +12011,54 @@
         <v>388</v>
       </c>
       <c r="E86" s="74" t="str">
+        <f t="shared" si="7"/>
+        <v>t-bdp-crkweb-lb-rule443</v>
+      </c>
+      <c r="F86" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-bdp-crkweb-lb-rule</v>
+      </c>
+      <c r="G86" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>t-bdp-crkweb-lb-fe</v>
+      </c>
+      <c r="H86" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I86" s="74">
+        <v>443</v>
+      </c>
+      <c r="J86" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" s="74" t="str">
         <f t="shared" si="6"/>
-        <v>t-bdp-crkweb-lb-rule443</v>
-      </c>
-      <c r="F86" s="74" t="str">
-        <f t="shared" si="4"/>
-        <v>t-bdp-crkweb-lb-fe</v>
-      </c>
-      <c r="G86" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H86" s="74">
+        <v>t-bdp-crkweb-lb-bp</v>
+      </c>
+      <c r="L86" s="74">
         <v>443</v>
       </c>
-      <c r="I86" s="74" t="b">
+      <c r="M86" s="74" t="str">
+        <f t="shared" si="9"/>
+        <v>t-bdp-crkweb-lb-pb443</v>
+      </c>
+      <c r="N86" s="74">
+        <v>443</v>
+      </c>
+      <c r="O86" s="74">
+        <v>4</v>
+      </c>
+      <c r="P86" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q86" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R86" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J86" s="74" t="str">
-        <f t="shared" si="5"/>
-        <v>t-bdp-crkweb-lb-bp</v>
-      </c>
-      <c r="K86" s="74">
-        <v>443</v>
-      </c>
-      <c r="L86" s="74" t="str">
-        <f t="shared" si="7"/>
-        <v>t-bdp-crkweb-lb-pb443</v>
-      </c>
-      <c r="M86" s="74">
-        <v>443</v>
-      </c>
-      <c r="N86" s="74">
-        <v>4</v>
-      </c>
-      <c r="O86" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P86" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q86" s="74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" s="84" t="s">
         <v>185</v>
       </c>
@@ -11725,50 +12073,54 @@
         <v>390</v>
       </c>
       <c r="E87" s="84" t="str">
+        <f t="shared" si="7"/>
+        <v>t-bdp-crkml-lb-rule8082</v>
+      </c>
+      <c r="F87" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-bdp-crkml-lb-rule</v>
+      </c>
+      <c r="G87" s="84" t="str">
+        <f t="shared" si="5"/>
+        <v>t-bdp-crkml-lb-fe</v>
+      </c>
+      <c r="H87" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I87" s="84">
+        <v>8082</v>
+      </c>
+      <c r="J87" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K87" s="84" t="str">
         <f t="shared" si="6"/>
-        <v>t-bdp-crkml-lb-rule8082</v>
-      </c>
-      <c r="F87" s="84" t="str">
-        <f t="shared" si="4"/>
-        <v>t-bdp-crkml-lb-fe</v>
-      </c>
-      <c r="G87" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H87" s="84">
+        <v>t-bdp-crkml-lb-bp</v>
+      </c>
+      <c r="L87" s="84">
         <v>8082</v>
       </c>
-      <c r="I87" s="84" t="b">
+      <c r="M87" s="84" t="str">
+        <f t="shared" si="9"/>
+        <v>t-bdp-crkml-lb-pb8082</v>
+      </c>
+      <c r="N87" s="84">
+        <v>8082</v>
+      </c>
+      <c r="O87" s="84">
+        <v>4</v>
+      </c>
+      <c r="P87" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q87" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R87" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="J87" s="84" t="str">
-        <f t="shared" si="5"/>
-        <v>t-bdp-crkml-lb-bp</v>
-      </c>
-      <c r="K87" s="84">
-        <v>8082</v>
-      </c>
-      <c r="L87" s="84" t="str">
-        <f t="shared" si="7"/>
-        <v>t-bdp-crkml-lb-pb8082</v>
-      </c>
-      <c r="M87" s="84">
-        <v>8082</v>
-      </c>
-      <c r="N87" s="84">
-        <v>4</v>
-      </c>
-      <c r="O87" s="84" t="s">
-        <v>125</v>
-      </c>
-      <c r="P87" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q87" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" s="74" t="s">
         <v>185</v>
       </c>
@@ -11783,52 +12135,56 @@
         <v>389</v>
       </c>
       <c r="E88" s="74" t="str">
+        <f t="shared" si="7"/>
+        <v>t-bdp-crkap-lb-rule8085</v>
+      </c>
+      <c r="F88" s="74" t="str">
+        <f t="shared" si="8"/>
+        <v>t-bdp-crkap-lb-rule</v>
+      </c>
+      <c r="G88" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>t-bdp-crkap-lb-fe</v>
+      </c>
+      <c r="H88" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I88" s="74">
+        <v>8085</v>
+      </c>
+      <c r="J88" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" s="74" t="str">
         <f t="shared" si="6"/>
-        <v>t-bdp-crkap-lb-rule8085</v>
-      </c>
-      <c r="F88" s="74" t="str">
-        <f t="shared" si="4"/>
-        <v>t-bdp-crkap-lb-fe</v>
-      </c>
-      <c r="G88" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H88" s="74">
+        <v>t-bdp-crkap-lb-bp</v>
+      </c>
+      <c r="L88" s="74">
         <v>8085</v>
       </c>
-      <c r="I88" s="74" t="b">
+      <c r="M88" s="74" t="str">
+        <f t="shared" si="9"/>
+        <v>t-bdp-crkap-lb-pb8085</v>
+      </c>
+      <c r="N88" s="74">
+        <v>8085</v>
+      </c>
+      <c r="O88" s="74">
+        <v>4</v>
+      </c>
+      <c r="P88" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q88" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R88" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J88" s="74" t="str">
-        <f t="shared" si="5"/>
-        <v>t-bdp-crkap-lb-bp</v>
-      </c>
-      <c r="K88" s="74">
-        <v>8085</v>
-      </c>
-      <c r="L88" s="74" t="str">
-        <f t="shared" si="7"/>
-        <v>t-bdp-crkap-lb-pb8085</v>
-      </c>
-      <c r="M88" s="74">
-        <v>8085</v>
-      </c>
-      <c r="N88" s="74">
-        <v>4</v>
-      </c>
-      <c r="O88" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="P88" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q88" s="74" t="b">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q88" xr:uid="{A4BC862D-08E7-4593-9A34-4D2B508CF25B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q50">
+  <autoFilter ref="A1:R88" xr:uid="{A4BC862D-08E7-4593-9A34-4D2B508CF25B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R50">
       <sortCondition descending="1" ref="B1"/>
     </sortState>
   </autoFilter>
@@ -33388,7 +33744,7 @@
         <v>374</v>
       </c>
       <c r="E66" s="85" t="str">
-        <f t="shared" ref="E66:E97" si="2">SUBSTITUTE(D66, "hazr-", "")&amp;"-pb"&amp;G66</f>
+        <f t="shared" ref="E66:E88" si="2">SUBSTITUTE(D66, "hazr-", "")&amp;"-pb"&amp;G66</f>
         <v>t-dip-ap-lb-pb8200</v>
       </c>
       <c r="F66" s="84" t="s">
@@ -34138,9 +34494,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -34288,26 +34647,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34331,9 +34679,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FE903F-F1A6-4E5B-8097-133FF63573C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0427039E-54CD-4D45-8059-E592C7171A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6961,7 +6961,7 @@
         <v>363</v>
       </c>
       <c r="E3" s="74" t="str">
-        <f t="shared" ref="E3:F66" si="0">SUBSTITUTE(D3, "hazr-", "")&amp;"-rule"&amp;N3</f>
+        <f t="shared" ref="E3:E66" si="0">SUBSTITUTE(D3, "hazr-", "")&amp;"-rule"&amp;N3</f>
         <v>t-dtg-web-lb-rule8081</v>
       </c>
       <c r="F3" s="74" t="str">
@@ -8015,10 +8015,7 @@
         <v>365</v>
       </c>
       <c r="E20" s="86"/>
-      <c r="F20" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdstap-lb-rule</v>
-      </c>
+      <c r="F20" s="74"/>
       <c r="G20" s="86" t="str">
         <f t="shared" si="3"/>
         <v>t-dtg-cdstap-lb-fe</v>
@@ -8499,10 +8496,7 @@
         <v>385</v>
       </c>
       <c r="E28" s="84"/>
-      <c r="F28" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-doip-web-lb-rule</v>
-      </c>
+      <c r="F28" s="74"/>
       <c r="G28" s="84" t="str">
         <f t="shared" si="3"/>
         <v>t-doip-web-lb-fe</v>
@@ -8549,10 +8543,7 @@
         <v>386</v>
       </c>
       <c r="E29" s="86"/>
-      <c r="F29" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-doip-ap-lb-rule</v>
-      </c>
+      <c r="F29" s="74"/>
       <c r="G29" s="86" t="str">
         <f t="shared" si="3"/>
         <v>t-doip-ap-lb-fe</v>
@@ -8599,10 +8590,7 @@
         <v>387</v>
       </c>
       <c r="E30" s="84"/>
-      <c r="F30" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-doip-adm-lb-rule</v>
-      </c>
+      <c r="F30" s="74"/>
       <c r="G30" s="84" t="str">
         <f t="shared" si="3"/>
         <v>t-doip-adm-lb-fe</v>
@@ -10633,10 +10621,7 @@
         <v>375</v>
       </c>
       <c r="E63" s="74"/>
-      <c r="F63" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-flk-lb-rule</v>
-      </c>
+      <c r="F63" s="74"/>
       <c r="G63" s="74" t="str">
         <f t="shared" si="5"/>
         <v>t-dip-flk-lb-fe</v>
@@ -10869,7 +10854,7 @@
         <v>374</v>
       </c>
       <c r="E67" s="84" t="str">
-        <f t="shared" ref="E67:F88" si="7">SUBSTITUTE(D67, "hazr-", "")&amp;"-rule"&amp;N67</f>
+        <f t="shared" ref="E67:E88" si="7">SUBSTITUTE(D67, "hazr-", "")&amp;"-rule"&amp;N67</f>
         <v>t-dip-ap-lb-rule8300</v>
       </c>
       <c r="F67" s="74" t="str">
@@ -11427,10 +11412,7 @@
         <v>383</v>
       </c>
       <c r="E76" s="84"/>
-      <c r="F76" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-cs-chtweb-lb-rule</v>
-      </c>
+      <c r="F76" s="74"/>
       <c r="G76" s="84" t="str">
         <f t="shared" si="5"/>
         <v>t-cs-chtweb-lb-fe</v>
@@ -11477,10 +11459,7 @@
         <v>384</v>
       </c>
       <c r="E77" s="74"/>
-      <c r="F77" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-cs-chtintweb-lb-rule</v>
-      </c>
+      <c r="F77" s="74"/>
       <c r="G77" s="74" t="str">
         <f t="shared" si="5"/>
         <v>t-cs-chtintweb-lb-fe</v>
@@ -11527,10 +11506,7 @@
         <v>382</v>
       </c>
       <c r="E78" s="84"/>
-      <c r="F78" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-cs-chtap-lb-rule</v>
-      </c>
+      <c r="F78" s="74"/>
       <c r="G78" s="84" t="str">
         <f t="shared" si="5"/>
         <v>t-cs-chtap-lb-fe</v>
@@ -34494,12 +34470,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -34647,15 +34620,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34679,17 +34663,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260422_리소스배포_테스트.xlsx
+++ b/서버정보/20260422_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0427039E-54CD-4D45-8059-E592C7171A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4380FE-265F-4B6A-950A-78B9DBBC2FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">LB!$B$1:$Q$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">LB_Probe!$A$1:$J$88</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">LB_Rule!$A$1:$R$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">LB_Rule!$A$1:$Q$88</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1573,7 +1573,7 @@
     <author>zenithn</author>
   </authors>
   <commentList>
-    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{6D097393-523D-44A5-B559-F99AED6EE617}">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{6D097393-523D-44A5-B559-F99AED6EE617}">
       <text>
         <r>
           <rPr>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4783" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4782" uniqueCount="632">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3967,10 +3967,6 @@
   </si>
   <si>
     <t>hazr-t-cs-rg</t>
-  </si>
-  <si>
-    <t>OldRuleName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6809,26 +6805,25 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BC862D-08E7-4593-9A34-4D2B508CF25B}">
-  <dimension ref="A1:R88"/>
+  <dimension ref="A1:Q88"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="22" customWidth="1"/>
-    <col min="21" max="21" width="13.875" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22" customWidth="1"/>
+    <col min="20" max="20" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
@@ -6845,46 +6840,43 @@
         <v>118</v>
       </c>
       <c r="F1" s="77" t="s">
-        <v>632</v>
-      </c>
-      <c r="G1" s="77" t="s">
         <v>104</v>
       </c>
+      <c r="G1" s="79" t="s">
+        <v>120</v>
+      </c>
       <c r="H1" s="79" t="s">
-        <v>120</v>
-      </c>
-      <c r="I1" s="79" t="s">
         <v>119</v>
       </c>
-      <c r="J1" s="102" t="s">
+      <c r="I1" s="102" t="s">
         <v>130</v>
       </c>
-      <c r="K1" s="77" t="s">
+      <c r="J1" s="77" t="s">
         <v>110</v>
       </c>
-      <c r="L1" s="79" t="s">
+      <c r="K1" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="M1" s="102" t="s">
+      <c r="L1" s="102" t="s">
         <v>112</v>
       </c>
-      <c r="N1" s="72" t="s">
+      <c r="M1" s="72" t="s">
         <v>629</v>
       </c>
-      <c r="O1" s="102" t="s">
+      <c r="N1" s="102" t="s">
         <v>123</v>
       </c>
-      <c r="P1" s="79" t="s">
+      <c r="O1" s="79" t="s">
         <v>124</v>
       </c>
+      <c r="P1" s="102" t="s">
+        <v>129</v>
+      </c>
       <c r="Q1" s="102" t="s">
-        <v>129</v>
-      </c>
-      <c r="R1" s="102" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="74" t="s">
         <v>185</v>
       </c>
@@ -6899,54 +6891,50 @@
         <v>363</v>
       </c>
       <c r="E2" s="74" t="str">
-        <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-rule"&amp;N2</f>
+        <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-rule"&amp;M2</f>
         <v>t-dtg-web-lb-rule8080</v>
       </c>
       <c r="F2" s="74" t="str">
-        <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-rule"</f>
-        <v>t-dtg-web-lb-rule</v>
-      </c>
-      <c r="G2" s="74" t="str">
         <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-web-lb-fe</v>
       </c>
-      <c r="H2" s="74" t="s">
+      <c r="G2" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I2" s="74">
+      <c r="H2" s="74">
         <v>8080</v>
       </c>
-      <c r="J2" s="74" t="b">
+      <c r="I2" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K2" s="74" t="str">
+      <c r="J2" s="74" t="str">
         <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-web-lb-bp</v>
       </c>
-      <c r="L2" s="74">
+      <c r="K2" s="74">
         <v>8080</v>
       </c>
-      <c r="M2" s="74" t="str">
-        <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-pb"&amp;IF(N2="", "", N2)</f>
+      <c r="L2" s="74" t="str">
+        <f>SUBSTITUTE(D2, "hazr-", "")&amp;"-pb"&amp;IF(M2="", "", M2)</f>
         <v>t-dtg-web-lb-pb8080</v>
       </c>
+      <c r="M2" s="74">
+        <v>8080</v>
+      </c>
       <c r="N2" s="74">
-        <v>8080</v>
-      </c>
-      <c r="O2" s="74">
         <v>4</v>
       </c>
-      <c r="P2" s="74" t="s">
+      <c r="O2" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P2" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q2" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="74" t="s">
         <v>185</v>
       </c>
@@ -6961,54 +6949,50 @@
         <v>363</v>
       </c>
       <c r="E3" s="74" t="str">
-        <f t="shared" ref="E3:E66" si="0">SUBSTITUTE(D3, "hazr-", "")&amp;"-rule"&amp;N3</f>
+        <f>SUBSTITUTE(D3, "hazr-", "")&amp;"-rule"&amp;M3</f>
         <v>t-dtg-web-lb-rule8081</v>
       </c>
       <c r="F3" s="74" t="str">
-        <f t="shared" ref="F3:F66" si="1">SUBSTITUTE(D3, "hazr-", "")&amp;"-rule"</f>
-        <v>t-dtg-web-lb-rule</v>
-      </c>
-      <c r="G3" s="74" t="str">
         <f>SUBSTITUTE(D3, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-web-lb-fe</v>
       </c>
-      <c r="H3" s="74" t="s">
+      <c r="G3" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I3" s="74">
+      <c r="H3" s="74">
         <v>8081</v>
       </c>
-      <c r="J3" s="74" t="b">
+      <c r="I3" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K3" s="74" t="str">
+      <c r="J3" s="74" t="str">
         <f>SUBSTITUTE(D3, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-web-lb-bp</v>
       </c>
-      <c r="L3" s="74">
+      <c r="K3" s="74">
         <v>8081</v>
       </c>
-      <c r="M3" s="74" t="str">
-        <f t="shared" ref="M3:M66" si="2">SUBSTITUTE(D3, "hazr-", "")&amp;"-pb"&amp;IF(N3="", "", N3)</f>
+      <c r="L3" s="74" t="str">
+        <f>SUBSTITUTE(D3, "hazr-", "")&amp;"-pb"&amp;IF(M3="", "", M3)</f>
         <v>t-dtg-web-lb-pb8081</v>
       </c>
+      <c r="M3" s="74">
+        <v>8081</v>
+      </c>
       <c r="N3" s="74">
-        <v>8081</v>
-      </c>
-      <c r="O3" s="74">
         <v>4</v>
       </c>
-      <c r="P3" s="74" t="s">
+      <c r="O3" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P3" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q3" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="84" t="s">
         <v>185</v>
       </c>
@@ -7023,54 +7007,50 @@
         <v>360</v>
       </c>
       <c r="E4" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D4, "hazr-", "")&amp;"-rule"&amp;M4</f>
         <v>t-dtg-mq-lb-rule1883</v>
       </c>
-      <c r="F4" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-mq-lb-rule</v>
-      </c>
-      <c r="G4" s="84" t="str">
+      <c r="F4" s="84" t="str">
         <f>SUBSTITUTE(D4, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-mq-lb-fe</v>
       </c>
-      <c r="H4" s="84" t="s">
+      <c r="G4" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I4" s="84">
+      <c r="H4" s="84">
         <v>1883</v>
       </c>
-      <c r="J4" s="84" t="b">
+      <c r="I4" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K4" s="84" t="str">
+      <c r="J4" s="84" t="str">
         <f>SUBSTITUTE(D4, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-mq-lb-bp</v>
       </c>
-      <c r="L4" s="84">
+      <c r="K4" s="84">
         <v>1883</v>
       </c>
-      <c r="M4" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L4" s="84" t="str">
+        <f>SUBSTITUTE(D4, "hazr-", "")&amp;"-pb"&amp;IF(M4="", "", M4)</f>
         <v>t-dtg-mq-lb-pb1883</v>
       </c>
+      <c r="M4" s="84">
+        <v>1883</v>
+      </c>
       <c r="N4" s="84">
-        <v>1883</v>
-      </c>
-      <c r="O4" s="84">
         <v>4</v>
       </c>
-      <c r="P4" s="84" t="s">
+      <c r="O4" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P4" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q4" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="84" t="s">
         <v>185</v>
       </c>
@@ -7085,54 +7065,50 @@
         <v>360</v>
       </c>
       <c r="E5" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D5, "hazr-", "")&amp;"-rule"&amp;M5</f>
         <v>t-dtg-mq-lb-rule1884</v>
       </c>
-      <c r="F5" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-mq-lb-rule</v>
-      </c>
-      <c r="G5" s="84" t="str">
+      <c r="F5" s="84" t="str">
         <f>SUBSTITUTE(D5, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-mq-lb-fe</v>
       </c>
-      <c r="H5" s="84" t="s">
+      <c r="G5" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I5" s="84">
+      <c r="H5" s="84">
         <v>1884</v>
       </c>
-      <c r="J5" s="84" t="b">
+      <c r="I5" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K5" s="84" t="str">
+      <c r="J5" s="84" t="str">
         <f>SUBSTITUTE(D5, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-mq-lb-bp</v>
       </c>
-      <c r="L5" s="84">
+      <c r="K5" s="84">
         <v>1884</v>
       </c>
-      <c r="M5" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L5" s="84" t="str">
+        <f>SUBSTITUTE(D5, "hazr-", "")&amp;"-pb"&amp;IF(M5="", "", M5)</f>
         <v>t-dtg-mq-lb-pb1884</v>
       </c>
+      <c r="M5" s="84">
+        <v>1884</v>
+      </c>
       <c r="N5" s="84">
-        <v>1884</v>
-      </c>
-      <c r="O5" s="84">
         <v>4</v>
       </c>
-      <c r="P5" s="84" t="s">
+      <c r="O5" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P5" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q5" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="86" t="s">
         <v>185</v>
       </c>
@@ -7147,54 +7123,50 @@
         <v>356</v>
       </c>
       <c r="E6" s="86" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D6, "hazr-", "")&amp;"-rule"&amp;M6</f>
         <v>t-dtg-ingap-lb-rule8081</v>
       </c>
-      <c r="F6" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-ingap-lb-rule</v>
-      </c>
-      <c r="G6" s="86" t="str">
-        <f t="shared" ref="G6:G50" si="3">SUBSTITUTE(D6, "hazr-", "")&amp;"-fe"</f>
+      <c r="F6" s="86" t="str">
+        <f>SUBSTITUTE(D6, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-ingap-lb-fe</v>
       </c>
-      <c r="H6" s="86" t="s">
+      <c r="G6" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="I6" s="86">
+      <c r="H6" s="86">
         <v>8081</v>
       </c>
-      <c r="J6" s="86" t="b">
+      <c r="I6" s="86" t="b">
         <v>0</v>
       </c>
-      <c r="K6" s="86" t="str">
+      <c r="J6" s="86" t="str">
         <f>SUBSTITUTE(D6, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-ingap-lb-bp</v>
       </c>
-      <c r="L6" s="86">
+      <c r="K6" s="86">
         <v>8081</v>
       </c>
-      <c r="M6" s="86" t="str">
-        <f t="shared" si="2"/>
+      <c r="L6" s="86" t="str">
+        <f>SUBSTITUTE(D6, "hazr-", "")&amp;"-pb"&amp;IF(M6="", "", M6)</f>
         <v>t-dtg-ingap-lb-pb8081</v>
       </c>
+      <c r="M6" s="86">
+        <v>8081</v>
+      </c>
       <c r="N6" s="86">
-        <v>8081</v>
-      </c>
-      <c r="O6" s="86">
         <v>4</v>
       </c>
-      <c r="P6" s="86" t="s">
+      <c r="O6" s="86" t="s">
         <v>125</v>
       </c>
+      <c r="P6" s="86" t="b">
+        <v>1</v>
+      </c>
       <c r="Q6" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" s="86" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="84" t="s">
         <v>185</v>
       </c>
@@ -7209,54 +7181,50 @@
         <v>359</v>
       </c>
       <c r="E7" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D7, "hazr-", "")&amp;"-rule"&amp;M7</f>
         <v>t-dtg-geoap-lb-rule8089</v>
       </c>
-      <c r="F7" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-geoap-lb-rule</v>
-      </c>
-      <c r="G7" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F7" s="84" t="str">
+        <f>SUBSTITUTE(D7, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-geoap-lb-fe</v>
       </c>
-      <c r="H7" s="84" t="s">
+      <c r="G7" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I7" s="84">
+      <c r="H7" s="84">
         <v>8089</v>
       </c>
-      <c r="J7" s="84" t="b">
+      <c r="I7" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K7" s="84" t="str">
-        <f t="shared" ref="K7:K50" si="4">SUBSTITUTE(D7, "hazr-", "")&amp;"-bp"</f>
+      <c r="J7" s="84" t="str">
+        <f>SUBSTITUTE(D7, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-geoap-lb-bp</v>
       </c>
-      <c r="L7" s="84">
+      <c r="K7" s="84">
         <v>8089</v>
       </c>
-      <c r="M7" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L7" s="84" t="str">
+        <f>SUBSTITUTE(D7, "hazr-", "")&amp;"-pb"&amp;IF(M7="", "", M7)</f>
         <v>t-dtg-geoap-lb-pb8089</v>
       </c>
+      <c r="M7" s="84">
+        <v>8089</v>
+      </c>
       <c r="N7" s="84">
-        <v>8089</v>
-      </c>
-      <c r="O7" s="84">
         <v>4</v>
       </c>
-      <c r="P7" s="84" t="s">
+      <c r="O7" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P7" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q7" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="84" t="s">
         <v>185</v>
       </c>
@@ -7271,54 +7239,50 @@
         <v>359</v>
       </c>
       <c r="E8" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D8, "hazr-", "")&amp;"-rule"&amp;M8</f>
         <v>t-dtg-geoap-lb-rule9089</v>
       </c>
-      <c r="F8" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-geoap-lb-rule</v>
-      </c>
-      <c r="G8" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F8" s="84" t="str">
+        <f>SUBSTITUTE(D8, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-geoap-lb-fe</v>
       </c>
-      <c r="H8" s="84" t="s">
+      <c r="G8" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="84">
+      <c r="H8" s="84">
         <v>9089</v>
       </c>
-      <c r="J8" s="84" t="b">
+      <c r="I8" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K8" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J8" s="84" t="str">
+        <f>SUBSTITUTE(D8, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-geoap-lb-bp</v>
       </c>
-      <c r="L8" s="84">
+      <c r="K8" s="84">
         <v>9089</v>
       </c>
-      <c r="M8" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L8" s="84" t="str">
+        <f>SUBSTITUTE(D8, "hazr-", "")&amp;"-pb"&amp;IF(M8="", "", M8)</f>
         <v>t-dtg-geoap-lb-pb9089</v>
       </c>
+      <c r="M8" s="84">
+        <v>9089</v>
+      </c>
       <c r="N8" s="84">
-        <v>9089</v>
-      </c>
-      <c r="O8" s="84">
         <v>4</v>
       </c>
-      <c r="P8" s="84" t="s">
+      <c r="O8" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P8" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q8" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="74" t="s">
         <v>185</v>
       </c>
@@ -7333,54 +7297,50 @@
         <v>358</v>
       </c>
       <c r="E9" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D9, "hazr-", "")&amp;"-rule"&amp;M9</f>
         <v>t-dtg-extgeoap-lb-rule3660</v>
       </c>
       <c r="F9" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-extgeoap-lb-rule</v>
-      </c>
-      <c r="G9" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D9, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-extgeoap-lb-fe</v>
       </c>
-      <c r="H9" s="74" t="s">
+      <c r="G9" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="74">
+      <c r="H9" s="74">
         <v>3660</v>
       </c>
-      <c r="J9" s="74" t="b">
+      <c r="I9" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K9" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J9" s="74" t="str">
+        <f>SUBSTITUTE(D9, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-extgeoap-lb-bp</v>
       </c>
-      <c r="L9" s="74">
+      <c r="K9" s="74">
         <v>3660</v>
       </c>
-      <c r="M9" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L9" s="74" t="str">
+        <f>SUBSTITUTE(D9, "hazr-", "")&amp;"-pb"&amp;IF(M9="", "", M9)</f>
         <v>t-dtg-extgeoap-lb-pb3660</v>
       </c>
+      <c r="M9" s="74">
+        <v>3660</v>
+      </c>
       <c r="N9" s="74">
-        <v>3660</v>
-      </c>
-      <c r="O9" s="74">
         <v>4</v>
       </c>
-      <c r="P9" s="74" t="s">
+      <c r="O9" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P9" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q9" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
         <v>185</v>
       </c>
@@ -7395,54 +7355,50 @@
         <v>358</v>
       </c>
       <c r="E10" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D10, "hazr-", "")&amp;"-rule"&amp;M10</f>
         <v>t-dtg-extgeoap-lb-rule3661</v>
       </c>
       <c r="F10" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-extgeoap-lb-rule</v>
-      </c>
-      <c r="G10" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D10, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-extgeoap-lb-fe</v>
       </c>
-      <c r="H10" s="74" t="s">
+      <c r="G10" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I10" s="74">
+      <c r="H10" s="74">
         <v>3661</v>
       </c>
-      <c r="J10" s="74" t="b">
+      <c r="I10" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K10" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J10" s="74" t="str">
+        <f>SUBSTITUTE(D10, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-extgeoap-lb-bp</v>
       </c>
-      <c r="L10" s="74">
+      <c r="K10" s="74">
         <v>3661</v>
       </c>
-      <c r="M10" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L10" s="74" t="str">
+        <f>SUBSTITUTE(D10, "hazr-", "")&amp;"-pb"&amp;IF(M10="", "", M10)</f>
         <v>t-dtg-extgeoap-lb-pb3661</v>
       </c>
+      <c r="M10" s="74">
+        <v>3661</v>
+      </c>
       <c r="N10" s="74">
-        <v>3661</v>
-      </c>
-      <c r="O10" s="74">
         <v>4</v>
       </c>
-      <c r="P10" s="74" t="s">
+      <c r="O10" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P10" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q10" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="84" t="s">
         <v>185</v>
       </c>
@@ -7457,54 +7413,50 @@
         <v>369</v>
       </c>
       <c r="E11" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D11, "hazr-", "")&amp;"-rule"&amp;M11</f>
         <v>t-dtg-dprweb-lb-rule443</v>
       </c>
-      <c r="F11" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-dprweb-lb-rule</v>
-      </c>
-      <c r="G11" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F11" s="84" t="str">
+        <f>SUBSTITUTE(D11, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-dprweb-lb-fe</v>
       </c>
-      <c r="H11" s="84" t="s">
+      <c r="G11" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I11" s="84">
+      <c r="H11" s="84">
         <v>443</v>
       </c>
-      <c r="J11" s="84" t="b">
+      <c r="I11" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K11" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J11" s="84" t="str">
+        <f>SUBSTITUTE(D11, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-dprweb-lb-bp</v>
       </c>
-      <c r="L11" s="84">
+      <c r="K11" s="84">
         <v>443</v>
       </c>
-      <c r="M11" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L11" s="84" t="str">
+        <f>SUBSTITUTE(D11, "hazr-", "")&amp;"-pb"&amp;IF(M11="", "", M11)</f>
         <v>t-dtg-dprweb-lb-pb443</v>
       </c>
+      <c r="M11" s="84">
+        <v>443</v>
+      </c>
       <c r="N11" s="84">
-        <v>443</v>
-      </c>
-      <c r="O11" s="84">
         <v>4</v>
       </c>
-      <c r="P11" s="84" t="s">
+      <c r="O11" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P11" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q11" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="86" t="s">
         <v>185</v>
       </c>
@@ -7519,54 +7471,50 @@
         <v>370</v>
       </c>
       <c r="E12" s="86" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D12, "hazr-", "")&amp;"-rule"&amp;M12</f>
         <v>t-dtg-dprap-lb-rule8082</v>
       </c>
-      <c r="F12" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-dprap-lb-rule</v>
-      </c>
-      <c r="G12" s="86" t="str">
-        <f t="shared" si="3"/>
+      <c r="F12" s="86" t="str">
+        <f>SUBSTITUTE(D12, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-dprap-lb-fe</v>
       </c>
-      <c r="H12" s="86" t="s">
+      <c r="G12" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="I12" s="86">
+      <c r="H12" s="86">
         <v>8082</v>
       </c>
-      <c r="J12" s="86" t="b">
+      <c r="I12" s="86" t="b">
         <v>0</v>
       </c>
-      <c r="K12" s="86" t="str">
-        <f t="shared" si="4"/>
+      <c r="J12" s="86" t="str">
+        <f>SUBSTITUTE(D12, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-dprap-lb-bp</v>
       </c>
-      <c r="L12" s="86">
+      <c r="K12" s="86">
         <v>8082</v>
       </c>
-      <c r="M12" s="86" t="str">
-        <f t="shared" si="2"/>
+      <c r="L12" s="86" t="str">
+        <f>SUBSTITUTE(D12, "hazr-", "")&amp;"-pb"&amp;IF(M12="", "", M12)</f>
         <v>t-dtg-dprap-lb-pb8082</v>
       </c>
+      <c r="M12" s="86">
+        <v>8082</v>
+      </c>
       <c r="N12" s="86">
-        <v>8082</v>
-      </c>
-      <c r="O12" s="86">
         <v>4</v>
       </c>
-      <c r="P12" s="86" t="s">
+      <c r="O12" s="86" t="s">
         <v>125</v>
       </c>
+      <c r="P12" s="86" t="b">
+        <v>1</v>
+      </c>
       <c r="Q12" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="R12" s="86" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="84" t="s">
         <v>185</v>
       </c>
@@ -7581,54 +7529,50 @@
         <v>368</v>
       </c>
       <c r="E13" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D13, "hazr-", "")&amp;"-rule"&amp;M13</f>
         <v>t-dtg-diosweb-lb-rule443</v>
       </c>
-      <c r="F13" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-diosweb-lb-rule</v>
-      </c>
-      <c r="G13" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F13" s="84" t="str">
+        <f>SUBSTITUTE(D13, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-diosweb-lb-fe</v>
       </c>
-      <c r="H13" s="84" t="s">
+      <c r="G13" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I13" s="84">
+      <c r="H13" s="84">
         <v>443</v>
       </c>
-      <c r="J13" s="84" t="b">
+      <c r="I13" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K13" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J13" s="84" t="str">
+        <f>SUBSTITUTE(D13, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-diosweb-lb-bp</v>
       </c>
-      <c r="L13" s="84">
+      <c r="K13" s="84">
         <v>443</v>
       </c>
-      <c r="M13" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L13" s="84" t="str">
+        <f>SUBSTITUTE(D13, "hazr-", "")&amp;"-pb"&amp;IF(M13="", "", M13)</f>
         <v>t-dtg-diosweb-lb-pb443</v>
       </c>
+      <c r="M13" s="84">
+        <v>443</v>
+      </c>
       <c r="N13" s="84">
-        <v>443</v>
-      </c>
-      <c r="O13" s="84">
         <v>4</v>
       </c>
-      <c r="P13" s="84" t="s">
+      <c r="O13" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P13" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q13" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R13" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="86" t="s">
         <v>185</v>
       </c>
@@ -7643,54 +7587,50 @@
         <v>367</v>
       </c>
       <c r="E14" s="86" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D14, "hazr-", "")&amp;"-rule"&amp;M14</f>
         <v>t-dtg-diosap-lb-rule8080</v>
       </c>
-      <c r="F14" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-diosap-lb-rule</v>
-      </c>
-      <c r="G14" s="86" t="str">
-        <f t="shared" si="3"/>
+      <c r="F14" s="86" t="str">
+        <f>SUBSTITUTE(D14, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-diosap-lb-fe</v>
       </c>
-      <c r="H14" s="86" t="s">
+      <c r="G14" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="I14" s="86">
+      <c r="H14" s="86">
         <v>8080</v>
       </c>
-      <c r="J14" s="86" t="b">
+      <c r="I14" s="86" t="b">
         <v>0</v>
       </c>
-      <c r="K14" s="86" t="str">
-        <f t="shared" si="4"/>
+      <c r="J14" s="86" t="str">
+        <f>SUBSTITUTE(D14, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-diosap-lb-bp</v>
       </c>
-      <c r="L14" s="86">
+      <c r="K14" s="86">
         <v>8080</v>
       </c>
-      <c r="M14" s="86" t="str">
-        <f t="shared" si="2"/>
+      <c r="L14" s="86" t="str">
+        <f>SUBSTITUTE(D14, "hazr-", "")&amp;"-pb"&amp;IF(M14="", "", M14)</f>
         <v>t-dtg-diosap-lb-pb8080</v>
       </c>
+      <c r="M14" s="86">
+        <v>8080</v>
+      </c>
       <c r="N14" s="86">
-        <v>8080</v>
-      </c>
-      <c r="O14" s="86">
         <v>4</v>
       </c>
-      <c r="P14" s="86" t="s">
+      <c r="O14" s="86" t="s">
         <v>125</v>
       </c>
+      <c r="P14" s="86" t="b">
+        <v>1</v>
+      </c>
       <c r="Q14" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="R14" s="86" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="84" t="s">
         <v>185</v>
       </c>
@@ -7705,54 +7645,50 @@
         <v>366</v>
       </c>
       <c r="E15" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D15, "hazr-", "")&amp;"-rule"&amp;M15</f>
         <v>t-dtg-cdsvadm-lb-rule9100</v>
       </c>
-      <c r="F15" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdsvadm-lb-rule</v>
-      </c>
-      <c r="G15" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F15" s="84" t="str">
+        <f>SUBSTITUTE(D15, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-cdsvadm-lb-fe</v>
       </c>
-      <c r="H15" s="84" t="s">
+      <c r="G15" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I15" s="84">
+      <c r="H15" s="84">
         <v>9100</v>
       </c>
-      <c r="J15" s="84" t="b">
+      <c r="I15" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K15" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J15" s="84" t="str">
+        <f>SUBSTITUTE(D15, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-cdsvadm-lb-bp</v>
       </c>
-      <c r="L15" s="84">
+      <c r="K15" s="84">
         <v>9100</v>
       </c>
-      <c r="M15" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L15" s="84" t="str">
+        <f>SUBSTITUTE(D15, "hazr-", "")&amp;"-pb"&amp;IF(M15="", "", M15)</f>
         <v>t-dtg-cdsvadm-lb-pb9100</v>
       </c>
+      <c r="M15" s="84">
+        <v>9100</v>
+      </c>
       <c r="N15" s="84">
-        <v>9100</v>
-      </c>
-      <c r="O15" s="84">
         <v>4</v>
       </c>
-      <c r="P15" s="84" t="s">
+      <c r="O15" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P15" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q15" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R15" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="84" t="s">
         <v>185</v>
       </c>
@@ -7767,54 +7703,50 @@
         <v>366</v>
       </c>
       <c r="E16" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D16, "hazr-", "")&amp;"-rule"&amp;M16</f>
         <v>t-dtg-cdsvadm-lb-rule9300</v>
       </c>
-      <c r="F16" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdsvadm-lb-rule</v>
-      </c>
-      <c r="G16" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F16" s="84" t="str">
+        <f>SUBSTITUTE(D16, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-cdsvadm-lb-fe</v>
       </c>
-      <c r="H16" s="84" t="s">
+      <c r="G16" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I16" s="84">
+      <c r="H16" s="84">
         <v>9300</v>
       </c>
-      <c r="J16" s="84" t="b">
+      <c r="I16" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K16" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J16" s="84" t="str">
+        <f>SUBSTITUTE(D16, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-cdsvadm-lb-bp</v>
       </c>
-      <c r="L16" s="84">
+      <c r="K16" s="84">
         <v>9300</v>
       </c>
-      <c r="M16" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L16" s="84" t="str">
+        <f>SUBSTITUTE(D16, "hazr-", "")&amp;"-pb"&amp;IF(M16="", "", M16)</f>
         <v>t-dtg-cdsvadm-lb-pb9300</v>
       </c>
+      <c r="M16" s="84">
+        <v>9300</v>
+      </c>
       <c r="N16" s="84">
-        <v>9300</v>
-      </c>
-      <c r="O16" s="84">
         <v>4</v>
       </c>
-      <c r="P16" s="84" t="s">
+      <c r="O16" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P16" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q16" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R16" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="84" t="s">
         <v>185</v>
       </c>
@@ -7829,54 +7761,50 @@
         <v>366</v>
       </c>
       <c r="E17" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D17, "hazr-", "")&amp;"-rule"&amp;M17</f>
         <v>t-dtg-cdsvadm-lb-rule9105</v>
       </c>
-      <c r="F17" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdsvadm-lb-rule</v>
-      </c>
-      <c r="G17" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F17" s="84" t="str">
+        <f>SUBSTITUTE(D17, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-cdsvadm-lb-fe</v>
       </c>
-      <c r="H17" s="84" t="s">
+      <c r="G17" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I17" s="84">
+      <c r="H17" s="84">
         <v>9105</v>
       </c>
-      <c r="J17" s="84" t="b">
+      <c r="I17" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K17" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J17" s="84" t="str">
+        <f>SUBSTITUTE(D17, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-cdsvadm-lb-bp</v>
       </c>
-      <c r="L17" s="84">
+      <c r="K17" s="84">
         <v>9105</v>
       </c>
-      <c r="M17" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L17" s="84" t="str">
+        <f>SUBSTITUTE(D17, "hazr-", "")&amp;"-pb"&amp;IF(M17="", "", M17)</f>
         <v>t-dtg-cdsvadm-lb-pb9105</v>
       </c>
+      <c r="M17" s="84">
+        <v>9105</v>
+      </c>
       <c r="N17" s="84">
-        <v>9105</v>
-      </c>
-      <c r="O17" s="84">
         <v>4</v>
       </c>
-      <c r="P17" s="84" t="s">
+      <c r="O17" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P17" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q17" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R17" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="84" t="s">
         <v>185</v>
       </c>
@@ -7891,54 +7819,50 @@
         <v>366</v>
       </c>
       <c r="E18" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D18, "hazr-", "")&amp;"-rule"&amp;M18</f>
         <v>t-dtg-cdsvadm-lb-rule9003</v>
       </c>
-      <c r="F18" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdsvadm-lb-rule</v>
-      </c>
-      <c r="G18" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F18" s="84" t="str">
+        <f>SUBSTITUTE(D18, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-cdsvadm-lb-fe</v>
       </c>
-      <c r="H18" s="84" t="s">
+      <c r="G18" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I18" s="84">
+      <c r="H18" s="84">
         <v>9003</v>
       </c>
-      <c r="J18" s="84" t="b">
+      <c r="I18" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K18" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J18" s="84" t="str">
+        <f>SUBSTITUTE(D18, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-cdsvadm-lb-bp</v>
       </c>
-      <c r="L18" s="84">
+      <c r="K18" s="84">
         <v>9003</v>
       </c>
-      <c r="M18" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L18" s="84" t="str">
+        <f>SUBSTITUTE(D18, "hazr-", "")&amp;"-pb"&amp;IF(M18="", "", M18)</f>
         <v>t-dtg-cdsvadm-lb-pb9003</v>
       </c>
+      <c r="M18" s="84">
+        <v>9003</v>
+      </c>
       <c r="N18" s="84">
-        <v>9003</v>
-      </c>
-      <c r="O18" s="84">
         <v>4</v>
       </c>
-      <c r="P18" s="84" t="s">
+      <c r="O18" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P18" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q18" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R18" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="84" t="s">
         <v>185</v>
       </c>
@@ -7953,54 +7877,50 @@
         <v>366</v>
       </c>
       <c r="E19" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D19, "hazr-", "")&amp;"-rule"&amp;M19</f>
         <v>t-dtg-cdsvadm-lb-rule8088</v>
       </c>
-      <c r="F19" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdsvadm-lb-rule</v>
-      </c>
-      <c r="G19" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F19" s="84" t="str">
+        <f>SUBSTITUTE(D19, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-cdsvadm-lb-fe</v>
       </c>
-      <c r="H19" s="84" t="s">
+      <c r="G19" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I19" s="84">
+      <c r="H19" s="84">
         <v>8088</v>
       </c>
-      <c r="J19" s="84" t="b">
+      <c r="I19" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K19" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J19" s="84" t="str">
+        <f>SUBSTITUTE(D19, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-cdsvadm-lb-bp</v>
       </c>
-      <c r="L19" s="84">
+      <c r="K19" s="84">
         <v>8088</v>
       </c>
-      <c r="M19" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L19" s="84" t="str">
+        <f>SUBSTITUTE(D19, "hazr-", "")&amp;"-pb"&amp;IF(M19="", "", M19)</f>
         <v>t-dtg-cdsvadm-lb-pb8088</v>
       </c>
+      <c r="M19" s="84">
+        <v>8088</v>
+      </c>
       <c r="N19" s="84">
-        <v>8088</v>
-      </c>
-      <c r="O19" s="84">
         <v>4</v>
       </c>
-      <c r="P19" s="84" t="s">
+      <c r="O19" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P19" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q19" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R19" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="86" t="s">
         <v>185</v>
       </c>
@@ -8015,39 +7935,38 @@
         <v>365</v>
       </c>
       <c r="E20" s="86"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="86" t="str">
-        <f t="shared" si="3"/>
+      <c r="F20" s="86" t="str">
+        <f>SUBSTITUTE(D20, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-cdstap-lb-fe</v>
       </c>
-      <c r="H20" s="86" t="s">
+      <c r="G20" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="I20" s="86"/>
-      <c r="J20" s="86" t="b">
+      <c r="H20" s="86"/>
+      <c r="I20" s="86" t="b">
         <v>0</v>
       </c>
-      <c r="K20" s="86" t="str">
-        <f t="shared" si="4"/>
+      <c r="J20" s="86" t="str">
+        <f>SUBSTITUTE(D20, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-cdstap-lb-bp</v>
       </c>
+      <c r="K20" s="86"/>
       <c r="L20" s="86"/>
       <c r="M20" s="86"/>
-      <c r="N20" s="86"/>
-      <c r="O20" s="86">
+      <c r="N20" s="86">
         <v>4</v>
       </c>
-      <c r="P20" s="86" t="s">
+      <c r="O20" s="86" t="s">
         <v>125</v>
       </c>
+      <c r="P20" s="86" t="b">
+        <v>1</v>
+      </c>
       <c r="Q20" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="R20" s="86" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="84" t="s">
         <v>185</v>
       </c>
@@ -8062,54 +7981,50 @@
         <v>364</v>
       </c>
       <c r="E21" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D21, "hazr-", "")&amp;"-rule"&amp;M21</f>
         <v>t-dtg-cdmlap-lb-rule9305</v>
       </c>
-      <c r="F21" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdmlap-lb-rule</v>
-      </c>
-      <c r="G21" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F21" s="84" t="str">
+        <f>SUBSTITUTE(D21, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-cdmlap-lb-fe</v>
       </c>
-      <c r="H21" s="84" t="s">
+      <c r="G21" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I21" s="84">
+      <c r="H21" s="84">
         <v>9305</v>
       </c>
-      <c r="J21" s="84" t="b">
+      <c r="I21" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K21" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J21" s="84" t="str">
+        <f>SUBSTITUTE(D21, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-cdmlap-lb-bp</v>
       </c>
-      <c r="L21" s="84">
+      <c r="K21" s="84">
         <v>9305</v>
       </c>
-      <c r="M21" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L21" s="84" t="str">
+        <f>SUBSTITUTE(D21, "hazr-", "")&amp;"-pb"&amp;IF(M21="", "", M21)</f>
         <v>t-dtg-cdmlap-lb-pb9305</v>
       </c>
+      <c r="M21" s="84">
+        <v>9305</v>
+      </c>
       <c r="N21" s="84">
-        <v>9305</v>
-      </c>
-      <c r="O21" s="84">
         <v>4</v>
       </c>
-      <c r="P21" s="84" t="s">
+      <c r="O21" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P21" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q21" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R21" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="84" t="s">
         <v>185</v>
       </c>
@@ -8124,54 +8039,50 @@
         <v>364</v>
       </c>
       <c r="E22" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D22, "hazr-", "")&amp;"-rule"&amp;M22</f>
         <v>t-dtg-cdmlap-lb-rule9306</v>
       </c>
-      <c r="F22" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdmlap-lb-rule</v>
-      </c>
-      <c r="G22" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F22" s="84" t="str">
+        <f>SUBSTITUTE(D22, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-cdmlap-lb-fe</v>
       </c>
-      <c r="H22" s="84" t="s">
+      <c r="G22" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I22" s="84">
+      <c r="H22" s="84">
         <v>9306</v>
       </c>
-      <c r="J22" s="84" t="b">
+      <c r="I22" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K22" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J22" s="84" t="str">
+        <f>SUBSTITUTE(D22, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-cdmlap-lb-bp</v>
       </c>
-      <c r="L22" s="84">
+      <c r="K22" s="84">
         <v>9306</v>
       </c>
-      <c r="M22" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L22" s="84" t="str">
+        <f>SUBSTITUTE(D22, "hazr-", "")&amp;"-pb"&amp;IF(M22="", "", M22)</f>
         <v>t-dtg-cdmlap-lb-pb9306</v>
       </c>
+      <c r="M22" s="84">
+        <v>9306</v>
+      </c>
       <c r="N22" s="84">
-        <v>9306</v>
-      </c>
-      <c r="O22" s="84">
         <v>4</v>
       </c>
-      <c r="P22" s="84" t="s">
+      <c r="O22" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P22" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q22" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R22" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
         <v>185</v>
       </c>
@@ -8186,54 +8097,50 @@
         <v>357</v>
       </c>
       <c r="E23" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D23, "hazr-", "")&amp;"-rule"&amp;M23</f>
         <v>t-dtg-ap-lb-rule8080</v>
       </c>
       <c r="F23" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-ap-lb-rule</v>
-      </c>
-      <c r="G23" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D23, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-ap-lb-fe</v>
       </c>
-      <c r="H23" s="74" t="s">
+      <c r="G23" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I23" s="74">
+      <c r="H23" s="74">
         <v>8080</v>
       </c>
-      <c r="J23" s="74" t="b">
+      <c r="I23" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K23" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J23" s="74" t="str">
+        <f>SUBSTITUTE(D23, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-ap-lb-bp</v>
       </c>
-      <c r="L23" s="74">
+      <c r="K23" s="74">
         <v>8080</v>
       </c>
-      <c r="M23" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L23" s="74" t="str">
+        <f>SUBSTITUTE(D23, "hazr-", "")&amp;"-pb"&amp;IF(M23="", "", M23)</f>
         <v>t-dtg-ap-lb-pb8080</v>
       </c>
+      <c r="M23" s="74">
+        <v>8080</v>
+      </c>
       <c r="N23" s="74">
-        <v>8080</v>
-      </c>
-      <c r="O23" s="74">
         <v>4</v>
       </c>
-      <c r="P23" s="74" t="s">
+      <c r="O23" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P23" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q23" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R23" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
         <v>185</v>
       </c>
@@ -8248,54 +8155,50 @@
         <v>357</v>
       </c>
       <c r="E24" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D24, "hazr-", "")&amp;"-rule"&amp;M24</f>
         <v>t-dtg-ap-lb-rule9087</v>
       </c>
       <c r="F24" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-ap-lb-rule</v>
-      </c>
-      <c r="G24" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D24, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-ap-lb-fe</v>
       </c>
-      <c r="H24" s="74" t="s">
+      <c r="G24" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I24" s="74">
+      <c r="H24" s="74">
         <v>9087</v>
       </c>
-      <c r="J24" s="74" t="b">
+      <c r="I24" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K24" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J24" s="74" t="str">
+        <f>SUBSTITUTE(D24, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-ap-lb-bp</v>
       </c>
-      <c r="L24" s="74">
+      <c r="K24" s="74">
         <v>9087</v>
       </c>
-      <c r="M24" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L24" s="74" t="str">
+        <f>SUBSTITUTE(D24, "hazr-", "")&amp;"-pb"&amp;IF(M24="", "", M24)</f>
         <v>t-dtg-ap-lb-pb9087</v>
       </c>
+      <c r="M24" s="74">
+        <v>9087</v>
+      </c>
       <c r="N24" s="74">
-        <v>9087</v>
-      </c>
-      <c r="O24" s="74">
         <v>4</v>
       </c>
-      <c r="P24" s="74" t="s">
+      <c r="O24" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P24" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q24" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R24" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="84" t="s">
         <v>185</v>
       </c>
@@ -8310,54 +8213,50 @@
         <v>361</v>
       </c>
       <c r="E25" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D25, "hazr-", "")&amp;"-rule"&amp;M25</f>
         <v>t-dtg-admweb-lb-rule8088</v>
       </c>
-      <c r="F25" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-admweb-lb-rule</v>
-      </c>
-      <c r="G25" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F25" s="84" t="str">
+        <f>SUBSTITUTE(D25, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-admweb-lb-fe</v>
       </c>
-      <c r="H25" s="84" t="s">
+      <c r="G25" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I25" s="84">
+      <c r="H25" s="84">
         <v>8088</v>
       </c>
-      <c r="J25" s="84" t="b">
+      <c r="I25" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K25" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J25" s="84" t="str">
+        <f>SUBSTITUTE(D25, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-admweb-lb-bp</v>
       </c>
-      <c r="L25" s="84">
+      <c r="K25" s="84">
         <v>8088</v>
       </c>
-      <c r="M25" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L25" s="84" t="str">
+        <f>SUBSTITUTE(D25, "hazr-", "")&amp;"-pb"&amp;IF(M25="", "", M25)</f>
         <v>t-dtg-admweb-lb-pb8088</v>
       </c>
+      <c r="M25" s="84">
+        <v>8088</v>
+      </c>
       <c r="N25" s="84">
-        <v>8088</v>
-      </c>
-      <c r="O25" s="84">
         <v>4</v>
       </c>
-      <c r="P25" s="84" t="s">
+      <c r="O25" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P25" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q25" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R25" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="74" t="s">
         <v>185</v>
       </c>
@@ -8372,54 +8271,50 @@
         <v>362</v>
       </c>
       <c r="E26" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D26, "hazr-", "")&amp;"-rule"&amp;M26</f>
         <v>t-dtg-admap-lb-rule8085</v>
       </c>
       <c r="F26" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-admap-lb-rule</v>
-      </c>
-      <c r="G26" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D26, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-admap-lb-fe</v>
       </c>
-      <c r="H26" s="74" t="s">
+      <c r="G26" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I26" s="74">
+      <c r="H26" s="74">
         <v>8085</v>
       </c>
-      <c r="J26" s="74" t="b">
+      <c r="I26" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K26" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J26" s="74" t="str">
+        <f>SUBSTITUTE(D26, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-admap-lb-bp</v>
       </c>
-      <c r="L26" s="74">
+      <c r="K26" s="74">
         <v>8085</v>
       </c>
-      <c r="M26" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L26" s="74" t="str">
+        <f>SUBSTITUTE(D26, "hazr-", "")&amp;"-pb"&amp;IF(M26="", "", M26)</f>
         <v>t-dtg-admap-lb-pb8085</v>
       </c>
+      <c r="M26" s="74">
+        <v>8085</v>
+      </c>
       <c r="N26" s="74">
-        <v>8085</v>
-      </c>
-      <c r="O26" s="74">
         <v>4</v>
       </c>
-      <c r="P26" s="74" t="s">
+      <c r="O26" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P26" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q26" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R26" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="74" t="s">
         <v>185</v>
       </c>
@@ -8434,54 +8329,50 @@
         <v>362</v>
       </c>
       <c r="E27" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D27, "hazr-", "")&amp;"-rule"&amp;M27</f>
         <v>t-dtg-admap-lb-rule8087</v>
       </c>
       <c r="F27" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-admap-lb-rule</v>
-      </c>
-      <c r="G27" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D27, "hazr-", "")&amp;"-fe"</f>
         <v>t-dtg-admap-lb-fe</v>
       </c>
-      <c r="H27" s="74" t="s">
+      <c r="G27" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I27" s="74">
+      <c r="H27" s="74">
         <v>8087</v>
       </c>
-      <c r="J27" s="74" t="b">
+      <c r="I27" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K27" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J27" s="74" t="str">
+        <f>SUBSTITUTE(D27, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-admap-lb-bp</v>
       </c>
-      <c r="L27" s="74">
+      <c r="K27" s="74">
         <v>8087</v>
       </c>
-      <c r="M27" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L27" s="74" t="str">
+        <f>SUBSTITUTE(D27, "hazr-", "")&amp;"-pb"&amp;IF(M27="", "", M27)</f>
         <v>t-dtg-admap-lb-pb8087</v>
       </c>
+      <c r="M27" s="74">
+        <v>8087</v>
+      </c>
       <c r="N27" s="74">
-        <v>8087</v>
-      </c>
-      <c r="O27" s="74">
         <v>4</v>
       </c>
-      <c r="P27" s="74" t="s">
+      <c r="O27" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P27" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q27" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R27" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="84" t="s">
         <v>185</v>
       </c>
@@ -8496,39 +8387,38 @@
         <v>385</v>
       </c>
       <c r="E28" s="84"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F28" s="84" t="str">
+        <f>SUBSTITUTE(D28, "hazr-", "")&amp;"-fe"</f>
         <v>t-doip-web-lb-fe</v>
       </c>
-      <c r="H28" s="84" t="s">
+      <c r="G28" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I28" s="84"/>
-      <c r="J28" s="84" t="b">
+      <c r="H28" s="84"/>
+      <c r="I28" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K28" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J28" s="84" t="str">
+        <f>SUBSTITUTE(D28, "hazr-", "")&amp;"-bp"</f>
         <v>t-doip-web-lb-bp</v>
       </c>
+      <c r="K28" s="84"/>
       <c r="L28" s="84"/>
       <c r="M28" s="84"/>
-      <c r="N28" s="84"/>
-      <c r="O28" s="84">
+      <c r="N28" s="84">
         <v>4</v>
       </c>
-      <c r="P28" s="84" t="s">
+      <c r="O28" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P28" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q28" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R28" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="86" t="s">
         <v>185</v>
       </c>
@@ -8543,39 +8433,38 @@
         <v>386</v>
       </c>
       <c r="E29" s="86"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="86" t="str">
-        <f t="shared" si="3"/>
+      <c r="F29" s="86" t="str">
+        <f>SUBSTITUTE(D29, "hazr-", "")&amp;"-fe"</f>
         <v>t-doip-ap-lb-fe</v>
       </c>
-      <c r="H29" s="86" t="s">
+      <c r="G29" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="I29" s="86"/>
-      <c r="J29" s="86" t="b">
+      <c r="H29" s="86"/>
+      <c r="I29" s="86" t="b">
         <v>0</v>
       </c>
-      <c r="K29" s="86" t="str">
-        <f t="shared" si="4"/>
+      <c r="J29" s="86" t="str">
+        <f>SUBSTITUTE(D29, "hazr-", "")&amp;"-bp"</f>
         <v>t-doip-ap-lb-bp</v>
       </c>
+      <c r="K29" s="86"/>
       <c r="L29" s="86"/>
       <c r="M29" s="86"/>
-      <c r="N29" s="86"/>
-      <c r="O29" s="86">
+      <c r="N29" s="86">
         <v>4</v>
       </c>
-      <c r="P29" s="86" t="s">
+      <c r="O29" s="86" t="s">
         <v>125</v>
       </c>
+      <c r="P29" s="86" t="b">
+        <v>1</v>
+      </c>
       <c r="Q29" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="R29" s="86" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="84" t="s">
         <v>185</v>
       </c>
@@ -8590,39 +8479,38 @@
         <v>387</v>
       </c>
       <c r="E30" s="84"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F30" s="84" t="str">
+        <f>SUBSTITUTE(D30, "hazr-", "")&amp;"-fe"</f>
         <v>t-doip-adm-lb-fe</v>
       </c>
-      <c r="H30" s="84" t="s">
+      <c r="G30" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I30" s="84"/>
-      <c r="J30" s="84" t="b">
+      <c r="H30" s="84"/>
+      <c r="I30" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K30" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J30" s="84" t="str">
+        <f>SUBSTITUTE(D30, "hazr-", "")&amp;"-bp"</f>
         <v>t-doip-adm-lb-bp</v>
       </c>
+      <c r="K30" s="84"/>
       <c r="L30" s="84"/>
       <c r="M30" s="84"/>
-      <c r="N30" s="84"/>
-      <c r="O30" s="84">
+      <c r="N30" s="84">
         <v>4</v>
       </c>
-      <c r="P30" s="84" t="s">
+      <c r="O30" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P30" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q30" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R30" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="74" t="s">
         <v>185</v>
       </c>
@@ -8637,54 +8525,50 @@
         <v>292</v>
       </c>
       <c r="E31" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D31, "hazr-", "")&amp;"-rule"&amp;M31</f>
         <v>t-dis-web-lb-rule80</v>
       </c>
       <c r="F31" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-web-lb-rule</v>
-      </c>
-      <c r="G31" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D31, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-web-lb-fe</v>
       </c>
-      <c r="H31" s="74" t="s">
+      <c r="G31" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I31" s="74">
+      <c r="H31" s="74">
         <v>80</v>
       </c>
-      <c r="J31" s="74" t="b">
+      <c r="I31" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K31" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J31" s="74" t="str">
+        <f>SUBSTITUTE(D31, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-web-lb-bp</v>
       </c>
-      <c r="L31" s="74">
+      <c r="K31" s="74">
         <v>80</v>
       </c>
-      <c r="M31" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L31" s="74" t="str">
+        <f>SUBSTITUTE(D31, "hazr-", "")&amp;"-pb"&amp;IF(M31="", "", M31)</f>
         <v>t-dis-web-lb-pb80</v>
       </c>
+      <c r="M31" s="74">
+        <v>80</v>
+      </c>
       <c r="N31" s="74">
-        <v>80</v>
-      </c>
-      <c r="O31" s="74">
         <v>4</v>
       </c>
-      <c r="P31" s="74" t="s">
+      <c r="O31" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P31" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q31" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R31" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="74" t="s">
         <v>185</v>
       </c>
@@ -8699,54 +8583,50 @@
         <v>292</v>
       </c>
       <c r="E32" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D32, "hazr-", "")&amp;"-rule"&amp;M32</f>
         <v>t-dis-web-lb-rule443</v>
       </c>
       <c r="F32" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-web-lb-rule</v>
-      </c>
-      <c r="G32" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D32, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-web-lb-fe</v>
       </c>
-      <c r="H32" s="74" t="s">
+      <c r="G32" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I32" s="74">
+      <c r="H32" s="74">
         <v>443</v>
       </c>
-      <c r="J32" s="74" t="b">
+      <c r="I32" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K32" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J32" s="74" t="str">
+        <f>SUBSTITUTE(D32, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-web-lb-bp</v>
       </c>
-      <c r="L32" s="74">
+      <c r="K32" s="74">
         <v>443</v>
       </c>
-      <c r="M32" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L32" s="74" t="str">
+        <f>SUBSTITUTE(D32, "hazr-", "")&amp;"-pb"&amp;IF(M32="", "", M32)</f>
         <v>t-dis-web-lb-pb443</v>
       </c>
+      <c r="M32" s="74">
+        <v>443</v>
+      </c>
       <c r="N32" s="74">
-        <v>443</v>
-      </c>
-      <c r="O32" s="74">
         <v>4</v>
       </c>
-      <c r="P32" s="74" t="s">
+      <c r="O32" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P32" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q32" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R32" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="84" t="s">
         <v>185</v>
       </c>
@@ -8761,54 +8641,50 @@
         <v>350</v>
       </c>
       <c r="E33" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D33, "hazr-", "")&amp;"-rule"&amp;M33</f>
         <v>t-dis-walkweb-lb-rule443</v>
       </c>
-      <c r="F33" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-walkweb-lb-rule</v>
-      </c>
-      <c r="G33" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F33" s="84" t="str">
+        <f>SUBSTITUTE(D33, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-walkweb-lb-fe</v>
       </c>
-      <c r="H33" s="84" t="s">
+      <c r="G33" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I33" s="84">
+      <c r="H33" s="84">
         <v>443</v>
       </c>
-      <c r="J33" s="84" t="b">
+      <c r="I33" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K33" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J33" s="84" t="str">
+        <f>SUBSTITUTE(D33, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-walkweb-lb-bp</v>
       </c>
-      <c r="L33" s="84">
+      <c r="K33" s="84">
         <v>443</v>
       </c>
-      <c r="M33" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L33" s="84" t="str">
+        <f>SUBSTITUTE(D33, "hazr-", "")&amp;"-pb"&amp;IF(M33="", "", M33)</f>
         <v>t-dis-walkweb-lb-pb443</v>
       </c>
+      <c r="M33" s="84">
+        <v>443</v>
+      </c>
       <c r="N33" s="84">
-        <v>443</v>
-      </c>
-      <c r="O33" s="84">
         <v>4</v>
       </c>
-      <c r="P33" s="84" t="s">
+      <c r="O33" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P33" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q33" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R33" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="74" t="s">
         <v>185</v>
       </c>
@@ -8823,54 +8699,50 @@
         <v>348</v>
       </c>
       <c r="E34" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D34, "hazr-", "")&amp;"-rule"&amp;M34</f>
         <v>t-dis-walkap-lb-rule8080</v>
       </c>
       <c r="F34" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-walkap-lb-rule</v>
-      </c>
-      <c r="G34" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D34, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-walkap-lb-fe</v>
       </c>
-      <c r="H34" s="74" t="s">
+      <c r="G34" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I34" s="74">
+      <c r="H34" s="74">
         <v>8080</v>
       </c>
-      <c r="J34" s="74" t="b">
+      <c r="I34" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K34" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J34" s="74" t="str">
+        <f>SUBSTITUTE(D34, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-walkap-lb-bp</v>
       </c>
-      <c r="L34" s="74">
+      <c r="K34" s="74">
         <v>8080</v>
       </c>
-      <c r="M34" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L34" s="74" t="str">
+        <f>SUBSTITUTE(D34, "hazr-", "")&amp;"-pb"&amp;IF(M34="", "", M34)</f>
         <v>t-dis-walkap-lb-pb8080</v>
       </c>
+      <c r="M34" s="74">
+        <v>8080</v>
+      </c>
       <c r="N34" s="74">
-        <v>8080</v>
-      </c>
-      <c r="O34" s="74">
         <v>4</v>
       </c>
-      <c r="P34" s="74" t="s">
+      <c r="O34" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P34" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q34" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R34" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="84" t="s">
         <v>185</v>
       </c>
@@ -8885,54 +8757,50 @@
         <v>351</v>
       </c>
       <c r="E35" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D35, "hazr-", "")&amp;"-rule"&amp;M35</f>
         <v>t-dis-drvmsgap-lb-rule8080</v>
       </c>
-      <c r="F35" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-drvmsgap-lb-rule</v>
-      </c>
-      <c r="G35" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F35" s="84" t="str">
+        <f>SUBSTITUTE(D35, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-drvmsgap-lb-fe</v>
       </c>
-      <c r="H35" s="84" t="s">
+      <c r="G35" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I35" s="84">
+      <c r="H35" s="84">
         <v>8080</v>
       </c>
-      <c r="J35" s="84" t="b">
+      <c r="I35" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K35" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J35" s="84" t="str">
+        <f>SUBSTITUTE(D35, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-drvmsgap-lb-bp</v>
       </c>
-      <c r="L35" s="84">
+      <c r="K35" s="84">
         <v>8080</v>
       </c>
-      <c r="M35" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L35" s="84" t="str">
+        <f>SUBSTITUTE(D35, "hazr-", "")&amp;"-pb"&amp;IF(M35="", "", M35)</f>
         <v>t-dis-drvmsgap-lb-pb8080</v>
       </c>
+      <c r="M35" s="84">
+        <v>8080</v>
+      </c>
       <c r="N35" s="84">
-        <v>8080</v>
-      </c>
-      <c r="O35" s="84">
         <v>4</v>
       </c>
-      <c r="P35" s="84" t="s">
+      <c r="O35" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P35" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q35" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R35" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="74" t="s">
         <v>185</v>
       </c>
@@ -8947,54 +8815,50 @@
         <v>349</v>
       </c>
       <c r="E36" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D36, "hazr-", "")&amp;"-rule"&amp;M36</f>
         <v>t-dis-drvcltap-lb-rule8081</v>
       </c>
       <c r="F36" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-drvcltap-lb-rule</v>
-      </c>
-      <c r="G36" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D36, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-drvcltap-lb-fe</v>
       </c>
-      <c r="H36" s="74" t="s">
+      <c r="G36" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I36" s="74">
+      <c r="H36" s="74">
         <v>8081</v>
       </c>
-      <c r="J36" s="74" t="b">
+      <c r="I36" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K36" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J36" s="74" t="str">
+        <f>SUBSTITUTE(D36, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-drvcltap-lb-bp</v>
       </c>
-      <c r="L36" s="74">
+      <c r="K36" s="74">
         <v>8081</v>
       </c>
-      <c r="M36" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L36" s="74" t="str">
+        <f>SUBSTITUTE(D36, "hazr-", "")&amp;"-pb"&amp;IF(M36="", "", M36)</f>
         <v>t-dis-drvcltap-lb-pb8081</v>
       </c>
+      <c r="M36" s="74">
+        <v>8081</v>
+      </c>
       <c r="N36" s="74">
-        <v>8081</v>
-      </c>
-      <c r="O36" s="74">
         <v>4</v>
       </c>
-      <c r="P36" s="74" t="s">
+      <c r="O36" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P36" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q36" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R36" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="84" t="s">
         <v>185</v>
       </c>
@@ -9009,54 +8873,50 @@
         <v>354</v>
       </c>
       <c r="E37" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D37, "hazr-", "")&amp;"-rule"&amp;M37</f>
         <v>t-dis-cmsweb-lb-rule80</v>
       </c>
-      <c r="F37" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-cmsweb-lb-rule</v>
-      </c>
-      <c r="G37" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F37" s="84" t="str">
+        <f>SUBSTITUTE(D37, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-cmsweb-lb-fe</v>
       </c>
-      <c r="H37" s="84" t="s">
+      <c r="G37" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I37" s="84">
+      <c r="H37" s="84">
         <v>80</v>
       </c>
-      <c r="J37" s="84" t="b">
+      <c r="I37" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K37" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J37" s="84" t="str">
+        <f>SUBSTITUTE(D37, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-cmsweb-lb-bp</v>
       </c>
-      <c r="L37" s="84">
+      <c r="K37" s="84">
         <v>80</v>
       </c>
-      <c r="M37" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L37" s="84" t="str">
+        <f>SUBSTITUTE(D37, "hazr-", "")&amp;"-pb"&amp;IF(M37="", "", M37)</f>
         <v>t-dis-cmsweb-lb-pb80</v>
       </c>
+      <c r="M37" s="84">
+        <v>80</v>
+      </c>
       <c r="N37" s="84">
-        <v>80</v>
-      </c>
-      <c r="O37" s="84">
         <v>4</v>
       </c>
-      <c r="P37" s="84" t="s">
+      <c r="O37" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P37" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q37" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R37" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="74" t="s">
         <v>185</v>
       </c>
@@ -9071,54 +8931,50 @@
         <v>354</v>
       </c>
       <c r="E38" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D38, "hazr-", "")&amp;"-rule"&amp;M38</f>
         <v>t-dis-cmsweb-lb-rule443</v>
       </c>
       <c r="F38" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-cmsweb-lb-rule</v>
-      </c>
-      <c r="G38" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D38, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-cmsweb-lb-fe</v>
       </c>
-      <c r="H38" s="74" t="s">
+      <c r="G38" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I38" s="74">
+      <c r="H38" s="74">
         <v>443</v>
       </c>
-      <c r="J38" s="74" t="b">
+      <c r="I38" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K38" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J38" s="74" t="str">
+        <f>SUBSTITUTE(D38, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-cmsweb-lb-bp</v>
       </c>
-      <c r="L38" s="74">
+      <c r="K38" s="74">
         <v>443</v>
       </c>
-      <c r="M38" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L38" s="74" t="str">
+        <f>SUBSTITUTE(D38, "hazr-", "")&amp;"-pb"&amp;IF(M38="", "", M38)</f>
         <v>t-dis-cmsweb-lb-pb443</v>
       </c>
+      <c r="M38" s="74">
+        <v>443</v>
+      </c>
       <c r="N38" s="74">
-        <v>443</v>
-      </c>
-      <c r="O38" s="74">
         <v>4</v>
       </c>
-      <c r="P38" s="74" t="s">
+      <c r="O38" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P38" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q38" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R38" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="84" t="s">
         <v>185</v>
       </c>
@@ -9133,54 +8989,50 @@
         <v>353</v>
       </c>
       <c r="E39" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D39, "hazr-", "")&amp;"-rule"&amp;M39</f>
         <v>t-dis-cmsap-lb-rule4001</v>
       </c>
-      <c r="F39" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-cmsap-lb-rule</v>
-      </c>
-      <c r="G39" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F39" s="84" t="str">
+        <f>SUBSTITUTE(D39, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-cmsap-lb-fe</v>
       </c>
-      <c r="H39" s="84" t="s">
+      <c r="G39" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I39" s="84">
+      <c r="H39" s="84">
         <v>4001</v>
       </c>
-      <c r="J39" s="84" t="b">
+      <c r="I39" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K39" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J39" s="84" t="str">
+        <f>SUBSTITUTE(D39, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-cmsap-lb-bp</v>
       </c>
-      <c r="L39" s="84">
+      <c r="K39" s="84">
         <v>4001</v>
       </c>
-      <c r="M39" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L39" s="84" t="str">
+        <f>SUBSTITUTE(D39, "hazr-", "")&amp;"-pb"&amp;IF(M39="", "", M39)</f>
         <v>t-dis-cmsap-lb-pb4001</v>
       </c>
+      <c r="M39" s="84">
+        <v>4001</v>
+      </c>
       <c r="N39" s="84">
-        <v>4001</v>
-      </c>
-      <c r="O39" s="84">
         <v>4</v>
       </c>
-      <c r="P39" s="84" t="s">
+      <c r="O39" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P39" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q39" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R39" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="74" t="s">
         <v>185</v>
       </c>
@@ -9195,54 +9047,50 @@
         <v>352</v>
       </c>
       <c r="E40" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D40, "hazr-", "")&amp;"-rule"&amp;M40</f>
         <v>t-dis-cmsadm-lb-rule443</v>
       </c>
       <c r="F40" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-cmsadm-lb-rule</v>
-      </c>
-      <c r="G40" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D40, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-cmsadm-lb-fe</v>
       </c>
-      <c r="H40" s="74" t="s">
+      <c r="G40" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I40" s="74">
+      <c r="H40" s="74">
         <v>443</v>
       </c>
-      <c r="J40" s="74" t="b">
+      <c r="I40" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K40" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J40" s="74" t="str">
+        <f>SUBSTITUTE(D40, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-cmsadm-lb-bp</v>
       </c>
-      <c r="L40" s="74">
+      <c r="K40" s="74">
         <v>443</v>
       </c>
-      <c r="M40" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L40" s="74" t="str">
+        <f>SUBSTITUTE(D40, "hazr-", "")&amp;"-pb"&amp;IF(M40="", "", M40)</f>
         <v>t-dis-cmsadm-lb-pb443</v>
       </c>
+      <c r="M40" s="74">
+        <v>443</v>
+      </c>
       <c r="N40" s="74">
-        <v>443</v>
-      </c>
-      <c r="O40" s="74">
         <v>4</v>
       </c>
-      <c r="P40" s="74" t="s">
+      <c r="O40" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P40" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q40" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R40" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="84" t="s">
         <v>185</v>
       </c>
@@ -9257,54 +9105,50 @@
         <v>355</v>
       </c>
       <c r="E41" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D41, "hazr-", "")&amp;"-rule"&amp;M41</f>
         <v>t-dis-cmbsap-lb-rule8080</v>
       </c>
-      <c r="F41" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-cmbsap-lb-rule</v>
-      </c>
-      <c r="G41" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F41" s="84" t="str">
+        <f>SUBSTITUTE(D41, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-cmbsap-lb-fe</v>
       </c>
-      <c r="H41" s="84" t="s">
+      <c r="G41" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I41" s="84">
+      <c r="H41" s="84">
         <v>8080</v>
       </c>
-      <c r="J41" s="84" t="b">
+      <c r="I41" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K41" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J41" s="84" t="str">
+        <f>SUBSTITUTE(D41, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-cmbsap-lb-bp</v>
       </c>
-      <c r="L41" s="84">
+      <c r="K41" s="84">
         <v>8080</v>
       </c>
-      <c r="M41" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L41" s="84" t="str">
+        <f>SUBSTITUTE(D41, "hazr-", "")&amp;"-pb"&amp;IF(M41="", "", M41)</f>
         <v>t-dis-cmbsap-lb-pb8080</v>
       </c>
+      <c r="M41" s="84">
+        <v>8080</v>
+      </c>
       <c r="N41" s="84">
-        <v>8080</v>
-      </c>
-      <c r="O41" s="84">
         <v>4</v>
       </c>
-      <c r="P41" s="84" t="s">
+      <c r="O41" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P41" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q41" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R41" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="74" t="s">
         <v>185</v>
       </c>
@@ -9319,54 +9163,50 @@
         <v>345</v>
       </c>
       <c r="E42" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D42, "hazr-", "")&amp;"-rule"&amp;M42</f>
         <v>t-dis-bbiweb-lb-rule443</v>
       </c>
       <c r="F42" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-bbiweb-lb-rule</v>
-      </c>
-      <c r="G42" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D42, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-bbiweb-lb-fe</v>
       </c>
-      <c r="H42" s="74" t="s">
+      <c r="G42" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I42" s="74">
+      <c r="H42" s="74">
         <v>443</v>
       </c>
-      <c r="J42" s="74" t="b">
+      <c r="I42" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K42" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J42" s="74" t="str">
+        <f>SUBSTITUTE(D42, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-bbiweb-lb-bp</v>
       </c>
-      <c r="L42" s="74">
+      <c r="K42" s="74">
         <v>443</v>
       </c>
-      <c r="M42" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L42" s="74" t="str">
+        <f>SUBSTITUTE(D42, "hazr-", "")&amp;"-pb"&amp;IF(M42="", "", M42)</f>
         <v>t-dis-bbiweb-lb-pb443</v>
       </c>
+      <c r="M42" s="74">
+        <v>443</v>
+      </c>
       <c r="N42" s="74">
-        <v>443</v>
-      </c>
-      <c r="O42" s="74">
         <v>4</v>
       </c>
-      <c r="P42" s="74" t="s">
+      <c r="O42" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P42" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q42" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R42" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="84" t="s">
         <v>185</v>
       </c>
@@ -9381,54 +9221,50 @@
         <v>347</v>
       </c>
       <c r="E43" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D43, "hazr-", "")&amp;"-rule"&amp;M43</f>
         <v>t-dis-bbimsgap-lb-rule20030</v>
       </c>
-      <c r="F43" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-bbimsgap-lb-rule</v>
-      </c>
-      <c r="G43" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F43" s="84" t="str">
+        <f>SUBSTITUTE(D43, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-bbimsgap-lb-fe</v>
       </c>
-      <c r="H43" s="84" t="s">
+      <c r="G43" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I43" s="84">
+      <c r="H43" s="84">
         <v>20030</v>
       </c>
-      <c r="J43" s="84" t="b">
+      <c r="I43" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K43" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J43" s="84" t="str">
+        <f>SUBSTITUTE(D43, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-bbimsgap-lb-bp</v>
       </c>
-      <c r="L43" s="84">
+      <c r="K43" s="84">
         <v>20030</v>
       </c>
-      <c r="M43" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L43" s="84" t="str">
+        <f>SUBSTITUTE(D43, "hazr-", "")&amp;"-pb"&amp;IF(M43="", "", M43)</f>
         <v>t-dis-bbimsgap-lb-pb20030</v>
       </c>
+      <c r="M43" s="84">
+        <v>20030</v>
+      </c>
       <c r="N43" s="84">
-        <v>20030</v>
-      </c>
-      <c r="O43" s="84">
         <v>4</v>
       </c>
-      <c r="P43" s="84" t="s">
+      <c r="O43" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P43" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q43" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R43" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="74" t="s">
         <v>185</v>
       </c>
@@ -9443,54 +9279,50 @@
         <v>346</v>
       </c>
       <c r="E44" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D44, "hazr-", "")&amp;"-rule"&amp;M44</f>
         <v>t-dis-bbicltap-lb-rule20000</v>
       </c>
       <c r="F44" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-bbicltap-lb-rule</v>
-      </c>
-      <c r="G44" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D44, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-bbicltap-lb-fe</v>
       </c>
-      <c r="H44" s="74" t="s">
+      <c r="G44" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I44" s="74">
+      <c r="H44" s="74">
         <v>20000</v>
       </c>
-      <c r="J44" s="74" t="b">
+      <c r="I44" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K44" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J44" s="74" t="str">
+        <f>SUBSTITUTE(D44, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-bbicltap-lb-bp</v>
       </c>
-      <c r="L44" s="74">
+      <c r="K44" s="74">
         <v>20000</v>
       </c>
-      <c r="M44" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L44" s="74" t="str">
+        <f>SUBSTITUTE(D44, "hazr-", "")&amp;"-pb"&amp;IF(M44="", "", M44)</f>
         <v>t-dis-bbicltap-lb-pb20000</v>
       </c>
+      <c r="M44" s="74">
+        <v>20000</v>
+      </c>
       <c r="N44" s="74">
-        <v>20000</v>
-      </c>
-      <c r="O44" s="74">
         <v>4</v>
       </c>
-      <c r="P44" s="74" t="s">
+      <c r="O44" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P44" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q44" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R44" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="74" t="s">
         <v>185</v>
       </c>
@@ -9505,54 +9337,50 @@
         <v>346</v>
       </c>
       <c r="E45" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D45, "hazr-", "")&amp;"-rule"&amp;M45</f>
         <v>t-dis-bbicltap-lb-rule21000</v>
       </c>
       <c r="F45" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-bbicltap-lb-rule</v>
-      </c>
-      <c r="G45" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D45, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-bbicltap-lb-fe</v>
       </c>
-      <c r="H45" s="74" t="s">
+      <c r="G45" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I45" s="74">
+      <c r="H45" s="74">
         <v>21000</v>
       </c>
-      <c r="J45" s="74" t="b">
+      <c r="I45" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K45" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J45" s="74" t="str">
+        <f>SUBSTITUTE(D45, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-bbicltap-lb-bp</v>
       </c>
-      <c r="L45" s="74">
+      <c r="K45" s="74">
         <v>21000</v>
       </c>
-      <c r="M45" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L45" s="74" t="str">
+        <f>SUBSTITUTE(D45, "hazr-", "")&amp;"-pb"&amp;IF(M45="", "", M45)</f>
         <v>t-dis-bbicltap-lb-pb21000</v>
       </c>
+      <c r="M45" s="74">
+        <v>21000</v>
+      </c>
       <c r="N45" s="74">
-        <v>21000</v>
-      </c>
-      <c r="O45" s="74">
         <v>4</v>
       </c>
-      <c r="P45" s="74" t="s">
+      <c r="O45" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P45" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q45" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R45" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="74" t="s">
         <v>185</v>
       </c>
@@ -9567,54 +9395,50 @@
         <v>346</v>
       </c>
       <c r="E46" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D46, "hazr-", "")&amp;"-rule"&amp;M46</f>
         <v>t-dis-bbicltap-lb-rule22000</v>
       </c>
       <c r="F46" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-bbicltap-lb-rule</v>
-      </c>
-      <c r="G46" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D46, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-bbicltap-lb-fe</v>
       </c>
-      <c r="H46" s="74" t="s">
+      <c r="G46" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I46" s="74">
+      <c r="H46" s="74">
         <v>22000</v>
       </c>
-      <c r="J46" s="74" t="b">
+      <c r="I46" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K46" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J46" s="74" t="str">
+        <f>SUBSTITUTE(D46, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-bbicltap-lb-bp</v>
       </c>
-      <c r="L46" s="74">
+      <c r="K46" s="74">
         <v>22000</v>
       </c>
-      <c r="M46" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L46" s="74" t="str">
+        <f>SUBSTITUTE(D46, "hazr-", "")&amp;"-pb"&amp;IF(M46="", "", M46)</f>
         <v>t-dis-bbicltap-lb-pb22000</v>
       </c>
+      <c r="M46" s="74">
+        <v>22000</v>
+      </c>
       <c r="N46" s="74">
-        <v>22000</v>
-      </c>
-      <c r="O46" s="74">
         <v>4</v>
       </c>
-      <c r="P46" s="74" t="s">
+      <c r="O46" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P46" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q46" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R46" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="84" t="s">
         <v>185</v>
       </c>
@@ -9629,54 +9453,50 @@
         <v>290</v>
       </c>
       <c r="E47" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D47, "hazr-", "")&amp;"-rule"&amp;M47</f>
         <v>t-dis-ap-lb-rule8080</v>
       </c>
-      <c r="F47" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-ap-lb-rule</v>
-      </c>
-      <c r="G47" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F47" s="84" t="str">
+        <f>SUBSTITUTE(D47, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-ap-lb-fe</v>
       </c>
-      <c r="H47" s="84" t="s">
+      <c r="G47" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I47" s="84">
+      <c r="H47" s="84">
         <v>8080</v>
       </c>
-      <c r="J47" s="84" t="b">
+      <c r="I47" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K47" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J47" s="84" t="str">
+        <f>SUBSTITUTE(D47, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-ap-lb-bp</v>
       </c>
-      <c r="L47" s="84">
+      <c r="K47" s="84">
         <v>8080</v>
       </c>
-      <c r="M47" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L47" s="84" t="str">
+        <f>SUBSTITUTE(D47, "hazr-", "")&amp;"-pb"&amp;IF(M47="", "", M47)</f>
         <v>t-dis-ap-lb-pb8080</v>
       </c>
+      <c r="M47" s="84">
+        <v>8080</v>
+      </c>
       <c r="N47" s="84">
-        <v>8080</v>
-      </c>
-      <c r="O47" s="84">
         <v>4</v>
       </c>
-      <c r="P47" s="84" t="s">
+      <c r="O47" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P47" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q47" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R47" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="74" t="s">
         <v>185</v>
       </c>
@@ -9691,54 +9511,50 @@
         <v>344</v>
       </c>
       <c r="E48" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D48, "hazr-", "")&amp;"-rule"&amp;M48</f>
         <v>t-dis-adm-lb-rule443</v>
       </c>
       <c r="F48" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dis-adm-lb-rule</v>
-      </c>
-      <c r="G48" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D48, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-adm-lb-fe</v>
       </c>
-      <c r="H48" s="74" t="s">
+      <c r="G48" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I48" s="74">
+      <c r="H48" s="74">
         <v>443</v>
       </c>
-      <c r="J48" s="74" t="b">
+      <c r="I48" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K48" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J48" s="74" t="str">
+        <f>SUBSTITUTE(D48, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-adm-lb-bp</v>
       </c>
-      <c r="L48" s="74">
+      <c r="K48" s="74">
         <v>443</v>
       </c>
-      <c r="M48" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L48" s="74" t="str">
+        <f>SUBSTITUTE(D48, "hazr-", "")&amp;"-pb"&amp;IF(M48="", "", M48)</f>
         <v>t-dis-adm-lb-pb443</v>
       </c>
+      <c r="M48" s="74">
+        <v>443</v>
+      </c>
       <c r="N48" s="74">
-        <v>443</v>
-      </c>
-      <c r="O48" s="74">
         <v>4</v>
       </c>
-      <c r="P48" s="74" t="s">
+      <c r="O48" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P48" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q48" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R48" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="84" t="s">
         <v>185</v>
       </c>
@@ -9753,54 +9569,50 @@
         <v>379</v>
       </c>
       <c r="E49" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D49, "hazr-", "")&amp;"-rule"&amp;M49</f>
         <v>t-dip-web-lb-rule443</v>
       </c>
-      <c r="F49" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-web-lb-rule</v>
-      </c>
-      <c r="G49" s="84" t="str">
-        <f t="shared" si="3"/>
+      <c r="F49" s="84" t="str">
+        <f>SUBSTITUTE(D49, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-web-lb-fe</v>
       </c>
-      <c r="H49" s="84" t="s">
+      <c r="G49" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I49" s="84">
+      <c r="H49" s="84">
         <v>443</v>
       </c>
-      <c r="J49" s="84" t="b">
+      <c r="I49" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K49" s="84" t="str">
-        <f t="shared" si="4"/>
+      <c r="J49" s="84" t="str">
+        <f>SUBSTITUTE(D49, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-web-lb-bp</v>
       </c>
-      <c r="L49" s="84">
+      <c r="K49" s="84">
         <v>443</v>
       </c>
-      <c r="M49" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L49" s="84" t="str">
+        <f>SUBSTITUTE(D49, "hazr-", "")&amp;"-pb"&amp;IF(M49="", "", M49)</f>
         <v>t-dip-web-lb-pb443</v>
       </c>
+      <c r="M49" s="84">
+        <v>443</v>
+      </c>
       <c r="N49" s="84">
-        <v>443</v>
-      </c>
-      <c r="O49" s="84">
         <v>4</v>
       </c>
-      <c r="P49" s="84" t="s">
+      <c r="O49" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P49" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q49" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R49" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="74" t="s">
         <v>185</v>
       </c>
@@ -9815,54 +9627,50 @@
         <v>379</v>
       </c>
       <c r="E50" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D50, "hazr-", "")&amp;"-rule"&amp;M50</f>
         <v>t-dip-web-lb-rule9100</v>
       </c>
       <c r="F50" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-web-lb-rule</v>
-      </c>
-      <c r="G50" s="74" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(D50, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-web-lb-fe</v>
       </c>
-      <c r="H50" s="74" t="s">
+      <c r="G50" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I50" s="74">
+      <c r="H50" s="74">
         <v>9100</v>
       </c>
-      <c r="J50" s="74" t="b">
+      <c r="I50" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K50" s="74" t="str">
-        <f t="shared" si="4"/>
+      <c r="J50" s="74" t="str">
+        <f>SUBSTITUTE(D50, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-web-lb-bp</v>
       </c>
-      <c r="L50" s="74">
+      <c r="K50" s="74">
         <v>9100</v>
       </c>
-      <c r="M50" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L50" s="74" t="str">
+        <f>SUBSTITUTE(D50, "hazr-", "")&amp;"-pb"&amp;IF(M50="", "", M50)</f>
         <v>t-dip-web-lb-pb9100</v>
       </c>
+      <c r="M50" s="74">
+        <v>9100</v>
+      </c>
       <c r="N50" s="74">
-        <v>9100</v>
-      </c>
-      <c r="O50" s="74">
         <v>4</v>
       </c>
-      <c r="P50" s="74" t="s">
+      <c r="O50" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P50" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q50" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R50" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="84" t="s">
         <v>185</v>
       </c>
@@ -9877,54 +9685,50 @@
         <v>378</v>
       </c>
       <c r="E51" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D51, "hazr-", "")&amp;"-rule"&amp;M51</f>
         <v>t-dip-mqweb-lb-rule8883</v>
       </c>
-      <c r="F51" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-mqweb-lb-rule</v>
-      </c>
-      <c r="G51" s="84" t="str">
+      <c r="F51" s="84" t="str">
         <f>SUBSTITUTE(D51, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-mqweb-lb-fe</v>
       </c>
-      <c r="H51" s="84" t="s">
+      <c r="G51" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I51" s="84">
+      <c r="H51" s="84">
         <v>8883</v>
       </c>
-      <c r="J51" s="84" t="b">
+      <c r="I51" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K51" s="84" t="str">
+      <c r="J51" s="84" t="str">
         <f>SUBSTITUTE(D51, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-mqweb-lb-bp</v>
       </c>
-      <c r="L51" s="84">
+      <c r="K51" s="84">
         <v>8883</v>
       </c>
-      <c r="M51" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L51" s="84" t="str">
+        <f>SUBSTITUTE(D51, "hazr-", "")&amp;"-pb"&amp;IF(M51="", "", M51)</f>
         <v>t-dip-mqweb-lb-pb8883</v>
       </c>
+      <c r="M51" s="84">
+        <v>8883</v>
+      </c>
       <c r="N51" s="84">
-        <v>8883</v>
-      </c>
-      <c r="O51" s="84">
         <v>4</v>
       </c>
-      <c r="P51" s="84" t="s">
+      <c r="O51" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P51" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q51" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R51" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="84" t="s">
         <v>185</v>
       </c>
@@ -9939,54 +9743,50 @@
         <v>378</v>
       </c>
       <c r="E52" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D52, "hazr-", "")&amp;"-rule"&amp;M52</f>
         <v>t-dip-mqweb-lb-rule1884</v>
       </c>
-      <c r="F52" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-mqweb-lb-rule</v>
-      </c>
-      <c r="G52" s="84" t="str">
+      <c r="F52" s="84" t="str">
         <f>SUBSTITUTE(D52, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-mqweb-lb-fe</v>
       </c>
-      <c r="H52" s="84" t="s">
+      <c r="G52" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I52" s="84">
+      <c r="H52" s="84">
         <v>1884</v>
       </c>
-      <c r="J52" s="84" t="b">
+      <c r="I52" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K52" s="84" t="str">
+      <c r="J52" s="84" t="str">
         <f>SUBSTITUTE(D52, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-mqweb-lb-bp</v>
       </c>
-      <c r="L52" s="84">
+      <c r="K52" s="84">
         <v>1884</v>
       </c>
-      <c r="M52" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L52" s="84" t="str">
+        <f>SUBSTITUTE(D52, "hazr-", "")&amp;"-pb"&amp;IF(M52="", "", M52)</f>
         <v>t-dip-mqweb-lb-pb1884</v>
       </c>
+      <c r="M52" s="84">
+        <v>1884</v>
+      </c>
       <c r="N52" s="84">
-        <v>1884</v>
-      </c>
-      <c r="O52" s="84">
         <v>4</v>
       </c>
-      <c r="P52" s="84" t="s">
+      <c r="O52" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P52" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q52" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R52" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="84" t="s">
         <v>185</v>
       </c>
@@ -10001,54 +9801,50 @@
         <v>378</v>
       </c>
       <c r="E53" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D53, "hazr-", "")&amp;"-rule"&amp;M53</f>
         <v>t-dip-mqweb-lb-rule9100</v>
       </c>
-      <c r="F53" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-mqweb-lb-rule</v>
-      </c>
-      <c r="G53" s="84" t="str">
+      <c r="F53" s="84" t="str">
         <f>SUBSTITUTE(D53, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-mqweb-lb-fe</v>
       </c>
-      <c r="H53" s="84" t="s">
+      <c r="G53" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I53" s="84">
+      <c r="H53" s="84">
         <v>9100</v>
       </c>
-      <c r="J53" s="84" t="b">
+      <c r="I53" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K53" s="84" t="str">
+      <c r="J53" s="84" t="str">
         <f>SUBSTITUTE(D53, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-mqweb-lb-bp</v>
       </c>
-      <c r="L53" s="84">
+      <c r="K53" s="84">
         <v>9100</v>
       </c>
-      <c r="M53" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L53" s="84" t="str">
+        <f>SUBSTITUTE(D53, "hazr-", "")&amp;"-pb"&amp;IF(M53="", "", M53)</f>
         <v>t-dip-mqweb-lb-pb9100</v>
       </c>
+      <c r="M53" s="84">
+        <v>9100</v>
+      </c>
       <c r="N53" s="84">
-        <v>9100</v>
-      </c>
-      <c r="O53" s="84">
         <v>4</v>
       </c>
-      <c r="P53" s="84" t="s">
+      <c r="O53" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P53" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q53" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R53" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="74" t="s">
         <v>185</v>
       </c>
@@ -10063,54 +9859,50 @@
         <v>377</v>
       </c>
       <c r="E54" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D54, "hazr-", "")&amp;"-rule"&amp;M54</f>
         <v>t-dip-mqap-lb-rule1883</v>
       </c>
       <c r="F54" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-mqap-lb-rule</v>
-      </c>
-      <c r="G54" s="74" t="str">
         <f>SUBSTITUTE(D54, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-mqap-lb-fe</v>
       </c>
-      <c r="H54" s="74" t="s">
+      <c r="G54" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I54" s="74">
+      <c r="H54" s="74">
         <v>1883</v>
       </c>
-      <c r="J54" s="74" t="b">
+      <c r="I54" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K54" s="74" t="str">
+      <c r="J54" s="74" t="str">
         <f>SUBSTITUTE(D54, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-mqap-lb-bp</v>
       </c>
-      <c r="L54" s="74">
+      <c r="K54" s="74">
         <v>1883</v>
       </c>
-      <c r="M54" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L54" s="74" t="str">
+        <f>SUBSTITUTE(D54, "hazr-", "")&amp;"-pb"&amp;IF(M54="", "", M54)</f>
         <v>t-dip-mqap-lb-pb1883</v>
       </c>
+      <c r="M54" s="74">
+        <v>1883</v>
+      </c>
       <c r="N54" s="74">
-        <v>1883</v>
-      </c>
-      <c r="O54" s="74">
         <v>4</v>
       </c>
-      <c r="P54" s="74" t="s">
+      <c r="O54" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P54" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q54" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R54" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="74" t="s">
         <v>185</v>
       </c>
@@ -10125,54 +9917,50 @@
         <v>377</v>
       </c>
       <c r="E55" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D55, "hazr-", "")&amp;"-rule"&amp;M55</f>
         <v>t-dip-mqap-lb-rule1884</v>
       </c>
       <c r="F55" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-mqap-lb-rule</v>
-      </c>
-      <c r="G55" s="74" t="str">
-        <f t="shared" ref="G55:G88" si="5">SUBSTITUTE(D55, "hazr-", "")&amp;"-fe"</f>
+        <f>SUBSTITUTE(D55, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-mqap-lb-fe</v>
       </c>
-      <c r="H55" s="74" t="s">
+      <c r="G55" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I55" s="74">
+      <c r="H55" s="74">
         <v>1884</v>
       </c>
-      <c r="J55" s="74" t="b">
+      <c r="I55" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K55" s="74" t="str">
+      <c r="J55" s="74" t="str">
         <f>SUBSTITUTE(D55, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-mqap-lb-bp</v>
       </c>
-      <c r="L55" s="74">
+      <c r="K55" s="74">
         <v>1884</v>
       </c>
-      <c r="M55" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L55" s="74" t="str">
+        <f>SUBSTITUTE(D55, "hazr-", "")&amp;"-pb"&amp;IF(M55="", "", M55)</f>
         <v>t-dip-mqap-lb-pb1884</v>
       </c>
+      <c r="M55" s="74">
+        <v>1884</v>
+      </c>
       <c r="N55" s="74">
-        <v>1884</v>
-      </c>
-      <c r="O55" s="74">
         <v>4</v>
       </c>
-      <c r="P55" s="74" t="s">
+      <c r="O55" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P55" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q55" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R55" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="74" t="s">
         <v>185</v>
       </c>
@@ -10187,54 +9975,50 @@
         <v>377</v>
       </c>
       <c r="E56" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D56, "hazr-", "")&amp;"-rule"&amp;M56</f>
         <v>t-dip-mqap-lb-rule18083</v>
       </c>
       <c r="F56" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-mqap-lb-rule</v>
-      </c>
-      <c r="G56" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f>SUBSTITUTE(D56, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-mqap-lb-fe</v>
       </c>
-      <c r="H56" s="74" t="s">
+      <c r="G56" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I56" s="74">
+      <c r="H56" s="74">
         <v>18083</v>
       </c>
-      <c r="J56" s="74" t="b">
+      <c r="I56" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K56" s="74" t="str">
-        <f t="shared" ref="K56:K88" si="6">SUBSTITUTE(D56, "hazr-", "")&amp;"-bp"</f>
+      <c r="J56" s="74" t="str">
+        <f>SUBSTITUTE(D56, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-mqap-lb-bp</v>
       </c>
-      <c r="L56" s="74">
+      <c r="K56" s="74">
         <v>18083</v>
       </c>
-      <c r="M56" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L56" s="74" t="str">
+        <f>SUBSTITUTE(D56, "hazr-", "")&amp;"-pb"&amp;IF(M56="", "", M56)</f>
         <v>t-dip-mqap-lb-pb18083</v>
       </c>
+      <c r="M56" s="74">
+        <v>18083</v>
+      </c>
       <c r="N56" s="74">
-        <v>18083</v>
-      </c>
-      <c r="O56" s="74">
         <v>4</v>
       </c>
-      <c r="P56" s="74" t="s">
+      <c r="O56" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P56" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q56" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R56" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="74" t="s">
         <v>185</v>
       </c>
@@ -10249,54 +10033,50 @@
         <v>377</v>
       </c>
       <c r="E57" s="74" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D57, "hazr-", "")&amp;"-rule"&amp;M57</f>
         <v>t-dip-mqap-lb-rule9100</v>
       </c>
       <c r="F57" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-mqap-lb-rule</v>
-      </c>
-      <c r="G57" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f>SUBSTITUTE(D57, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-mqap-lb-fe</v>
       </c>
-      <c r="H57" s="74" t="s">
+      <c r="G57" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I57" s="74">
+      <c r="H57" s="74">
         <v>9100</v>
       </c>
-      <c r="J57" s="74" t="b">
+      <c r="I57" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K57" s="74" t="str">
-        <f t="shared" si="6"/>
+      <c r="J57" s="74" t="str">
+        <f>SUBSTITUTE(D57, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-mqap-lb-bp</v>
       </c>
-      <c r="L57" s="74">
+      <c r="K57" s="74">
         <v>9100</v>
       </c>
-      <c r="M57" s="74" t="str">
-        <f t="shared" si="2"/>
+      <c r="L57" s="74" t="str">
+        <f>SUBSTITUTE(D57, "hazr-", "")&amp;"-pb"&amp;IF(M57="", "", M57)</f>
         <v>t-dip-mqap-lb-pb9100</v>
       </c>
+      <c r="M57" s="74">
+        <v>9100</v>
+      </c>
       <c r="N57" s="74">
-        <v>9100</v>
-      </c>
-      <c r="O57" s="74">
         <v>4</v>
       </c>
-      <c r="P57" s="74" t="s">
+      <c r="O57" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P57" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q57" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R57" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="84" t="s">
         <v>185</v>
       </c>
@@ -10311,54 +10091,50 @@
         <v>376</v>
       </c>
       <c r="E58" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D58, "hazr-", "")&amp;"-rule"&amp;M58</f>
         <v>t-dip-geoap-lb-rule3660</v>
       </c>
-      <c r="F58" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-geoap-lb-rule</v>
-      </c>
-      <c r="G58" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F58" s="84" t="str">
+        <f>SUBSTITUTE(D58, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-geoap-lb-fe</v>
       </c>
-      <c r="H58" s="84" t="s">
+      <c r="G58" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I58" s="84">
+      <c r="H58" s="84">
         <v>3660</v>
       </c>
-      <c r="J58" s="84" t="b">
+      <c r="I58" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K58" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J58" s="84" t="str">
+        <f>SUBSTITUTE(D58, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-geoap-lb-bp</v>
       </c>
-      <c r="L58" s="84">
+      <c r="K58" s="84">
         <v>3660</v>
       </c>
-      <c r="M58" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L58" s="84" t="str">
+        <f>SUBSTITUTE(D58, "hazr-", "")&amp;"-pb"&amp;IF(M58="", "", M58)</f>
         <v>t-dip-geoap-lb-pb3660</v>
       </c>
+      <c r="M58" s="84">
+        <v>3660</v>
+      </c>
       <c r="N58" s="84">
-        <v>3660</v>
-      </c>
-      <c r="O58" s="84">
         <v>4</v>
       </c>
-      <c r="P58" s="84" t="s">
+      <c r="O58" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P58" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q58" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R58" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="84" t="s">
         <v>185</v>
       </c>
@@ -10373,54 +10149,50 @@
         <v>376</v>
       </c>
       <c r="E59" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D59, "hazr-", "")&amp;"-rule"&amp;M59</f>
         <v>t-dip-geoap-lb-rule3661</v>
       </c>
-      <c r="F59" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-geoap-lb-rule</v>
-      </c>
-      <c r="G59" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F59" s="84" t="str">
+        <f>SUBSTITUTE(D59, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-geoap-lb-fe</v>
       </c>
-      <c r="H59" s="84" t="s">
+      <c r="G59" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I59" s="84">
+      <c r="H59" s="84">
         <v>3661</v>
       </c>
-      <c r="J59" s="84" t="b">
+      <c r="I59" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K59" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J59" s="84" t="str">
+        <f>SUBSTITUTE(D59, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-geoap-lb-bp</v>
       </c>
-      <c r="L59" s="84">
+      <c r="K59" s="84">
         <v>3661</v>
       </c>
-      <c r="M59" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L59" s="84" t="str">
+        <f>SUBSTITUTE(D59, "hazr-", "")&amp;"-pb"&amp;IF(M59="", "", M59)</f>
         <v>t-dip-geoap-lb-pb3661</v>
       </c>
+      <c r="M59" s="84">
+        <v>3661</v>
+      </c>
       <c r="N59" s="84">
-        <v>3661</v>
-      </c>
-      <c r="O59" s="84">
         <v>4</v>
       </c>
-      <c r="P59" s="84" t="s">
+      <c r="O59" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P59" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q59" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R59" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="84" t="s">
         <v>185</v>
       </c>
@@ -10435,54 +10207,50 @@
         <v>376</v>
       </c>
       <c r="E60" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D60, "hazr-", "")&amp;"-rule"&amp;M60</f>
         <v>t-dip-geoap-lb-rule3670</v>
       </c>
-      <c r="F60" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-geoap-lb-rule</v>
-      </c>
-      <c r="G60" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F60" s="84" t="str">
+        <f>SUBSTITUTE(D60, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-geoap-lb-fe</v>
       </c>
-      <c r="H60" s="84" t="s">
+      <c r="G60" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I60" s="84">
+      <c r="H60" s="84">
         <v>3670</v>
       </c>
-      <c r="J60" s="84" t="b">
+      <c r="I60" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K60" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J60" s="84" t="str">
+        <f>SUBSTITUTE(D60, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-geoap-lb-bp</v>
       </c>
-      <c r="L60" s="84">
+      <c r="K60" s="84">
         <v>3670</v>
       </c>
-      <c r="M60" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L60" s="84" t="str">
+        <f>SUBSTITUTE(D60, "hazr-", "")&amp;"-pb"&amp;IF(M60="", "", M60)</f>
         <v>t-dip-geoap-lb-pb3670</v>
       </c>
+      <c r="M60" s="84">
+        <v>3670</v>
+      </c>
       <c r="N60" s="84">
-        <v>3670</v>
-      </c>
-      <c r="O60" s="84">
         <v>4</v>
       </c>
-      <c r="P60" s="84" t="s">
+      <c r="O60" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P60" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q60" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R60" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="84" t="s">
         <v>185</v>
       </c>
@@ -10497,54 +10265,50 @@
         <v>376</v>
       </c>
       <c r="E61" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D61, "hazr-", "")&amp;"-rule"&amp;M61</f>
         <v>t-dip-geoap-lb-rule3671</v>
       </c>
-      <c r="F61" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-geoap-lb-rule</v>
-      </c>
-      <c r="G61" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F61" s="84" t="str">
+        <f>SUBSTITUTE(D61, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-geoap-lb-fe</v>
       </c>
-      <c r="H61" s="84" t="s">
+      <c r="G61" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I61" s="84">
+      <c r="H61" s="84">
         <v>3671</v>
       </c>
-      <c r="J61" s="84" t="b">
+      <c r="I61" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K61" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J61" s="84" t="str">
+        <f>SUBSTITUTE(D61, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-geoap-lb-bp</v>
       </c>
-      <c r="L61" s="84">
+      <c r="K61" s="84">
         <v>3671</v>
       </c>
-      <c r="M61" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L61" s="84" t="str">
+        <f>SUBSTITUTE(D61, "hazr-", "")&amp;"-pb"&amp;IF(M61="", "", M61)</f>
         <v>t-dip-geoap-lb-pb3671</v>
       </c>
+      <c r="M61" s="84">
+        <v>3671</v>
+      </c>
       <c r="N61" s="84">
-        <v>3671</v>
-      </c>
-      <c r="O61" s="84">
         <v>4</v>
       </c>
-      <c r="P61" s="84" t="s">
+      <c r="O61" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P61" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q61" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R61" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="84" t="s">
         <v>185</v>
       </c>
@@ -10559,54 +10323,50 @@
         <v>376</v>
       </c>
       <c r="E62" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D62, "hazr-", "")&amp;"-rule"&amp;M62</f>
         <v>t-dip-geoap-lb-rule9100</v>
       </c>
-      <c r="F62" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-geoap-lb-rule</v>
-      </c>
-      <c r="G62" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F62" s="84" t="str">
+        <f>SUBSTITUTE(D62, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-geoap-lb-fe</v>
       </c>
-      <c r="H62" s="84" t="s">
+      <c r="G62" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I62" s="84">
+      <c r="H62" s="84">
         <v>9100</v>
       </c>
-      <c r="J62" s="84" t="b">
+      <c r="I62" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K62" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J62" s="84" t="str">
+        <f>SUBSTITUTE(D62, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-geoap-lb-bp</v>
       </c>
-      <c r="L62" s="84">
+      <c r="K62" s="84">
         <v>9100</v>
       </c>
-      <c r="M62" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L62" s="84" t="str">
+        <f>SUBSTITUTE(D62, "hazr-", "")&amp;"-pb"&amp;IF(M62="", "", M62)</f>
         <v>t-dip-geoap-lb-pb9100</v>
       </c>
+      <c r="M62" s="84">
+        <v>9100</v>
+      </c>
       <c r="N62" s="84">
-        <v>9100</v>
-      </c>
-      <c r="O62" s="84">
         <v>4</v>
       </c>
-      <c r="P62" s="84" t="s">
+      <c r="O62" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P62" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q62" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R62" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="74" t="s">
         <v>185</v>
       </c>
@@ -10621,39 +10381,38 @@
         <v>375</v>
       </c>
       <c r="E63" s="74"/>
-      <c r="F63" s="74"/>
-      <c r="G63" s="74" t="str">
-        <f t="shared" si="5"/>
+      <c r="F63" s="74" t="str">
+        <f>SUBSTITUTE(D63, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-flk-lb-fe</v>
       </c>
-      <c r="H63" s="74" t="s">
+      <c r="G63" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I63" s="74"/>
-      <c r="J63" s="74" t="b">
+      <c r="H63" s="74"/>
+      <c r="I63" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K63" s="74" t="str">
-        <f t="shared" si="6"/>
+      <c r="J63" s="74" t="str">
+        <f>SUBSTITUTE(D63, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-flk-lb-bp</v>
       </c>
+      <c r="K63" s="74"/>
       <c r="L63" s="74"/>
       <c r="M63" s="74"/>
-      <c r="N63" s="74"/>
-      <c r="O63" s="74">
+      <c r="N63" s="74">
         <v>4</v>
       </c>
-      <c r="P63" s="74" t="s">
+      <c r="O63" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P63" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q63" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R63" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="84" t="s">
         <v>185</v>
       </c>
@@ -10668,54 +10427,50 @@
         <v>374</v>
       </c>
       <c r="E64" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D64, "hazr-", "")&amp;"-rule"&amp;M64</f>
         <v>t-dip-ap-lb-rule443</v>
       </c>
-      <c r="F64" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-ap-lb-rule</v>
-      </c>
-      <c r="G64" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F64" s="84" t="str">
+        <f>SUBSTITUTE(D64, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-ap-lb-fe</v>
       </c>
-      <c r="H64" s="84" t="s">
+      <c r="G64" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I64" s="84">
+      <c r="H64" s="84">
         <v>443</v>
       </c>
-      <c r="J64" s="84" t="b">
+      <c r="I64" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K64" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J64" s="84" t="str">
+        <f>SUBSTITUTE(D64, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-ap-lb-bp</v>
       </c>
-      <c r="L64" s="84">
+      <c r="K64" s="84">
         <v>443</v>
       </c>
-      <c r="M64" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L64" s="84" t="str">
+        <f>SUBSTITUTE(D64, "hazr-", "")&amp;"-pb"&amp;IF(M64="", "", M64)</f>
         <v>t-dip-ap-lb-pb443</v>
       </c>
+      <c r="M64" s="84">
+        <v>443</v>
+      </c>
       <c r="N64" s="84">
-        <v>443</v>
-      </c>
-      <c r="O64" s="84">
         <v>4</v>
       </c>
-      <c r="P64" s="84" t="s">
+      <c r="O64" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P64" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q64" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R64" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="84" t="s">
         <v>185</v>
       </c>
@@ -10730,54 +10485,50 @@
         <v>374</v>
       </c>
       <c r="E65" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D65, "hazr-", "")&amp;"-rule"&amp;M65</f>
         <v>t-dip-ap-lb-rule8100</v>
       </c>
-      <c r="F65" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-ap-lb-rule</v>
-      </c>
-      <c r="G65" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F65" s="84" t="str">
+        <f>SUBSTITUTE(D65, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-ap-lb-fe</v>
       </c>
-      <c r="H65" s="84" t="s">
+      <c r="G65" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I65" s="84">
+      <c r="H65" s="84">
         <v>8100</v>
       </c>
-      <c r="J65" s="84" t="b">
+      <c r="I65" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K65" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J65" s="84" t="str">
+        <f>SUBSTITUTE(D65, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-ap-lb-bp</v>
       </c>
-      <c r="L65" s="84">
+      <c r="K65" s="84">
         <v>8100</v>
       </c>
-      <c r="M65" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L65" s="84" t="str">
+        <f>SUBSTITUTE(D65, "hazr-", "")&amp;"-pb"&amp;IF(M65="", "", M65)</f>
         <v>t-dip-ap-lb-pb8100</v>
       </c>
+      <c r="M65" s="84">
+        <v>8100</v>
+      </c>
       <c r="N65" s="84">
-        <v>8100</v>
-      </c>
-      <c r="O65" s="84">
         <v>4</v>
       </c>
-      <c r="P65" s="84" t="s">
+      <c r="O65" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P65" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q65" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R65" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="84" t="s">
         <v>185</v>
       </c>
@@ -10792,54 +10543,50 @@
         <v>374</v>
       </c>
       <c r="E66" s="84" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(D66, "hazr-", "")&amp;"-rule"&amp;M66</f>
         <v>t-dip-ap-lb-rule8200</v>
       </c>
-      <c r="F66" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dip-ap-lb-rule</v>
-      </c>
-      <c r="G66" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F66" s="84" t="str">
+        <f>SUBSTITUTE(D66, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-ap-lb-fe</v>
       </c>
-      <c r="H66" s="84" t="s">
+      <c r="G66" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I66" s="84">
+      <c r="H66" s="84">
         <v>8200</v>
       </c>
-      <c r="J66" s="84" t="b">
+      <c r="I66" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K66" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J66" s="84" t="str">
+        <f>SUBSTITUTE(D66, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-ap-lb-bp</v>
       </c>
-      <c r="L66" s="84">
+      <c r="K66" s="84">
         <v>8200</v>
       </c>
-      <c r="M66" s="84" t="str">
-        <f t="shared" si="2"/>
+      <c r="L66" s="84" t="str">
+        <f>SUBSTITUTE(D66, "hazr-", "")&amp;"-pb"&amp;IF(M66="", "", M66)</f>
         <v>t-dip-ap-lb-pb8200</v>
       </c>
+      <c r="M66" s="84">
+        <v>8200</v>
+      </c>
       <c r="N66" s="84">
-        <v>8200</v>
-      </c>
-      <c r="O66" s="84">
         <v>4</v>
       </c>
-      <c r="P66" s="84" t="s">
+      <c r="O66" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P66" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q66" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R66" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="84" t="s">
         <v>185</v>
       </c>
@@ -10854,54 +10601,50 @@
         <v>374</v>
       </c>
       <c r="E67" s="84" t="str">
-        <f t="shared" ref="E67:E88" si="7">SUBSTITUTE(D67, "hazr-", "")&amp;"-rule"&amp;N67</f>
+        <f>SUBSTITUTE(D67, "hazr-", "")&amp;"-rule"&amp;M67</f>
         <v>t-dip-ap-lb-rule8300</v>
       </c>
-      <c r="F67" s="74" t="str">
-        <f t="shared" ref="F67:F88" si="8">SUBSTITUTE(D67, "hazr-", "")&amp;"-rule"</f>
-        <v>t-dip-ap-lb-rule</v>
-      </c>
-      <c r="G67" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F67" s="84" t="str">
+        <f>SUBSTITUTE(D67, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-ap-lb-fe</v>
       </c>
-      <c r="H67" s="84" t="s">
+      <c r="G67" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I67" s="84">
+      <c r="H67" s="84">
         <v>8300</v>
       </c>
-      <c r="J67" s="84" t="b">
+      <c r="I67" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K67" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J67" s="84" t="str">
+        <f>SUBSTITUTE(D67, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-ap-lb-bp</v>
       </c>
-      <c r="L67" s="84">
+      <c r="K67" s="84">
         <v>8300</v>
       </c>
-      <c r="M67" s="84" t="str">
-        <f t="shared" ref="M67:M88" si="9">SUBSTITUTE(D67, "hazr-", "")&amp;"-pb"&amp;IF(N67="", "", N67)</f>
+      <c r="L67" s="84" t="str">
+        <f>SUBSTITUTE(D67, "hazr-", "")&amp;"-pb"&amp;IF(M67="", "", M67)</f>
         <v>t-dip-ap-lb-pb8300</v>
       </c>
+      <c r="M67" s="84">
+        <v>8300</v>
+      </c>
       <c r="N67" s="84">
-        <v>8300</v>
-      </c>
-      <c r="O67" s="84">
         <v>4</v>
       </c>
-      <c r="P67" s="84" t="s">
+      <c r="O67" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P67" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q67" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R67" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="84" t="s">
         <v>185</v>
       </c>
@@ -10916,54 +10659,50 @@
         <v>374</v>
       </c>
       <c r="E68" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D68, "hazr-", "")&amp;"-rule"&amp;M68</f>
         <v>t-dip-ap-lb-rule8400</v>
       </c>
-      <c r="F68" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-dip-ap-lb-rule</v>
-      </c>
-      <c r="G68" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F68" s="84" t="str">
+        <f>SUBSTITUTE(D68, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-ap-lb-fe</v>
       </c>
-      <c r="H68" s="84" t="s">
+      <c r="G68" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I68" s="84">
+      <c r="H68" s="84">
         <v>8400</v>
       </c>
-      <c r="J68" s="84" t="b">
+      <c r="I68" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K68" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J68" s="84" t="str">
+        <f>SUBSTITUTE(D68, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-ap-lb-bp</v>
       </c>
-      <c r="L68" s="84">
+      <c r="K68" s="84">
         <v>8400</v>
       </c>
-      <c r="M68" s="84" t="str">
-        <f t="shared" si="9"/>
+      <c r="L68" s="84" t="str">
+        <f>SUBSTITUTE(D68, "hazr-", "")&amp;"-pb"&amp;IF(M68="", "", M68)</f>
         <v>t-dip-ap-lb-pb8400</v>
       </c>
+      <c r="M68" s="84">
+        <v>8400</v>
+      </c>
       <c r="N68" s="84">
-        <v>8400</v>
-      </c>
-      <c r="O68" s="84">
         <v>4</v>
       </c>
-      <c r="P68" s="84" t="s">
+      <c r="O68" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P68" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q68" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R68" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="84" t="s">
         <v>185</v>
       </c>
@@ -10978,54 +10717,50 @@
         <v>374</v>
       </c>
       <c r="E69" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D69, "hazr-", "")&amp;"-rule"&amp;M69</f>
         <v>t-dip-ap-lb-rule9100</v>
       </c>
-      <c r="F69" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-dip-ap-lb-rule</v>
-      </c>
-      <c r="G69" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F69" s="84" t="str">
+        <f>SUBSTITUTE(D69, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-ap-lb-fe</v>
       </c>
-      <c r="H69" s="84" t="s">
+      <c r="G69" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I69" s="84">
+      <c r="H69" s="84">
         <v>9100</v>
       </c>
-      <c r="J69" s="84" t="b">
+      <c r="I69" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K69" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J69" s="84" t="str">
+        <f>SUBSTITUTE(D69, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-ap-lb-bp</v>
       </c>
-      <c r="L69" s="84">
+      <c r="K69" s="84">
         <v>9100</v>
       </c>
-      <c r="M69" s="84" t="str">
-        <f t="shared" si="9"/>
+      <c r="L69" s="84" t="str">
+        <f>SUBSTITUTE(D69, "hazr-", "")&amp;"-pb"&amp;IF(M69="", "", M69)</f>
         <v>t-dip-ap-lb-pb9100</v>
       </c>
+      <c r="M69" s="84">
+        <v>9100</v>
+      </c>
       <c r="N69" s="84">
-        <v>9100</v>
-      </c>
-      <c r="O69" s="84">
         <v>4</v>
       </c>
-      <c r="P69" s="84" t="s">
+      <c r="O69" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P69" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q69" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R69" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="84" t="s">
         <v>185</v>
       </c>
@@ -11040,54 +10775,50 @@
         <v>374</v>
       </c>
       <c r="E70" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D70, "hazr-", "")&amp;"-rule"&amp;M70</f>
         <v>t-dip-ap-lb-rule9113</v>
       </c>
-      <c r="F70" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-dip-ap-lb-rule</v>
-      </c>
-      <c r="G70" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F70" s="84" t="str">
+        <f>SUBSTITUTE(D70, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-ap-lb-fe</v>
       </c>
-      <c r="H70" s="84" t="s">
+      <c r="G70" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I70" s="84">
+      <c r="H70" s="84">
         <v>9113</v>
       </c>
-      <c r="J70" s="84" t="b">
+      <c r="I70" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K70" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J70" s="84" t="str">
+        <f>SUBSTITUTE(D70, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-ap-lb-bp</v>
       </c>
-      <c r="L70" s="84">
+      <c r="K70" s="84">
         <v>9113</v>
       </c>
-      <c r="M70" s="84" t="str">
-        <f t="shared" si="9"/>
+      <c r="L70" s="84" t="str">
+        <f>SUBSTITUTE(D70, "hazr-", "")&amp;"-pb"&amp;IF(M70="", "", M70)</f>
         <v>t-dip-ap-lb-pb9113</v>
       </c>
+      <c r="M70" s="84">
+        <v>9113</v>
+      </c>
       <c r="N70" s="84">
-        <v>9113</v>
-      </c>
-      <c r="O70" s="84">
         <v>4</v>
       </c>
-      <c r="P70" s="84" t="s">
+      <c r="O70" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P70" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q70" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R70" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="74" t="s">
         <v>185</v>
       </c>
@@ -11102,54 +10833,50 @@
         <v>373</v>
       </c>
       <c r="E71" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D71, "hazr-", "")&amp;"-rule"&amp;M71</f>
         <v>t-dip-adm-lb-rule443</v>
       </c>
       <c r="F71" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-dip-adm-lb-rule</v>
-      </c>
-      <c r="G71" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f>SUBSTITUTE(D71, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-adm-lb-fe</v>
       </c>
-      <c r="H71" s="74" t="s">
+      <c r="G71" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I71" s="74">
+      <c r="H71" s="74">
         <v>443</v>
       </c>
-      <c r="J71" s="74" t="b">
+      <c r="I71" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K71" s="74" t="str">
-        <f t="shared" si="6"/>
+      <c r="J71" s="74" t="str">
+        <f>SUBSTITUTE(D71, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-adm-lb-bp</v>
       </c>
-      <c r="L71" s="74">
+      <c r="K71" s="74">
         <v>443</v>
       </c>
-      <c r="M71" s="74" t="str">
-        <f t="shared" si="9"/>
+      <c r="L71" s="74" t="str">
+        <f>SUBSTITUTE(D71, "hazr-", "")&amp;"-pb"&amp;IF(M71="", "", M71)</f>
         <v>t-dip-adm-lb-pb443</v>
       </c>
+      <c r="M71" s="74">
+        <v>443</v>
+      </c>
       <c r="N71" s="74">
-        <v>443</v>
-      </c>
-      <c r="O71" s="74">
         <v>4</v>
       </c>
-      <c r="P71" s="74" t="s">
+      <c r="O71" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P71" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q71" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R71" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="74" t="s">
         <v>185</v>
       </c>
@@ -11164,54 +10891,50 @@
         <v>373</v>
       </c>
       <c r="E72" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D72, "hazr-", "")&amp;"-rule"&amp;M72</f>
         <v>t-dip-adm-lb-rule8085</v>
       </c>
       <c r="F72" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-dip-adm-lb-rule</v>
-      </c>
-      <c r="G72" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f>SUBSTITUTE(D72, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-adm-lb-fe</v>
       </c>
-      <c r="H72" s="74" t="s">
+      <c r="G72" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I72" s="74">
+      <c r="H72" s="74">
         <v>8085</v>
       </c>
-      <c r="J72" s="74" t="b">
+      <c r="I72" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K72" s="74" t="str">
-        <f t="shared" si="6"/>
+      <c r="J72" s="74" t="str">
+        <f>SUBSTITUTE(D72, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-adm-lb-bp</v>
       </c>
-      <c r="L72" s="74">
+      <c r="K72" s="74">
         <v>8085</v>
       </c>
-      <c r="M72" s="74" t="str">
-        <f t="shared" si="9"/>
+      <c r="L72" s="74" t="str">
+        <f>SUBSTITUTE(D72, "hazr-", "")&amp;"-pb"&amp;IF(M72="", "", M72)</f>
         <v>t-dip-adm-lb-pb8085</v>
       </c>
+      <c r="M72" s="74">
+        <v>8085</v>
+      </c>
       <c r="N72" s="74">
-        <v>8085</v>
-      </c>
-      <c r="O72" s="74">
         <v>4</v>
       </c>
-      <c r="P72" s="74" t="s">
+      <c r="O72" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P72" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q72" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R72" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="74" t="s">
         <v>185</v>
       </c>
@@ -11226,54 +10949,50 @@
         <v>373</v>
       </c>
       <c r="E73" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D73, "hazr-", "")&amp;"-rule"&amp;M73</f>
         <v>t-dip-adm-lb-rule8900</v>
       </c>
       <c r="F73" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-dip-adm-lb-rule</v>
-      </c>
-      <c r="G73" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f>SUBSTITUTE(D73, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-adm-lb-fe</v>
       </c>
-      <c r="H73" s="74" t="s">
+      <c r="G73" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I73" s="74">
+      <c r="H73" s="74">
         <v>8900</v>
       </c>
-      <c r="J73" s="74" t="b">
+      <c r="I73" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K73" s="74" t="str">
-        <f t="shared" si="6"/>
+      <c r="J73" s="74" t="str">
+        <f>SUBSTITUTE(D73, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-adm-lb-bp</v>
       </c>
-      <c r="L73" s="74">
+      <c r="K73" s="74">
         <v>8900</v>
       </c>
-      <c r="M73" s="74" t="str">
-        <f t="shared" si="9"/>
+      <c r="L73" s="74" t="str">
+        <f>SUBSTITUTE(D73, "hazr-", "")&amp;"-pb"&amp;IF(M73="", "", M73)</f>
         <v>t-dip-adm-lb-pb8900</v>
       </c>
+      <c r="M73" s="74">
+        <v>8900</v>
+      </c>
       <c r="N73" s="74">
-        <v>8900</v>
-      </c>
-      <c r="O73" s="74">
         <v>4</v>
       </c>
-      <c r="P73" s="74" t="s">
+      <c r="O73" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P73" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q73" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R73" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="74" t="s">
         <v>185</v>
       </c>
@@ -11288,54 +11007,50 @@
         <v>373</v>
       </c>
       <c r="E74" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D74, "hazr-", "")&amp;"-rule"&amp;M74</f>
         <v>t-dip-adm-lb-rule8901</v>
       </c>
       <c r="F74" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-dip-adm-lb-rule</v>
-      </c>
-      <c r="G74" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f>SUBSTITUTE(D74, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-adm-lb-fe</v>
       </c>
-      <c r="H74" s="74" t="s">
+      <c r="G74" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I74" s="74">
+      <c r="H74" s="74">
         <v>8901</v>
       </c>
-      <c r="J74" s="74" t="b">
+      <c r="I74" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K74" s="74" t="str">
-        <f t="shared" si="6"/>
+      <c r="J74" s="74" t="str">
+        <f>SUBSTITUTE(D74, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-adm-lb-bp</v>
       </c>
-      <c r="L74" s="74">
+      <c r="K74" s="74">
         <v>8901</v>
       </c>
-      <c r="M74" s="74" t="str">
-        <f t="shared" si="9"/>
+      <c r="L74" s="74" t="str">
+        <f>SUBSTITUTE(D74, "hazr-", "")&amp;"-pb"&amp;IF(M74="", "", M74)</f>
         <v>t-dip-adm-lb-pb8901</v>
       </c>
+      <c r="M74" s="74">
+        <v>8901</v>
+      </c>
       <c r="N74" s="74">
-        <v>8901</v>
-      </c>
-      <c r="O74" s="74">
         <v>4</v>
       </c>
-      <c r="P74" s="74" t="s">
+      <c r="O74" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P74" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q74" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R74" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="74" t="s">
         <v>185</v>
       </c>
@@ -11350,54 +11065,50 @@
         <v>373</v>
       </c>
       <c r="E75" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D75, "hazr-", "")&amp;"-rule"&amp;M75</f>
         <v>t-dip-adm-lb-rule9100</v>
       </c>
       <c r="F75" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-dip-adm-lb-rule</v>
-      </c>
-      <c r="G75" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f>SUBSTITUTE(D75, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-adm-lb-fe</v>
       </c>
-      <c r="H75" s="74" t="s">
+      <c r="G75" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I75" s="74">
+      <c r="H75" s="74">
         <v>9100</v>
       </c>
-      <c r="J75" s="74" t="b">
+      <c r="I75" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K75" s="74" t="str">
-        <f t="shared" si="6"/>
+      <c r="J75" s="74" t="str">
+        <f>SUBSTITUTE(D75, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-adm-lb-bp</v>
       </c>
-      <c r="L75" s="74">
+      <c r="K75" s="74">
         <v>9100</v>
       </c>
-      <c r="M75" s="74" t="str">
-        <f t="shared" si="9"/>
+      <c r="L75" s="74" t="str">
+        <f>SUBSTITUTE(D75, "hazr-", "")&amp;"-pb"&amp;IF(M75="", "", M75)</f>
         <v>t-dip-adm-lb-pb9100</v>
       </c>
+      <c r="M75" s="74">
+        <v>9100</v>
+      </c>
       <c r="N75" s="74">
-        <v>9100</v>
-      </c>
-      <c r="O75" s="74">
         <v>4</v>
       </c>
-      <c r="P75" s="74" t="s">
+      <c r="O75" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P75" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q75" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R75" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="84" t="s">
         <v>185</v>
       </c>
@@ -11412,39 +11123,38 @@
         <v>383</v>
       </c>
       <c r="E76" s="84"/>
-      <c r="F76" s="74"/>
-      <c r="G76" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F76" s="84" t="str">
+        <f>SUBSTITUTE(D76, "hazr-", "")&amp;"-fe"</f>
         <v>t-cs-chtweb-lb-fe</v>
       </c>
-      <c r="H76" s="84" t="s">
+      <c r="G76" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I76" s="84"/>
-      <c r="J76" s="84" t="b">
+      <c r="H76" s="84"/>
+      <c r="I76" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K76" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J76" s="84" t="str">
+        <f>SUBSTITUTE(D76, "hazr-", "")&amp;"-bp"</f>
         <v>t-cs-chtweb-lb-bp</v>
       </c>
+      <c r="K76" s="84"/>
       <c r="L76" s="84"/>
       <c r="M76" s="84"/>
-      <c r="N76" s="84"/>
-      <c r="O76" s="84">
+      <c r="N76" s="84">
         <v>4</v>
       </c>
-      <c r="P76" s="84" t="s">
+      <c r="O76" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P76" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q76" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R76" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="74" t="s">
         <v>185</v>
       </c>
@@ -11459,39 +11169,38 @@
         <v>384</v>
       </c>
       <c r="E77" s="74"/>
-      <c r="F77" s="74"/>
-      <c r="G77" s="74" t="str">
-        <f t="shared" si="5"/>
+      <c r="F77" s="74" t="str">
+        <f>SUBSTITUTE(D77, "hazr-", "")&amp;"-fe"</f>
         <v>t-cs-chtintweb-lb-fe</v>
       </c>
-      <c r="H77" s="74" t="s">
+      <c r="G77" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I77" s="74"/>
-      <c r="J77" s="74" t="b">
+      <c r="H77" s="74"/>
+      <c r="I77" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K77" s="74" t="str">
-        <f t="shared" si="6"/>
+      <c r="J77" s="74" t="str">
+        <f>SUBSTITUTE(D77, "hazr-", "")&amp;"-bp"</f>
         <v>t-cs-chtintweb-lb-bp</v>
       </c>
+      <c r="K77" s="74"/>
       <c r="L77" s="74"/>
       <c r="M77" s="74"/>
-      <c r="N77" s="74"/>
-      <c r="O77" s="74">
+      <c r="N77" s="74">
         <v>4</v>
       </c>
-      <c r="P77" s="74" t="s">
+      <c r="O77" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P77" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q77" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R77" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="84" t="s">
         <v>185</v>
       </c>
@@ -11506,39 +11215,38 @@
         <v>382</v>
       </c>
       <c r="E78" s="84"/>
-      <c r="F78" s="74"/>
-      <c r="G78" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F78" s="84" t="str">
+        <f>SUBSTITUTE(D78, "hazr-", "")&amp;"-fe"</f>
         <v>t-cs-chtap-lb-fe</v>
       </c>
-      <c r="H78" s="84" t="s">
+      <c r="G78" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I78" s="84"/>
-      <c r="J78" s="84" t="b">
+      <c r="H78" s="84"/>
+      <c r="I78" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K78" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J78" s="84" t="str">
+        <f>SUBSTITUTE(D78, "hazr-", "")&amp;"-bp"</f>
         <v>t-cs-chtap-lb-bp</v>
       </c>
+      <c r="K78" s="84"/>
       <c r="L78" s="84"/>
       <c r="M78" s="84"/>
-      <c r="N78" s="84"/>
-      <c r="O78" s="84">
+      <c r="N78" s="84">
         <v>4</v>
       </c>
-      <c r="P78" s="84" t="s">
+      <c r="O78" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P78" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q78" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R78" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="74" t="s">
         <v>185</v>
       </c>
@@ -11553,54 +11261,50 @@
         <v>381</v>
       </c>
       <c r="E79" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D79, "hazr-", "")&amp;"-rule"&amp;M79</f>
         <v>t-com-proxy-lb-rule443</v>
       </c>
       <c r="F79" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-com-proxy-lb-rule</v>
-      </c>
-      <c r="G79" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f>SUBSTITUTE(D79, "hazr-", "")&amp;"-fe"</f>
         <v>t-com-proxy-lb-fe</v>
       </c>
-      <c r="H79" s="74" t="s">
+      <c r="G79" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I79" s="74">
+      <c r="H79" s="74">
         <v>443</v>
       </c>
-      <c r="J79" s="74" t="b">
+      <c r="I79" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K79" s="74" t="str">
-        <f t="shared" si="6"/>
+      <c r="J79" s="74" t="str">
+        <f>SUBSTITUTE(D79, "hazr-", "")&amp;"-bp"</f>
         <v>t-com-proxy-lb-bp</v>
       </c>
-      <c r="L79" s="74">
+      <c r="K79" s="74">
         <v>443</v>
       </c>
-      <c r="M79" s="74" t="str">
-        <f t="shared" si="9"/>
+      <c r="L79" s="74" t="str">
+        <f>SUBSTITUTE(D79, "hazr-", "")&amp;"-pb"&amp;IF(M79="", "", M79)</f>
         <v>t-com-proxy-lb-pb443</v>
       </c>
+      <c r="M79" s="74">
+        <v>443</v>
+      </c>
       <c r="N79" s="74">
-        <v>443</v>
-      </c>
-      <c r="O79" s="74">
         <v>4</v>
       </c>
-      <c r="P79" s="74" t="s">
+      <c r="O79" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P79" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q79" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R79" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="74" t="s">
         <v>185</v>
       </c>
@@ -11615,54 +11319,50 @@
         <v>381</v>
       </c>
       <c r="E80" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D80, "hazr-", "")&amp;"-rule"&amp;M80</f>
         <v>t-com-proxy-lb-rule8080</v>
       </c>
       <c r="F80" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-com-proxy-lb-rule</v>
-      </c>
-      <c r="G80" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f>SUBSTITUTE(D80, "hazr-", "")&amp;"-fe"</f>
         <v>t-com-proxy-lb-fe</v>
       </c>
-      <c r="H80" s="74" t="s">
+      <c r="G80" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I80" s="74">
+      <c r="H80" s="74">
         <v>8080</v>
       </c>
-      <c r="J80" s="74" t="b">
+      <c r="I80" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K80" s="74" t="str">
-        <f t="shared" si="6"/>
+      <c r="J80" s="74" t="str">
+        <f>SUBSTITUTE(D80, "hazr-", "")&amp;"-bp"</f>
         <v>t-com-proxy-lb-bp</v>
       </c>
-      <c r="L80" s="74">
+      <c r="K80" s="74">
         <v>8080</v>
       </c>
-      <c r="M80" s="74" t="str">
-        <f t="shared" si="9"/>
+      <c r="L80" s="74" t="str">
+        <f>SUBSTITUTE(D80, "hazr-", "")&amp;"-pb"&amp;IF(M80="", "", M80)</f>
         <v>t-com-proxy-lb-pb8080</v>
       </c>
+      <c r="M80" s="74">
+        <v>8080</v>
+      </c>
       <c r="N80" s="74">
-        <v>8080</v>
-      </c>
-      <c r="O80" s="74">
         <v>4</v>
       </c>
-      <c r="P80" s="74" t="s">
+      <c r="O80" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P80" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q80" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R80" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="84" t="s">
         <v>185</v>
       </c>
@@ -11677,54 +11377,50 @@
         <v>380</v>
       </c>
       <c r="E81" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D81, "hazr-", "")&amp;"-rule"&amp;M81</f>
         <v>t-com-auth-lb-rule8088</v>
       </c>
-      <c r="F81" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-com-auth-lb-rule</v>
-      </c>
-      <c r="G81" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F81" s="84" t="str">
+        <f>SUBSTITUTE(D81, "hazr-", "")&amp;"-fe"</f>
         <v>t-com-auth-lb-fe</v>
       </c>
-      <c r="H81" s="84" t="s">
+      <c r="G81" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I81" s="84">
+      <c r="H81" s="84">
         <v>8088</v>
       </c>
-      <c r="J81" s="84" t="b">
+      <c r="I81" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K81" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J81" s="84" t="str">
+        <f>SUBSTITUTE(D81, "hazr-", "")&amp;"-bp"</f>
         <v>t-com-auth-lb-bp</v>
       </c>
-      <c r="L81" s="84">
+      <c r="K81" s="84">
         <v>8088</v>
       </c>
-      <c r="M81" s="84" t="str">
-        <f t="shared" si="9"/>
+      <c r="L81" s="84" t="str">
+        <f>SUBSTITUTE(D81, "hazr-", "")&amp;"-pb"&amp;IF(M81="", "", M81)</f>
         <v>t-com-auth-lb-pb8088</v>
       </c>
+      <c r="M81" s="84">
+        <v>8088</v>
+      </c>
       <c r="N81" s="84">
-        <v>8088</v>
-      </c>
-      <c r="O81" s="84">
         <v>4</v>
       </c>
-      <c r="P81" s="84" t="s">
+      <c r="O81" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P81" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q81" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R81" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="84" t="s">
         <v>185</v>
       </c>
@@ -11739,54 +11435,50 @@
         <v>380</v>
       </c>
       <c r="E82" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D82, "hazr-", "")&amp;"-rule"&amp;M82</f>
         <v>t-com-auth-lb-rule9003</v>
       </c>
-      <c r="F82" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-com-auth-lb-rule</v>
-      </c>
-      <c r="G82" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F82" s="84" t="str">
+        <f>SUBSTITUTE(D82, "hazr-", "")&amp;"-fe"</f>
         <v>t-com-auth-lb-fe</v>
       </c>
-      <c r="H82" s="84" t="s">
+      <c r="G82" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I82" s="84">
+      <c r="H82" s="84">
         <v>9003</v>
       </c>
-      <c r="J82" s="84" t="b">
+      <c r="I82" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K82" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J82" s="84" t="str">
+        <f>SUBSTITUTE(D82, "hazr-", "")&amp;"-bp"</f>
         <v>t-com-auth-lb-bp</v>
       </c>
-      <c r="L82" s="84">
+      <c r="K82" s="84">
         <v>9003</v>
       </c>
-      <c r="M82" s="84" t="str">
-        <f t="shared" si="9"/>
+      <c r="L82" s="84" t="str">
+        <f>SUBSTITUTE(D82, "hazr-", "")&amp;"-pb"&amp;IF(M82="", "", M82)</f>
         <v>t-com-auth-lb-pb9003</v>
       </c>
+      <c r="M82" s="84">
+        <v>9003</v>
+      </c>
       <c r="N82" s="84">
-        <v>9003</v>
-      </c>
-      <c r="O82" s="84">
         <v>4</v>
       </c>
-      <c r="P82" s="84" t="s">
+      <c r="O82" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P82" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q82" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R82" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="84" t="s">
         <v>185</v>
       </c>
@@ -11801,54 +11493,50 @@
         <v>380</v>
       </c>
       <c r="E83" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D83, "hazr-", "")&amp;"-rule"&amp;M83</f>
         <v>t-com-auth-lb-rule9005</v>
       </c>
-      <c r="F83" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-com-auth-lb-rule</v>
-      </c>
-      <c r="G83" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F83" s="84" t="str">
+        <f>SUBSTITUTE(D83, "hazr-", "")&amp;"-fe"</f>
         <v>t-com-auth-lb-fe</v>
       </c>
-      <c r="H83" s="84" t="s">
+      <c r="G83" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I83" s="84">
+      <c r="H83" s="84">
         <v>9005</v>
       </c>
-      <c r="J83" s="84" t="b">
+      <c r="I83" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K83" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J83" s="84" t="str">
+        <f>SUBSTITUTE(D83, "hazr-", "")&amp;"-bp"</f>
         <v>t-com-auth-lb-bp</v>
       </c>
-      <c r="L83" s="84">
+      <c r="K83" s="84">
         <v>9005</v>
       </c>
-      <c r="M83" s="84" t="str">
-        <f t="shared" si="9"/>
+      <c r="L83" s="84" t="str">
+        <f>SUBSTITUTE(D83, "hazr-", "")&amp;"-pb"&amp;IF(M83="", "", M83)</f>
         <v>t-com-auth-lb-pb9005</v>
       </c>
+      <c r="M83" s="84">
+        <v>9005</v>
+      </c>
       <c r="N83" s="84">
-        <v>9005</v>
-      </c>
-      <c r="O83" s="84">
         <v>4</v>
       </c>
-      <c r="P83" s="84" t="s">
+      <c r="O83" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P83" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q83" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R83" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="74" t="s">
         <v>185</v>
       </c>
@@ -11863,54 +11551,50 @@
         <v>372</v>
       </c>
       <c r="E84" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D84, "hazr-", "")&amp;"-rule"&amp;M84</f>
         <v>t-bdp-slap-lb-rule443</v>
       </c>
       <c r="F84" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-bdp-slap-lb-rule</v>
-      </c>
-      <c r="G84" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f>SUBSTITUTE(D84, "hazr-", "")&amp;"-fe"</f>
         <v>t-bdp-slap-lb-fe</v>
       </c>
-      <c r="H84" s="74" t="s">
+      <c r="G84" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I84" s="74">
+      <c r="H84" s="74">
         <v>443</v>
       </c>
-      <c r="J84" s="74" t="b">
+      <c r="I84" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K84" s="74" t="str">
-        <f t="shared" si="6"/>
+      <c r="J84" s="74" t="str">
+        <f>SUBSTITUTE(D84, "hazr-", "")&amp;"-bp"</f>
         <v>t-bdp-slap-lb-bp</v>
       </c>
-      <c r="L84" s="74">
+      <c r="K84" s="74">
         <v>443</v>
       </c>
-      <c r="M84" s="74" t="str">
-        <f t="shared" si="9"/>
+      <c r="L84" s="74" t="str">
+        <f>SUBSTITUTE(D84, "hazr-", "")&amp;"-pb"&amp;IF(M84="", "", M84)</f>
         <v>t-bdp-slap-lb-pb443</v>
       </c>
+      <c r="M84" s="74">
+        <v>443</v>
+      </c>
       <c r="N84" s="74">
-        <v>443</v>
-      </c>
-      <c r="O84" s="74">
         <v>4</v>
       </c>
-      <c r="P84" s="74" t="s">
+      <c r="O84" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P84" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q84" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R84" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="84" t="s">
         <v>185</v>
       </c>
@@ -11925,54 +11609,50 @@
         <v>371</v>
       </c>
       <c r="E85" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D85, "hazr-", "")&amp;"-rule"&amp;M85</f>
         <v>t-bdp-cxmadm-lb-rule443</v>
       </c>
-      <c r="F85" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-bdp-cxmadm-lb-rule</v>
-      </c>
-      <c r="G85" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F85" s="84" t="str">
+        <f>SUBSTITUTE(D85, "hazr-", "")&amp;"-fe"</f>
         <v>t-bdp-cxmadm-lb-fe</v>
       </c>
-      <c r="H85" s="84" t="s">
+      <c r="G85" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I85" s="84">
+      <c r="H85" s="84">
         <v>443</v>
       </c>
-      <c r="J85" s="84" t="b">
+      <c r="I85" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K85" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J85" s="84" t="str">
+        <f>SUBSTITUTE(D85, "hazr-", "")&amp;"-bp"</f>
         <v>t-bdp-cxmadm-lb-bp</v>
       </c>
-      <c r="L85" s="84">
+      <c r="K85" s="84">
         <v>443</v>
       </c>
-      <c r="M85" s="84" t="str">
-        <f t="shared" si="9"/>
+      <c r="L85" s="84" t="str">
+        <f>SUBSTITUTE(D85, "hazr-", "")&amp;"-pb"&amp;IF(M85="", "", M85)</f>
         <v>t-bdp-cxmadm-lb-pb443</v>
       </c>
+      <c r="M85" s="84">
+        <v>443</v>
+      </c>
       <c r="N85" s="84">
-        <v>443</v>
-      </c>
-      <c r="O85" s="84">
         <v>4</v>
       </c>
-      <c r="P85" s="84" t="s">
+      <c r="O85" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P85" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q85" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R85" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="74" t="s">
         <v>185</v>
       </c>
@@ -11987,54 +11667,50 @@
         <v>388</v>
       </c>
       <c r="E86" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D86, "hazr-", "")&amp;"-rule"&amp;M86</f>
         <v>t-bdp-crkweb-lb-rule443</v>
       </c>
       <c r="F86" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-bdp-crkweb-lb-rule</v>
-      </c>
-      <c r="G86" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f>SUBSTITUTE(D86, "hazr-", "")&amp;"-fe"</f>
         <v>t-bdp-crkweb-lb-fe</v>
       </c>
-      <c r="H86" s="74" t="s">
+      <c r="G86" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I86" s="74">
+      <c r="H86" s="74">
         <v>443</v>
       </c>
-      <c r="J86" s="74" t="b">
+      <c r="I86" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K86" s="74" t="str">
-        <f t="shared" si="6"/>
+      <c r="J86" s="74" t="str">
+        <f>SUBSTITUTE(D86, "hazr-", "")&amp;"-bp"</f>
         <v>t-bdp-crkweb-lb-bp</v>
       </c>
-      <c r="L86" s="74">
+      <c r="K86" s="74">
         <v>443</v>
       </c>
-      <c r="M86" s="74" t="str">
-        <f t="shared" si="9"/>
+      <c r="L86" s="74" t="str">
+        <f>SUBSTITUTE(D86, "hazr-", "")&amp;"-pb"&amp;IF(M86="", "", M86)</f>
         <v>t-bdp-crkweb-lb-pb443</v>
       </c>
+      <c r="M86" s="74">
+        <v>443</v>
+      </c>
       <c r="N86" s="74">
-        <v>443</v>
-      </c>
-      <c r="O86" s="74">
         <v>4</v>
       </c>
-      <c r="P86" s="74" t="s">
+      <c r="O86" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P86" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q86" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R86" s="74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="84" t="s">
         <v>185</v>
       </c>
@@ -12049,54 +11725,50 @@
         <v>390</v>
       </c>
       <c r="E87" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D87, "hazr-", "")&amp;"-rule"&amp;M87</f>
         <v>t-bdp-crkml-lb-rule8082</v>
       </c>
-      <c r="F87" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-bdp-crkml-lb-rule</v>
-      </c>
-      <c r="G87" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="F87" s="84" t="str">
+        <f>SUBSTITUTE(D87, "hazr-", "")&amp;"-fe"</f>
         <v>t-bdp-crkml-lb-fe</v>
       </c>
-      <c r="H87" s="84" t="s">
+      <c r="G87" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="I87" s="84">
+      <c r="H87" s="84">
         <v>8082</v>
       </c>
-      <c r="J87" s="84" t="b">
+      <c r="I87" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="K87" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="J87" s="84" t="str">
+        <f>SUBSTITUTE(D87, "hazr-", "")&amp;"-bp"</f>
         <v>t-bdp-crkml-lb-bp</v>
       </c>
-      <c r="L87" s="84">
+      <c r="K87" s="84">
         <v>8082</v>
       </c>
-      <c r="M87" s="84" t="str">
-        <f t="shared" si="9"/>
+      <c r="L87" s="84" t="str">
+        <f>SUBSTITUTE(D87, "hazr-", "")&amp;"-pb"&amp;IF(M87="", "", M87)</f>
         <v>t-bdp-crkml-lb-pb8082</v>
       </c>
+      <c r="M87" s="84">
+        <v>8082</v>
+      </c>
       <c r="N87" s="84">
-        <v>8082</v>
-      </c>
-      <c r="O87" s="84">
         <v>4</v>
       </c>
-      <c r="P87" s="84" t="s">
+      <c r="O87" s="84" t="s">
         <v>125</v>
       </c>
+      <c r="P87" s="84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q87" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R87" s="84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="74" t="s">
         <v>185</v>
       </c>
@@ -12111,56 +11783,52 @@
         <v>389</v>
       </c>
       <c r="E88" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f>SUBSTITUTE(D88, "hazr-", "")&amp;"-rule"&amp;M88</f>
         <v>t-bdp-crkap-lb-rule8085</v>
       </c>
       <c r="F88" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>t-bdp-crkap-lb-rule</v>
-      </c>
-      <c r="G88" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f>SUBSTITUTE(D88, "hazr-", "")&amp;"-fe"</f>
         <v>t-bdp-crkap-lb-fe</v>
       </c>
-      <c r="H88" s="74" t="s">
+      <c r="G88" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I88" s="74">
+      <c r="H88" s="74">
         <v>8085</v>
       </c>
-      <c r="J88" s="74" t="b">
+      <c r="I88" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K88" s="74" t="str">
-        <f t="shared" si="6"/>
+      <c r="J88" s="74" t="str">
+        <f>SUBSTITUTE(D88, "hazr-", "")&amp;"-bp"</f>
         <v>t-bdp-crkap-lb-bp</v>
       </c>
-      <c r="L88" s="74">
+      <c r="K88" s="74">
         <v>8085</v>
       </c>
-      <c r="M88" s="74" t="str">
-        <f t="shared" si="9"/>
+      <c r="L88" s="74" t="str">
+        <f>SUBSTITUTE(D88, "hazr-", "")&amp;"-pb"&amp;IF(M88="", "", M88)</f>
         <v>t-bdp-crkap-lb-pb8085</v>
       </c>
+      <c r="M88" s="74">
+        <v>8085</v>
+      </c>
       <c r="N88" s="74">
-        <v>8085</v>
-      </c>
-      <c r="O88" s="74">
         <v>4</v>
       </c>
-      <c r="P88" s="74" t="s">
+      <c r="O88" s="74" t="s">
         <v>125</v>
       </c>
+      <c r="P88" s="74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q88" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R88" s="74" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R88" xr:uid="{A4BC862D-08E7-4593-9A34-4D2B508CF25B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R50">
+  <autoFilter ref="A1:Q88" xr:uid="{A4BC862D-08E7-4593-9A34-4D2B508CF25B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q50">
       <sortCondition descending="1" ref="B1"/>
     </sortState>
   </autoFilter>
